--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -19,7 +19,7 @@
     <numFmt formatCode="&quot;&quot;#&quot;歳&quot;" numFmtId="165"/>
     <numFmt formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@" numFmtId="166"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="游ゴシック"/>
       <color theme="1"/>
@@ -143,11 +143,23 @@
     </font>
     <font>
       <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
       <color rgb="0053657A"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -214,6 +226,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F1F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDF3F8"/>
       </patternFill>
     </fill>
@@ -2515,7 +2537,7 @@
     </xf>
     <xf borderId="84" fillId="0" fontId="1" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="928">
+  <cellXfs count="941">
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5034,11 +5056,16 @@
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="39" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" textRotation="90" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" borderId="46" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" textRotation="90" vertical="center"/>
+    <xf applyAlignment="1" borderId="117" fillId="14" fontId="23" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="166" fillId="14" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="167" fillId="14" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="39" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="46" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyAlignment="1" borderId="118" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5049,10 +5076,10 @@
     <xf applyAlignment="1" borderId="120" fillId="0" fontId="7" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="35" fillId="14" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="35" fillId="16" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="36" fillId="14" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="36" fillId="16" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyAlignment="1" borderId="110" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5061,10 +5088,13 @@
     <xf applyAlignment="1" borderId="173" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="110" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" borderId="131" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="110" fillId="13" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="110" fillId="15" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="131" fillId="13" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf applyAlignment="1" borderId="172" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5073,15 +5103,26 @@
     <xf applyAlignment="1" borderId="172" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="122" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="122" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="170" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf applyAlignment="1" borderId="172" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="118" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="123" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="123" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="171" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="131" fillId="15" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="170" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="171" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="118" fillId="17" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="233" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="173" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="84" fillId="0" fontId="23" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="84" fillId="0" fontId="25" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5324,7 +5365,14 @@
     <col customWidth="1" max="8" min="8" style="593" width="20.1640625"/>
     <col customWidth="1" max="10" min="9" style="593" width="18.6640625"/>
     <col customWidth="1" max="11" min="11" style="593" width="19"/>
-    <col customWidth="1" max="19" min="12" style="593" width="3.6640625"/>
+    <col customWidth="1" max="12" min="12" style="593" width="8.5"/>
+    <col customWidth="1" max="13" min="13" style="782" width="8.5"/>
+    <col customWidth="1" max="14" min="14" style="782" width="8.5"/>
+    <col customWidth="1" max="15" min="15" style="782" width="8.5"/>
+    <col customWidth="1" max="16" min="16" style="782" width="8.5"/>
+    <col customWidth="1" max="17" min="17" style="782" width="8.5"/>
+    <col customWidth="1" max="18" min="18" style="782" width="8.5"/>
+    <col customWidth="1" max="19" min="19" style="782" width="8.5"/>
     <col customWidth="1" max="20" min="20" style="593" width="2.6640625"/>
     <col customWidth="1" max="16384" min="21" style="593" width="9"/>
   </cols>
@@ -5609,7 +5657,7 @@
       <c r="R9" s="548" t="n"/>
       <c r="S9" s="552" t="n"/>
     </row>
-    <row customHeight="1" ht="169" r="10" s="782">
+    <row customHeight="1" ht="153" r="10" s="782">
       <c r="A10" s="889" t="n"/>
       <c r="B10" s="906" t="inlineStr">
         <is>
@@ -5709,20 +5757,20 @@
 ツール等</t>
         </is>
       </c>
-      <c r="L12" s="558" t="inlineStr">
+      <c r="L12" s="910" t="inlineStr">
         <is>
           <t>担当工程</t>
         </is>
       </c>
-      <c r="M12" s="559" t="n"/>
-      <c r="N12" s="559" t="n"/>
-      <c r="O12" s="559" t="n"/>
-      <c r="P12" s="559" t="n"/>
-      <c r="Q12" s="559" t="n"/>
-      <c r="R12" s="559" t="n"/>
-      <c r="S12" s="560" t="n"/>
+      <c r="M12" s="911" t="n"/>
+      <c r="N12" s="911" t="n"/>
+      <c r="O12" s="911" t="n"/>
+      <c r="P12" s="911" t="n"/>
+      <c r="Q12" s="911" t="n"/>
+      <c r="R12" s="911" t="n"/>
+      <c r="S12" s="912" t="n"/>
     </row>
-    <row customHeight="1" ht="105" r="13" s="782">
+    <row customHeight="1" ht="46" r="13" s="782">
       <c r="B13" s="807" t="n"/>
       <c r="C13" s="808" t="n"/>
       <c r="D13" s="808" t="n"/>
@@ -5733,93 +5781,100 @@
       <c r="I13" s="810" t="n"/>
       <c r="J13" s="810" t="n"/>
       <c r="K13" s="810" t="n"/>
-      <c r="L13" s="910" t="inlineStr">
-        <is>
-          <t>要件定義</t>
-        </is>
-      </c>
-      <c r="M13" s="910" t="inlineStr">
-        <is>
-          <t>基本設計</t>
-        </is>
-      </c>
-      <c r="N13" s="910" t="inlineStr">
-        <is>
-          <t>詳細設計</t>
-        </is>
-      </c>
-      <c r="O13" s="910" t="inlineStr">
+      <c r="L13" s="913" t="inlineStr">
+        <is>
+          <t>要件
+定義</t>
+        </is>
+      </c>
+      <c r="M13" s="913" t="inlineStr">
+        <is>
+          <t>基本
+設計</t>
+        </is>
+      </c>
+      <c r="N13" s="913" t="inlineStr">
+        <is>
+          <t>詳細
+設計</t>
+        </is>
+      </c>
+      <c r="O13" s="913" t="inlineStr">
         <is>
           <t>実装</t>
         </is>
       </c>
-      <c r="P13" s="910" t="inlineStr">
-        <is>
-          <t>単体テスト</t>
-        </is>
-      </c>
-      <c r="Q13" s="910" t="inlineStr">
-        <is>
-          <t>結合テスト</t>
-        </is>
-      </c>
-      <c r="R13" s="910" t="inlineStr">
-        <is>
-          <t>総合テスト</t>
-        </is>
-      </c>
-      <c r="S13" s="911" t="inlineStr">
-        <is>
-          <t>保守・運用</t>
+      <c r="P13" s="913" t="inlineStr">
+        <is>
+          <t>単体
+テスト</t>
+        </is>
+      </c>
+      <c r="Q13" s="913" t="inlineStr">
+        <is>
+          <t>結合
+テスト</t>
+        </is>
+      </c>
+      <c r="R13" s="913" t="inlineStr">
+        <is>
+          <t>総合
+テスト</t>
+        </is>
+      </c>
+      <c r="S13" s="914" t="inlineStr">
+        <is>
+          <t>保守
+運用</t>
         </is>
       </c>
     </row>
     <row customHeight="1" ht="41" r="14" s="782">
       <c r="A14" s="889" t="n"/>
-      <c r="B14" s="912" t="n">
+      <c r="B14" s="915" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="913" t="inlineStr">
+      <c r="C14" s="916" t="inlineStr">
         <is>
           <t>2024/10</t>
         </is>
       </c>
-      <c r="D14" s="914" t="inlineStr">
+      <c r="D14" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E14" s="913" t="inlineStr">
+      <c r="E14" s="916" t="inlineStr">
         <is>
           <t>現在</t>
         </is>
       </c>
-      <c r="F14" s="915" t="inlineStr">
+      <c r="F14" s="918" t="inlineStr">
         <is>
           <t>■自治体連携DX推進支援プラットフォームの開発</t>
         </is>
       </c>
-      <c r="G14" s="916" t="inlineStr">
+      <c r="G14" s="919" t="inlineStr">
         <is>
           <t>リードエンジニア</t>
         </is>
       </c>
-      <c r="H14" s="917" t="inlineStr">
+      <c r="H14" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript, Python</t>
         </is>
       </c>
-      <c r="I14" s="917" t="inlineStr">
+      <c r="I14" s="920" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J14" s="917" t="inlineStr">
+      <c r="J14" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K14" s="918" t="inlineStr">
+      <c r="K14" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、React
 エディタ/IDE：Cursor、Orca
@@ -5829,26 +5884,26 @@
 コミュニケーション：Slack、Jira、Notion</t>
         </is>
       </c>
-      <c r="L14" s="919" t="n"/>
-      <c r="M14" s="919" t="n"/>
-      <c r="N14" s="919" t="n"/>
-      <c r="O14" s="919" t="inlineStr">
+      <c r="L14" s="922" t="n"/>
+      <c r="M14" s="922" t="n"/>
+      <c r="N14" s="922" t="n"/>
+      <c r="O14" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P14" s="919" t="inlineStr">
+      <c r="P14" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q14" s="919" t="inlineStr">
+      <c r="Q14" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R14" s="919" t="n"/>
-      <c r="S14" s="920" t="n"/>
+      <c r="R14" s="922" t="n"/>
+      <c r="S14" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="232" r="15" s="782">
       <c r="A15" s="889" t="n"/>
@@ -5856,7 +5911,7 @@
       <c r="C15" s="573" t="n"/>
       <c r="D15" s="574" t="n"/>
       <c r="E15" s="573" t="n"/>
-      <c r="F15" s="921" t="inlineStr">
+      <c r="F15" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 自治体連携DX推進支援プラットフォームの開発(2024年10月〜、随時更新）
@@ -5866,7 +5921,7 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G15" s="922" t="inlineStr">
+      <c r="G15" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、PdM、エンジニア、SRE、デザイナー、QA</t>
@@ -5876,19 +5931,19 @@
       <c r="I15" s="574" t="n"/>
       <c r="J15" s="574" t="n"/>
       <c r="K15" s="577" t="n"/>
-      <c r="L15" s="574" t="n"/>
-      <c r="M15" s="574" t="n"/>
-      <c r="N15" s="574" t="n"/>
-      <c r="O15" s="574" t="n"/>
-      <c r="P15" s="574" t="n"/>
-      <c r="Q15" s="574" t="n"/>
-      <c r="R15" s="574" t="n"/>
-      <c r="S15" s="820" t="n"/>
+      <c r="L15" s="927" t="n"/>
+      <c r="M15" s="927" t="n"/>
+      <c r="N15" s="927" t="n"/>
+      <c r="O15" s="928" t="n"/>
+      <c r="P15" s="928" t="n"/>
+      <c r="Q15" s="928" t="n"/>
+      <c r="R15" s="927" t="n"/>
+      <c r="S15" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="16" s="782">
       <c r="A16" s="889" t="n"/>
       <c r="B16" s="579" t="n"/>
-      <c r="C16" s="923" t="inlineStr">
+      <c r="C16" s="930" t="inlineStr">
         <is>
           <t>随時更新</t>
         </is>
@@ -5901,61 +5956,61 @@
       <c r="I16" s="583" t="n"/>
       <c r="J16" s="583" t="n"/>
       <c r="K16" s="584" t="n"/>
-      <c r="L16" s="583" t="n"/>
-      <c r="M16" s="583" t="n"/>
-      <c r="N16" s="583" t="n"/>
-      <c r="O16" s="583" t="n"/>
-      <c r="P16" s="583" t="n"/>
-      <c r="Q16" s="583" t="n"/>
-      <c r="R16" s="583" t="n"/>
-      <c r="S16" s="827" t="n"/>
+      <c r="L16" s="931" t="n"/>
+      <c r="M16" s="931" t="n"/>
+      <c r="N16" s="931" t="n"/>
+      <c r="O16" s="932" t="n"/>
+      <c r="P16" s="932" t="n"/>
+      <c r="Q16" s="932" t="n"/>
+      <c r="R16" s="931" t="n"/>
+      <c r="S16" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="17" s="782">
       <c r="A17" s="889" t="n"/>
-      <c r="B17" s="912" t="n">
+      <c r="B17" s="915" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="913" t="inlineStr">
+      <c r="C17" s="916" t="inlineStr">
         <is>
           <t>2024/04</t>
         </is>
       </c>
-      <c r="D17" s="914" t="inlineStr">
+      <c r="D17" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E17" s="913" t="inlineStr">
+      <c r="E17" s="916" t="inlineStr">
         <is>
           <t>2024/08</t>
         </is>
       </c>
-      <c r="F17" s="915" t="inlineStr">
+      <c r="F17" s="918" t="inlineStr">
         <is>
           <t>■電気自動車のEV充電ローミングプロジェクトの新規開発</t>
         </is>
       </c>
-      <c r="G17" s="916" t="inlineStr">
+      <c r="G17" s="919" t="inlineStr">
         <is>
           <t>リードエンジニア</t>
         </is>
       </c>
-      <c r="H17" s="917" t="inlineStr">
+      <c r="H17" s="920" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I17" s="917" t="inlineStr">
+      <c r="I17" s="920" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J17" s="917" t="inlineStr">
+      <c r="J17" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K17" s="918" t="inlineStr">
+      <c r="K17" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec
 エディタ/IDE：VSCode
@@ -5963,22 +6018,22 @@
 コミュニケーション：Slack、Google Meet</t>
         </is>
       </c>
-      <c r="L17" s="919" t="n"/>
-      <c r="M17" s="919" t="inlineStr">
+      <c r="L17" s="922" t="n"/>
+      <c r="M17" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N17" s="919" t="n"/>
-      <c r="O17" s="919" t="inlineStr">
+      <c r="N17" s="922" t="n"/>
+      <c r="O17" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P17" s="919" t="n"/>
-      <c r="Q17" s="919" t="n"/>
-      <c r="R17" s="919" t="n"/>
-      <c r="S17" s="920" t="n"/>
+      <c r="P17" s="922" t="n"/>
+      <c r="Q17" s="922" t="n"/>
+      <c r="R17" s="922" t="n"/>
+      <c r="S17" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="161" r="18" s="782">
       <c r="A18" s="889" t="n"/>
@@ -5986,7 +6041,7 @@
       <c r="C18" s="573" t="n"/>
       <c r="D18" s="574" t="n"/>
       <c r="E18" s="573" t="n"/>
-      <c r="F18" s="921" t="inlineStr">
+      <c r="F18" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 電気自動車のEV充電ローミングプロジェクトの新規開発(2024年4月〜2024年8月：5ヶ月)
@@ -5996,7 +6051,7 @@
 リモート、ウォーターフォール開発</t>
         </is>
       </c>
-      <c r="G18" s="922" t="inlineStr">
+      <c r="G18" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
@@ -6006,19 +6061,19 @@
       <c r="I18" s="574" t="n"/>
       <c r="J18" s="574" t="n"/>
       <c r="K18" s="577" t="n"/>
-      <c r="L18" s="574" t="n"/>
-      <c r="M18" s="574" t="n"/>
-      <c r="N18" s="574" t="n"/>
-      <c r="O18" s="574" t="n"/>
-      <c r="P18" s="574" t="n"/>
-      <c r="Q18" s="574" t="n"/>
-      <c r="R18" s="574" t="n"/>
-      <c r="S18" s="820" t="n"/>
+      <c r="L18" s="927" t="n"/>
+      <c r="M18" s="928" t="n"/>
+      <c r="N18" s="927" t="n"/>
+      <c r="O18" s="928" t="n"/>
+      <c r="P18" s="927" t="n"/>
+      <c r="Q18" s="927" t="n"/>
+      <c r="R18" s="927" t="n"/>
+      <c r="S18" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="19" s="782">
       <c r="A19" s="889" t="n"/>
       <c r="B19" s="579" t="n"/>
-      <c r="C19" s="923" t="inlineStr">
+      <c r="C19" s="930" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
@@ -6031,61 +6086,61 @@
       <c r="I19" s="583" t="n"/>
       <c r="J19" s="583" t="n"/>
       <c r="K19" s="584" t="n"/>
-      <c r="L19" s="583" t="n"/>
-      <c r="M19" s="583" t="n"/>
-      <c r="N19" s="583" t="n"/>
-      <c r="O19" s="583" t="n"/>
-      <c r="P19" s="583" t="n"/>
-      <c r="Q19" s="583" t="n"/>
-      <c r="R19" s="583" t="n"/>
-      <c r="S19" s="827" t="n"/>
+      <c r="L19" s="931" t="n"/>
+      <c r="M19" s="932" t="n"/>
+      <c r="N19" s="931" t="n"/>
+      <c r="O19" s="932" t="n"/>
+      <c r="P19" s="931" t="n"/>
+      <c r="Q19" s="931" t="n"/>
+      <c r="R19" s="931" t="n"/>
+      <c r="S19" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="25" r="20" s="782">
       <c r="A20" s="889" t="n"/>
-      <c r="B20" s="912" t="n">
+      <c r="B20" s="915" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="913" t="inlineStr">
+      <c r="C20" s="916" t="inlineStr">
         <is>
           <t>2023/07</t>
         </is>
       </c>
-      <c r="D20" s="914" t="inlineStr">
+      <c r="D20" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E20" s="913" t="inlineStr">
+      <c r="E20" s="916" t="inlineStr">
         <is>
           <t>2024/03</t>
         </is>
       </c>
-      <c r="F20" s="915" t="inlineStr">
+      <c r="F20" s="918" t="inlineStr">
         <is>
           <t>■不動産テックのバーティカルSaaSプロダクト開発</t>
         </is>
       </c>
-      <c r="G20" s="916" t="inlineStr">
+      <c r="G20" s="919" t="inlineStr">
         <is>
           <t>webエンジニア</t>
         </is>
       </c>
-      <c r="H20" s="917" t="inlineStr">
+      <c r="H20" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、 TypeScript</t>
         </is>
       </c>
-      <c r="I20" s="917" t="inlineStr">
+      <c r="I20" s="920" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J20" s="917" t="inlineStr">
+      <c r="J20" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K20" s="918" t="inlineStr">
+      <c r="K20" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、 React、 Next.js
 エディタ/IDE：VSCode
@@ -6093,26 +6148,26 @@
 コミュニケーション：Slack、Google Meet</t>
         </is>
       </c>
-      <c r="L20" s="919" t="n"/>
-      <c r="M20" s="919" t="n"/>
-      <c r="N20" s="919" t="n"/>
-      <c r="O20" s="919" t="inlineStr">
+      <c r="L20" s="922" t="n"/>
+      <c r="M20" s="922" t="n"/>
+      <c r="N20" s="922" t="n"/>
+      <c r="O20" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P20" s="919" t="inlineStr">
+      <c r="P20" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q20" s="919" t="inlineStr">
+      <c r="Q20" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R20" s="919" t="n"/>
-      <c r="S20" s="920" t="n"/>
+      <c r="R20" s="922" t="n"/>
+      <c r="S20" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="168" r="21" s="782">
       <c r="A21" s="889" t="n"/>
@@ -6120,7 +6175,7 @@
       <c r="C21" s="573" t="n"/>
       <c r="D21" s="574" t="n"/>
       <c r="E21" s="573" t="n"/>
-      <c r="F21" s="921" t="inlineStr">
+      <c r="F21" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 不動産テックのバーティカルSaaSプロダクト開発(2023年7月〜2024年3月：9ヶ月)
@@ -6130,7 +6185,7 @@
 リモート及び出社、アジャイル開発</t>
         </is>
       </c>
-      <c r="G21" s="922" t="inlineStr">
+      <c r="G21" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
@@ -6140,19 +6195,19 @@
       <c r="I21" s="574" t="n"/>
       <c r="J21" s="574" t="n"/>
       <c r="K21" s="577" t="n"/>
-      <c r="L21" s="574" t="n"/>
-      <c r="M21" s="574" t="n"/>
-      <c r="N21" s="574" t="n"/>
-      <c r="O21" s="574" t="n"/>
-      <c r="P21" s="574" t="n"/>
-      <c r="Q21" s="574" t="n"/>
-      <c r="R21" s="574" t="n"/>
-      <c r="S21" s="820" t="n"/>
+      <c r="L21" s="927" t="n"/>
+      <c r="M21" s="927" t="n"/>
+      <c r="N21" s="927" t="n"/>
+      <c r="O21" s="928" t="n"/>
+      <c r="P21" s="928" t="n"/>
+      <c r="Q21" s="928" t="n"/>
+      <c r="R21" s="927" t="n"/>
+      <c r="S21" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="22" s="782">
       <c r="A22" s="889" t="n"/>
       <c r="B22" s="579" t="n"/>
-      <c r="C22" s="923" t="inlineStr">
+      <c r="C22" s="930" t="inlineStr">
         <is>
           <t>9ヶ月</t>
         </is>
@@ -6165,61 +6220,61 @@
       <c r="I22" s="583" t="n"/>
       <c r="J22" s="583" t="n"/>
       <c r="K22" s="584" t="n"/>
-      <c r="L22" s="583" t="n"/>
-      <c r="M22" s="583" t="n"/>
-      <c r="N22" s="583" t="n"/>
-      <c r="O22" s="583" t="n"/>
-      <c r="P22" s="583" t="n"/>
-      <c r="Q22" s="583" t="n"/>
-      <c r="R22" s="583" t="n"/>
-      <c r="S22" s="827" t="n"/>
+      <c r="L22" s="931" t="n"/>
+      <c r="M22" s="931" t="n"/>
+      <c r="N22" s="931" t="n"/>
+      <c r="O22" s="932" t="n"/>
+      <c r="P22" s="932" t="n"/>
+      <c r="Q22" s="932" t="n"/>
+      <c r="R22" s="931" t="n"/>
+      <c r="S22" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="23" s="782">
       <c r="A23" s="889" t="n"/>
-      <c r="B23" s="912" t="n">
+      <c r="B23" s="915" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="913" t="inlineStr">
+      <c r="C23" s="916" t="inlineStr">
         <is>
           <t>2022/12</t>
         </is>
       </c>
-      <c r="D23" s="914" t="inlineStr">
+      <c r="D23" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E23" s="913" t="inlineStr">
+      <c r="E23" s="916" t="inlineStr">
         <is>
           <t>2023/06</t>
         </is>
       </c>
-      <c r="F23" s="915" t="inlineStr">
+      <c r="F23" s="918" t="inlineStr">
         <is>
           <t>■ブロックチェーンを活用したクラウドファンディングサービスのサーバーサイド開発</t>
         </is>
       </c>
-      <c r="G23" s="916" t="inlineStr">
+      <c r="G23" s="919" t="inlineStr">
         <is>
           <t>webエンジニア</t>
         </is>
       </c>
-      <c r="H23" s="917" t="inlineStr">
+      <c r="H23" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript、Solidity</t>
         </is>
       </c>
-      <c r="I23" s="917" t="inlineStr">
+      <c r="I23" s="920" t="inlineStr">
         <is>
           <t>MySQL、Firestore</t>
         </is>
       </c>
-      <c r="J23" s="917" t="inlineStr">
+      <c r="J23" s="920" t="inlineStr">
         <is>
           <t>GCP</t>
         </is>
       </c>
-      <c r="K23" s="918" t="inlineStr">
+      <c r="K23" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、React、Next.js、Jest
 エディタ/IDE：VSCode
@@ -6227,26 +6282,26 @@
 コミュニケーション：Slack、Google Meet、Zoom</t>
         </is>
       </c>
-      <c r="L23" s="919" t="n"/>
-      <c r="M23" s="919" t="n"/>
-      <c r="N23" s="919" t="n"/>
-      <c r="O23" s="919" t="inlineStr">
+      <c r="L23" s="922" t="n"/>
+      <c r="M23" s="922" t="n"/>
+      <c r="N23" s="922" t="n"/>
+      <c r="O23" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P23" s="919" t="inlineStr">
+      <c r="P23" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q23" s="919" t="inlineStr">
+      <c r="Q23" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R23" s="919" t="n"/>
-      <c r="S23" s="920" t="n"/>
+      <c r="R23" s="922" t="n"/>
+      <c r="S23" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="184" r="24" s="782">
       <c r="A24" s="889" t="n"/>
@@ -6254,7 +6309,7 @@
       <c r="C24" s="573" t="n"/>
       <c r="D24" s="574" t="n"/>
       <c r="E24" s="573" t="n"/>
-      <c r="F24" s="921" t="inlineStr">
+      <c r="F24" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 ブロックチェーンを活用したクラウドファンディングサービスのサーバーサイド開発(2022年12月〜2023年6月:7ヶ月)
@@ -6264,7 +6319,7 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G24" s="922" t="inlineStr">
+      <c r="G24" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
@@ -6274,19 +6329,19 @@
       <c r="I24" s="574" t="n"/>
       <c r="J24" s="574" t="n"/>
       <c r="K24" s="577" t="n"/>
-      <c r="L24" s="574" t="n"/>
-      <c r="M24" s="574" t="n"/>
-      <c r="N24" s="574" t="n"/>
-      <c r="O24" s="574" t="n"/>
-      <c r="P24" s="574" t="n"/>
-      <c r="Q24" s="574" t="n"/>
-      <c r="R24" s="574" t="n"/>
-      <c r="S24" s="820" t="n"/>
+      <c r="L24" s="927" t="n"/>
+      <c r="M24" s="927" t="n"/>
+      <c r="N24" s="927" t="n"/>
+      <c r="O24" s="928" t="n"/>
+      <c r="P24" s="928" t="n"/>
+      <c r="Q24" s="928" t="n"/>
+      <c r="R24" s="927" t="n"/>
+      <c r="S24" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="25" s="782">
       <c r="A25" s="889" t="n"/>
       <c r="B25" s="579" t="n"/>
-      <c r="C25" s="923" t="inlineStr">
+      <c r="C25" s="930" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
@@ -6299,61 +6354,61 @@
       <c r="I25" s="583" t="n"/>
       <c r="J25" s="583" t="n"/>
       <c r="K25" s="584" t="n"/>
-      <c r="L25" s="583" t="n"/>
-      <c r="M25" s="583" t="n"/>
-      <c r="N25" s="583" t="n"/>
-      <c r="O25" s="583" t="n"/>
-      <c r="P25" s="583" t="n"/>
-      <c r="Q25" s="583" t="n"/>
-      <c r="R25" s="583" t="n"/>
-      <c r="S25" s="827" t="n"/>
+      <c r="L25" s="931" t="n"/>
+      <c r="M25" s="931" t="n"/>
+      <c r="N25" s="931" t="n"/>
+      <c r="O25" s="932" t="n"/>
+      <c r="P25" s="932" t="n"/>
+      <c r="Q25" s="932" t="n"/>
+      <c r="R25" s="931" t="n"/>
+      <c r="S25" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="26" s="782">
       <c r="A26" s="889" t="n"/>
-      <c r="B26" s="912" t="n">
+      <c r="B26" s="915" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="913" t="inlineStr">
+      <c r="C26" s="916" t="inlineStr">
         <is>
           <t>2021/04</t>
         </is>
       </c>
-      <c r="D26" s="914" t="inlineStr">
+      <c r="D26" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E26" s="913" t="inlineStr">
+      <c r="E26" s="916" t="inlineStr">
         <is>
           <t>2022/10</t>
         </is>
       </c>
-      <c r="F26" s="915" t="inlineStr">
+      <c r="F26" s="918" t="inlineStr">
         <is>
           <t>■大手携帯ショップの販売端末価格デジタルサイネージアプリケーション開発</t>
         </is>
       </c>
-      <c r="G26" s="916" t="inlineStr">
+      <c r="G26" s="919" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H26" s="917" t="inlineStr">
+      <c r="H26" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css、 kotlin</t>
         </is>
       </c>
-      <c r="I26" s="917" t="inlineStr">
+      <c r="I26" s="920" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J26" s="917" t="inlineStr">
+      <c r="J26" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K26" s="918" t="inlineStr">
+      <c r="K26" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、Bootstrap、Vue.js、Nuxt.js
 アプリ：PWA
@@ -6362,26 +6417,26 @@
 コミュニケーション：Slack、Teams、Zoom、Miro、Jira</t>
         </is>
       </c>
-      <c r="L26" s="919" t="n"/>
-      <c r="M26" s="919" t="n"/>
-      <c r="N26" s="919" t="n"/>
-      <c r="O26" s="919" t="inlineStr">
+      <c r="L26" s="922" t="n"/>
+      <c r="M26" s="922" t="n"/>
+      <c r="N26" s="922" t="n"/>
+      <c r="O26" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P26" s="919" t="inlineStr">
+      <c r="P26" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q26" s="919" t="inlineStr">
+      <c r="Q26" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R26" s="919" t="n"/>
-      <c r="S26" s="920" t="n"/>
+      <c r="R26" s="922" t="n"/>
+      <c r="S26" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="248" r="27" s="782">
       <c r="A27" s="889" t="n"/>
@@ -6389,7 +6444,7 @@
       <c r="C27" s="573" t="n"/>
       <c r="D27" s="574" t="n"/>
       <c r="E27" s="573" t="n"/>
-      <c r="F27" s="921" t="inlineStr">
+      <c r="F27" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 大手携帯ショップの販売端末価格デジタルサイネージアプリケーション開発(2021年4月〜2022年10月：19ヶ月)
@@ -6399,7 +6454,7 @@
 フルリモート、スクラム（2週間スプリント）、ペアプロ/モブプロ</t>
         </is>
       </c>
-      <c r="G27" s="922" t="inlineStr">
+      <c r="G27" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PO、SM、デザイナー、エンジニア、QA</t>
@@ -6409,19 +6464,19 @@
       <c r="I27" s="574" t="n"/>
       <c r="J27" s="574" t="n"/>
       <c r="K27" s="577" t="n"/>
-      <c r="L27" s="574" t="n"/>
-      <c r="M27" s="574" t="n"/>
-      <c r="N27" s="574" t="n"/>
-      <c r="O27" s="574" t="n"/>
-      <c r="P27" s="574" t="n"/>
-      <c r="Q27" s="574" t="n"/>
-      <c r="R27" s="574" t="n"/>
-      <c r="S27" s="820" t="n"/>
+      <c r="L27" s="927" t="n"/>
+      <c r="M27" s="927" t="n"/>
+      <c r="N27" s="927" t="n"/>
+      <c r="O27" s="928" t="n"/>
+      <c r="P27" s="928" t="n"/>
+      <c r="Q27" s="928" t="n"/>
+      <c r="R27" s="927" t="n"/>
+      <c r="S27" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="28" s="782">
       <c r="A28" s="889" t="n"/>
       <c r="B28" s="579" t="n"/>
-      <c r="C28" s="923" t="inlineStr">
+      <c r="C28" s="930" t="inlineStr">
         <is>
           <t>19ヶ月</t>
         </is>
@@ -6434,61 +6489,61 @@
       <c r="I28" s="583" t="n"/>
       <c r="J28" s="583" t="n"/>
       <c r="K28" s="584" t="n"/>
-      <c r="L28" s="583" t="n"/>
-      <c r="M28" s="583" t="n"/>
-      <c r="N28" s="583" t="n"/>
-      <c r="O28" s="583" t="n"/>
-      <c r="P28" s="583" t="n"/>
-      <c r="Q28" s="583" t="n"/>
-      <c r="R28" s="583" t="n"/>
-      <c r="S28" s="827" t="n"/>
+      <c r="L28" s="931" t="n"/>
+      <c r="M28" s="931" t="n"/>
+      <c r="N28" s="931" t="n"/>
+      <c r="O28" s="932" t="n"/>
+      <c r="P28" s="932" t="n"/>
+      <c r="Q28" s="932" t="n"/>
+      <c r="R28" s="931" t="n"/>
+      <c r="S28" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="29" s="782">
       <c r="A29" s="889" t="n"/>
-      <c r="B29" s="912" t="n">
+      <c r="B29" s="915" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="913" t="inlineStr">
+      <c r="C29" s="916" t="inlineStr">
         <is>
           <t>2020/08</t>
         </is>
       </c>
-      <c r="D29" s="914" t="inlineStr">
+      <c r="D29" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E29" s="913" t="inlineStr">
+      <c r="E29" s="916" t="inlineStr">
         <is>
           <t>2021/01</t>
         </is>
       </c>
-      <c r="F29" s="915" t="inlineStr">
+      <c r="F29" s="918" t="inlineStr">
         <is>
           <t>■医療従事者向けプラットフォーム事業のマイクロサービス開発</t>
         </is>
       </c>
-      <c r="G29" s="916" t="inlineStr">
+      <c r="G29" s="919" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H29" s="917" t="inlineStr">
+      <c r="H29" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、css、TypeScript</t>
         </is>
       </c>
-      <c r="I29" s="917" t="inlineStr">
+      <c r="I29" s="920" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J29" s="917" t="inlineStr">
+      <c r="J29" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K29" s="918" t="inlineStr">
+      <c r="K29" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、React、BULMA
 エディタ/IDE：VSCode
@@ -6496,34 +6551,34 @@
 コミュニケーション：Slack、Zoom</t>
         </is>
       </c>
-      <c r="L29" s="919" t="n"/>
-      <c r="M29" s="919" t="inlineStr">
+      <c r="L29" s="922" t="n"/>
+      <c r="M29" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N29" s="919" t="inlineStr">
+      <c r="N29" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O29" s="919" t="inlineStr">
+      <c r="O29" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P29" s="919" t="inlineStr">
+      <c r="P29" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q29" s="919" t="inlineStr">
+      <c r="Q29" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R29" s="919" t="n"/>
-      <c r="S29" s="920" t="n"/>
+      <c r="R29" s="922" t="n"/>
+      <c r="S29" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="152" r="30" s="782">
       <c r="A30" s="889" t="n"/>
@@ -6531,7 +6586,7 @@
       <c r="C30" s="573" t="n"/>
       <c r="D30" s="574" t="n"/>
       <c r="E30" s="573" t="n"/>
-      <c r="F30" s="921" t="inlineStr">
+      <c r="F30" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 医療従事者向けプラットフォーム事業のマイクロサービス開発(2020年8月〜2021年1月：６ヶ月)
@@ -6541,7 +6596,7 @@
 フルリモート、issue駆動開発、スクラム（1週間スプリント）</t>
         </is>
       </c>
-      <c r="G30" s="922" t="inlineStr">
+      <c r="G30" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、デザイナー、エンジニア、QA</t>
@@ -6551,19 +6606,19 @@
       <c r="I30" s="574" t="n"/>
       <c r="J30" s="574" t="n"/>
       <c r="K30" s="577" t="n"/>
-      <c r="L30" s="574" t="n"/>
-      <c r="M30" s="574" t="n"/>
-      <c r="N30" s="574" t="n"/>
-      <c r="O30" s="574" t="n"/>
-      <c r="P30" s="574" t="n"/>
-      <c r="Q30" s="574" t="n"/>
-      <c r="R30" s="574" t="n"/>
-      <c r="S30" s="820" t="n"/>
+      <c r="L30" s="927" t="n"/>
+      <c r="M30" s="928" t="n"/>
+      <c r="N30" s="928" t="n"/>
+      <c r="O30" s="928" t="n"/>
+      <c r="P30" s="928" t="n"/>
+      <c r="Q30" s="928" t="n"/>
+      <c r="R30" s="927" t="n"/>
+      <c r="S30" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="31" s="782">
       <c r="A31" s="889" t="n"/>
       <c r="B31" s="579" t="n"/>
-      <c r="C31" s="923" t="inlineStr">
+      <c r="C31" s="930" t="inlineStr">
         <is>
           <t>６ヶ月</t>
         </is>
@@ -6576,61 +6631,61 @@
       <c r="I31" s="583" t="n"/>
       <c r="J31" s="583" t="n"/>
       <c r="K31" s="584" t="n"/>
-      <c r="L31" s="583" t="n"/>
-      <c r="M31" s="583" t="n"/>
-      <c r="N31" s="583" t="n"/>
-      <c r="O31" s="583" t="n"/>
-      <c r="P31" s="583" t="n"/>
-      <c r="Q31" s="583" t="n"/>
-      <c r="R31" s="583" t="n"/>
-      <c r="S31" s="827" t="n"/>
+      <c r="L31" s="931" t="n"/>
+      <c r="M31" s="932" t="n"/>
+      <c r="N31" s="932" t="n"/>
+      <c r="O31" s="932" t="n"/>
+      <c r="P31" s="932" t="n"/>
+      <c r="Q31" s="932" t="n"/>
+      <c r="R31" s="931" t="n"/>
+      <c r="S31" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="32" s="782">
       <c r="A32" s="889" t="n"/>
-      <c r="B32" s="912" t="n">
+      <c r="B32" s="915" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="913" t="inlineStr">
+      <c r="C32" s="916" t="inlineStr">
         <is>
           <t>2018/05</t>
         </is>
       </c>
-      <c r="D32" s="914" t="inlineStr">
+      <c r="D32" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E32" s="913" t="inlineStr">
+      <c r="E32" s="916" t="inlineStr">
         <is>
           <t>2020/06</t>
         </is>
       </c>
-      <c r="F32" s="915" t="inlineStr">
+      <c r="F32" s="918" t="inlineStr">
         <is>
           <t>■自動車会社向けIoTシステムの新規事業開発</t>
         </is>
       </c>
-      <c r="G32" s="916" t="inlineStr">
+      <c r="G32" s="919" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H32" s="917" t="inlineStr">
+      <c r="H32" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css、Python</t>
         </is>
       </c>
-      <c r="I32" s="917" t="inlineStr">
+      <c r="I32" s="920" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J32" s="917" t="inlineStr">
+      <c r="J32" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K32" s="918" t="inlineStr">
+      <c r="K32" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、Bootstrap
 エディタ/IDE：VSCode
@@ -6638,38 +6693,38 @@
 コミュニケーション：Slack、Zoom、Miro</t>
         </is>
       </c>
-      <c r="L32" s="919" t="inlineStr">
+      <c r="L32" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M32" s="919" t="inlineStr">
+      <c r="M32" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N32" s="919" t="inlineStr">
+      <c r="N32" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O32" s="919" t="inlineStr">
+      <c r="O32" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P32" s="919" t="inlineStr">
+      <c r="P32" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q32" s="919" t="inlineStr">
+      <c r="Q32" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R32" s="919" t="n"/>
-      <c r="S32" s="920" t="inlineStr">
+      <c r="R32" s="922" t="n"/>
+      <c r="S32" s="934" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -6681,7 +6736,7 @@
       <c r="C33" s="573" t="n"/>
       <c r="D33" s="574" t="n"/>
       <c r="E33" s="573" t="n"/>
-      <c r="F33" s="921" t="inlineStr">
+      <c r="F33" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 自動車会社向けIoTシステムの新規事業開発(2018年5月〜2020年6月：26ヶ月)
@@ -6691,7 +6746,7 @@
 スクラム（1週間スプリント）、ペアプロ/モブプロ</t>
         </is>
       </c>
-      <c r="G33" s="922" t="inlineStr">
+      <c r="G33" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PO、SM、エンジニア</t>
@@ -6701,19 +6756,19 @@
       <c r="I33" s="574" t="n"/>
       <c r="J33" s="574" t="n"/>
       <c r="K33" s="577" t="n"/>
-      <c r="L33" s="574" t="n"/>
-      <c r="M33" s="574" t="n"/>
-      <c r="N33" s="574" t="n"/>
-      <c r="O33" s="574" t="n"/>
-      <c r="P33" s="574" t="n"/>
-      <c r="Q33" s="574" t="n"/>
-      <c r="R33" s="574" t="n"/>
-      <c r="S33" s="820" t="n"/>
+      <c r="L33" s="928" t="n"/>
+      <c r="M33" s="928" t="n"/>
+      <c r="N33" s="928" t="n"/>
+      <c r="O33" s="928" t="n"/>
+      <c r="P33" s="928" t="n"/>
+      <c r="Q33" s="928" t="n"/>
+      <c r="R33" s="927" t="n"/>
+      <c r="S33" s="935" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="34" s="782">
       <c r="A34" s="889" t="n"/>
       <c r="B34" s="579" t="n"/>
-      <c r="C34" s="923" t="inlineStr">
+      <c r="C34" s="930" t="inlineStr">
         <is>
           <t>26ヶ月</t>
         </is>
@@ -6726,87 +6781,87 @@
       <c r="I34" s="583" t="n"/>
       <c r="J34" s="583" t="n"/>
       <c r="K34" s="584" t="n"/>
-      <c r="L34" s="583" t="n"/>
-      <c r="M34" s="583" t="n"/>
-      <c r="N34" s="583" t="n"/>
-      <c r="O34" s="583" t="n"/>
-      <c r="P34" s="583" t="n"/>
-      <c r="Q34" s="583" t="n"/>
-      <c r="R34" s="583" t="n"/>
-      <c r="S34" s="827" t="n"/>
+      <c r="L34" s="932" t="n"/>
+      <c r="M34" s="932" t="n"/>
+      <c r="N34" s="932" t="n"/>
+      <c r="O34" s="932" t="n"/>
+      <c r="P34" s="932" t="n"/>
+      <c r="Q34" s="932" t="n"/>
+      <c r="R34" s="931" t="n"/>
+      <c r="S34" s="936" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="35" s="782">
       <c r="A35" s="889" t="n"/>
-      <c r="B35" s="912" t="n">
+      <c r="B35" s="915" t="n">
         <v>8</v>
       </c>
-      <c r="C35" s="913" t="inlineStr">
+      <c r="C35" s="916" t="inlineStr">
         <is>
           <t>2017/10</t>
         </is>
       </c>
-      <c r="D35" s="914" t="inlineStr">
+      <c r="D35" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E35" s="913" t="inlineStr">
+      <c r="E35" s="916" t="inlineStr">
         <is>
           <t>2018/04</t>
         </is>
       </c>
-      <c r="F35" s="915" t="inlineStr">
+      <c r="F35" s="918" t="inlineStr">
         <is>
           <t>■航空会社向けECサイト開発</t>
         </is>
       </c>
-      <c r="G35" s="916" t="inlineStr">
+      <c r="G35" s="919" t="inlineStr">
         <is>
           <t>システムエンジニア</t>
         </is>
       </c>
-      <c r="H35" s="917" t="inlineStr">
+      <c r="H35" s="920" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I35" s="917" t="inlineStr">
+      <c r="I35" s="920" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J35" s="917" t="inlineStr"/>
-      <c r="K35" s="918" t="inlineStr">
+      <c r="J35" s="920" t="inlineStr"/>
+      <c r="K35" s="921" t="inlineStr">
         <is>
           <t>エディタ/IDE：Eclipse
 その他：Slack、Redmine、svn
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L35" s="919" t="n"/>
-      <c r="M35" s="919" t="n"/>
-      <c r="N35" s="919" t="inlineStr">
+      <c r="L35" s="922" t="n"/>
+      <c r="M35" s="922" t="n"/>
+      <c r="N35" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O35" s="919" t="inlineStr">
+      <c r="O35" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P35" s="919" t="inlineStr">
+      <c r="P35" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q35" s="919" t="inlineStr">
+      <c r="Q35" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R35" s="919" t="n"/>
-      <c r="S35" s="920" t="n"/>
+      <c r="R35" s="922" t="n"/>
+      <c r="S35" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="113" r="36" s="782">
       <c r="A36" s="889" t="n"/>
@@ -6814,7 +6869,7 @@
       <c r="C36" s="573" t="n"/>
       <c r="D36" s="574" t="n"/>
       <c r="E36" s="573" t="n"/>
-      <c r="F36" s="921" t="inlineStr">
+      <c r="F36" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 航空会社向けECサイト開発(2017年10月〜2018年4月：7ヶ月)
@@ -6824,7 +6879,7 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G36" s="922" t="inlineStr">
+      <c r="G36" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア、テスター</t>
@@ -6834,19 +6889,19 @@
       <c r="I36" s="574" t="n"/>
       <c r="J36" s="574" t="n"/>
       <c r="K36" s="577" t="n"/>
-      <c r="L36" s="574" t="n"/>
-      <c r="M36" s="574" t="n"/>
-      <c r="N36" s="574" t="n"/>
-      <c r="O36" s="574" t="n"/>
-      <c r="P36" s="574" t="n"/>
-      <c r="Q36" s="574" t="n"/>
-      <c r="R36" s="574" t="n"/>
-      <c r="S36" s="820" t="n"/>
+      <c r="L36" s="927" t="n"/>
+      <c r="M36" s="927" t="n"/>
+      <c r="N36" s="928" t="n"/>
+      <c r="O36" s="928" t="n"/>
+      <c r="P36" s="928" t="n"/>
+      <c r="Q36" s="928" t="n"/>
+      <c r="R36" s="927" t="n"/>
+      <c r="S36" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="37" s="782">
       <c r="A37" s="889" t="n"/>
       <c r="B37" s="579" t="n"/>
-      <c r="C37" s="923" t="inlineStr">
+      <c r="C37" s="930" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
@@ -6859,87 +6914,87 @@
       <c r="I37" s="583" t="n"/>
       <c r="J37" s="583" t="n"/>
       <c r="K37" s="584" t="n"/>
-      <c r="L37" s="583" t="n"/>
-      <c r="M37" s="583" t="n"/>
-      <c r="N37" s="583" t="n"/>
-      <c r="O37" s="583" t="n"/>
-      <c r="P37" s="583" t="n"/>
-      <c r="Q37" s="583" t="n"/>
-      <c r="R37" s="583" t="n"/>
-      <c r="S37" s="827" t="n"/>
+      <c r="L37" s="931" t="n"/>
+      <c r="M37" s="931" t="n"/>
+      <c r="N37" s="932" t="n"/>
+      <c r="O37" s="932" t="n"/>
+      <c r="P37" s="932" t="n"/>
+      <c r="Q37" s="932" t="n"/>
+      <c r="R37" s="931" t="n"/>
+      <c r="S37" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="38" s="782">
       <c r="A38" s="889" t="n"/>
-      <c r="B38" s="912" t="n">
+      <c r="B38" s="915" t="n">
         <v>9</v>
       </c>
-      <c r="C38" s="913" t="inlineStr">
+      <c r="C38" s="916" t="inlineStr">
         <is>
           <t>2016/08</t>
         </is>
       </c>
-      <c r="D38" s="914" t="inlineStr">
+      <c r="D38" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E38" s="913" t="inlineStr">
+      <c r="E38" s="916" t="inlineStr">
         <is>
           <t>2017/09</t>
         </is>
       </c>
-      <c r="F38" s="915" t="inlineStr">
+      <c r="F38" s="918" t="inlineStr">
         <is>
           <t>■全自動倉庫管理システム開発</t>
         </is>
       </c>
-      <c r="G38" s="916" t="inlineStr">
+      <c r="G38" s="919" t="inlineStr">
         <is>
           <t>システムエンジニア</t>
         </is>
       </c>
-      <c r="H38" s="917" t="inlineStr">
+      <c r="H38" s="920" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I38" s="917" t="inlineStr">
+      <c r="I38" s="920" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J38" s="917" t="inlineStr"/>
-      <c r="K38" s="918" t="inlineStr">
+      <c r="J38" s="920" t="inlineStr"/>
+      <c r="K38" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Spring
 エディタ/IDE：Eclipse
 その他：Redmine、svn</t>
         </is>
       </c>
-      <c r="L38" s="919" t="n"/>
-      <c r="M38" s="919" t="n"/>
-      <c r="N38" s="919" t="inlineStr">
+      <c r="L38" s="922" t="n"/>
+      <c r="M38" s="922" t="n"/>
+      <c r="N38" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O38" s="919" t="inlineStr">
+      <c r="O38" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P38" s="919" t="inlineStr">
+      <c r="P38" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q38" s="919" t="inlineStr">
+      <c r="Q38" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R38" s="919" t="n"/>
-      <c r="S38" s="920" t="n"/>
+      <c r="R38" s="922" t="n"/>
+      <c r="S38" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="113" r="39" s="782">
       <c r="A39" s="889" t="n"/>
@@ -6947,7 +7002,7 @@
       <c r="C39" s="573" t="n"/>
       <c r="D39" s="574" t="n"/>
       <c r="E39" s="573" t="n"/>
-      <c r="F39" s="921" t="inlineStr">
+      <c r="F39" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 全自動倉庫管理システム開発(2016年8月〜2017年9月：14ヶ月)
@@ -6957,7 +7012,7 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G39" s="922" t="inlineStr">
+      <c r="G39" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、リーダー、エンジニア</t>
@@ -6967,19 +7022,19 @@
       <c r="I39" s="574" t="n"/>
       <c r="J39" s="574" t="n"/>
       <c r="K39" s="577" t="n"/>
-      <c r="L39" s="574" t="n"/>
-      <c r="M39" s="574" t="n"/>
-      <c r="N39" s="574" t="n"/>
-      <c r="O39" s="574" t="n"/>
-      <c r="P39" s="574" t="n"/>
-      <c r="Q39" s="574" t="n"/>
-      <c r="R39" s="574" t="n"/>
-      <c r="S39" s="820" t="n"/>
+      <c r="L39" s="927" t="n"/>
+      <c r="M39" s="927" t="n"/>
+      <c r="N39" s="928" t="n"/>
+      <c r="O39" s="928" t="n"/>
+      <c r="P39" s="928" t="n"/>
+      <c r="Q39" s="928" t="n"/>
+      <c r="R39" s="927" t="n"/>
+      <c r="S39" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="40" s="782">
       <c r="A40" s="889" t="n"/>
       <c r="B40" s="579" t="n"/>
-      <c r="C40" s="923" t="inlineStr">
+      <c r="C40" s="930" t="inlineStr">
         <is>
           <t>14ヶ月</t>
         </is>
@@ -6992,94 +7047,94 @@
       <c r="I40" s="583" t="n"/>
       <c r="J40" s="583" t="n"/>
       <c r="K40" s="584" t="n"/>
-      <c r="L40" s="583" t="n"/>
-      <c r="M40" s="583" t="n"/>
-      <c r="N40" s="583" t="n"/>
-      <c r="O40" s="583" t="n"/>
-      <c r="P40" s="583" t="n"/>
-      <c r="Q40" s="583" t="n"/>
-      <c r="R40" s="583" t="n"/>
-      <c r="S40" s="827" t="n"/>
+      <c r="L40" s="931" t="n"/>
+      <c r="M40" s="931" t="n"/>
+      <c r="N40" s="932" t="n"/>
+      <c r="O40" s="932" t="n"/>
+      <c r="P40" s="932" t="n"/>
+      <c r="Q40" s="932" t="n"/>
+      <c r="R40" s="931" t="n"/>
+      <c r="S40" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="57" r="41" s="782">
       <c r="A41" s="889" t="n"/>
-      <c r="B41" s="912" t="n">
+      <c r="B41" s="915" t="n">
         <v>10</v>
       </c>
-      <c r="C41" s="913" t="inlineStr">
+      <c r="C41" s="916" t="inlineStr">
         <is>
           <t>2013/09</t>
         </is>
       </c>
-      <c r="D41" s="914" t="inlineStr">
+      <c r="D41" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E41" s="913" t="inlineStr">
+      <c r="E41" s="916" t="inlineStr">
         <is>
           <t>2016/08</t>
         </is>
       </c>
-      <c r="F41" s="915" t="inlineStr">
+      <c r="F41" s="918" t="inlineStr">
         <is>
           <t>■製油所向けオフサイトシステム</t>
         </is>
       </c>
-      <c r="G41" s="916" t="inlineStr">
+      <c r="G41" s="919" t="inlineStr">
         <is>
           <t>プログラマー、システムエンジニア</t>
         </is>
       </c>
-      <c r="H41" s="917" t="inlineStr">
+      <c r="H41" s="920" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I41" s="917" t="inlineStr">
+      <c r="I41" s="920" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J41" s="917" t="inlineStr"/>
-      <c r="K41" s="918" t="inlineStr">
+      <c r="J41" s="920" t="inlineStr"/>
+      <c r="K41" s="921" t="inlineStr">
         <is>
           <t>エディタ/IDE：Eclipse
 その他：svn</t>
         </is>
       </c>
-      <c r="L41" s="919" t="n"/>
-      <c r="M41" s="919" t="inlineStr">
+      <c r="L41" s="922" t="n"/>
+      <c r="M41" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N41" s="919" t="inlineStr">
+      <c r="N41" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O41" s="919" t="inlineStr">
+      <c r="O41" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P41" s="919" t="inlineStr">
+      <c r="P41" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q41" s="919" t="inlineStr">
+      <c r="Q41" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R41" s="919" t="inlineStr">
+      <c r="R41" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S41" s="920" t="inlineStr">
+      <c r="S41" s="934" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -7091,7 +7146,7 @@
       <c r="C42" s="573" t="n"/>
       <c r="D42" s="574" t="n"/>
       <c r="E42" s="573" t="n"/>
-      <c r="F42" s="921" t="inlineStr">
+      <c r="F42" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 製油所向けオフサイトシステム(2013年9月〜2016年8月：36ヶ月)
@@ -7101,7 +7156,7 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G42" s="922" t="inlineStr">
+      <c r="G42" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、リーダー、エンジニア</t>
@@ -7111,19 +7166,19 @@
       <c r="I42" s="574" t="n"/>
       <c r="J42" s="574" t="n"/>
       <c r="K42" s="577" t="n"/>
-      <c r="L42" s="574" t="n"/>
-      <c r="M42" s="574" t="n"/>
-      <c r="N42" s="574" t="n"/>
-      <c r="O42" s="574" t="n"/>
-      <c r="P42" s="574" t="n"/>
-      <c r="Q42" s="574" t="n"/>
-      <c r="R42" s="574" t="n"/>
-      <c r="S42" s="820" t="n"/>
+      <c r="L42" s="927" t="n"/>
+      <c r="M42" s="928" t="n"/>
+      <c r="N42" s="928" t="n"/>
+      <c r="O42" s="928" t="n"/>
+      <c r="P42" s="928" t="n"/>
+      <c r="Q42" s="928" t="n"/>
+      <c r="R42" s="928" t="n"/>
+      <c r="S42" s="935" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="43" s="782">
       <c r="A43" s="889" t="n"/>
       <c r="B43" s="579" t="n"/>
-      <c r="C43" s="923" t="inlineStr">
+      <c r="C43" s="930" t="inlineStr">
         <is>
           <t>36ヶ月</t>
         </is>
@@ -7136,86 +7191,86 @@
       <c r="I43" s="583" t="n"/>
       <c r="J43" s="583" t="n"/>
       <c r="K43" s="584" t="n"/>
-      <c r="L43" s="583" t="n"/>
-      <c r="M43" s="583" t="n"/>
-      <c r="N43" s="583" t="n"/>
-      <c r="O43" s="583" t="n"/>
-      <c r="P43" s="583" t="n"/>
-      <c r="Q43" s="583" t="n"/>
-      <c r="R43" s="583" t="n"/>
-      <c r="S43" s="827" t="n"/>
+      <c r="L43" s="931" t="n"/>
+      <c r="M43" s="932" t="n"/>
+      <c r="N43" s="932" t="n"/>
+      <c r="O43" s="932" t="n"/>
+      <c r="P43" s="932" t="n"/>
+      <c r="Q43" s="932" t="n"/>
+      <c r="R43" s="932" t="n"/>
+      <c r="S43" s="936" t="n"/>
     </row>
     <row customHeight="1" ht="28" r="44" s="782">
       <c r="A44" s="889" t="n"/>
-      <c r="B44" s="924" t="inlineStr">
+      <c r="B44" s="937" t="inlineStr">
         <is>
           <t>副業案件</t>
         </is>
       </c>
-      <c r="C44" s="925" t="n"/>
-      <c r="D44" s="925" t="n"/>
-      <c r="E44" s="925" t="n"/>
-      <c r="F44" s="925" t="n"/>
-      <c r="G44" s="925" t="n"/>
-      <c r="H44" s="925" t="n"/>
-      <c r="I44" s="925" t="n"/>
-      <c r="J44" s="925" t="n"/>
-      <c r="K44" s="925" t="n"/>
-      <c r="L44" s="925" t="n"/>
-      <c r="M44" s="925" t="n"/>
-      <c r="N44" s="925" t="n"/>
-      <c r="O44" s="925" t="n"/>
-      <c r="P44" s="925" t="n"/>
-      <c r="Q44" s="925" t="n"/>
-      <c r="R44" s="925" t="n"/>
-      <c r="S44" s="926" t="n"/>
+      <c r="C44" s="938" t="n"/>
+      <c r="D44" s="938" t="n"/>
+      <c r="E44" s="938" t="n"/>
+      <c r="F44" s="938" t="n"/>
+      <c r="G44" s="938" t="n"/>
+      <c r="H44" s="938" t="n"/>
+      <c r="I44" s="938" t="n"/>
+      <c r="J44" s="938" t="n"/>
+      <c r="K44" s="938" t="n"/>
+      <c r="L44" s="938" t="n"/>
+      <c r="M44" s="938" t="n"/>
+      <c r="N44" s="938" t="n"/>
+      <c r="O44" s="938" t="n"/>
+      <c r="P44" s="938" t="n"/>
+      <c r="Q44" s="938" t="n"/>
+      <c r="R44" s="938" t="n"/>
+      <c r="S44" s="939" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="45" s="782">
       <c r="A45" s="889" t="n"/>
-      <c r="B45" s="912" t="n">
+      <c r="B45" s="915" t="n">
         <v>11</v>
       </c>
-      <c r="C45" s="913" t="inlineStr">
+      <c r="C45" s="916" t="inlineStr">
         <is>
           <t>2025/08</t>
         </is>
       </c>
-      <c r="D45" s="914" t="inlineStr">
+      <c r="D45" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E45" s="913" t="inlineStr">
+      <c r="E45" s="916" t="inlineStr">
         <is>
           <t>2026/06</t>
         </is>
       </c>
-      <c r="F45" s="915" t="inlineStr">
+      <c r="F45" s="918" t="inlineStr">
         <is>
           <t>■富裕層向けの旅行代事業のCRM新規開発</t>
         </is>
       </c>
-      <c r="G45" s="916" t="inlineStr">
+      <c r="G45" s="919" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H45" s="917" t="inlineStr">
+      <c r="H45" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript</t>
         </is>
       </c>
-      <c r="I45" s="917" t="inlineStr">
+      <c r="I45" s="920" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J45" s="917" t="inlineStr">
+      <c r="J45" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K45" s="918" t="inlineStr">
+      <c r="K45" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Next.js
 エディタ/IDE：Cursor
@@ -7224,18 +7279,18 @@
 コミュニケーション：Slack、Notion</t>
         </is>
       </c>
-      <c r="L45" s="919" t="n"/>
-      <c r="M45" s="919" t="n"/>
-      <c r="N45" s="919" t="n"/>
-      <c r="O45" s="919" t="inlineStr">
+      <c r="L45" s="922" t="n"/>
+      <c r="M45" s="922" t="n"/>
+      <c r="N45" s="922" t="n"/>
+      <c r="O45" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P45" s="919" t="n"/>
-      <c r="Q45" s="919" t="n"/>
-      <c r="R45" s="919" t="n"/>
-      <c r="S45" s="920" t="n"/>
+      <c r="P45" s="922" t="n"/>
+      <c r="Q45" s="922" t="n"/>
+      <c r="R45" s="922" t="n"/>
+      <c r="S45" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="152" r="46" s="782">
       <c r="A46" s="889" t="n"/>
@@ -7243,7 +7298,7 @@
       <c r="C46" s="573" t="n"/>
       <c r="D46" s="574" t="n"/>
       <c r="E46" s="573" t="n"/>
-      <c r="F46" s="921" t="inlineStr">
+      <c r="F46" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 富裕層向けの旅行代事業のCRM新規開発(2025年8月〜2026年6月：11ヶ月）
@@ -7253,7 +7308,7 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G46" s="922" t="inlineStr">
+      <c r="G46" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア、デザイナー</t>
@@ -7263,19 +7318,19 @@
       <c r="I46" s="574" t="n"/>
       <c r="J46" s="574" t="n"/>
       <c r="K46" s="577" t="n"/>
-      <c r="L46" s="574" t="n"/>
-      <c r="M46" s="574" t="n"/>
-      <c r="N46" s="574" t="n"/>
-      <c r="O46" s="574" t="n"/>
-      <c r="P46" s="574" t="n"/>
-      <c r="Q46" s="574" t="n"/>
-      <c r="R46" s="574" t="n"/>
-      <c r="S46" s="820" t="n"/>
+      <c r="L46" s="927" t="n"/>
+      <c r="M46" s="927" t="n"/>
+      <c r="N46" s="927" t="n"/>
+      <c r="O46" s="928" t="n"/>
+      <c r="P46" s="927" t="n"/>
+      <c r="Q46" s="927" t="n"/>
+      <c r="R46" s="927" t="n"/>
+      <c r="S46" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="47" s="782">
       <c r="A47" s="889" t="n"/>
       <c r="B47" s="579" t="n"/>
-      <c r="C47" s="923" t="inlineStr">
+      <c r="C47" s="930" t="inlineStr">
         <is>
           <t>11ヶ月</t>
         </is>
@@ -7288,57 +7343,57 @@
       <c r="I47" s="583" t="n"/>
       <c r="J47" s="583" t="n"/>
       <c r="K47" s="584" t="n"/>
-      <c r="L47" s="583" t="n"/>
-      <c r="M47" s="583" t="n"/>
-      <c r="N47" s="583" t="n"/>
-      <c r="O47" s="583" t="n"/>
-      <c r="P47" s="583" t="n"/>
-      <c r="Q47" s="583" t="n"/>
-      <c r="R47" s="583" t="n"/>
-      <c r="S47" s="827" t="n"/>
+      <c r="L47" s="931" t="n"/>
+      <c r="M47" s="931" t="n"/>
+      <c r="N47" s="931" t="n"/>
+      <c r="O47" s="932" t="n"/>
+      <c r="P47" s="931" t="n"/>
+      <c r="Q47" s="931" t="n"/>
+      <c r="R47" s="931" t="n"/>
+      <c r="S47" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="25" r="48" s="782">
       <c r="A48" s="889" t="n"/>
-      <c r="B48" s="912" t="n">
+      <c r="B48" s="915" t="n">
         <v>12</v>
       </c>
-      <c r="C48" s="913" t="inlineStr">
+      <c r="C48" s="916" t="inlineStr">
         <is>
           <t>2025/03</t>
         </is>
       </c>
-      <c r="D48" s="914" t="inlineStr">
+      <c r="D48" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E48" s="913" t="inlineStr">
+      <c r="E48" s="916" t="inlineStr">
         <is>
           <t>2025/07</t>
         </is>
       </c>
-      <c r="F48" s="915" t="inlineStr">
+      <c r="F48" s="918" t="inlineStr">
         <is>
           <t>■パスキー認証システムの管理サービス開発＜副業＞</t>
         </is>
       </c>
-      <c r="G48" s="916" t="inlineStr">
+      <c r="G48" s="919" t="inlineStr">
         <is>
           <t>エンジニア</t>
         </is>
       </c>
-      <c r="H48" s="917" t="inlineStr">
+      <c r="H48" s="920" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I48" s="917" t="inlineStr">
+      <c r="I48" s="920" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J48" s="917" t="inlineStr"/>
-      <c r="K48" s="918" t="inlineStr">
+      <c r="J48" s="920" t="inlineStr"/>
+      <c r="K48" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails
 エディタ/IDE：Cursor
@@ -7347,18 +7402,18 @@
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L48" s="919" t="n"/>
-      <c r="M48" s="919" t="n"/>
-      <c r="N48" s="919" t="n"/>
-      <c r="O48" s="919" t="inlineStr">
+      <c r="L48" s="922" t="n"/>
+      <c r="M48" s="922" t="n"/>
+      <c r="N48" s="922" t="n"/>
+      <c r="O48" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P48" s="919" t="n"/>
-      <c r="Q48" s="919" t="n"/>
-      <c r="R48" s="919" t="n"/>
-      <c r="S48" s="920" t="n"/>
+      <c r="P48" s="922" t="n"/>
+      <c r="Q48" s="922" t="n"/>
+      <c r="R48" s="922" t="n"/>
+      <c r="S48" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="136" r="49" s="782">
       <c r="A49" s="889" t="n"/>
@@ -7366,7 +7421,7 @@
       <c r="C49" s="573" t="n"/>
       <c r="D49" s="574" t="n"/>
       <c r="E49" s="573" t="n"/>
-      <c r="F49" s="921" t="inlineStr">
+      <c r="F49" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 パスキー認証システムの管理サービス開発(2025年3月〜2025年7月：5ヶ月）＜副業＞
@@ -7376,7 +7431,7 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G49" s="922" t="inlineStr">
+      <c r="G49" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
@@ -7386,19 +7441,19 @@
       <c r="I49" s="574" t="n"/>
       <c r="J49" s="574" t="n"/>
       <c r="K49" s="577" t="n"/>
-      <c r="L49" s="574" t="n"/>
-      <c r="M49" s="574" t="n"/>
-      <c r="N49" s="574" t="n"/>
-      <c r="O49" s="574" t="n"/>
-      <c r="P49" s="574" t="n"/>
-      <c r="Q49" s="574" t="n"/>
-      <c r="R49" s="574" t="n"/>
-      <c r="S49" s="820" t="n"/>
+      <c r="L49" s="927" t="n"/>
+      <c r="M49" s="927" t="n"/>
+      <c r="N49" s="927" t="n"/>
+      <c r="O49" s="928" t="n"/>
+      <c r="P49" s="927" t="n"/>
+      <c r="Q49" s="927" t="n"/>
+      <c r="R49" s="927" t="n"/>
+      <c r="S49" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="50" s="782">
       <c r="A50" s="889" t="n"/>
       <c r="B50" s="579" t="n"/>
-      <c r="C50" s="923" t="inlineStr">
+      <c r="C50" s="930" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
@@ -7411,57 +7466,57 @@
       <c r="I50" s="583" t="n"/>
       <c r="J50" s="583" t="n"/>
       <c r="K50" s="584" t="n"/>
-      <c r="L50" s="583" t="n"/>
-      <c r="M50" s="583" t="n"/>
-      <c r="N50" s="583" t="n"/>
-      <c r="O50" s="583" t="n"/>
-      <c r="P50" s="583" t="n"/>
-      <c r="Q50" s="583" t="n"/>
-      <c r="R50" s="583" t="n"/>
-      <c r="S50" s="827" t="n"/>
+      <c r="L50" s="931" t="n"/>
+      <c r="M50" s="931" t="n"/>
+      <c r="N50" s="931" t="n"/>
+      <c r="O50" s="932" t="n"/>
+      <c r="P50" s="931" t="n"/>
+      <c r="Q50" s="931" t="n"/>
+      <c r="R50" s="931" t="n"/>
+      <c r="S50" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="51" s="782">
       <c r="A51" s="889" t="n"/>
-      <c r="B51" s="912" t="n">
+      <c r="B51" s="915" t="n">
         <v>13</v>
       </c>
-      <c r="C51" s="913" t="inlineStr">
+      <c r="C51" s="916" t="inlineStr">
         <is>
           <t>2022/04</t>
         </is>
       </c>
-      <c r="D51" s="914" t="inlineStr">
+      <c r="D51" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E51" s="913" t="inlineStr">
+      <c r="E51" s="916" t="inlineStr">
         <is>
           <t>2022/08</t>
         </is>
       </c>
-      <c r="F51" s="915" t="inlineStr">
+      <c r="F51" s="918" t="inlineStr">
         <is>
           <t>■セールステック領域SaaSのプロダクト開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G51" s="916" t="inlineStr">
+      <c r="G51" s="919" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H51" s="917" t="inlineStr">
+      <c r="H51" s="920" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I51" s="917" t="inlineStr">
+      <c r="I51" s="920" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J51" s="917" t="inlineStr"/>
-      <c r="K51" s="918" t="inlineStr">
+      <c r="J51" s="920" t="inlineStr"/>
+      <c r="K51" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec
 エディタ/IDE：VSCode
@@ -7469,18 +7524,18 @@
 コミュニケーション：Slack、Zoom</t>
         </is>
       </c>
-      <c r="L51" s="919" t="n"/>
-      <c r="M51" s="919" t="n"/>
-      <c r="N51" s="919" t="n"/>
-      <c r="O51" s="919" t="inlineStr">
+      <c r="L51" s="922" t="n"/>
+      <c r="M51" s="922" t="n"/>
+      <c r="N51" s="922" t="n"/>
+      <c r="O51" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P51" s="919" t="n"/>
-      <c r="Q51" s="919" t="n"/>
-      <c r="R51" s="919" t="n"/>
-      <c r="S51" s="920" t="n"/>
+      <c r="P51" s="922" t="n"/>
+      <c r="Q51" s="922" t="n"/>
+      <c r="R51" s="922" t="n"/>
+      <c r="S51" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="129" r="52" s="782">
       <c r="A52" s="889" t="n"/>
@@ -7488,7 +7543,7 @@
       <c r="C52" s="573" t="n"/>
       <c r="D52" s="574" t="n"/>
       <c r="E52" s="573" t="n"/>
-      <c r="F52" s="921" t="inlineStr">
+      <c r="F52" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 セールステック領域SaaSのプロダクト開発(2022年4月〜2022年8月：5ヶ月) ＜副業＞
@@ -7498,7 +7553,7 @@
 フルリモート、チケット駆動開発</t>
         </is>
       </c>
-      <c r="G52" s="922" t="inlineStr">
+      <c r="G52" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
@@ -7508,19 +7563,19 @@
       <c r="I52" s="574" t="n"/>
       <c r="J52" s="574" t="n"/>
       <c r="K52" s="577" t="n"/>
-      <c r="L52" s="574" t="n"/>
-      <c r="M52" s="574" t="n"/>
-      <c r="N52" s="574" t="n"/>
-      <c r="O52" s="574" t="n"/>
-      <c r="P52" s="574" t="n"/>
-      <c r="Q52" s="574" t="n"/>
-      <c r="R52" s="574" t="n"/>
-      <c r="S52" s="820" t="n"/>
+      <c r="L52" s="927" t="n"/>
+      <c r="M52" s="927" t="n"/>
+      <c r="N52" s="927" t="n"/>
+      <c r="O52" s="928" t="n"/>
+      <c r="P52" s="927" t="n"/>
+      <c r="Q52" s="927" t="n"/>
+      <c r="R52" s="927" t="n"/>
+      <c r="S52" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="53" s="782">
       <c r="A53" s="889" t="n"/>
       <c r="B53" s="579" t="n"/>
-      <c r="C53" s="923" t="inlineStr">
+      <c r="C53" s="930" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
@@ -7533,57 +7588,57 @@
       <c r="I53" s="583" t="n"/>
       <c r="J53" s="583" t="n"/>
       <c r="K53" s="584" t="n"/>
-      <c r="L53" s="583" t="n"/>
-      <c r="M53" s="583" t="n"/>
-      <c r="N53" s="583" t="n"/>
-      <c r="O53" s="583" t="n"/>
-      <c r="P53" s="583" t="n"/>
-      <c r="Q53" s="583" t="n"/>
-      <c r="R53" s="583" t="n"/>
-      <c r="S53" s="827" t="n"/>
+      <c r="L53" s="931" t="n"/>
+      <c r="M53" s="931" t="n"/>
+      <c r="N53" s="931" t="n"/>
+      <c r="O53" s="932" t="n"/>
+      <c r="P53" s="931" t="n"/>
+      <c r="Q53" s="931" t="n"/>
+      <c r="R53" s="931" t="n"/>
+      <c r="S53" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="54" s="782">
       <c r="A54" s="889" t="n"/>
-      <c r="B54" s="912" t="n">
+      <c r="B54" s="915" t="n">
         <v>14</v>
       </c>
-      <c r="C54" s="913" t="inlineStr">
+      <c r="C54" s="916" t="inlineStr">
         <is>
           <t>2020/10</t>
         </is>
       </c>
-      <c r="D54" s="914" t="inlineStr">
+      <c r="D54" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E54" s="913" t="inlineStr">
+      <c r="E54" s="916" t="inlineStr">
         <is>
           <t>2021/01</t>
         </is>
       </c>
-      <c r="F54" s="915" t="inlineStr">
+      <c r="F54" s="918" t="inlineStr">
         <is>
           <t>■営業支援SaaSのプロダクト開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G54" s="916" t="inlineStr">
+      <c r="G54" s="919" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H54" s="917" t="inlineStr">
+      <c r="H54" s="920" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="I54" s="917" t="inlineStr">
+      <c r="I54" s="920" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J54" s="917" t="inlineStr"/>
-      <c r="K54" s="918" t="inlineStr">
+      <c r="J54" s="920" t="inlineStr"/>
+      <c r="K54" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Django、Tailwind CSS
 エディタ/IDE：VSCode
@@ -7591,18 +7646,18 @@
 コミュニケーション：Slack、trello</t>
         </is>
       </c>
-      <c r="L54" s="919" t="n"/>
-      <c r="M54" s="919" t="n"/>
-      <c r="N54" s="919" t="n"/>
-      <c r="O54" s="919" t="inlineStr">
+      <c r="L54" s="922" t="n"/>
+      <c r="M54" s="922" t="n"/>
+      <c r="N54" s="922" t="n"/>
+      <c r="O54" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P54" s="919" t="n"/>
-      <c r="Q54" s="919" t="n"/>
-      <c r="R54" s="919" t="n"/>
-      <c r="S54" s="920" t="n"/>
+      <c r="P54" s="922" t="n"/>
+      <c r="Q54" s="922" t="n"/>
+      <c r="R54" s="922" t="n"/>
+      <c r="S54" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="129" r="55" s="782">
       <c r="A55" s="889" t="n"/>
@@ -7610,7 +7665,7 @@
       <c r="C55" s="573" t="n"/>
       <c r="D55" s="574" t="n"/>
       <c r="E55" s="573" t="n"/>
-      <c r="F55" s="921" t="inlineStr">
+      <c r="F55" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 営業支援SaaSのプロダクト開発(2020年10月〜2021年1月：４ヶ月) ＜副業＞
@@ -7620,7 +7675,7 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G55" s="922" t="inlineStr">
+      <c r="G55" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
@@ -7630,19 +7685,19 @@
       <c r="I55" s="574" t="n"/>
       <c r="J55" s="574" t="n"/>
       <c r="K55" s="577" t="n"/>
-      <c r="L55" s="574" t="n"/>
-      <c r="M55" s="574" t="n"/>
-      <c r="N55" s="574" t="n"/>
-      <c r="O55" s="574" t="n"/>
-      <c r="P55" s="574" t="n"/>
-      <c r="Q55" s="574" t="n"/>
-      <c r="R55" s="574" t="n"/>
-      <c r="S55" s="820" t="n"/>
+      <c r="L55" s="927" t="n"/>
+      <c r="M55" s="927" t="n"/>
+      <c r="N55" s="927" t="n"/>
+      <c r="O55" s="928" t="n"/>
+      <c r="P55" s="927" t="n"/>
+      <c r="Q55" s="927" t="n"/>
+      <c r="R55" s="927" t="n"/>
+      <c r="S55" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="56" s="782">
       <c r="A56" s="889" t="n"/>
       <c r="B56" s="579" t="n"/>
-      <c r="C56" s="923" t="inlineStr">
+      <c r="C56" s="930" t="inlineStr">
         <is>
           <t>４ヶ月</t>
         </is>
@@ -7655,57 +7710,57 @@
       <c r="I56" s="583" t="n"/>
       <c r="J56" s="583" t="n"/>
       <c r="K56" s="584" t="n"/>
-      <c r="L56" s="583" t="n"/>
-      <c r="M56" s="583" t="n"/>
-      <c r="N56" s="583" t="n"/>
-      <c r="O56" s="583" t="n"/>
-      <c r="P56" s="583" t="n"/>
-      <c r="Q56" s="583" t="n"/>
-      <c r="R56" s="583" t="n"/>
-      <c r="S56" s="827" t="n"/>
+      <c r="L56" s="931" t="n"/>
+      <c r="M56" s="931" t="n"/>
+      <c r="N56" s="931" t="n"/>
+      <c r="O56" s="932" t="n"/>
+      <c r="P56" s="931" t="n"/>
+      <c r="Q56" s="931" t="n"/>
+      <c r="R56" s="931" t="n"/>
+      <c r="S56" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="41" r="57" s="782">
       <c r="A57" s="889" t="n"/>
-      <c r="B57" s="912" t="n">
+      <c r="B57" s="915" t="n">
         <v>15</v>
       </c>
-      <c r="C57" s="913" t="inlineStr">
+      <c r="C57" s="916" t="inlineStr">
         <is>
           <t>2020/02</t>
         </is>
       </c>
-      <c r="D57" s="914" t="inlineStr">
+      <c r="D57" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E57" s="913" t="inlineStr">
+      <c r="E57" s="916" t="inlineStr">
         <is>
           <t>2020/07</t>
         </is>
       </c>
-      <c r="F57" s="915" t="inlineStr">
+      <c r="F57" s="918" t="inlineStr">
         <is>
           <t>■エンジニア組織のパフォーマンス最大化サービス開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G57" s="916" t="inlineStr">
+      <c r="G57" s="919" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H57" s="917" t="inlineStr">
+      <c r="H57" s="920" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I57" s="917" t="inlineStr">
+      <c r="I57" s="920" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J57" s="917" t="inlineStr"/>
-      <c r="K57" s="918" t="inlineStr">
+      <c r="J57" s="920" t="inlineStr"/>
+      <c r="K57" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails
 エディタ/IDE：VSCode
@@ -7713,18 +7768,18 @@
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L57" s="919" t="n"/>
-      <c r="M57" s="919" t="n"/>
-      <c r="N57" s="919" t="n"/>
-      <c r="O57" s="919" t="inlineStr">
+      <c r="L57" s="922" t="n"/>
+      <c r="M57" s="922" t="n"/>
+      <c r="N57" s="922" t="n"/>
+      <c r="O57" s="923" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P57" s="919" t="n"/>
-      <c r="Q57" s="919" t="n"/>
-      <c r="R57" s="919" t="n"/>
-      <c r="S57" s="920" t="n"/>
+      <c r="P57" s="922" t="n"/>
+      <c r="Q57" s="922" t="n"/>
+      <c r="R57" s="922" t="n"/>
+      <c r="S57" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="129" r="58" s="782">
       <c r="A58" s="889" t="n"/>
@@ -7732,7 +7787,7 @@
       <c r="C58" s="573" t="n"/>
       <c r="D58" s="574" t="n"/>
       <c r="E58" s="573" t="n"/>
-      <c r="F58" s="921" t="inlineStr">
+      <c r="F58" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 エンジニア組織のパフォーマンス最大化サービス開発(2020年2月〜2020年7月:6ヶ月) ＜副業＞
@@ -7742,7 +7797,7 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G58" s="922" t="inlineStr">
+      <c r="G58" s="926" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
@@ -7752,19 +7807,19 @@
       <c r="I58" s="574" t="n"/>
       <c r="J58" s="574" t="n"/>
       <c r="K58" s="577" t="n"/>
-      <c r="L58" s="574" t="n"/>
-      <c r="M58" s="574" t="n"/>
-      <c r="N58" s="574" t="n"/>
-      <c r="O58" s="574" t="n"/>
-      <c r="P58" s="574" t="n"/>
-      <c r="Q58" s="574" t="n"/>
-      <c r="R58" s="574" t="n"/>
-      <c r="S58" s="820" t="n"/>
+      <c r="L58" s="927" t="n"/>
+      <c r="M58" s="927" t="n"/>
+      <c r="N58" s="927" t="n"/>
+      <c r="O58" s="928" t="n"/>
+      <c r="P58" s="927" t="n"/>
+      <c r="Q58" s="927" t="n"/>
+      <c r="R58" s="927" t="n"/>
+      <c r="S58" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="59" s="782">
       <c r="A59" s="889" t="n"/>
       <c r="B59" s="579" t="n"/>
-      <c r="C59" s="923" t="inlineStr">
+      <c r="C59" s="930" t="inlineStr">
         <is>
           <t>6ヶ月</t>
         </is>
@@ -7777,75 +7832,75 @@
       <c r="I59" s="583" t="n"/>
       <c r="J59" s="583" t="n"/>
       <c r="K59" s="584" t="n"/>
-      <c r="L59" s="583" t="n"/>
-      <c r="M59" s="583" t="n"/>
-      <c r="N59" s="583" t="n"/>
-      <c r="O59" s="583" t="n"/>
-      <c r="P59" s="583" t="n"/>
-      <c r="Q59" s="583" t="n"/>
-      <c r="R59" s="583" t="n"/>
-      <c r="S59" s="827" t="n"/>
+      <c r="L59" s="931" t="n"/>
+      <c r="M59" s="931" t="n"/>
+      <c r="N59" s="931" t="n"/>
+      <c r="O59" s="932" t="n"/>
+      <c r="P59" s="931" t="n"/>
+      <c r="Q59" s="931" t="n"/>
+      <c r="R59" s="931" t="n"/>
+      <c r="S59" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="25" r="60" s="782">
       <c r="A60" s="889" t="n"/>
-      <c r="B60" s="912" t="n">
+      <c r="B60" s="915" t="n">
         <v>16</v>
       </c>
-      <c r="C60" s="913" t="inlineStr">
+      <c r="C60" s="916" t="inlineStr">
         <is>
           <t>2019/05</t>
         </is>
       </c>
-      <c r="D60" s="914" t="inlineStr">
+      <c r="D60" s="917" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E60" s="913" t="inlineStr">
+      <c r="E60" s="916" t="inlineStr">
         <is>
           <t>2019/12</t>
         </is>
       </c>
-      <c r="F60" s="915" t="inlineStr">
+      <c r="F60" s="918" t="inlineStr">
         <is>
           <t>■プログラミングスクール学習サポート ＜副業＞</t>
         </is>
       </c>
-      <c r="G60" s="916" t="inlineStr">
+      <c r="G60" s="919" t="inlineStr">
         <is>
           <t>メンター</t>
         </is>
       </c>
-      <c r="H60" s="917" t="inlineStr">
+      <c r="H60" s="920" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I60" s="917" t="inlineStr">
+      <c r="I60" s="920" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J60" s="917" t="inlineStr">
+      <c r="J60" s="920" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K60" s="918" t="inlineStr">
+      <c r="K60" s="921" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Bootstrap
 エディタ/IDE：VSCode
 その他：Git、Vagrant、Bootstrap</t>
         </is>
       </c>
-      <c r="L60" s="919" t="n"/>
-      <c r="M60" s="919" t="n"/>
-      <c r="N60" s="919" t="n"/>
-      <c r="O60" s="919" t="n"/>
-      <c r="P60" s="919" t="n"/>
-      <c r="Q60" s="919" t="n"/>
-      <c r="R60" s="919" t="n"/>
-      <c r="S60" s="920" t="n"/>
+      <c r="L60" s="922" t="n"/>
+      <c r="M60" s="922" t="n"/>
+      <c r="N60" s="922" t="n"/>
+      <c r="O60" s="922" t="n"/>
+      <c r="P60" s="922" t="n"/>
+      <c r="Q60" s="922" t="n"/>
+      <c r="R60" s="922" t="n"/>
+      <c r="S60" s="924" t="n"/>
     </row>
     <row customHeight="1" ht="88" r="61" s="782">
       <c r="A61" s="889" t="n"/>
@@ -7853,7 +7908,7 @@
       <c r="C61" s="573" t="n"/>
       <c r="D61" s="574" t="n"/>
       <c r="E61" s="573" t="n"/>
-      <c r="F61" s="921" t="inlineStr">
+      <c r="F61" s="925" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 プログラミングスクール学習サポート(2019年5月〜2019年12月：8ヶ月) ＜副業＞
@@ -7861,24 +7916,24 @@
 受講生サポート、コードレビュー</t>
         </is>
       </c>
-      <c r="G61" s="922" t="inlineStr"/>
+      <c r="G61" s="926" t="inlineStr"/>
       <c r="H61" s="574" t="n"/>
       <c r="I61" s="574" t="n"/>
       <c r="J61" s="574" t="n"/>
       <c r="K61" s="577" t="n"/>
-      <c r="L61" s="574" t="n"/>
-      <c r="M61" s="574" t="n"/>
-      <c r="N61" s="574" t="n"/>
-      <c r="O61" s="574" t="n"/>
-      <c r="P61" s="574" t="n"/>
-      <c r="Q61" s="574" t="n"/>
-      <c r="R61" s="574" t="n"/>
-      <c r="S61" s="820" t="n"/>
+      <c r="L61" s="927" t="n"/>
+      <c r="M61" s="927" t="n"/>
+      <c r="N61" s="927" t="n"/>
+      <c r="O61" s="927" t="n"/>
+      <c r="P61" s="927" t="n"/>
+      <c r="Q61" s="927" t="n"/>
+      <c r="R61" s="927" t="n"/>
+      <c r="S61" s="929" t="n"/>
     </row>
     <row customHeight="1" ht="24" r="62" s="782">
       <c r="A62" s="889" t="n"/>
       <c r="B62" s="579" t="n"/>
-      <c r="C62" s="923" t="inlineStr">
+      <c r="C62" s="930" t="inlineStr">
         <is>
           <t>8ヶ月</t>
         </is>
@@ -7891,18 +7946,18 @@
       <c r="I62" s="583" t="n"/>
       <c r="J62" s="583" t="n"/>
       <c r="K62" s="584" t="n"/>
-      <c r="L62" s="583" t="n"/>
-      <c r="M62" s="583" t="n"/>
-      <c r="N62" s="583" t="n"/>
-      <c r="O62" s="583" t="n"/>
-      <c r="P62" s="583" t="n"/>
-      <c r="Q62" s="583" t="n"/>
-      <c r="R62" s="583" t="n"/>
-      <c r="S62" s="827" t="n"/>
+      <c r="L62" s="931" t="n"/>
+      <c r="M62" s="931" t="n"/>
+      <c r="N62" s="931" t="n"/>
+      <c r="O62" s="931" t="n"/>
+      <c r="P62" s="931" t="n"/>
+      <c r="Q62" s="931" t="n"/>
+      <c r="R62" s="931" t="n"/>
+      <c r="S62" s="933" t="n"/>
     </row>
     <row customHeight="1" ht="28" r="63" s="782">
       <c r="A63" s="889" t="n"/>
-      <c r="B63" s="927" t="inlineStr">
+      <c r="B63" s="940" t="inlineStr">
         <is>
           <t>●：READMEの工程/作業に明記された担当工程。空欄：未記載（経験なしを意味しません）。案件名のリンクから詳細を確認できます。</t>
         </is>
@@ -8267,15 +8322,6 @@
     <mergeCell ref="S57:S59"/>
     <mergeCell ref="S60:S62"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="1" showInputMessage="0" sqref="D4:F5"/>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="1" sqref="I4:S4" type="list">
-      <formula1>"男性,女性,　　　　"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="1" showInputMessage="1" sqref="L14:S31" type="list">
-      <formula1>"●"</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId2"/>
@@ -8302,14 +8348,12 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="7" manualBreakCount="7">
+  <rowBreaks count="5" manualBreakCount="5">
     <brk id="11" man="1" max="16383" min="0"/>
-    <brk id="19" man="1" max="16383" min="0"/>
-    <brk id="25" man="1" max="16383" min="0"/>
+    <brk id="22" man="1" max="16383" min="0"/>
     <brk id="31" man="1" max="16383" min="0"/>
-    <brk id="40" man="1" max="16383" min="0"/>
     <brk id="43" man="1" max="16383" min="0"/>
-    <brk id="53" man="1" max="16383" min="0"/>
+    <brk id="56" man="1" max="16383" min="0"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -19,7 +19,7 @@
     <numFmt formatCode="&quot;&quot;#&quot;歳&quot;" numFmtId="165"/>
     <numFmt formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@" numFmtId="166"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="34">
     <font>
       <name val="游ゴシック"/>
       <color theme="1"/>
@@ -155,11 +155,55 @@
     </font>
     <font>
       <name val="メイリオ"/>
-      <color rgb="0053657A"/>
+      <color rgb="0017365D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="メイリオ"/>
+      <color rgb="0017365D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="0017365D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="0017365D"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -234,18 +278,8 @@
         <fgColor rgb="00E9F1F8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDF3F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="234">
+  <borders count="296">
     <border/>
     <border>
       <bottom style="medium">
@@ -2528,6 +2562,682 @@
       </top>
       <bottom style="thin">
         <color indexed="58"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="double">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="double">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <bottom style="double">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <bottom style="double">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <bottom style="double">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <bottom style="hair">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
       </bottom>
     </border>
   </borders>
@@ -2537,7 +3247,7 @@
     </xf>
     <xf borderId="84" fillId="0" fontId="1" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="941">
+  <cellXfs count="973">
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4989,140 +5699,180 @@
     <xf applyAlignment="1" borderId="36" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="84" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="84" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="84" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="84" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="84" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="84" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="84" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="89" fillId="13" fontId="21" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="90" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="204" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf applyAlignment="1" borderId="234" fillId="14" fontId="20" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="234" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="235" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="236" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="237" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="94" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="95" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf borderId="238" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="239" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="240" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="241" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="96" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="97" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf borderId="242" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="243" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="244" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="245" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="98" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="99" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf borderId="246" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="247" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="248" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="249" fillId="13" fontId="26" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="97" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="250" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="245" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="99" fillId="0" fontId="7" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf applyAlignment="1" borderId="249" fillId="13" fontId="26" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="100" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="101" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="251" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="252" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="253" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="103" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="105" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="254" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="255" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="256" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="106" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="111" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="176" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="257" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="258" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="258" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="259" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="260" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="261" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="262" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="84" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="117" fillId="14" fontId="23" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="166" fillId="14" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="167" fillId="14" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="39" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="46" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="118" fillId="4" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="86" fillId="0" fontId="4" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="120" fillId="0" fontId="7" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="84" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="263" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="264" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="265" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="266" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="266" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="267" fillId="14" fontId="23" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="268" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="269" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="270" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="271" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="272" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="273" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="274" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="275" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="276" fillId="14" fontId="33" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="277" fillId="13" fontId="26" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="278" fillId="13" fontId="26" numFmtId="166" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="35" fillId="16" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="277" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="36" fillId="16" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="110" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="279" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="280" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="173" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="281" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="110" fillId="13" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" borderId="110" fillId="15" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" borderId="131" fillId="13" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf applyAlignment="1" borderId="172" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="280" fillId="15" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="282" fillId="15" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="283" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="284" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="285" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="286" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="172" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="122" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="122" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="170" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="172" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="123" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="123" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="171" fillId="13" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="131" fillId="15" fontId="24" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="170" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="171" fillId="15" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="118" fillId="17" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="233" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="173" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="84" fillId="0" fontId="25" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="286" fillId="13" fontId="26" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="287" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="285" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="288" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="289" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="290" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="291" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="292" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="293" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="292" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="294" fillId="15" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="280" fillId="13" fontId="30" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyAlignment="1" borderId="282" fillId="13" fontId="30" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="288" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="294" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="276" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="295" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="281" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="84" fillId="13" fontId="25" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5349,37 +6099,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0017365D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="19"/>
   <cols>
-    <col customWidth="1" max="1" min="1" style="593" width="2.6640625"/>
-    <col customWidth="1" max="2" min="2" style="593" width="3.83203125"/>
-    <col customWidth="1" max="3" min="3" style="593" width="12.6640625"/>
-    <col customWidth="1" max="4" min="4" style="593" width="2.6640625"/>
-    <col customWidth="1" max="5" min="5" style="593" width="12.6640625"/>
-    <col customWidth="1" max="6" min="6" style="593" width="74"/>
-    <col customWidth="1" max="7" min="7" style="593" width="18"/>
-    <col customWidth="1" max="8" min="8" style="593" width="20.1640625"/>
-    <col customWidth="1" max="10" min="9" style="593" width="18.6640625"/>
-    <col customWidth="1" max="11" min="11" style="593" width="19"/>
-    <col customWidth="1" max="12" min="12" style="593" width="8.5"/>
-    <col customWidth="1" max="13" min="13" style="782" width="8.5"/>
-    <col customWidth="1" max="14" min="14" style="782" width="8.5"/>
-    <col customWidth="1" max="15" min="15" style="782" width="8.5"/>
-    <col customWidth="1" max="16" min="16" style="782" width="8.5"/>
-    <col customWidth="1" max="17" min="17" style="782" width="8.5"/>
-    <col customWidth="1" max="18" min="18" style="782" width="8.5"/>
-    <col customWidth="1" max="19" min="19" style="782" width="8.5"/>
-    <col customWidth="1" max="20" min="20" style="593" width="2.6640625"/>
-    <col customWidth="1" max="16384" min="21" style="593" width="9"/>
+    <col customWidth="1" max="1" min="1" style="887" width="2.6640625"/>
+    <col customWidth="1" max="2" min="2" style="887" width="3.83203125"/>
+    <col customWidth="1" max="3" min="3" style="887" width="12.6640625"/>
+    <col customWidth="1" max="4" min="4" style="887" width="2.6640625"/>
+    <col customWidth="1" max="5" min="5" style="887" width="12.6640625"/>
+    <col customWidth="1" max="6" min="6" style="887" width="74"/>
+    <col customWidth="1" max="7" min="7" style="887" width="18"/>
+    <col customWidth="1" max="8" min="8" style="887" width="20.1640625"/>
+    <col customWidth="1" max="10" min="9" style="887" width="18.6640625"/>
+    <col customWidth="1" max="11" min="11" style="887" width="19"/>
+    <col customWidth="1" max="12" min="12" style="887" width="8.5"/>
+    <col customWidth="1" max="13" min="13" style="888" width="8.5"/>
+    <col customWidth="1" max="14" min="14" style="888" width="8.5"/>
+    <col customWidth="1" max="15" min="15" style="888" width="8.5"/>
+    <col customWidth="1" max="16" min="16" style="888" width="8.5"/>
+    <col customWidth="1" max="17" min="17" style="888" width="8.5"/>
+    <col customWidth="1" max="18" min="18" style="888" width="8.5"/>
+    <col customWidth="1" max="19" min="19" style="888" width="8.5"/>
+    <col customWidth="1" max="20" min="20" style="887" width="2.6640625"/>
+    <col customWidth="1" max="16384" min="21" style="887" width="9"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="24" r="1" s="782">
-      <c r="G1" s="773" t="n"/>
-      <c r="M1" s="887" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="1" s="888">
+      <c r="A1" s="888" t="n"/>
+      <c r="B1" s="888" t="n"/>
+      <c r="C1" s="888" t="n"/>
+      <c r="D1" s="888" t="n"/>
+      <c r="E1" s="888" t="n"/>
+      <c r="F1" s="888" t="n"/>
+      <c r="G1" s="889" t="n"/>
+      <c r="H1" s="888" t="n"/>
+      <c r="I1" s="888" t="n"/>
+      <c r="J1" s="888" t="n"/>
+      <c r="K1" s="888" t="n"/>
+      <c r="L1" s="888" t="n"/>
+      <c r="M1" s="890" t="inlineStr">
         <is>
           <t>2026/10 更新</t>
         </is>
@@ -5391,211 +6153,211 @@
       <c r="R1" s="888" t="n"/>
       <c r="S1" s="888" t="n"/>
     </row>
-    <row customHeight="1" ht="30" r="2" s="782">
-      <c r="A2" s="889" t="n"/>
-      <c r="B2" s="890" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="30" r="2" s="888">
+      <c r="A2" s="891" t="n"/>
+      <c r="B2" s="892" t="inlineStr">
         <is>
           <t>スキルシート</t>
         </is>
       </c>
-      <c r="C2" s="521" t="n"/>
-      <c r="D2" s="521" t="n"/>
-      <c r="E2" s="521" t="n"/>
-      <c r="F2" s="521" t="n"/>
-      <c r="G2" s="521" t="n"/>
-      <c r="H2" s="521" t="n"/>
-      <c r="I2" s="521" t="n"/>
-      <c r="J2" s="521" t="n"/>
-      <c r="K2" s="521" t="n"/>
-      <c r="L2" s="521" t="n"/>
-      <c r="M2" s="521" t="n"/>
-      <c r="N2" s="521" t="n"/>
-      <c r="O2" s="521" t="n"/>
-      <c r="P2" s="521" t="n"/>
-      <c r="Q2" s="521" t="n"/>
-      <c r="R2" s="521" t="n"/>
-      <c r="S2" s="521" t="n"/>
+      <c r="C2" s="893" t="n"/>
+      <c r="D2" s="893" t="n"/>
+      <c r="E2" s="893" t="n"/>
+      <c r="F2" s="893" t="n"/>
+      <c r="G2" s="893" t="n"/>
+      <c r="H2" s="893" t="n"/>
+      <c r="I2" s="893" t="n"/>
+      <c r="J2" s="893" t="n"/>
+      <c r="K2" s="893" t="n"/>
+      <c r="L2" s="893" t="n"/>
+      <c r="M2" s="893" t="n"/>
+      <c r="N2" s="893" t="n"/>
+      <c r="O2" s="893" t="n"/>
+      <c r="P2" s="893" t="n"/>
+      <c r="Q2" s="893" t="n"/>
+      <c r="R2" s="893" t="n"/>
+      <c r="S2" s="893" t="n"/>
     </row>
-    <row customHeight="1" ht="25" r="3" s="782">
-      <c r="A3" s="889" t="n"/>
-      <c r="B3" s="891" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="25" r="3" s="888">
+      <c r="A3" s="891" t="n"/>
+      <c r="B3" s="894" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
       </c>
-      <c r="C3" s="784" t="n"/>
-      <c r="D3" s="892" t="inlineStr">
+      <c r="C3" s="895" t="n"/>
+      <c r="D3" s="896" t="inlineStr">
         <is>
           <t>ヒラタ トモアキ</t>
         </is>
       </c>
-      <c r="E3" s="525" t="n"/>
-      <c r="F3" s="526" t="n"/>
-      <c r="G3" s="893" t="inlineStr">
+      <c r="E3" s="897" t="n"/>
+      <c r="F3" s="898" t="n"/>
+      <c r="G3" s="899" t="inlineStr">
         <is>
           <t>業界経験</t>
         </is>
       </c>
-      <c r="H3" s="784" t="n"/>
-      <c r="I3" s="894" t="inlineStr">
+      <c r="H3" s="895" t="n"/>
+      <c r="I3" s="900" t="inlineStr">
         <is>
           <t>14年目</t>
         </is>
       </c>
-      <c r="J3" s="788" t="n"/>
-      <c r="K3" s="788" t="n"/>
-      <c r="L3" s="788" t="n"/>
-      <c r="M3" s="788" t="n"/>
-      <c r="N3" s="788" t="n"/>
-      <c r="O3" s="788" t="n"/>
-      <c r="P3" s="788" t="n"/>
-      <c r="Q3" s="788" t="n"/>
-      <c r="R3" s="788" t="n"/>
-      <c r="S3" s="789" t="n"/>
+      <c r="J3" s="897" t="n"/>
+      <c r="K3" s="897" t="n"/>
+      <c r="L3" s="897" t="n"/>
+      <c r="M3" s="897" t="n"/>
+      <c r="N3" s="897" t="n"/>
+      <c r="O3" s="897" t="n"/>
+      <c r="P3" s="897" t="n"/>
+      <c r="Q3" s="897" t="n"/>
+      <c r="R3" s="897" t="n"/>
+      <c r="S3" s="901" t="n"/>
     </row>
-    <row customHeight="1" ht="25" r="4" s="782">
-      <c r="A4" s="889" t="n"/>
-      <c r="B4" s="895" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="25" r="4" s="888">
+      <c r="A4" s="891" t="n"/>
+      <c r="B4" s="902" t="inlineStr">
         <is>
           <t>氏　　名</t>
         </is>
       </c>
-      <c r="C4" s="790" t="n"/>
-      <c r="D4" s="896" t="inlineStr">
+      <c r="C4" s="903" t="n"/>
+      <c r="D4" s="904" t="inlineStr">
         <is>
           <t>平田 智昭</t>
         </is>
       </c>
-      <c r="E4" s="791" t="n"/>
-      <c r="F4" s="792" t="n"/>
-      <c r="G4" s="897" t="inlineStr">
+      <c r="E4" s="905" t="n"/>
+      <c r="F4" s="906" t="n"/>
+      <c r="G4" s="907" t="inlineStr">
         <is>
           <t>性　　別</t>
         </is>
       </c>
-      <c r="H4" s="790" t="n"/>
-      <c r="I4" s="898" t="inlineStr">
+      <c r="H4" s="903" t="n"/>
+      <c r="I4" s="908" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="J4" s="793" t="n"/>
-      <c r="K4" s="793" t="n"/>
-      <c r="L4" s="793" t="n"/>
-      <c r="M4" s="793" t="n"/>
-      <c r="N4" s="793" t="n"/>
-      <c r="O4" s="793" t="n"/>
-      <c r="P4" s="793" t="n"/>
-      <c r="Q4" s="793" t="n"/>
-      <c r="R4" s="793" t="n"/>
-      <c r="S4" s="794" t="n"/>
+      <c r="J4" s="905" t="n"/>
+      <c r="K4" s="905" t="n"/>
+      <c r="L4" s="905" t="n"/>
+      <c r="M4" s="905" t="n"/>
+      <c r="N4" s="905" t="n"/>
+      <c r="O4" s="905" t="n"/>
+      <c r="P4" s="905" t="n"/>
+      <c r="Q4" s="905" t="n"/>
+      <c r="R4" s="905" t="n"/>
+      <c r="S4" s="909" t="n"/>
     </row>
-    <row customHeight="1" ht="25" r="5" s="782">
-      <c r="A5" s="889" t="n"/>
-      <c r="B5" s="895" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="25" r="5" s="888">
+      <c r="A5" s="891" t="n"/>
+      <c r="B5" s="902" t="inlineStr">
         <is>
           <t>最 寄 駅</t>
         </is>
       </c>
-      <c r="C5" s="790" t="n"/>
-      <c r="D5" s="899" t="inlineStr">
+      <c r="C5" s="903" t="n"/>
+      <c r="D5" s="910" t="inlineStr">
         <is>
           <t>東海道線 平塚駅 / 基本リモート(必要に応じて出社)</t>
         </is>
       </c>
-      <c r="E5" s="791" t="n"/>
-      <c r="F5" s="792" t="n"/>
-      <c r="G5" s="897" t="inlineStr">
+      <c r="E5" s="905" t="n"/>
+      <c r="F5" s="906" t="n"/>
+      <c r="G5" s="907" t="inlineStr">
         <is>
           <t>年　　齢</t>
         </is>
       </c>
-      <c r="H5" s="790" t="n"/>
-      <c r="I5" s="900" t="inlineStr">
+      <c r="H5" s="903" t="n"/>
+      <c r="I5" s="911" t="inlineStr">
         <is>
           <t>38歳</t>
         </is>
       </c>
-      <c r="J5" s="793" t="n"/>
-      <c r="K5" s="793" t="n"/>
-      <c r="L5" s="793" t="n"/>
-      <c r="M5" s="793" t="n"/>
-      <c r="N5" s="793" t="n"/>
-      <c r="O5" s="793" t="n"/>
-      <c r="P5" s="793" t="n"/>
-      <c r="Q5" s="793" t="n"/>
-      <c r="R5" s="793" t="n"/>
-      <c r="S5" s="794" t="n"/>
+      <c r="J5" s="905" t="n"/>
+      <c r="K5" s="905" t="n"/>
+      <c r="L5" s="905" t="n"/>
+      <c r="M5" s="905" t="n"/>
+      <c r="N5" s="905" t="n"/>
+      <c r="O5" s="905" t="n"/>
+      <c r="P5" s="905" t="n"/>
+      <c r="Q5" s="905" t="n"/>
+      <c r="R5" s="905" t="n"/>
+      <c r="S5" s="909" t="n"/>
     </row>
-    <row customHeight="1" ht="57" r="6" s="782">
-      <c r="A6" s="889" t="n"/>
-      <c r="B6" s="901" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="57" r="6" s="888">
+      <c r="A6" s="891" t="n"/>
+      <c r="B6" s="912" t="inlineStr">
         <is>
           <t>資　　格</t>
         </is>
       </c>
-      <c r="C6" s="795" t="n"/>
-      <c r="D6" s="902" t="inlineStr">
+      <c r="C6" s="913" t="n"/>
+      <c r="D6" s="914" t="inlineStr">
         <is>
           <t>認定スクラムマスター(LSM) ※2022/12 失効
 基本情報技術者
 Ruby Association Certified Ruby Programmer Gold Version 3</t>
         </is>
       </c>
-      <c r="E6" s="543" t="n"/>
-      <c r="F6" s="543" t="n"/>
-      <c r="G6" s="903" t="inlineStr">
+      <c r="E6" s="915" t="n"/>
+      <c r="F6" s="915" t="n"/>
+      <c r="G6" s="916" t="inlineStr">
         <is>
           <t>学　　歴</t>
         </is>
       </c>
-      <c r="H6" s="795" t="n"/>
-      <c r="I6" s="904" t="inlineStr">
+      <c r="H6" s="913" t="n"/>
+      <c r="I6" s="917" t="inlineStr">
         <is>
           <t>工学院大学 工学部 機械システム工学科卒</t>
         </is>
       </c>
-      <c r="J6" s="797" t="n"/>
-      <c r="K6" s="797" t="n"/>
-      <c r="L6" s="797" t="n"/>
-      <c r="M6" s="797" t="n"/>
-      <c r="N6" s="797" t="n"/>
-      <c r="O6" s="797" t="n"/>
-      <c r="P6" s="797" t="n"/>
-      <c r="Q6" s="797" t="n"/>
-      <c r="R6" s="797" t="n"/>
-      <c r="S6" s="798" t="n"/>
+      <c r="J6" s="915" t="n"/>
+      <c r="K6" s="915" t="n"/>
+      <c r="L6" s="915" t="n"/>
+      <c r="M6" s="915" t="n"/>
+      <c r="N6" s="915" t="n"/>
+      <c r="O6" s="915" t="n"/>
+      <c r="P6" s="915" t="n"/>
+      <c r="Q6" s="915" t="n"/>
+      <c r="R6" s="915" t="n"/>
+      <c r="S6" s="918" t="n"/>
     </row>
-    <row customHeight="1" ht="10" r="7" s="782">
-      <c r="A7" s="889" t="n"/>
-      <c r="B7" s="905" t="n"/>
-      <c r="C7" s="548" t="n"/>
-      <c r="D7" s="548" t="n"/>
-      <c r="E7" s="548" t="n"/>
-      <c r="F7" s="548" t="n"/>
-      <c r="G7" s="548" t="n"/>
-      <c r="H7" s="548" t="n"/>
-      <c r="I7" s="548" t="n"/>
-      <c r="J7" s="548" t="n"/>
-      <c r="K7" s="548" t="n"/>
-      <c r="L7" s="548" t="n"/>
-      <c r="M7" s="548" t="n"/>
-      <c r="N7" s="548" t="n"/>
-      <c r="O7" s="548" t="n"/>
-      <c r="P7" s="548" t="n"/>
-      <c r="Q7" s="548" t="n"/>
-      <c r="R7" s="548" t="n"/>
-      <c r="S7" s="548" t="n"/>
+    <row customFormat="1" customHeight="1" ht="10" r="7" s="888">
+      <c r="A7" s="891" t="n"/>
+      <c r="B7" s="919" t="n"/>
+      <c r="C7" s="920" t="n"/>
+      <c r="D7" s="920" t="n"/>
+      <c r="E7" s="920" t="n"/>
+      <c r="F7" s="920" t="n"/>
+      <c r="G7" s="920" t="n"/>
+      <c r="H7" s="920" t="n"/>
+      <c r="I7" s="920" t="n"/>
+      <c r="J7" s="920" t="n"/>
+      <c r="K7" s="920" t="n"/>
+      <c r="L7" s="920" t="n"/>
+      <c r="M7" s="920" t="n"/>
+      <c r="N7" s="920" t="n"/>
+      <c r="O7" s="920" t="n"/>
+      <c r="P7" s="920" t="n"/>
+      <c r="Q7" s="920" t="n"/>
+      <c r="R7" s="920" t="n"/>
+      <c r="S7" s="920" t="n"/>
     </row>
-    <row customHeight="1" ht="201" r="8" s="782">
-      <c r="A8" s="889" t="n"/>
-      <c r="B8" s="906" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="201" r="8" s="888">
+      <c r="A8" s="891" t="n"/>
+      <c r="B8" s="921" t="inlineStr">
         <is>
           <t>職務要約</t>
         </is>
       </c>
-      <c r="C8" s="550" t="n"/>
-      <c r="D8" s="907" t="inlineStr">
+      <c r="C8" s="922" t="n"/>
+      <c r="D8" s="923" t="inlineStr">
         <is>
           <t>新卒にて中小ソフトウェア企業に入社後、2013年から正社員として5年間、受託開発や客先開発でJavaやOracleを使ったシステム開発に携わりました。
 2017年にフリーランスに転身してから現在まで8年間、Ruby on Railsを主軸としたバックエンド開発をメインとしながら、React/Next.jsなどのモダンフロントエンド技術、AWSインフラ構築、DBパフォーマンスチューニングまで幅広くフルスタックに対応してきました。
@@ -5604,31 +6366,31 @@
 今後も、AIツールを効果的に活用しながら開発生産性を向上させつつ、チームリードとしての責任を果たし、ビジネス価値の高いプロダクト開発に貢献していきたいと考えております。何卒よろしくお願いいたします。</t>
         </is>
       </c>
-      <c r="E8" s="548" t="n"/>
-      <c r="F8" s="548" t="n"/>
-      <c r="G8" s="548" t="n"/>
-      <c r="H8" s="548" t="n"/>
-      <c r="I8" s="548" t="n"/>
-      <c r="J8" s="548" t="n"/>
-      <c r="K8" s="548" t="n"/>
-      <c r="L8" s="548" t="n"/>
-      <c r="M8" s="548" t="n"/>
-      <c r="N8" s="548" t="n"/>
-      <c r="O8" s="548" t="n"/>
-      <c r="P8" s="548" t="n"/>
-      <c r="Q8" s="548" t="n"/>
-      <c r="R8" s="548" t="n"/>
-      <c r="S8" s="552" t="n"/>
+      <c r="E8" s="920" t="n"/>
+      <c r="F8" s="920" t="n"/>
+      <c r="G8" s="920" t="n"/>
+      <c r="H8" s="920" t="n"/>
+      <c r="I8" s="920" t="n"/>
+      <c r="J8" s="920" t="n"/>
+      <c r="K8" s="920" t="n"/>
+      <c r="L8" s="920" t="n"/>
+      <c r="M8" s="920" t="n"/>
+      <c r="N8" s="920" t="n"/>
+      <c r="O8" s="920" t="n"/>
+      <c r="P8" s="920" t="n"/>
+      <c r="Q8" s="920" t="n"/>
+      <c r="R8" s="920" t="n"/>
+      <c r="S8" s="924" t="n"/>
     </row>
-    <row customHeight="1" ht="169" r="9" s="782">
-      <c r="A9" s="889" t="n"/>
-      <c r="B9" s="906" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="169" r="9" s="888">
+      <c r="A9" s="891" t="n"/>
+      <c r="B9" s="921" t="inlineStr">
         <is>
           <t>得意とする分野</t>
         </is>
       </c>
-      <c r="C9" s="550" t="n"/>
-      <c r="D9" s="907" t="inlineStr">
+      <c r="C9" s="922" t="n"/>
+      <c r="D9" s="923" t="inlineStr">
         <is>
           <t>- Ruby on Railsを中心としたWebアプリケーションのバックエンド開発
 - React/Next.js/TypeScriptを用いたフロントエンド開発
@@ -5641,31 +6403,31 @@
 所属：フリーランス</t>
         </is>
       </c>
-      <c r="E9" s="548" t="n"/>
-      <c r="F9" s="548" t="n"/>
-      <c r="G9" s="548" t="n"/>
-      <c r="H9" s="548" t="n"/>
-      <c r="I9" s="548" t="n"/>
-      <c r="J9" s="548" t="n"/>
-      <c r="K9" s="548" t="n"/>
-      <c r="L9" s="548" t="n"/>
-      <c r="M9" s="548" t="n"/>
-      <c r="N9" s="548" t="n"/>
-      <c r="O9" s="548" t="n"/>
-      <c r="P9" s="548" t="n"/>
-      <c r="Q9" s="548" t="n"/>
-      <c r="R9" s="548" t="n"/>
-      <c r="S9" s="552" t="n"/>
+      <c r="E9" s="920" t="n"/>
+      <c r="F9" s="920" t="n"/>
+      <c r="G9" s="920" t="n"/>
+      <c r="H9" s="920" t="n"/>
+      <c r="I9" s="920" t="n"/>
+      <c r="J9" s="920" t="n"/>
+      <c r="K9" s="920" t="n"/>
+      <c r="L9" s="920" t="n"/>
+      <c r="M9" s="920" t="n"/>
+      <c r="N9" s="920" t="n"/>
+      <c r="O9" s="920" t="n"/>
+      <c r="P9" s="920" t="n"/>
+      <c r="Q9" s="920" t="n"/>
+      <c r="R9" s="920" t="n"/>
+      <c r="S9" s="924" t="n"/>
     </row>
-    <row customHeight="1" ht="153" r="10" s="782">
-      <c r="A10" s="889" t="n"/>
-      <c r="B10" s="906" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="153" r="10" s="888">
+      <c r="A10" s="891" t="n"/>
+      <c r="B10" s="921" t="inlineStr">
         <is>
           <t>スキル</t>
         </is>
       </c>
-      <c r="C10" s="550" t="n"/>
-      <c r="D10" s="907" t="inlineStr">
+      <c r="C10" s="922" t="n"/>
+      <c r="D10" s="923" t="inlineStr">
         <is>
           <t>・キャリア：フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09
 ・プログラミング言語：HTML 10年、CSS  10年、Javascript 10年、SQL 10年、Ruby 8年、Java 5年、TypeScript 3年、Python 2年、Kotlin 1年未満
@@ -5676,205 +6438,207 @@
 ・その他ソフトウェアツール、サービス：Slack 8年、Docker 6年、Eclipse 4年、Redmine 3年、CircleCI 3年、Swagger 3年、Google Analytics 2年、Jira 3年、Confluence 2年、Terraform 2年、GitHubActions 2年、Twilio 1年、Vagrant 1年、Zabbix 1年、Jmeter 1年、AndroidStudio 1年</t>
         </is>
       </c>
-      <c r="E10" s="548" t="n"/>
-      <c r="F10" s="548" t="n"/>
-      <c r="G10" s="548" t="n"/>
-      <c r="H10" s="548" t="n"/>
-      <c r="I10" s="548" t="n"/>
-      <c r="J10" s="548" t="n"/>
-      <c r="K10" s="548" t="n"/>
-      <c r="L10" s="548" t="n"/>
-      <c r="M10" s="548" t="n"/>
-      <c r="N10" s="548" t="n"/>
-      <c r="O10" s="548" t="n"/>
-      <c r="P10" s="548" t="n"/>
-      <c r="Q10" s="548" t="n"/>
-      <c r="R10" s="548" t="n"/>
-      <c r="S10" s="552" t="n"/>
+      <c r="E10" s="920" t="n"/>
+      <c r="F10" s="920" t="n"/>
+      <c r="G10" s="920" t="n"/>
+      <c r="H10" s="920" t="n"/>
+      <c r="I10" s="920" t="n"/>
+      <c r="J10" s="920" t="n"/>
+      <c r="K10" s="920" t="n"/>
+      <c r="L10" s="920" t="n"/>
+      <c r="M10" s="920" t="n"/>
+      <c r="N10" s="920" t="n"/>
+      <c r="O10" s="920" t="n"/>
+      <c r="P10" s="920" t="n"/>
+      <c r="Q10" s="920" t="n"/>
+      <c r="R10" s="920" t="n"/>
+      <c r="S10" s="924" t="n"/>
     </row>
-    <row customHeight="1" ht="10" r="11" s="782">
-      <c r="A11" s="889" t="n"/>
-      <c r="B11" s="889" t="n"/>
-      <c r="C11" s="889" t="n"/>
-      <c r="D11" s="908" t="n"/>
-      <c r="E11" s="889" t="n"/>
-      <c r="F11" s="908" t="n"/>
-      <c r="G11" s="909" t="n"/>
-      <c r="H11" s="908" t="n"/>
-      <c r="I11" s="908" t="n"/>
-      <c r="J11" s="908" t="n"/>
-      <c r="K11" s="908" t="n"/>
-      <c r="L11" s="889" t="n"/>
-      <c r="M11" s="889" t="n"/>
-      <c r="N11" s="889" t="n"/>
-      <c r="O11" s="889" t="n"/>
-      <c r="P11" s="889" t="n"/>
-      <c r="Q11" s="889" t="n"/>
-      <c r="R11" s="889" t="n"/>
-      <c r="S11" s="889" t="n"/>
+    <row customFormat="1" customHeight="1" ht="10" r="11" s="888">
+      <c r="A11" s="891" t="n"/>
+      <c r="B11" s="891" t="n"/>
+      <c r="C11" s="891" t="n"/>
+      <c r="D11" s="925" t="n"/>
+      <c r="E11" s="891" t="n"/>
+      <c r="F11" s="925" t="n"/>
+      <c r="G11" s="926" t="n"/>
+      <c r="H11" s="925" t="n"/>
+      <c r="I11" s="925" t="n"/>
+      <c r="J11" s="925" t="n"/>
+      <c r="K11" s="925" t="n"/>
+      <c r="L11" s="891" t="n"/>
+      <c r="M11" s="891" t="n"/>
+      <c r="N11" s="891" t="n"/>
+      <c r="O11" s="891" t="n"/>
+      <c r="P11" s="891" t="n"/>
+      <c r="Q11" s="891" t="n"/>
+      <c r="R11" s="891" t="n"/>
+      <c r="S11" s="891" t="n"/>
     </row>
-    <row customHeight="1" ht="26" r="12" s="782">
-      <c r="B12" s="554" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="26" r="12" s="888">
+      <c r="A12" s="888" t="n"/>
+      <c r="B12" s="927" t="inlineStr">
         <is>
           <t>期間</t>
         </is>
       </c>
-      <c r="C12" s="555" t="n"/>
-      <c r="D12" s="555" t="n"/>
-      <c r="E12" s="556" t="n"/>
-      <c r="F12" s="557" t="inlineStr">
+      <c r="C12" s="928" t="n"/>
+      <c r="D12" s="928" t="n"/>
+      <c r="E12" s="929" t="n"/>
+      <c r="F12" s="930" t="inlineStr">
         <is>
           <t>業務内容</t>
         </is>
       </c>
-      <c r="G12" s="197" t="inlineStr">
+      <c r="G12" s="931" t="inlineStr">
         <is>
           <t>役割
 規模</t>
         </is>
       </c>
-      <c r="H12" s="557" t="inlineStr">
+      <c r="H12" s="930" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="I12" s="557" t="inlineStr">
+      <c r="I12" s="930" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="J12" s="557" t="inlineStr">
+      <c r="J12" s="930" t="inlineStr">
         <is>
           <t>機種
 ・
 OS</t>
         </is>
       </c>
-      <c r="K12" s="557" t="inlineStr">
+      <c r="K12" s="930" t="inlineStr">
         <is>
           <t>FW
 ・
 ツール等</t>
         </is>
       </c>
-      <c r="L12" s="910" t="inlineStr">
+      <c r="L12" s="932" t="inlineStr">
         <is>
           <t>担当工程</t>
         </is>
       </c>
-      <c r="M12" s="911" t="n"/>
-      <c r="N12" s="911" t="n"/>
-      <c r="O12" s="911" t="n"/>
-      <c r="P12" s="911" t="n"/>
-      <c r="Q12" s="911" t="n"/>
-      <c r="R12" s="911" t="n"/>
-      <c r="S12" s="912" t="n"/>
+      <c r="M12" s="933" t="n"/>
+      <c r="N12" s="933" t="n"/>
+      <c r="O12" s="933" t="n"/>
+      <c r="P12" s="933" t="n"/>
+      <c r="Q12" s="933" t="n"/>
+      <c r="R12" s="933" t="n"/>
+      <c r="S12" s="934" t="n"/>
     </row>
-    <row customHeight="1" ht="46" r="13" s="782">
-      <c r="B13" s="807" t="n"/>
-      <c r="C13" s="808" t="n"/>
-      <c r="D13" s="808" t="n"/>
-      <c r="E13" s="809" t="n"/>
-      <c r="F13" s="810" t="n"/>
-      <c r="G13" s="810" t="n"/>
-      <c r="H13" s="810" t="n"/>
-      <c r="I13" s="810" t="n"/>
-      <c r="J13" s="810" t="n"/>
-      <c r="K13" s="810" t="n"/>
-      <c r="L13" s="913" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="46" r="13" s="888">
+      <c r="A13" s="888" t="n"/>
+      <c r="B13" s="935" t="n"/>
+      <c r="C13" s="936" t="n"/>
+      <c r="D13" s="936" t="n"/>
+      <c r="E13" s="937" t="n"/>
+      <c r="F13" s="938" t="n"/>
+      <c r="G13" s="938" t="n"/>
+      <c r="H13" s="938" t="n"/>
+      <c r="I13" s="938" t="n"/>
+      <c r="J13" s="938" t="n"/>
+      <c r="K13" s="938" t="n"/>
+      <c r="L13" s="939" t="inlineStr">
         <is>
           <t>要件
 定義</t>
         </is>
       </c>
-      <c r="M13" s="913" t="inlineStr">
+      <c r="M13" s="939" t="inlineStr">
         <is>
           <t>基本
 設計</t>
         </is>
       </c>
-      <c r="N13" s="913" t="inlineStr">
+      <c r="N13" s="939" t="inlineStr">
         <is>
           <t>詳細
 設計</t>
         </is>
       </c>
-      <c r="O13" s="913" t="inlineStr">
+      <c r="O13" s="939" t="inlineStr">
         <is>
           <t>実装</t>
         </is>
       </c>
-      <c r="P13" s="913" t="inlineStr">
+      <c r="P13" s="939" t="inlineStr">
         <is>
           <t>単体
 テスト</t>
         </is>
       </c>
-      <c r="Q13" s="913" t="inlineStr">
+      <c r="Q13" s="939" t="inlineStr">
         <is>
           <t>結合
 テスト</t>
         </is>
       </c>
-      <c r="R13" s="913" t="inlineStr">
+      <c r="R13" s="939" t="inlineStr">
         <is>
           <t>総合
 テスト</t>
         </is>
       </c>
-      <c r="S13" s="914" t="inlineStr">
+      <c r="S13" s="940" t="inlineStr">
         <is>
           <t>保守
 運用</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="41" r="14" s="782">
-      <c r="A14" s="889" t="n"/>
-      <c r="B14" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="14" s="888">
+      <c r="A14" s="891" t="n"/>
+      <c r="B14" s="941" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="916" t="inlineStr">
+      <c r="C14" s="942" t="inlineStr">
         <is>
           <t>2024/10</t>
         </is>
       </c>
-      <c r="D14" s="917" t="inlineStr">
+      <c r="D14" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E14" s="916" t="inlineStr">
+      <c r="E14" s="942" t="inlineStr">
         <is>
           <t>現在</t>
         </is>
       </c>
-      <c r="F14" s="918" t="inlineStr">
+      <c r="F14" s="944" t="inlineStr">
         <is>
           <t>■自治体連携DX推進支援プラットフォームの開発</t>
         </is>
       </c>
-      <c r="G14" s="919" t="inlineStr">
+      <c r="G14" s="945" t="inlineStr">
         <is>
           <t>リードエンジニア</t>
         </is>
       </c>
-      <c r="H14" s="920" t="inlineStr">
+      <c r="H14" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript, Python</t>
         </is>
       </c>
-      <c r="I14" s="920" t="inlineStr">
+      <c r="I14" s="946" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J14" s="920" t="inlineStr">
+      <c r="J14" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K14" s="921" t="inlineStr">
+      <c r="K14" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、React
 エディタ/IDE：Cursor、Orca
@@ -5884,34 +6648,54 @@
 コミュニケーション：Slack、Jira、Notion</t>
         </is>
       </c>
-      <c r="L14" s="922" t="n"/>
-      <c r="M14" s="922" t="n"/>
-      <c r="N14" s="922" t="n"/>
-      <c r="O14" s="923" t="inlineStr">
+      <c r="L14" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P14" s="923" t="inlineStr">
+      <c r="M14" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q14" s="923" t="inlineStr">
+      <c r="N14" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R14" s="922" t="n"/>
-      <c r="S14" s="924" t="n"/>
+      <c r="O14" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="P14" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q14" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="R14" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="S14" s="949" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
-    <row customHeight="1" ht="232" r="15" s="782">
-      <c r="A15" s="889" t="n"/>
-      <c r="B15" s="814" t="n"/>
-      <c r="C15" s="573" t="n"/>
-      <c r="D15" s="574" t="n"/>
-      <c r="E15" s="573" t="n"/>
-      <c r="F15" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="232" r="15" s="888">
+      <c r="A15" s="891" t="n"/>
+      <c r="B15" s="950" t="n"/>
+      <c r="C15" s="951" t="n"/>
+      <c r="D15" s="952" t="n"/>
+      <c r="E15" s="951" t="n"/>
+      <c r="F15" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 自治体連携DX推進支援プラットフォームの開発(2024年10月〜、随時更新）
@@ -5921,96 +6705,96 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G15" s="926" t="inlineStr">
+      <c r="G15" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、PdM、エンジニア、SRE、デザイナー、QA</t>
         </is>
       </c>
-      <c r="H15" s="574" t="n"/>
-      <c r="I15" s="574" t="n"/>
-      <c r="J15" s="574" t="n"/>
-      <c r="K15" s="577" t="n"/>
-      <c r="L15" s="927" t="n"/>
-      <c r="M15" s="927" t="n"/>
-      <c r="N15" s="927" t="n"/>
-      <c r="O15" s="928" t="n"/>
-      <c r="P15" s="928" t="n"/>
-      <c r="Q15" s="928" t="n"/>
-      <c r="R15" s="927" t="n"/>
-      <c r="S15" s="929" t="n"/>
+      <c r="H15" s="952" t="n"/>
+      <c r="I15" s="952" t="n"/>
+      <c r="J15" s="952" t="n"/>
+      <c r="K15" s="955" t="n"/>
+      <c r="L15" s="956" t="n"/>
+      <c r="M15" s="956" t="n"/>
+      <c r="N15" s="956" t="n"/>
+      <c r="O15" s="956" t="n"/>
+      <c r="P15" s="956" t="n"/>
+      <c r="Q15" s="956" t="n"/>
+      <c r="R15" s="956" t="n"/>
+      <c r="S15" s="957" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="16" s="782">
-      <c r="A16" s="889" t="n"/>
-      <c r="B16" s="579" t="n"/>
-      <c r="C16" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="16" s="888">
+      <c r="A16" s="891" t="n"/>
+      <c r="B16" s="958" t="n"/>
+      <c r="C16" s="954" t="inlineStr">
         <is>
           <t>随時更新</t>
         </is>
       </c>
-      <c r="D16" s="581" t="n"/>
-      <c r="E16" s="582" t="n"/>
-      <c r="F16" s="583" t="n"/>
-      <c r="G16" s="583" t="n"/>
-      <c r="H16" s="583" t="n"/>
-      <c r="I16" s="583" t="n"/>
-      <c r="J16" s="583" t="n"/>
-      <c r="K16" s="584" t="n"/>
-      <c r="L16" s="931" t="n"/>
-      <c r="M16" s="931" t="n"/>
-      <c r="N16" s="931" t="n"/>
-      <c r="O16" s="932" t="n"/>
-      <c r="P16" s="932" t="n"/>
-      <c r="Q16" s="932" t="n"/>
-      <c r="R16" s="931" t="n"/>
-      <c r="S16" s="933" t="n"/>
+      <c r="D16" s="959" t="n"/>
+      <c r="E16" s="960" t="n"/>
+      <c r="F16" s="961" t="n"/>
+      <c r="G16" s="961" t="n"/>
+      <c r="H16" s="961" t="n"/>
+      <c r="I16" s="961" t="n"/>
+      <c r="J16" s="961" t="n"/>
+      <c r="K16" s="962" t="n"/>
+      <c r="L16" s="963" t="n"/>
+      <c r="M16" s="963" t="n"/>
+      <c r="N16" s="963" t="n"/>
+      <c r="O16" s="963" t="n"/>
+      <c r="P16" s="963" t="n"/>
+      <c r="Q16" s="963" t="n"/>
+      <c r="R16" s="963" t="n"/>
+      <c r="S16" s="964" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="17" s="782">
-      <c r="A17" s="889" t="n"/>
-      <c r="B17" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="17" s="888">
+      <c r="A17" s="891" t="n"/>
+      <c r="B17" s="941" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="916" t="inlineStr">
+      <c r="C17" s="942" t="inlineStr">
         <is>
           <t>2024/04</t>
         </is>
       </c>
-      <c r="D17" s="917" t="inlineStr">
+      <c r="D17" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E17" s="916" t="inlineStr">
+      <c r="E17" s="942" t="inlineStr">
         <is>
           <t>2024/08</t>
         </is>
       </c>
-      <c r="F17" s="918" t="inlineStr">
+      <c r="F17" s="944" t="inlineStr">
         <is>
           <t>■電気自動車のEV充電ローミングプロジェクトの新規開発</t>
         </is>
       </c>
-      <c r="G17" s="919" t="inlineStr">
+      <c r="G17" s="945" t="inlineStr">
         <is>
           <t>リードエンジニア</t>
         </is>
       </c>
-      <c r="H17" s="920" t="inlineStr">
+      <c r="H17" s="946" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I17" s="920" t="inlineStr">
+      <c r="I17" s="946" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J17" s="920" t="inlineStr">
+      <c r="J17" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K17" s="921" t="inlineStr">
+      <c r="K17" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec
 エディタ/IDE：VSCode
@@ -6018,30 +6802,42 @@
 コミュニケーション：Slack、Google Meet</t>
         </is>
       </c>
-      <c r="L17" s="922" t="n"/>
-      <c r="M17" s="923" t="inlineStr">
+      <c r="L17" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N17" s="922" t="n"/>
-      <c r="O17" s="923" t="inlineStr">
+      <c r="M17" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P17" s="922" t="n"/>
-      <c r="Q17" s="922" t="n"/>
-      <c r="R17" s="922" t="n"/>
-      <c r="S17" s="924" t="n"/>
+      <c r="N17" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="O17" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="P17" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q17" s="965" t="n"/>
+      <c r="R17" s="965" t="n"/>
+      <c r="S17" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="161" r="18" s="782">
-      <c r="A18" s="889" t="n"/>
-      <c r="B18" s="814" t="n"/>
-      <c r="C18" s="573" t="n"/>
-      <c r="D18" s="574" t="n"/>
-      <c r="E18" s="573" t="n"/>
-      <c r="F18" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="161" r="18" s="888">
+      <c r="A18" s="891" t="n"/>
+      <c r="B18" s="950" t="n"/>
+      <c r="C18" s="951" t="n"/>
+      <c r="D18" s="952" t="n"/>
+      <c r="E18" s="951" t="n"/>
+      <c r="F18" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 電気自動車のEV充電ローミングプロジェクトの新規開発(2024年4月〜2024年8月：5ヶ月)
@@ -6051,96 +6847,96 @@
 リモート、ウォーターフォール開発</t>
         </is>
       </c>
-      <c r="G18" s="926" t="inlineStr">
+      <c r="G18" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H18" s="574" t="n"/>
-      <c r="I18" s="574" t="n"/>
-      <c r="J18" s="574" t="n"/>
-      <c r="K18" s="577" t="n"/>
-      <c r="L18" s="927" t="n"/>
-      <c r="M18" s="928" t="n"/>
-      <c r="N18" s="927" t="n"/>
-      <c r="O18" s="928" t="n"/>
-      <c r="P18" s="927" t="n"/>
-      <c r="Q18" s="927" t="n"/>
-      <c r="R18" s="927" t="n"/>
-      <c r="S18" s="929" t="n"/>
+      <c r="H18" s="952" t="n"/>
+      <c r="I18" s="952" t="n"/>
+      <c r="J18" s="952" t="n"/>
+      <c r="K18" s="955" t="n"/>
+      <c r="L18" s="956" t="n"/>
+      <c r="M18" s="956" t="n"/>
+      <c r="N18" s="956" t="n"/>
+      <c r="O18" s="956" t="n"/>
+      <c r="P18" s="956" t="n"/>
+      <c r="Q18" s="952" t="n"/>
+      <c r="R18" s="952" t="n"/>
+      <c r="S18" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="19" s="782">
-      <c r="A19" s="889" t="n"/>
-      <c r="B19" s="579" t="n"/>
-      <c r="C19" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="19" s="888">
+      <c r="A19" s="891" t="n"/>
+      <c r="B19" s="958" t="n"/>
+      <c r="C19" s="954" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D19" s="581" t="n"/>
-      <c r="E19" s="582" t="n"/>
-      <c r="F19" s="583" t="n"/>
-      <c r="G19" s="583" t="n"/>
-      <c r="H19" s="583" t="n"/>
-      <c r="I19" s="583" t="n"/>
-      <c r="J19" s="583" t="n"/>
-      <c r="K19" s="584" t="n"/>
-      <c r="L19" s="931" t="n"/>
-      <c r="M19" s="932" t="n"/>
-      <c r="N19" s="931" t="n"/>
-      <c r="O19" s="932" t="n"/>
-      <c r="P19" s="931" t="n"/>
-      <c r="Q19" s="931" t="n"/>
-      <c r="R19" s="931" t="n"/>
-      <c r="S19" s="933" t="n"/>
+      <c r="D19" s="959" t="n"/>
+      <c r="E19" s="960" t="n"/>
+      <c r="F19" s="961" t="n"/>
+      <c r="G19" s="961" t="n"/>
+      <c r="H19" s="961" t="n"/>
+      <c r="I19" s="961" t="n"/>
+      <c r="J19" s="961" t="n"/>
+      <c r="K19" s="962" t="n"/>
+      <c r="L19" s="963" t="n"/>
+      <c r="M19" s="963" t="n"/>
+      <c r="N19" s="963" t="n"/>
+      <c r="O19" s="963" t="n"/>
+      <c r="P19" s="963" t="n"/>
+      <c r="Q19" s="961" t="n"/>
+      <c r="R19" s="961" t="n"/>
+      <c r="S19" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="25" r="20" s="782">
-      <c r="A20" s="889" t="n"/>
-      <c r="B20" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="25" r="20" s="888">
+      <c r="A20" s="891" t="n"/>
+      <c r="B20" s="941" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="916" t="inlineStr">
+      <c r="C20" s="942" t="inlineStr">
         <is>
           <t>2023/07</t>
         </is>
       </c>
-      <c r="D20" s="917" t="inlineStr">
+      <c r="D20" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E20" s="916" t="inlineStr">
+      <c r="E20" s="942" t="inlineStr">
         <is>
           <t>2024/03</t>
         </is>
       </c>
-      <c r="F20" s="918" t="inlineStr">
+      <c r="F20" s="944" t="inlineStr">
         <is>
           <t>■不動産テックのバーティカルSaaSプロダクト開発</t>
         </is>
       </c>
-      <c r="G20" s="919" t="inlineStr">
+      <c r="G20" s="945" t="inlineStr">
         <is>
           <t>webエンジニア</t>
         </is>
       </c>
-      <c r="H20" s="920" t="inlineStr">
+      <c r="H20" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、 TypeScript</t>
         </is>
       </c>
-      <c r="I20" s="920" t="inlineStr">
+      <c r="I20" s="946" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J20" s="920" t="inlineStr">
+      <c r="J20" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K20" s="921" t="inlineStr">
+      <c r="K20" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、 React、 Next.js
 エディタ/IDE：VSCode
@@ -6148,34 +6944,34 @@
 コミュニケーション：Slack、Google Meet</t>
         </is>
       </c>
-      <c r="L20" s="922" t="n"/>
-      <c r="M20" s="922" t="n"/>
-      <c r="N20" s="922" t="n"/>
-      <c r="O20" s="923" t="inlineStr">
+      <c r="L20" s="965" t="n"/>
+      <c r="M20" s="965" t="n"/>
+      <c r="N20" s="965" t="n"/>
+      <c r="O20" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P20" s="923" t="inlineStr">
+      <c r="P20" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q20" s="923" t="inlineStr">
+      <c r="Q20" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R20" s="922" t="n"/>
-      <c r="S20" s="924" t="n"/>
+      <c r="R20" s="965" t="n"/>
+      <c r="S20" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="168" r="21" s="782">
-      <c r="A21" s="889" t="n"/>
-      <c r="B21" s="814" t="n"/>
-      <c r="C21" s="573" t="n"/>
-      <c r="D21" s="574" t="n"/>
-      <c r="E21" s="573" t="n"/>
-      <c r="F21" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="168" r="21" s="888">
+      <c r="A21" s="891" t="n"/>
+      <c r="B21" s="950" t="n"/>
+      <c r="C21" s="951" t="n"/>
+      <c r="D21" s="952" t="n"/>
+      <c r="E21" s="951" t="n"/>
+      <c r="F21" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 不動産テックのバーティカルSaaSプロダクト開発(2023年7月〜2024年3月：9ヶ月)
@@ -6185,96 +6981,96 @@
 リモート及び出社、アジャイル開発</t>
         </is>
       </c>
-      <c r="G21" s="926" t="inlineStr">
+      <c r="G21" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H21" s="574" t="n"/>
-      <c r="I21" s="574" t="n"/>
-      <c r="J21" s="574" t="n"/>
-      <c r="K21" s="577" t="n"/>
-      <c r="L21" s="927" t="n"/>
-      <c r="M21" s="927" t="n"/>
-      <c r="N21" s="927" t="n"/>
-      <c r="O21" s="928" t="n"/>
-      <c r="P21" s="928" t="n"/>
-      <c r="Q21" s="928" t="n"/>
-      <c r="R21" s="927" t="n"/>
-      <c r="S21" s="929" t="n"/>
+      <c r="H21" s="952" t="n"/>
+      <c r="I21" s="952" t="n"/>
+      <c r="J21" s="952" t="n"/>
+      <c r="K21" s="955" t="n"/>
+      <c r="L21" s="952" t="n"/>
+      <c r="M21" s="952" t="n"/>
+      <c r="N21" s="952" t="n"/>
+      <c r="O21" s="956" t="n"/>
+      <c r="P21" s="956" t="n"/>
+      <c r="Q21" s="956" t="n"/>
+      <c r="R21" s="952" t="n"/>
+      <c r="S21" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="22" s="782">
-      <c r="A22" s="889" t="n"/>
-      <c r="B22" s="579" t="n"/>
-      <c r="C22" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="22" s="888">
+      <c r="A22" s="891" t="n"/>
+      <c r="B22" s="958" t="n"/>
+      <c r="C22" s="954" t="inlineStr">
         <is>
           <t>9ヶ月</t>
         </is>
       </c>
-      <c r="D22" s="581" t="n"/>
-      <c r="E22" s="582" t="n"/>
-      <c r="F22" s="583" t="n"/>
-      <c r="G22" s="583" t="n"/>
-      <c r="H22" s="583" t="n"/>
-      <c r="I22" s="583" t="n"/>
-      <c r="J22" s="583" t="n"/>
-      <c r="K22" s="584" t="n"/>
-      <c r="L22" s="931" t="n"/>
-      <c r="M22" s="931" t="n"/>
-      <c r="N22" s="931" t="n"/>
-      <c r="O22" s="932" t="n"/>
-      <c r="P22" s="932" t="n"/>
-      <c r="Q22" s="932" t="n"/>
-      <c r="R22" s="931" t="n"/>
-      <c r="S22" s="933" t="n"/>
+      <c r="D22" s="959" t="n"/>
+      <c r="E22" s="960" t="n"/>
+      <c r="F22" s="961" t="n"/>
+      <c r="G22" s="961" t="n"/>
+      <c r="H22" s="961" t="n"/>
+      <c r="I22" s="961" t="n"/>
+      <c r="J22" s="961" t="n"/>
+      <c r="K22" s="962" t="n"/>
+      <c r="L22" s="961" t="n"/>
+      <c r="M22" s="961" t="n"/>
+      <c r="N22" s="961" t="n"/>
+      <c r="O22" s="963" t="n"/>
+      <c r="P22" s="963" t="n"/>
+      <c r="Q22" s="963" t="n"/>
+      <c r="R22" s="961" t="n"/>
+      <c r="S22" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="23" s="782">
-      <c r="A23" s="889" t="n"/>
-      <c r="B23" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="23" s="888">
+      <c r="A23" s="891" t="n"/>
+      <c r="B23" s="941" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="916" t="inlineStr">
+      <c r="C23" s="942" t="inlineStr">
         <is>
           <t>2022/12</t>
         </is>
       </c>
-      <c r="D23" s="917" t="inlineStr">
+      <c r="D23" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E23" s="916" t="inlineStr">
+      <c r="E23" s="942" t="inlineStr">
         <is>
           <t>2023/06</t>
         </is>
       </c>
-      <c r="F23" s="918" t="inlineStr">
+      <c r="F23" s="944" t="inlineStr">
         <is>
           <t>■ブロックチェーンを活用したクラウドファンディングサービスのサーバーサイド開発</t>
         </is>
       </c>
-      <c r="G23" s="919" t="inlineStr">
+      <c r="G23" s="945" t="inlineStr">
         <is>
           <t>webエンジニア</t>
         </is>
       </c>
-      <c r="H23" s="920" t="inlineStr">
+      <c r="H23" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript、Solidity</t>
         </is>
       </c>
-      <c r="I23" s="920" t="inlineStr">
+      <c r="I23" s="946" t="inlineStr">
         <is>
           <t>MySQL、Firestore</t>
         </is>
       </c>
-      <c r="J23" s="920" t="inlineStr">
+      <c r="J23" s="946" t="inlineStr">
         <is>
           <t>GCP</t>
         </is>
       </c>
-      <c r="K23" s="921" t="inlineStr">
+      <c r="K23" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、React、Next.js、Jest
 エディタ/IDE：VSCode
@@ -6282,34 +7078,34 @@
 コミュニケーション：Slack、Google Meet、Zoom</t>
         </is>
       </c>
-      <c r="L23" s="922" t="n"/>
-      <c r="M23" s="922" t="n"/>
-      <c r="N23" s="922" t="n"/>
-      <c r="O23" s="923" t="inlineStr">
+      <c r="L23" s="965" t="n"/>
+      <c r="M23" s="965" t="n"/>
+      <c r="N23" s="965" t="n"/>
+      <c r="O23" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P23" s="923" t="inlineStr">
+      <c r="P23" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q23" s="923" t="inlineStr">
+      <c r="Q23" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R23" s="922" t="n"/>
-      <c r="S23" s="924" t="n"/>
+      <c r="R23" s="965" t="n"/>
+      <c r="S23" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="184" r="24" s="782">
-      <c r="A24" s="889" t="n"/>
-      <c r="B24" s="814" t="n"/>
-      <c r="C24" s="573" t="n"/>
-      <c r="D24" s="574" t="n"/>
-      <c r="E24" s="573" t="n"/>
-      <c r="F24" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="184" r="24" s="888">
+      <c r="A24" s="891" t="n"/>
+      <c r="B24" s="950" t="n"/>
+      <c r="C24" s="951" t="n"/>
+      <c r="D24" s="952" t="n"/>
+      <c r="E24" s="951" t="n"/>
+      <c r="F24" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 ブロックチェーンを活用したクラウドファンディングサービスのサーバーサイド開発(2022年12月〜2023年6月:7ヶ月)
@@ -6319,96 +7115,96 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G24" s="926" t="inlineStr">
+      <c r="G24" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H24" s="574" t="n"/>
-      <c r="I24" s="574" t="n"/>
-      <c r="J24" s="574" t="n"/>
-      <c r="K24" s="577" t="n"/>
-      <c r="L24" s="927" t="n"/>
-      <c r="M24" s="927" t="n"/>
-      <c r="N24" s="927" t="n"/>
-      <c r="O24" s="928" t="n"/>
-      <c r="P24" s="928" t="n"/>
-      <c r="Q24" s="928" t="n"/>
-      <c r="R24" s="927" t="n"/>
-      <c r="S24" s="929" t="n"/>
+      <c r="H24" s="952" t="n"/>
+      <c r="I24" s="952" t="n"/>
+      <c r="J24" s="952" t="n"/>
+      <c r="K24" s="955" t="n"/>
+      <c r="L24" s="952" t="n"/>
+      <c r="M24" s="952" t="n"/>
+      <c r="N24" s="952" t="n"/>
+      <c r="O24" s="956" t="n"/>
+      <c r="P24" s="956" t="n"/>
+      <c r="Q24" s="956" t="n"/>
+      <c r="R24" s="952" t="n"/>
+      <c r="S24" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="25" s="782">
-      <c r="A25" s="889" t="n"/>
-      <c r="B25" s="579" t="n"/>
-      <c r="C25" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="25" s="888">
+      <c r="A25" s="891" t="n"/>
+      <c r="B25" s="958" t="n"/>
+      <c r="C25" s="954" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
       </c>
-      <c r="D25" s="581" t="n"/>
-      <c r="E25" s="582" t="n"/>
-      <c r="F25" s="583" t="n"/>
-      <c r="G25" s="583" t="n"/>
-      <c r="H25" s="583" t="n"/>
-      <c r="I25" s="583" t="n"/>
-      <c r="J25" s="583" t="n"/>
-      <c r="K25" s="584" t="n"/>
-      <c r="L25" s="931" t="n"/>
-      <c r="M25" s="931" t="n"/>
-      <c r="N25" s="931" t="n"/>
-      <c r="O25" s="932" t="n"/>
-      <c r="P25" s="932" t="n"/>
-      <c r="Q25" s="932" t="n"/>
-      <c r="R25" s="931" t="n"/>
-      <c r="S25" s="933" t="n"/>
+      <c r="D25" s="959" t="n"/>
+      <c r="E25" s="960" t="n"/>
+      <c r="F25" s="961" t="n"/>
+      <c r="G25" s="961" t="n"/>
+      <c r="H25" s="961" t="n"/>
+      <c r="I25" s="961" t="n"/>
+      <c r="J25" s="961" t="n"/>
+      <c r="K25" s="962" t="n"/>
+      <c r="L25" s="961" t="n"/>
+      <c r="M25" s="961" t="n"/>
+      <c r="N25" s="961" t="n"/>
+      <c r="O25" s="963" t="n"/>
+      <c r="P25" s="963" t="n"/>
+      <c r="Q25" s="963" t="n"/>
+      <c r="R25" s="961" t="n"/>
+      <c r="S25" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="26" s="782">
-      <c r="A26" s="889" t="n"/>
-      <c r="B26" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="26" s="888">
+      <c r="A26" s="891" t="n"/>
+      <c r="B26" s="941" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="916" t="inlineStr">
+      <c r="C26" s="942" t="inlineStr">
         <is>
           <t>2021/04</t>
         </is>
       </c>
-      <c r="D26" s="917" t="inlineStr">
+      <c r="D26" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E26" s="916" t="inlineStr">
+      <c r="E26" s="942" t="inlineStr">
         <is>
           <t>2022/10</t>
         </is>
       </c>
-      <c r="F26" s="918" t="inlineStr">
+      <c r="F26" s="944" t="inlineStr">
         <is>
           <t>■大手携帯ショップの販売端末価格デジタルサイネージアプリケーション開発</t>
         </is>
       </c>
-      <c r="G26" s="919" t="inlineStr">
+      <c r="G26" s="945" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H26" s="920" t="inlineStr">
+      <c r="H26" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css、 kotlin</t>
         </is>
       </c>
-      <c r="I26" s="920" t="inlineStr">
+      <c r="I26" s="946" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J26" s="920" t="inlineStr">
+      <c r="J26" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K26" s="921" t="inlineStr">
+      <c r="K26" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、Bootstrap、Vue.js、Nuxt.js
 アプリ：PWA
@@ -6417,34 +7213,54 @@
 コミュニケーション：Slack、Teams、Zoom、Miro、Jira</t>
         </is>
       </c>
-      <c r="L26" s="922" t="n"/>
-      <c r="M26" s="922" t="n"/>
-      <c r="N26" s="922" t="n"/>
-      <c r="O26" s="923" t="inlineStr">
+      <c r="L26" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P26" s="923" t="inlineStr">
+      <c r="M26" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q26" s="923" t="inlineStr">
+      <c r="N26" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R26" s="922" t="n"/>
-      <c r="S26" s="924" t="n"/>
+      <c r="O26" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="P26" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q26" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="R26" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="S26" s="949" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
-    <row customHeight="1" ht="248" r="27" s="782">
-      <c r="A27" s="889" t="n"/>
-      <c r="B27" s="814" t="n"/>
-      <c r="C27" s="573" t="n"/>
-      <c r="D27" s="574" t="n"/>
-      <c r="E27" s="573" t="n"/>
-      <c r="F27" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="248" r="27" s="888">
+      <c r="A27" s="891" t="n"/>
+      <c r="B27" s="950" t="n"/>
+      <c r="C27" s="951" t="n"/>
+      <c r="D27" s="952" t="n"/>
+      <c r="E27" s="951" t="n"/>
+      <c r="F27" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 大手携帯ショップの販売端末価格デジタルサイネージアプリケーション開発(2021年4月〜2022年10月：19ヶ月)
@@ -6454,96 +7270,96 @@
 フルリモート、スクラム（2週間スプリント）、ペアプロ/モブプロ</t>
         </is>
       </c>
-      <c r="G27" s="926" t="inlineStr">
+      <c r="G27" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PO、SM、デザイナー、エンジニア、QA</t>
         </is>
       </c>
-      <c r="H27" s="574" t="n"/>
-      <c r="I27" s="574" t="n"/>
-      <c r="J27" s="574" t="n"/>
-      <c r="K27" s="577" t="n"/>
-      <c r="L27" s="927" t="n"/>
-      <c r="M27" s="927" t="n"/>
-      <c r="N27" s="927" t="n"/>
-      <c r="O27" s="928" t="n"/>
-      <c r="P27" s="928" t="n"/>
-      <c r="Q27" s="928" t="n"/>
-      <c r="R27" s="927" t="n"/>
-      <c r="S27" s="929" t="n"/>
+      <c r="H27" s="952" t="n"/>
+      <c r="I27" s="952" t="n"/>
+      <c r="J27" s="952" t="n"/>
+      <c r="K27" s="955" t="n"/>
+      <c r="L27" s="956" t="n"/>
+      <c r="M27" s="956" t="n"/>
+      <c r="N27" s="956" t="n"/>
+      <c r="O27" s="956" t="n"/>
+      <c r="P27" s="956" t="n"/>
+      <c r="Q27" s="956" t="n"/>
+      <c r="R27" s="956" t="n"/>
+      <c r="S27" s="957" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="28" s="782">
-      <c r="A28" s="889" t="n"/>
-      <c r="B28" s="579" t="n"/>
-      <c r="C28" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="28" s="888">
+      <c r="A28" s="891" t="n"/>
+      <c r="B28" s="958" t="n"/>
+      <c r="C28" s="954" t="inlineStr">
         <is>
           <t>19ヶ月</t>
         </is>
       </c>
-      <c r="D28" s="581" t="n"/>
-      <c r="E28" s="582" t="n"/>
-      <c r="F28" s="583" t="n"/>
-      <c r="G28" s="583" t="n"/>
-      <c r="H28" s="583" t="n"/>
-      <c r="I28" s="583" t="n"/>
-      <c r="J28" s="583" t="n"/>
-      <c r="K28" s="584" t="n"/>
-      <c r="L28" s="931" t="n"/>
-      <c r="M28" s="931" t="n"/>
-      <c r="N28" s="931" t="n"/>
-      <c r="O28" s="932" t="n"/>
-      <c r="P28" s="932" t="n"/>
-      <c r="Q28" s="932" t="n"/>
-      <c r="R28" s="931" t="n"/>
-      <c r="S28" s="933" t="n"/>
+      <c r="D28" s="959" t="n"/>
+      <c r="E28" s="960" t="n"/>
+      <c r="F28" s="961" t="n"/>
+      <c r="G28" s="961" t="n"/>
+      <c r="H28" s="961" t="n"/>
+      <c r="I28" s="961" t="n"/>
+      <c r="J28" s="961" t="n"/>
+      <c r="K28" s="962" t="n"/>
+      <c r="L28" s="963" t="n"/>
+      <c r="M28" s="963" t="n"/>
+      <c r="N28" s="963" t="n"/>
+      <c r="O28" s="963" t="n"/>
+      <c r="P28" s="963" t="n"/>
+      <c r="Q28" s="963" t="n"/>
+      <c r="R28" s="963" t="n"/>
+      <c r="S28" s="964" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="29" s="782">
-      <c r="A29" s="889" t="n"/>
-      <c r="B29" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="29" s="888">
+      <c r="A29" s="891" t="n"/>
+      <c r="B29" s="941" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="916" t="inlineStr">
+      <c r="C29" s="942" t="inlineStr">
         <is>
           <t>2020/08</t>
         </is>
       </c>
-      <c r="D29" s="917" t="inlineStr">
+      <c r="D29" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E29" s="916" t="inlineStr">
+      <c r="E29" s="942" t="inlineStr">
         <is>
           <t>2021/01</t>
         </is>
       </c>
-      <c r="F29" s="918" t="inlineStr">
+      <c r="F29" s="944" t="inlineStr">
         <is>
           <t>■医療従事者向けプラットフォーム事業のマイクロサービス開発</t>
         </is>
       </c>
-      <c r="G29" s="919" t="inlineStr">
+      <c r="G29" s="945" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H29" s="920" t="inlineStr">
+      <c r="H29" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、css、TypeScript</t>
         </is>
       </c>
-      <c r="I29" s="920" t="inlineStr">
+      <c r="I29" s="946" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J29" s="920" t="inlineStr">
+      <c r="J29" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K29" s="921" t="inlineStr">
+      <c r="K29" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、React、BULMA
 エディタ/IDE：VSCode
@@ -6551,42 +7367,42 @@
 コミュニケーション：Slack、Zoom</t>
         </is>
       </c>
-      <c r="L29" s="922" t="n"/>
-      <c r="M29" s="923" t="inlineStr">
+      <c r="L29" s="965" t="n"/>
+      <c r="M29" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N29" s="923" t="inlineStr">
+      <c r="N29" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O29" s="923" t="inlineStr">
+      <c r="O29" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P29" s="923" t="inlineStr">
+      <c r="P29" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q29" s="923" t="inlineStr">
+      <c r="Q29" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R29" s="922" t="n"/>
-      <c r="S29" s="924" t="n"/>
+      <c r="R29" s="965" t="n"/>
+      <c r="S29" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="152" r="30" s="782">
-      <c r="A30" s="889" t="n"/>
-      <c r="B30" s="814" t="n"/>
-      <c r="C30" s="573" t="n"/>
-      <c r="D30" s="574" t="n"/>
-      <c r="E30" s="573" t="n"/>
-      <c r="F30" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="152" r="30" s="888">
+      <c r="A30" s="891" t="n"/>
+      <c r="B30" s="950" t="n"/>
+      <c r="C30" s="951" t="n"/>
+      <c r="D30" s="952" t="n"/>
+      <c r="E30" s="951" t="n"/>
+      <c r="F30" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 医療従事者向けプラットフォーム事業のマイクロサービス開発(2020年8月〜2021年1月：６ヶ月)
@@ -6596,96 +7412,96 @@
 フルリモート、issue駆動開発、スクラム（1週間スプリント）</t>
         </is>
       </c>
-      <c r="G30" s="926" t="inlineStr">
+      <c r="G30" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、デザイナー、エンジニア、QA</t>
         </is>
       </c>
-      <c r="H30" s="574" t="n"/>
-      <c r="I30" s="574" t="n"/>
-      <c r="J30" s="574" t="n"/>
-      <c r="K30" s="577" t="n"/>
-      <c r="L30" s="927" t="n"/>
-      <c r="M30" s="928" t="n"/>
-      <c r="N30" s="928" t="n"/>
-      <c r="O30" s="928" t="n"/>
-      <c r="P30" s="928" t="n"/>
-      <c r="Q30" s="928" t="n"/>
-      <c r="R30" s="927" t="n"/>
-      <c r="S30" s="929" t="n"/>
+      <c r="H30" s="952" t="n"/>
+      <c r="I30" s="952" t="n"/>
+      <c r="J30" s="952" t="n"/>
+      <c r="K30" s="955" t="n"/>
+      <c r="L30" s="952" t="n"/>
+      <c r="M30" s="956" t="n"/>
+      <c r="N30" s="956" t="n"/>
+      <c r="O30" s="956" t="n"/>
+      <c r="P30" s="956" t="n"/>
+      <c r="Q30" s="956" t="n"/>
+      <c r="R30" s="952" t="n"/>
+      <c r="S30" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="31" s="782">
-      <c r="A31" s="889" t="n"/>
-      <c r="B31" s="579" t="n"/>
-      <c r="C31" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="31" s="888">
+      <c r="A31" s="891" t="n"/>
+      <c r="B31" s="958" t="n"/>
+      <c r="C31" s="954" t="inlineStr">
         <is>
           <t>６ヶ月</t>
         </is>
       </c>
-      <c r="D31" s="581" t="n"/>
-      <c r="E31" s="582" t="n"/>
-      <c r="F31" s="583" t="n"/>
-      <c r="G31" s="583" t="n"/>
-      <c r="H31" s="583" t="n"/>
-      <c r="I31" s="583" t="n"/>
-      <c r="J31" s="583" t="n"/>
-      <c r="K31" s="584" t="n"/>
-      <c r="L31" s="931" t="n"/>
-      <c r="M31" s="932" t="n"/>
-      <c r="N31" s="932" t="n"/>
-      <c r="O31" s="932" t="n"/>
-      <c r="P31" s="932" t="n"/>
-      <c r="Q31" s="932" t="n"/>
-      <c r="R31" s="931" t="n"/>
-      <c r="S31" s="933" t="n"/>
+      <c r="D31" s="959" t="n"/>
+      <c r="E31" s="960" t="n"/>
+      <c r="F31" s="961" t="n"/>
+      <c r="G31" s="961" t="n"/>
+      <c r="H31" s="961" t="n"/>
+      <c r="I31" s="961" t="n"/>
+      <c r="J31" s="961" t="n"/>
+      <c r="K31" s="962" t="n"/>
+      <c r="L31" s="961" t="n"/>
+      <c r="M31" s="963" t="n"/>
+      <c r="N31" s="963" t="n"/>
+      <c r="O31" s="963" t="n"/>
+      <c r="P31" s="963" t="n"/>
+      <c r="Q31" s="963" t="n"/>
+      <c r="R31" s="961" t="n"/>
+      <c r="S31" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="32" s="782">
-      <c r="A32" s="889" t="n"/>
-      <c r="B32" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="32" s="888">
+      <c r="A32" s="891" t="n"/>
+      <c r="B32" s="941" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="916" t="inlineStr">
+      <c r="C32" s="942" t="inlineStr">
         <is>
           <t>2018/05</t>
         </is>
       </c>
-      <c r="D32" s="917" t="inlineStr">
+      <c r="D32" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E32" s="916" t="inlineStr">
+      <c r="E32" s="942" t="inlineStr">
         <is>
           <t>2020/06</t>
         </is>
       </c>
-      <c r="F32" s="918" t="inlineStr">
+      <c r="F32" s="944" t="inlineStr">
         <is>
           <t>■自動車会社向けIoTシステムの新規事業開発</t>
         </is>
       </c>
-      <c r="G32" s="919" t="inlineStr">
+      <c r="G32" s="945" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H32" s="920" t="inlineStr">
+      <c r="H32" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css、Python</t>
         </is>
       </c>
-      <c r="I32" s="920" t="inlineStr">
+      <c r="I32" s="946" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J32" s="920" t="inlineStr">
+      <c r="J32" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K32" s="921" t="inlineStr">
+      <c r="K32" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、Bootstrap
 エディタ/IDE：VSCode
@@ -6693,50 +7509,54 @@
 コミュニケーション：Slack、Zoom、Miro</t>
         </is>
       </c>
-      <c r="L32" s="923" t="inlineStr">
+      <c r="L32" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M32" s="923" t="inlineStr">
+      <c r="M32" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N32" s="923" t="inlineStr">
+      <c r="N32" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O32" s="923" t="inlineStr">
+      <c r="O32" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P32" s="923" t="inlineStr">
+      <c r="P32" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q32" s="923" t="inlineStr">
+      <c r="Q32" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R32" s="922" t="n"/>
-      <c r="S32" s="934" t="inlineStr">
+      <c r="R32" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
+      <c r="S32" s="949" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
-    <row customHeight="1" ht="200" r="33" s="782">
-      <c r="A33" s="889" t="n"/>
-      <c r="B33" s="814" t="n"/>
-      <c r="C33" s="573" t="n"/>
-      <c r="D33" s="574" t="n"/>
-      <c r="E33" s="573" t="n"/>
-      <c r="F33" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="200" r="33" s="888">
+      <c r="A33" s="891" t="n"/>
+      <c r="B33" s="950" t="n"/>
+      <c r="C33" s="951" t="n"/>
+      <c r="D33" s="952" t="n"/>
+      <c r="E33" s="951" t="n"/>
+      <c r="F33" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 自動車会社向けIoTシステムの新規事業開発(2018年5月〜2020年6月：26ヶ月)
@@ -6746,130 +7566,130 @@
 スクラム（1週間スプリント）、ペアプロ/モブプロ</t>
         </is>
       </c>
-      <c r="G33" s="926" t="inlineStr">
+      <c r="G33" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PO、SM、エンジニア</t>
         </is>
       </c>
-      <c r="H33" s="574" t="n"/>
-      <c r="I33" s="574" t="n"/>
-      <c r="J33" s="574" t="n"/>
-      <c r="K33" s="577" t="n"/>
-      <c r="L33" s="928" t="n"/>
-      <c r="M33" s="928" t="n"/>
-      <c r="N33" s="928" t="n"/>
-      <c r="O33" s="928" t="n"/>
-      <c r="P33" s="928" t="n"/>
-      <c r="Q33" s="928" t="n"/>
-      <c r="R33" s="927" t="n"/>
-      <c r="S33" s="935" t="n"/>
+      <c r="H33" s="952" t="n"/>
+      <c r="I33" s="952" t="n"/>
+      <c r="J33" s="952" t="n"/>
+      <c r="K33" s="955" t="n"/>
+      <c r="L33" s="956" t="n"/>
+      <c r="M33" s="956" t="n"/>
+      <c r="N33" s="956" t="n"/>
+      <c r="O33" s="956" t="n"/>
+      <c r="P33" s="956" t="n"/>
+      <c r="Q33" s="956" t="n"/>
+      <c r="R33" s="956" t="n"/>
+      <c r="S33" s="957" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="34" s="782">
-      <c r="A34" s="889" t="n"/>
-      <c r="B34" s="579" t="n"/>
-      <c r="C34" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="34" s="888">
+      <c r="A34" s="891" t="n"/>
+      <c r="B34" s="958" t="n"/>
+      <c r="C34" s="954" t="inlineStr">
         <is>
           <t>26ヶ月</t>
         </is>
       </c>
-      <c r="D34" s="581" t="n"/>
-      <c r="E34" s="582" t="n"/>
-      <c r="F34" s="583" t="n"/>
-      <c r="G34" s="583" t="n"/>
-      <c r="H34" s="583" t="n"/>
-      <c r="I34" s="583" t="n"/>
-      <c r="J34" s="583" t="n"/>
-      <c r="K34" s="584" t="n"/>
-      <c r="L34" s="932" t="n"/>
-      <c r="M34" s="932" t="n"/>
-      <c r="N34" s="932" t="n"/>
-      <c r="O34" s="932" t="n"/>
-      <c r="P34" s="932" t="n"/>
-      <c r="Q34" s="932" t="n"/>
-      <c r="R34" s="931" t="n"/>
-      <c r="S34" s="936" t="n"/>
+      <c r="D34" s="959" t="n"/>
+      <c r="E34" s="960" t="n"/>
+      <c r="F34" s="961" t="n"/>
+      <c r="G34" s="961" t="n"/>
+      <c r="H34" s="961" t="n"/>
+      <c r="I34" s="961" t="n"/>
+      <c r="J34" s="961" t="n"/>
+      <c r="K34" s="962" t="n"/>
+      <c r="L34" s="963" t="n"/>
+      <c r="M34" s="963" t="n"/>
+      <c r="N34" s="963" t="n"/>
+      <c r="O34" s="963" t="n"/>
+      <c r="P34" s="963" t="n"/>
+      <c r="Q34" s="963" t="n"/>
+      <c r="R34" s="963" t="n"/>
+      <c r="S34" s="964" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="35" s="782">
-      <c r="A35" s="889" t="n"/>
-      <c r="B35" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="35" s="888">
+      <c r="A35" s="891" t="n"/>
+      <c r="B35" s="941" t="n">
         <v>8</v>
       </c>
-      <c r="C35" s="916" t="inlineStr">
+      <c r="C35" s="942" t="inlineStr">
         <is>
           <t>2017/10</t>
         </is>
       </c>
-      <c r="D35" s="917" t="inlineStr">
+      <c r="D35" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E35" s="916" t="inlineStr">
+      <c r="E35" s="942" t="inlineStr">
         <is>
           <t>2018/04</t>
         </is>
       </c>
-      <c r="F35" s="918" t="inlineStr">
+      <c r="F35" s="944" t="inlineStr">
         <is>
           <t>■航空会社向けECサイト開発</t>
         </is>
       </c>
-      <c r="G35" s="919" t="inlineStr">
+      <c r="G35" s="945" t="inlineStr">
         <is>
           <t>システムエンジニア</t>
         </is>
       </c>
-      <c r="H35" s="920" t="inlineStr">
+      <c r="H35" s="946" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I35" s="920" t="inlineStr">
+      <c r="I35" s="946" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J35" s="920" t="inlineStr"/>
-      <c r="K35" s="921" t="inlineStr">
+      <c r="J35" s="946" t="inlineStr"/>
+      <c r="K35" s="947" t="inlineStr">
         <is>
           <t>エディタ/IDE：Eclipse
 その他：Slack、Redmine、svn
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L35" s="922" t="n"/>
-      <c r="M35" s="922" t="n"/>
-      <c r="N35" s="923" t="inlineStr">
+      <c r="L35" s="965" t="n"/>
+      <c r="M35" s="965" t="n"/>
+      <c r="N35" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O35" s="923" t="inlineStr">
+      <c r="O35" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P35" s="923" t="inlineStr">
+      <c r="P35" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q35" s="923" t="inlineStr">
+      <c r="Q35" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R35" s="922" t="n"/>
-      <c r="S35" s="924" t="n"/>
+      <c r="R35" s="965" t="n"/>
+      <c r="S35" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="113" r="36" s="782">
-      <c r="A36" s="889" t="n"/>
-      <c r="B36" s="814" t="n"/>
-      <c r="C36" s="573" t="n"/>
-      <c r="D36" s="574" t="n"/>
-      <c r="E36" s="573" t="n"/>
-      <c r="F36" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="113" r="36" s="888">
+      <c r="A36" s="891" t="n"/>
+      <c r="B36" s="950" t="n"/>
+      <c r="C36" s="951" t="n"/>
+      <c r="D36" s="952" t="n"/>
+      <c r="E36" s="951" t="n"/>
+      <c r="F36" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 航空会社向けECサイト開発(2017年10月〜2018年4月：7ヶ月)
@@ -6879,130 +7699,130 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G36" s="926" t="inlineStr">
+      <c r="G36" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア、テスター</t>
         </is>
       </c>
-      <c r="H36" s="574" t="n"/>
-      <c r="I36" s="574" t="n"/>
-      <c r="J36" s="574" t="n"/>
-      <c r="K36" s="577" t="n"/>
-      <c r="L36" s="927" t="n"/>
-      <c r="M36" s="927" t="n"/>
-      <c r="N36" s="928" t="n"/>
-      <c r="O36" s="928" t="n"/>
-      <c r="P36" s="928" t="n"/>
-      <c r="Q36" s="928" t="n"/>
-      <c r="R36" s="927" t="n"/>
-      <c r="S36" s="929" t="n"/>
+      <c r="H36" s="952" t="n"/>
+      <c r="I36" s="952" t="n"/>
+      <c r="J36" s="952" t="n"/>
+      <c r="K36" s="955" t="n"/>
+      <c r="L36" s="952" t="n"/>
+      <c r="M36" s="952" t="n"/>
+      <c r="N36" s="956" t="n"/>
+      <c r="O36" s="956" t="n"/>
+      <c r="P36" s="956" t="n"/>
+      <c r="Q36" s="956" t="n"/>
+      <c r="R36" s="952" t="n"/>
+      <c r="S36" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="37" s="782">
-      <c r="A37" s="889" t="n"/>
-      <c r="B37" s="579" t="n"/>
-      <c r="C37" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="37" s="888">
+      <c r="A37" s="891" t="n"/>
+      <c r="B37" s="958" t="n"/>
+      <c r="C37" s="954" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
       </c>
-      <c r="D37" s="581" t="n"/>
-      <c r="E37" s="582" t="n"/>
-      <c r="F37" s="583" t="n"/>
-      <c r="G37" s="583" t="n"/>
-      <c r="H37" s="583" t="n"/>
-      <c r="I37" s="583" t="n"/>
-      <c r="J37" s="583" t="n"/>
-      <c r="K37" s="584" t="n"/>
-      <c r="L37" s="931" t="n"/>
-      <c r="M37" s="931" t="n"/>
-      <c r="N37" s="932" t="n"/>
-      <c r="O37" s="932" t="n"/>
-      <c r="P37" s="932" t="n"/>
-      <c r="Q37" s="932" t="n"/>
-      <c r="R37" s="931" t="n"/>
-      <c r="S37" s="933" t="n"/>
+      <c r="D37" s="959" t="n"/>
+      <c r="E37" s="960" t="n"/>
+      <c r="F37" s="961" t="n"/>
+      <c r="G37" s="961" t="n"/>
+      <c r="H37" s="961" t="n"/>
+      <c r="I37" s="961" t="n"/>
+      <c r="J37" s="961" t="n"/>
+      <c r="K37" s="962" t="n"/>
+      <c r="L37" s="961" t="n"/>
+      <c r="M37" s="961" t="n"/>
+      <c r="N37" s="963" t="n"/>
+      <c r="O37" s="963" t="n"/>
+      <c r="P37" s="963" t="n"/>
+      <c r="Q37" s="963" t="n"/>
+      <c r="R37" s="961" t="n"/>
+      <c r="S37" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="38" s="782">
-      <c r="A38" s="889" t="n"/>
-      <c r="B38" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="38" s="888">
+      <c r="A38" s="891" t="n"/>
+      <c r="B38" s="941" t="n">
         <v>9</v>
       </c>
-      <c r="C38" s="916" t="inlineStr">
+      <c r="C38" s="942" t="inlineStr">
         <is>
           <t>2016/08</t>
         </is>
       </c>
-      <c r="D38" s="917" t="inlineStr">
+      <c r="D38" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E38" s="916" t="inlineStr">
+      <c r="E38" s="942" t="inlineStr">
         <is>
           <t>2017/09</t>
         </is>
       </c>
-      <c r="F38" s="918" t="inlineStr">
+      <c r="F38" s="944" t="inlineStr">
         <is>
           <t>■全自動倉庫管理システム開発</t>
         </is>
       </c>
-      <c r="G38" s="919" t="inlineStr">
+      <c r="G38" s="945" t="inlineStr">
         <is>
           <t>システムエンジニア</t>
         </is>
       </c>
-      <c r="H38" s="920" t="inlineStr">
+      <c r="H38" s="946" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I38" s="920" t="inlineStr">
+      <c r="I38" s="946" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J38" s="920" t="inlineStr"/>
-      <c r="K38" s="921" t="inlineStr">
+      <c r="J38" s="946" t="inlineStr"/>
+      <c r="K38" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Spring
 エディタ/IDE：Eclipse
 その他：Redmine、svn</t>
         </is>
       </c>
-      <c r="L38" s="922" t="n"/>
-      <c r="M38" s="922" t="n"/>
-      <c r="N38" s="923" t="inlineStr">
+      <c r="L38" s="965" t="n"/>
+      <c r="M38" s="965" t="n"/>
+      <c r="N38" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O38" s="923" t="inlineStr">
+      <c r="O38" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P38" s="923" t="inlineStr">
+      <c r="P38" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q38" s="923" t="inlineStr">
+      <c r="Q38" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R38" s="922" t="n"/>
-      <c r="S38" s="924" t="n"/>
+      <c r="R38" s="965" t="n"/>
+      <c r="S38" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="113" r="39" s="782">
-      <c r="A39" s="889" t="n"/>
-      <c r="B39" s="814" t="n"/>
-      <c r="C39" s="573" t="n"/>
-      <c r="D39" s="574" t="n"/>
-      <c r="E39" s="573" t="n"/>
-      <c r="F39" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="113" r="39" s="888">
+      <c r="A39" s="891" t="n"/>
+      <c r="B39" s="950" t="n"/>
+      <c r="C39" s="951" t="n"/>
+      <c r="D39" s="952" t="n"/>
+      <c r="E39" s="951" t="n"/>
+      <c r="F39" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 全自動倉庫管理システム開発(2016年8月〜2017年9月：14ヶ月)
@@ -7012,141 +7832,141 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G39" s="926" t="inlineStr">
+      <c r="G39" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、リーダー、エンジニア</t>
         </is>
       </c>
-      <c r="H39" s="574" t="n"/>
-      <c r="I39" s="574" t="n"/>
-      <c r="J39" s="574" t="n"/>
-      <c r="K39" s="577" t="n"/>
-      <c r="L39" s="927" t="n"/>
-      <c r="M39" s="927" t="n"/>
-      <c r="N39" s="928" t="n"/>
-      <c r="O39" s="928" t="n"/>
-      <c r="P39" s="928" t="n"/>
-      <c r="Q39" s="928" t="n"/>
-      <c r="R39" s="927" t="n"/>
-      <c r="S39" s="929" t="n"/>
+      <c r="H39" s="952" t="n"/>
+      <c r="I39" s="952" t="n"/>
+      <c r="J39" s="952" t="n"/>
+      <c r="K39" s="955" t="n"/>
+      <c r="L39" s="952" t="n"/>
+      <c r="M39" s="952" t="n"/>
+      <c r="N39" s="956" t="n"/>
+      <c r="O39" s="956" t="n"/>
+      <c r="P39" s="956" t="n"/>
+      <c r="Q39" s="956" t="n"/>
+      <c r="R39" s="952" t="n"/>
+      <c r="S39" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="40" s="782">
-      <c r="A40" s="889" t="n"/>
-      <c r="B40" s="579" t="n"/>
-      <c r="C40" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="40" s="888">
+      <c r="A40" s="891" t="n"/>
+      <c r="B40" s="958" t="n"/>
+      <c r="C40" s="954" t="inlineStr">
         <is>
           <t>14ヶ月</t>
         </is>
       </c>
-      <c r="D40" s="581" t="n"/>
-      <c r="E40" s="582" t="n"/>
-      <c r="F40" s="583" t="n"/>
-      <c r="G40" s="583" t="n"/>
-      <c r="H40" s="583" t="n"/>
-      <c r="I40" s="583" t="n"/>
-      <c r="J40" s="583" t="n"/>
-      <c r="K40" s="584" t="n"/>
-      <c r="L40" s="931" t="n"/>
-      <c r="M40" s="931" t="n"/>
-      <c r="N40" s="932" t="n"/>
-      <c r="O40" s="932" t="n"/>
-      <c r="P40" s="932" t="n"/>
-      <c r="Q40" s="932" t="n"/>
-      <c r="R40" s="931" t="n"/>
-      <c r="S40" s="933" t="n"/>
+      <c r="D40" s="959" t="n"/>
+      <c r="E40" s="960" t="n"/>
+      <c r="F40" s="961" t="n"/>
+      <c r="G40" s="961" t="n"/>
+      <c r="H40" s="961" t="n"/>
+      <c r="I40" s="961" t="n"/>
+      <c r="J40" s="961" t="n"/>
+      <c r="K40" s="962" t="n"/>
+      <c r="L40" s="961" t="n"/>
+      <c r="M40" s="961" t="n"/>
+      <c r="N40" s="963" t="n"/>
+      <c r="O40" s="963" t="n"/>
+      <c r="P40" s="963" t="n"/>
+      <c r="Q40" s="963" t="n"/>
+      <c r="R40" s="961" t="n"/>
+      <c r="S40" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="57" r="41" s="782">
-      <c r="A41" s="889" t="n"/>
-      <c r="B41" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="57" r="41" s="888">
+      <c r="A41" s="891" t="n"/>
+      <c r="B41" s="941" t="n">
         <v>10</v>
       </c>
-      <c r="C41" s="916" t="inlineStr">
+      <c r="C41" s="942" t="inlineStr">
         <is>
           <t>2013/09</t>
         </is>
       </c>
-      <c r="D41" s="917" t="inlineStr">
+      <c r="D41" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E41" s="916" t="inlineStr">
+      <c r="E41" s="942" t="inlineStr">
         <is>
           <t>2016/08</t>
         </is>
       </c>
-      <c r="F41" s="918" t="inlineStr">
+      <c r="F41" s="944" t="inlineStr">
         <is>
           <t>■製油所向けオフサイトシステム</t>
         </is>
       </c>
-      <c r="G41" s="919" t="inlineStr">
+      <c r="G41" s="945" t="inlineStr">
         <is>
           <t>プログラマー、システムエンジニア</t>
         </is>
       </c>
-      <c r="H41" s="920" t="inlineStr">
+      <c r="H41" s="946" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I41" s="920" t="inlineStr">
+      <c r="I41" s="946" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J41" s="920" t="inlineStr"/>
-      <c r="K41" s="921" t="inlineStr">
+      <c r="J41" s="946" t="inlineStr"/>
+      <c r="K41" s="947" t="inlineStr">
         <is>
           <t>エディタ/IDE：Eclipse
 その他：svn</t>
         </is>
       </c>
-      <c r="L41" s="922" t="n"/>
-      <c r="M41" s="923" t="inlineStr">
+      <c r="L41" s="965" t="n"/>
+      <c r="M41" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N41" s="923" t="inlineStr">
+      <c r="N41" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O41" s="923" t="inlineStr">
+      <c r="O41" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P41" s="923" t="inlineStr">
+      <c r="P41" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q41" s="923" t="inlineStr">
+      <c r="Q41" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R41" s="923" t="inlineStr">
+      <c r="R41" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S41" s="934" t="inlineStr">
+      <c r="S41" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="129" r="42" s="782">
-      <c r="A42" s="889" t="n"/>
-      <c r="B42" s="814" t="n"/>
-      <c r="C42" s="573" t="n"/>
-      <c r="D42" s="574" t="n"/>
-      <c r="E42" s="573" t="n"/>
-      <c r="F42" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="129" r="42" s="888">
+      <c r="A42" s="891" t="n"/>
+      <c r="B42" s="950" t="n"/>
+      <c r="C42" s="951" t="n"/>
+      <c r="D42" s="952" t="n"/>
+      <c r="E42" s="951" t="n"/>
+      <c r="F42" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 製油所向けオフサイトシステム(2013年9月〜2016年8月：36ヶ月)
@@ -7156,121 +7976,121 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G42" s="926" t="inlineStr">
+      <c r="G42" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、リーダー、エンジニア</t>
         </is>
       </c>
-      <c r="H42" s="574" t="n"/>
-      <c r="I42" s="574" t="n"/>
-      <c r="J42" s="574" t="n"/>
-      <c r="K42" s="577" t="n"/>
-      <c r="L42" s="927" t="n"/>
-      <c r="M42" s="928" t="n"/>
-      <c r="N42" s="928" t="n"/>
-      <c r="O42" s="928" t="n"/>
-      <c r="P42" s="928" t="n"/>
-      <c r="Q42" s="928" t="n"/>
-      <c r="R42" s="928" t="n"/>
-      <c r="S42" s="935" t="n"/>
+      <c r="H42" s="952" t="n"/>
+      <c r="I42" s="952" t="n"/>
+      <c r="J42" s="952" t="n"/>
+      <c r="K42" s="955" t="n"/>
+      <c r="L42" s="952" t="n"/>
+      <c r="M42" s="956" t="n"/>
+      <c r="N42" s="956" t="n"/>
+      <c r="O42" s="956" t="n"/>
+      <c r="P42" s="956" t="n"/>
+      <c r="Q42" s="956" t="n"/>
+      <c r="R42" s="956" t="n"/>
+      <c r="S42" s="957" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="43" s="782">
-      <c r="A43" s="889" t="n"/>
-      <c r="B43" s="579" t="n"/>
-      <c r="C43" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="43" s="888">
+      <c r="A43" s="891" t="n"/>
+      <c r="B43" s="958" t="n"/>
+      <c r="C43" s="954" t="inlineStr">
         <is>
           <t>36ヶ月</t>
         </is>
       </c>
-      <c r="D43" s="581" t="n"/>
-      <c r="E43" s="582" t="n"/>
-      <c r="F43" s="583" t="n"/>
-      <c r="G43" s="583" t="n"/>
-      <c r="H43" s="583" t="n"/>
-      <c r="I43" s="583" t="n"/>
-      <c r="J43" s="583" t="n"/>
-      <c r="K43" s="584" t="n"/>
-      <c r="L43" s="931" t="n"/>
-      <c r="M43" s="932" t="n"/>
-      <c r="N43" s="932" t="n"/>
-      <c r="O43" s="932" t="n"/>
-      <c r="P43" s="932" t="n"/>
-      <c r="Q43" s="932" t="n"/>
-      <c r="R43" s="932" t="n"/>
-      <c r="S43" s="936" t="n"/>
+      <c r="D43" s="959" t="n"/>
+      <c r="E43" s="960" t="n"/>
+      <c r="F43" s="961" t="n"/>
+      <c r="G43" s="961" t="n"/>
+      <c r="H43" s="961" t="n"/>
+      <c r="I43" s="961" t="n"/>
+      <c r="J43" s="961" t="n"/>
+      <c r="K43" s="962" t="n"/>
+      <c r="L43" s="961" t="n"/>
+      <c r="M43" s="963" t="n"/>
+      <c r="N43" s="963" t="n"/>
+      <c r="O43" s="963" t="n"/>
+      <c r="P43" s="963" t="n"/>
+      <c r="Q43" s="963" t="n"/>
+      <c r="R43" s="963" t="n"/>
+      <c r="S43" s="964" t="n"/>
     </row>
-    <row customHeight="1" ht="28" r="44" s="782">
-      <c r="A44" s="889" t="n"/>
-      <c r="B44" s="937" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="28" r="44" s="888">
+      <c r="A44" s="891" t="n"/>
+      <c r="B44" s="969" t="inlineStr">
         <is>
           <t>副業案件</t>
         </is>
       </c>
-      <c r="C44" s="938" t="n"/>
-      <c r="D44" s="938" t="n"/>
-      <c r="E44" s="938" t="n"/>
-      <c r="F44" s="938" t="n"/>
-      <c r="G44" s="938" t="n"/>
-      <c r="H44" s="938" t="n"/>
-      <c r="I44" s="938" t="n"/>
-      <c r="J44" s="938" t="n"/>
-      <c r="K44" s="938" t="n"/>
-      <c r="L44" s="938" t="n"/>
-      <c r="M44" s="938" t="n"/>
-      <c r="N44" s="938" t="n"/>
-      <c r="O44" s="938" t="n"/>
-      <c r="P44" s="938" t="n"/>
-      <c r="Q44" s="938" t="n"/>
-      <c r="R44" s="938" t="n"/>
-      <c r="S44" s="939" t="n"/>
+      <c r="C44" s="970" t="n"/>
+      <c r="D44" s="970" t="n"/>
+      <c r="E44" s="970" t="n"/>
+      <c r="F44" s="970" t="n"/>
+      <c r="G44" s="970" t="n"/>
+      <c r="H44" s="970" t="n"/>
+      <c r="I44" s="970" t="n"/>
+      <c r="J44" s="970" t="n"/>
+      <c r="K44" s="970" t="n"/>
+      <c r="L44" s="970" t="n"/>
+      <c r="M44" s="970" t="n"/>
+      <c r="N44" s="970" t="n"/>
+      <c r="O44" s="970" t="n"/>
+      <c r="P44" s="970" t="n"/>
+      <c r="Q44" s="970" t="n"/>
+      <c r="R44" s="970" t="n"/>
+      <c r="S44" s="971" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="45" s="782">
-      <c r="A45" s="889" t="n"/>
-      <c r="B45" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="45" s="888">
+      <c r="A45" s="891" t="n"/>
+      <c r="B45" s="941" t="n">
         <v>11</v>
       </c>
-      <c r="C45" s="916" t="inlineStr">
+      <c r="C45" s="942" t="inlineStr">
         <is>
           <t>2025/08</t>
         </is>
       </c>
-      <c r="D45" s="917" t="inlineStr">
+      <c r="D45" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E45" s="916" t="inlineStr">
+      <c r="E45" s="942" t="inlineStr">
         <is>
           <t>2026/06</t>
         </is>
       </c>
-      <c r="F45" s="918" t="inlineStr">
-        <is>
-          <t>■富裕層向けの旅行代事業のCRM新規開発</t>
-        </is>
-      </c>
-      <c r="G45" s="919" t="inlineStr">
+      <c r="F45" s="944" t="inlineStr">
+        <is>
+          <t>■富裕層向けの旅行代事業のCRM新規開発 ＜副業＞</t>
+        </is>
+      </c>
+      <c r="G45" s="945" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H45" s="920" t="inlineStr">
+      <c r="H45" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript</t>
         </is>
       </c>
-      <c r="I45" s="920" t="inlineStr">
+      <c r="I45" s="946" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J45" s="920" t="inlineStr">
+      <c r="J45" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K45" s="921" t="inlineStr">
+      <c r="K45" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Next.js
 エディタ/IDE：Cursor
@@ -7279,121 +8099,125 @@
 コミュニケーション：Slack、Notion</t>
         </is>
       </c>
-      <c r="L45" s="922" t="n"/>
-      <c r="M45" s="922" t="n"/>
-      <c r="N45" s="922" t="n"/>
-      <c r="O45" s="923" t="inlineStr">
+      <c r="L45" s="965" t="n"/>
+      <c r="M45" s="965" t="n"/>
+      <c r="N45" s="965" t="n"/>
+      <c r="O45" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P45" s="922" t="n"/>
-      <c r="Q45" s="922" t="n"/>
-      <c r="R45" s="922" t="n"/>
-      <c r="S45" s="924" t="n"/>
+      <c r="P45" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q45" s="965" t="n"/>
+      <c r="R45" s="965" t="n"/>
+      <c r="S45" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="152" r="46" s="782">
-      <c r="A46" s="889" t="n"/>
-      <c r="B46" s="814" t="n"/>
-      <c r="C46" s="573" t="n"/>
-      <c r="D46" s="574" t="n"/>
-      <c r="E46" s="573" t="n"/>
-      <c r="F46" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="152" r="46" s="888">
+      <c r="A46" s="891" t="n"/>
+      <c r="B46" s="950" t="n"/>
+      <c r="C46" s="951" t="n"/>
+      <c r="D46" s="952" t="n"/>
+      <c r="E46" s="951" t="n"/>
+      <c r="F46" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
-富裕層向けの旅行代事業のCRM新規開発(2025年8月〜2026年6月：11ヶ月）
+富裕層向けの旅行代事業のCRM新規開発(2025年8月〜2026年6月：11ヶ月） ＜副業＞
 ≪担当業務≫
 開発、コードレビュー
 ≪開発手法≫
 フルリモート</t>
         </is>
       </c>
-      <c r="G46" s="926" t="inlineStr">
+      <c r="G46" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア、デザイナー</t>
         </is>
       </c>
-      <c r="H46" s="574" t="n"/>
-      <c r="I46" s="574" t="n"/>
-      <c r="J46" s="574" t="n"/>
-      <c r="K46" s="577" t="n"/>
-      <c r="L46" s="927" t="n"/>
-      <c r="M46" s="927" t="n"/>
-      <c r="N46" s="927" t="n"/>
-      <c r="O46" s="928" t="n"/>
-      <c r="P46" s="927" t="n"/>
-      <c r="Q46" s="927" t="n"/>
-      <c r="R46" s="927" t="n"/>
-      <c r="S46" s="929" t="n"/>
+      <c r="H46" s="952" t="n"/>
+      <c r="I46" s="952" t="n"/>
+      <c r="J46" s="952" t="n"/>
+      <c r="K46" s="955" t="n"/>
+      <c r="L46" s="952" t="n"/>
+      <c r="M46" s="952" t="n"/>
+      <c r="N46" s="952" t="n"/>
+      <c r="O46" s="956" t="n"/>
+      <c r="P46" s="956" t="n"/>
+      <c r="Q46" s="952" t="n"/>
+      <c r="R46" s="952" t="n"/>
+      <c r="S46" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="47" s="782">
-      <c r="A47" s="889" t="n"/>
-      <c r="B47" s="579" t="n"/>
-      <c r="C47" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="47" s="888">
+      <c r="A47" s="891" t="n"/>
+      <c r="B47" s="958" t="n"/>
+      <c r="C47" s="954" t="inlineStr">
         <is>
           <t>11ヶ月</t>
         </is>
       </c>
-      <c r="D47" s="581" t="n"/>
-      <c r="E47" s="582" t="n"/>
-      <c r="F47" s="583" t="n"/>
-      <c r="G47" s="583" t="n"/>
-      <c r="H47" s="583" t="n"/>
-      <c r="I47" s="583" t="n"/>
-      <c r="J47" s="583" t="n"/>
-      <c r="K47" s="584" t="n"/>
-      <c r="L47" s="931" t="n"/>
-      <c r="M47" s="931" t="n"/>
-      <c r="N47" s="931" t="n"/>
-      <c r="O47" s="932" t="n"/>
-      <c r="P47" s="931" t="n"/>
-      <c r="Q47" s="931" t="n"/>
-      <c r="R47" s="931" t="n"/>
-      <c r="S47" s="933" t="n"/>
+      <c r="D47" s="959" t="n"/>
+      <c r="E47" s="960" t="n"/>
+      <c r="F47" s="961" t="n"/>
+      <c r="G47" s="961" t="n"/>
+      <c r="H47" s="961" t="n"/>
+      <c r="I47" s="961" t="n"/>
+      <c r="J47" s="961" t="n"/>
+      <c r="K47" s="962" t="n"/>
+      <c r="L47" s="961" t="n"/>
+      <c r="M47" s="961" t="n"/>
+      <c r="N47" s="961" t="n"/>
+      <c r="O47" s="963" t="n"/>
+      <c r="P47" s="963" t="n"/>
+      <c r="Q47" s="961" t="n"/>
+      <c r="R47" s="961" t="n"/>
+      <c r="S47" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="25" r="48" s="782">
-      <c r="A48" s="889" t="n"/>
-      <c r="B48" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="25" r="48" s="888">
+      <c r="A48" s="891" t="n"/>
+      <c r="B48" s="941" t="n">
         <v>12</v>
       </c>
-      <c r="C48" s="916" t="inlineStr">
+      <c r="C48" s="942" t="inlineStr">
         <is>
           <t>2025/03</t>
         </is>
       </c>
-      <c r="D48" s="917" t="inlineStr">
+      <c r="D48" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E48" s="916" t="inlineStr">
+      <c r="E48" s="942" t="inlineStr">
         <is>
           <t>2025/07</t>
         </is>
       </c>
-      <c r="F48" s="918" t="inlineStr">
+      <c r="F48" s="944" t="inlineStr">
         <is>
           <t>■パスキー認証システムの管理サービス開発＜副業＞</t>
         </is>
       </c>
-      <c r="G48" s="919" t="inlineStr">
+      <c r="G48" s="945" t="inlineStr">
         <is>
           <t>エンジニア</t>
         </is>
       </c>
-      <c r="H48" s="920" t="inlineStr">
+      <c r="H48" s="946" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I48" s="920" t="inlineStr">
+      <c r="I48" s="946" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J48" s="920" t="inlineStr"/>
-      <c r="K48" s="921" t="inlineStr">
+      <c r="J48" s="946" t="inlineStr"/>
+      <c r="K48" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails
 エディタ/IDE：Cursor
@@ -7402,26 +8226,30 @@
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L48" s="922" t="n"/>
-      <c r="M48" s="922" t="n"/>
-      <c r="N48" s="922" t="n"/>
-      <c r="O48" s="923" t="inlineStr">
+      <c r="L48" s="965" t="n"/>
+      <c r="M48" s="965" t="n"/>
+      <c r="N48" s="965" t="n"/>
+      <c r="O48" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P48" s="922" t="n"/>
-      <c r="Q48" s="922" t="n"/>
-      <c r="R48" s="922" t="n"/>
-      <c r="S48" s="924" t="n"/>
+      <c r="P48" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q48" s="965" t="n"/>
+      <c r="R48" s="965" t="n"/>
+      <c r="S48" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="136" r="49" s="782">
-      <c r="A49" s="889" t="n"/>
-      <c r="B49" s="814" t="n"/>
-      <c r="C49" s="573" t="n"/>
-      <c r="D49" s="574" t="n"/>
-      <c r="E49" s="573" t="n"/>
-      <c r="F49" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="136" r="49" s="888">
+      <c r="A49" s="891" t="n"/>
+      <c r="B49" s="950" t="n"/>
+      <c r="C49" s="951" t="n"/>
+      <c r="D49" s="952" t="n"/>
+      <c r="E49" s="951" t="n"/>
+      <c r="F49" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 パスキー認証システムの管理サービス開発(2025年3月〜2025年7月：5ヶ月）＜副業＞
@@ -7431,92 +8259,92 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G49" s="926" t="inlineStr">
+      <c r="G49" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H49" s="574" t="n"/>
-      <c r="I49" s="574" t="n"/>
-      <c r="J49" s="574" t="n"/>
-      <c r="K49" s="577" t="n"/>
-      <c r="L49" s="927" t="n"/>
-      <c r="M49" s="927" t="n"/>
-      <c r="N49" s="927" t="n"/>
-      <c r="O49" s="928" t="n"/>
-      <c r="P49" s="927" t="n"/>
-      <c r="Q49" s="927" t="n"/>
-      <c r="R49" s="927" t="n"/>
-      <c r="S49" s="929" t="n"/>
+      <c r="H49" s="952" t="n"/>
+      <c r="I49" s="952" t="n"/>
+      <c r="J49" s="952" t="n"/>
+      <c r="K49" s="955" t="n"/>
+      <c r="L49" s="952" t="n"/>
+      <c r="M49" s="952" t="n"/>
+      <c r="N49" s="952" t="n"/>
+      <c r="O49" s="956" t="n"/>
+      <c r="P49" s="956" t="n"/>
+      <c r="Q49" s="952" t="n"/>
+      <c r="R49" s="952" t="n"/>
+      <c r="S49" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="50" s="782">
-      <c r="A50" s="889" t="n"/>
-      <c r="B50" s="579" t="n"/>
-      <c r="C50" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="50" s="888">
+      <c r="A50" s="891" t="n"/>
+      <c r="B50" s="958" t="n"/>
+      <c r="C50" s="954" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D50" s="581" t="n"/>
-      <c r="E50" s="582" t="n"/>
-      <c r="F50" s="583" t="n"/>
-      <c r="G50" s="583" t="n"/>
-      <c r="H50" s="583" t="n"/>
-      <c r="I50" s="583" t="n"/>
-      <c r="J50" s="583" t="n"/>
-      <c r="K50" s="584" t="n"/>
-      <c r="L50" s="931" t="n"/>
-      <c r="M50" s="931" t="n"/>
-      <c r="N50" s="931" t="n"/>
-      <c r="O50" s="932" t="n"/>
-      <c r="P50" s="931" t="n"/>
-      <c r="Q50" s="931" t="n"/>
-      <c r="R50" s="931" t="n"/>
-      <c r="S50" s="933" t="n"/>
+      <c r="D50" s="959" t="n"/>
+      <c r="E50" s="960" t="n"/>
+      <c r="F50" s="961" t="n"/>
+      <c r="G50" s="961" t="n"/>
+      <c r="H50" s="961" t="n"/>
+      <c r="I50" s="961" t="n"/>
+      <c r="J50" s="961" t="n"/>
+      <c r="K50" s="962" t="n"/>
+      <c r="L50" s="961" t="n"/>
+      <c r="M50" s="961" t="n"/>
+      <c r="N50" s="961" t="n"/>
+      <c r="O50" s="963" t="n"/>
+      <c r="P50" s="963" t="n"/>
+      <c r="Q50" s="961" t="n"/>
+      <c r="R50" s="961" t="n"/>
+      <c r="S50" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="51" s="782">
-      <c r="A51" s="889" t="n"/>
-      <c r="B51" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="51" s="888">
+      <c r="A51" s="891" t="n"/>
+      <c r="B51" s="941" t="n">
         <v>13</v>
       </c>
-      <c r="C51" s="916" t="inlineStr">
+      <c r="C51" s="942" t="inlineStr">
         <is>
           <t>2022/04</t>
         </is>
       </c>
-      <c r="D51" s="917" t="inlineStr">
+      <c r="D51" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E51" s="916" t="inlineStr">
+      <c r="E51" s="942" t="inlineStr">
         <is>
           <t>2022/08</t>
         </is>
       </c>
-      <c r="F51" s="918" t="inlineStr">
+      <c r="F51" s="944" t="inlineStr">
         <is>
           <t>■セールステック領域SaaSのプロダクト開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G51" s="919" t="inlineStr">
+      <c r="G51" s="945" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H51" s="920" t="inlineStr">
+      <c r="H51" s="946" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I51" s="920" t="inlineStr">
+      <c r="I51" s="946" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J51" s="920" t="inlineStr"/>
-      <c r="K51" s="921" t="inlineStr">
+      <c r="J51" s="946" t="inlineStr"/>
+      <c r="K51" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec
 エディタ/IDE：VSCode
@@ -7524,26 +8352,30 @@
 コミュニケーション：Slack、Zoom</t>
         </is>
       </c>
-      <c r="L51" s="922" t="n"/>
-      <c r="M51" s="922" t="n"/>
-      <c r="N51" s="922" t="n"/>
-      <c r="O51" s="923" t="inlineStr">
+      <c r="L51" s="965" t="n"/>
+      <c r="M51" s="965" t="n"/>
+      <c r="N51" s="965" t="n"/>
+      <c r="O51" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P51" s="922" t="n"/>
-      <c r="Q51" s="922" t="n"/>
-      <c r="R51" s="922" t="n"/>
-      <c r="S51" s="924" t="n"/>
+      <c r="P51" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q51" s="965" t="n"/>
+      <c r="R51" s="965" t="n"/>
+      <c r="S51" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="129" r="52" s="782">
-      <c r="A52" s="889" t="n"/>
-      <c r="B52" s="814" t="n"/>
-      <c r="C52" s="573" t="n"/>
-      <c r="D52" s="574" t="n"/>
-      <c r="E52" s="573" t="n"/>
-      <c r="F52" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="129" r="52" s="888">
+      <c r="A52" s="891" t="n"/>
+      <c r="B52" s="950" t="n"/>
+      <c r="C52" s="951" t="n"/>
+      <c r="D52" s="952" t="n"/>
+      <c r="E52" s="951" t="n"/>
+      <c r="F52" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 セールステック領域SaaSのプロダクト開発(2022年4月〜2022年8月：5ヶ月) ＜副業＞
@@ -7553,92 +8385,92 @@
 フルリモート、チケット駆動開発</t>
         </is>
       </c>
-      <c r="G52" s="926" t="inlineStr">
+      <c r="G52" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H52" s="574" t="n"/>
-      <c r="I52" s="574" t="n"/>
-      <c r="J52" s="574" t="n"/>
-      <c r="K52" s="577" t="n"/>
-      <c r="L52" s="927" t="n"/>
-      <c r="M52" s="927" t="n"/>
-      <c r="N52" s="927" t="n"/>
-      <c r="O52" s="928" t="n"/>
-      <c r="P52" s="927" t="n"/>
-      <c r="Q52" s="927" t="n"/>
-      <c r="R52" s="927" t="n"/>
-      <c r="S52" s="929" t="n"/>
+      <c r="H52" s="952" t="n"/>
+      <c r="I52" s="952" t="n"/>
+      <c r="J52" s="952" t="n"/>
+      <c r="K52" s="955" t="n"/>
+      <c r="L52" s="952" t="n"/>
+      <c r="M52" s="952" t="n"/>
+      <c r="N52" s="952" t="n"/>
+      <c r="O52" s="956" t="n"/>
+      <c r="P52" s="956" t="n"/>
+      <c r="Q52" s="952" t="n"/>
+      <c r="R52" s="952" t="n"/>
+      <c r="S52" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="53" s="782">
-      <c r="A53" s="889" t="n"/>
-      <c r="B53" s="579" t="n"/>
-      <c r="C53" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="53" s="888">
+      <c r="A53" s="891" t="n"/>
+      <c r="B53" s="958" t="n"/>
+      <c r="C53" s="954" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D53" s="581" t="n"/>
-      <c r="E53" s="582" t="n"/>
-      <c r="F53" s="583" t="n"/>
-      <c r="G53" s="583" t="n"/>
-      <c r="H53" s="583" t="n"/>
-      <c r="I53" s="583" t="n"/>
-      <c r="J53" s="583" t="n"/>
-      <c r="K53" s="584" t="n"/>
-      <c r="L53" s="931" t="n"/>
-      <c r="M53" s="931" t="n"/>
-      <c r="N53" s="931" t="n"/>
-      <c r="O53" s="932" t="n"/>
-      <c r="P53" s="931" t="n"/>
-      <c r="Q53" s="931" t="n"/>
-      <c r="R53" s="931" t="n"/>
-      <c r="S53" s="933" t="n"/>
+      <c r="D53" s="959" t="n"/>
+      <c r="E53" s="960" t="n"/>
+      <c r="F53" s="961" t="n"/>
+      <c r="G53" s="961" t="n"/>
+      <c r="H53" s="961" t="n"/>
+      <c r="I53" s="961" t="n"/>
+      <c r="J53" s="961" t="n"/>
+      <c r="K53" s="962" t="n"/>
+      <c r="L53" s="961" t="n"/>
+      <c r="M53" s="961" t="n"/>
+      <c r="N53" s="961" t="n"/>
+      <c r="O53" s="963" t="n"/>
+      <c r="P53" s="963" t="n"/>
+      <c r="Q53" s="961" t="n"/>
+      <c r="R53" s="961" t="n"/>
+      <c r="S53" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="54" s="782">
-      <c r="A54" s="889" t="n"/>
-      <c r="B54" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="54" s="888">
+      <c r="A54" s="891" t="n"/>
+      <c r="B54" s="941" t="n">
         <v>14</v>
       </c>
-      <c r="C54" s="916" t="inlineStr">
+      <c r="C54" s="942" t="inlineStr">
         <is>
           <t>2020/10</t>
         </is>
       </c>
-      <c r="D54" s="917" t="inlineStr">
+      <c r="D54" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E54" s="916" t="inlineStr">
+      <c r="E54" s="942" t="inlineStr">
         <is>
           <t>2021/01</t>
         </is>
       </c>
-      <c r="F54" s="918" t="inlineStr">
+      <c r="F54" s="944" t="inlineStr">
         <is>
           <t>■営業支援SaaSのプロダクト開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G54" s="919" t="inlineStr">
+      <c r="G54" s="945" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H54" s="920" t="inlineStr">
+      <c r="H54" s="946" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="I54" s="920" t="inlineStr">
+      <c r="I54" s="946" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J54" s="920" t="inlineStr"/>
-      <c r="K54" s="921" t="inlineStr">
+      <c r="J54" s="946" t="inlineStr"/>
+      <c r="K54" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Django、Tailwind CSS
 エディタ/IDE：VSCode
@@ -7646,26 +8478,30 @@
 コミュニケーション：Slack、trello</t>
         </is>
       </c>
-      <c r="L54" s="922" t="n"/>
-      <c r="M54" s="922" t="n"/>
-      <c r="N54" s="922" t="n"/>
-      <c r="O54" s="923" t="inlineStr">
+      <c r="L54" s="965" t="n"/>
+      <c r="M54" s="965" t="n"/>
+      <c r="N54" s="965" t="n"/>
+      <c r="O54" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P54" s="922" t="n"/>
-      <c r="Q54" s="922" t="n"/>
-      <c r="R54" s="922" t="n"/>
-      <c r="S54" s="924" t="n"/>
+      <c r="P54" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q54" s="965" t="n"/>
+      <c r="R54" s="965" t="n"/>
+      <c r="S54" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="129" r="55" s="782">
-      <c r="A55" s="889" t="n"/>
-      <c r="B55" s="814" t="n"/>
-      <c r="C55" s="573" t="n"/>
-      <c r="D55" s="574" t="n"/>
-      <c r="E55" s="573" t="n"/>
-      <c r="F55" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="129" r="55" s="888">
+      <c r="A55" s="891" t="n"/>
+      <c r="B55" s="950" t="n"/>
+      <c r="C55" s="951" t="n"/>
+      <c r="D55" s="952" t="n"/>
+      <c r="E55" s="951" t="n"/>
+      <c r="F55" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 営業支援SaaSのプロダクト開発(2020年10月〜2021年1月：４ヶ月) ＜副業＞
@@ -7675,92 +8511,92 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G55" s="926" t="inlineStr">
+      <c r="G55" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H55" s="574" t="n"/>
-      <c r="I55" s="574" t="n"/>
-      <c r="J55" s="574" t="n"/>
-      <c r="K55" s="577" t="n"/>
-      <c r="L55" s="927" t="n"/>
-      <c r="M55" s="927" t="n"/>
-      <c r="N55" s="927" t="n"/>
-      <c r="O55" s="928" t="n"/>
-      <c r="P55" s="927" t="n"/>
-      <c r="Q55" s="927" t="n"/>
-      <c r="R55" s="927" t="n"/>
-      <c r="S55" s="929" t="n"/>
+      <c r="H55" s="952" t="n"/>
+      <c r="I55" s="952" t="n"/>
+      <c r="J55" s="952" t="n"/>
+      <c r="K55" s="955" t="n"/>
+      <c r="L55" s="952" t="n"/>
+      <c r="M55" s="952" t="n"/>
+      <c r="N55" s="952" t="n"/>
+      <c r="O55" s="956" t="n"/>
+      <c r="P55" s="956" t="n"/>
+      <c r="Q55" s="952" t="n"/>
+      <c r="R55" s="952" t="n"/>
+      <c r="S55" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="56" s="782">
-      <c r="A56" s="889" t="n"/>
-      <c r="B56" s="579" t="n"/>
-      <c r="C56" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="56" s="888">
+      <c r="A56" s="891" t="n"/>
+      <c r="B56" s="958" t="n"/>
+      <c r="C56" s="954" t="inlineStr">
         <is>
           <t>４ヶ月</t>
         </is>
       </c>
-      <c r="D56" s="581" t="n"/>
-      <c r="E56" s="582" t="n"/>
-      <c r="F56" s="583" t="n"/>
-      <c r="G56" s="583" t="n"/>
-      <c r="H56" s="583" t="n"/>
-      <c r="I56" s="583" t="n"/>
-      <c r="J56" s="583" t="n"/>
-      <c r="K56" s="584" t="n"/>
-      <c r="L56" s="931" t="n"/>
-      <c r="M56" s="931" t="n"/>
-      <c r="N56" s="931" t="n"/>
-      <c r="O56" s="932" t="n"/>
-      <c r="P56" s="931" t="n"/>
-      <c r="Q56" s="931" t="n"/>
-      <c r="R56" s="931" t="n"/>
-      <c r="S56" s="933" t="n"/>
+      <c r="D56" s="959" t="n"/>
+      <c r="E56" s="960" t="n"/>
+      <c r="F56" s="961" t="n"/>
+      <c r="G56" s="961" t="n"/>
+      <c r="H56" s="961" t="n"/>
+      <c r="I56" s="961" t="n"/>
+      <c r="J56" s="961" t="n"/>
+      <c r="K56" s="962" t="n"/>
+      <c r="L56" s="961" t="n"/>
+      <c r="M56" s="961" t="n"/>
+      <c r="N56" s="961" t="n"/>
+      <c r="O56" s="963" t="n"/>
+      <c r="P56" s="963" t="n"/>
+      <c r="Q56" s="961" t="n"/>
+      <c r="R56" s="961" t="n"/>
+      <c r="S56" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="41" r="57" s="782">
-      <c r="A57" s="889" t="n"/>
-      <c r="B57" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="41" r="57" s="888">
+      <c r="A57" s="891" t="n"/>
+      <c r="B57" s="941" t="n">
         <v>15</v>
       </c>
-      <c r="C57" s="916" t="inlineStr">
+      <c r="C57" s="942" t="inlineStr">
         <is>
           <t>2020/02</t>
         </is>
       </c>
-      <c r="D57" s="917" t="inlineStr">
+      <c r="D57" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E57" s="916" t="inlineStr">
+      <c r="E57" s="942" t="inlineStr">
         <is>
           <t>2020/07</t>
         </is>
       </c>
-      <c r="F57" s="918" t="inlineStr">
+      <c r="F57" s="944" t="inlineStr">
         <is>
           <t>■エンジニア組織のパフォーマンス最大化サービス開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G57" s="919" t="inlineStr">
+      <c r="G57" s="945" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H57" s="920" t="inlineStr">
+      <c r="H57" s="946" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I57" s="920" t="inlineStr">
+      <c r="I57" s="946" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J57" s="920" t="inlineStr"/>
-      <c r="K57" s="921" t="inlineStr">
+      <c r="J57" s="946" t="inlineStr"/>
+      <c r="K57" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails
 エディタ/IDE：VSCode
@@ -7768,26 +8604,30 @@
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L57" s="922" t="n"/>
-      <c r="M57" s="922" t="n"/>
-      <c r="N57" s="922" t="n"/>
-      <c r="O57" s="923" t="inlineStr">
+      <c r="L57" s="965" t="n"/>
+      <c r="M57" s="965" t="n"/>
+      <c r="N57" s="965" t="n"/>
+      <c r="O57" s="948" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P57" s="922" t="n"/>
-      <c r="Q57" s="922" t="n"/>
-      <c r="R57" s="922" t="n"/>
-      <c r="S57" s="924" t="n"/>
+      <c r="P57" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q57" s="965" t="n"/>
+      <c r="R57" s="965" t="n"/>
+      <c r="S57" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="129" r="58" s="782">
-      <c r="A58" s="889" t="n"/>
-      <c r="B58" s="814" t="n"/>
-      <c r="C58" s="573" t="n"/>
-      <c r="D58" s="574" t="n"/>
-      <c r="E58" s="573" t="n"/>
-      <c r="F58" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="129" r="58" s="888">
+      <c r="A58" s="891" t="n"/>
+      <c r="B58" s="950" t="n"/>
+      <c r="C58" s="951" t="n"/>
+      <c r="D58" s="952" t="n"/>
+      <c r="E58" s="951" t="n"/>
+      <c r="F58" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 エンジニア組織のパフォーマンス最大化サービス開発(2020年2月〜2020年7月:6ヶ月) ＜副業＞
@@ -7797,118 +8637,126 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G58" s="926" t="inlineStr">
+      <c r="G58" s="954" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H58" s="574" t="n"/>
-      <c r="I58" s="574" t="n"/>
-      <c r="J58" s="574" t="n"/>
-      <c r="K58" s="577" t="n"/>
-      <c r="L58" s="927" t="n"/>
-      <c r="M58" s="927" t="n"/>
-      <c r="N58" s="927" t="n"/>
-      <c r="O58" s="928" t="n"/>
-      <c r="P58" s="927" t="n"/>
-      <c r="Q58" s="927" t="n"/>
-      <c r="R58" s="927" t="n"/>
-      <c r="S58" s="929" t="n"/>
+      <c r="H58" s="952" t="n"/>
+      <c r="I58" s="952" t="n"/>
+      <c r="J58" s="952" t="n"/>
+      <c r="K58" s="955" t="n"/>
+      <c r="L58" s="952" t="n"/>
+      <c r="M58" s="952" t="n"/>
+      <c r="N58" s="952" t="n"/>
+      <c r="O58" s="956" t="n"/>
+      <c r="P58" s="956" t="n"/>
+      <c r="Q58" s="952" t="n"/>
+      <c r="R58" s="952" t="n"/>
+      <c r="S58" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="59" s="782">
-      <c r="A59" s="889" t="n"/>
-      <c r="B59" s="579" t="n"/>
-      <c r="C59" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="59" s="888">
+      <c r="A59" s="891" t="n"/>
+      <c r="B59" s="958" t="n"/>
+      <c r="C59" s="954" t="inlineStr">
         <is>
           <t>6ヶ月</t>
         </is>
       </c>
-      <c r="D59" s="581" t="n"/>
-      <c r="E59" s="582" t="n"/>
-      <c r="F59" s="583" t="n"/>
-      <c r="G59" s="583" t="n"/>
-      <c r="H59" s="583" t="n"/>
-      <c r="I59" s="583" t="n"/>
-      <c r="J59" s="583" t="n"/>
-      <c r="K59" s="584" t="n"/>
-      <c r="L59" s="931" t="n"/>
-      <c r="M59" s="931" t="n"/>
-      <c r="N59" s="931" t="n"/>
-      <c r="O59" s="932" t="n"/>
-      <c r="P59" s="931" t="n"/>
-      <c r="Q59" s="931" t="n"/>
-      <c r="R59" s="931" t="n"/>
-      <c r="S59" s="933" t="n"/>
+      <c r="D59" s="959" t="n"/>
+      <c r="E59" s="960" t="n"/>
+      <c r="F59" s="961" t="n"/>
+      <c r="G59" s="961" t="n"/>
+      <c r="H59" s="961" t="n"/>
+      <c r="I59" s="961" t="n"/>
+      <c r="J59" s="961" t="n"/>
+      <c r="K59" s="962" t="n"/>
+      <c r="L59" s="961" t="n"/>
+      <c r="M59" s="961" t="n"/>
+      <c r="N59" s="961" t="n"/>
+      <c r="O59" s="963" t="n"/>
+      <c r="P59" s="963" t="n"/>
+      <c r="Q59" s="961" t="n"/>
+      <c r="R59" s="961" t="n"/>
+      <c r="S59" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="25" r="60" s="782">
-      <c r="A60" s="889" t="n"/>
-      <c r="B60" s="915" t="n">
+    <row customFormat="1" customHeight="1" ht="25" r="60" s="888">
+      <c r="A60" s="891" t="n"/>
+      <c r="B60" s="941" t="n">
         <v>16</v>
       </c>
-      <c r="C60" s="916" t="inlineStr">
+      <c r="C60" s="942" t="inlineStr">
         <is>
           <t>2019/05</t>
         </is>
       </c>
-      <c r="D60" s="917" t="inlineStr">
+      <c r="D60" s="943" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E60" s="916" t="inlineStr">
+      <c r="E60" s="942" t="inlineStr">
         <is>
           <t>2019/12</t>
         </is>
       </c>
-      <c r="F60" s="918" t="inlineStr">
+      <c r="F60" s="944" t="inlineStr">
         <is>
           <t>■プログラミングスクール学習サポート ＜副業＞</t>
         </is>
       </c>
-      <c r="G60" s="919" t="inlineStr">
+      <c r="G60" s="945" t="inlineStr">
         <is>
           <t>メンター</t>
         </is>
       </c>
-      <c r="H60" s="920" t="inlineStr">
+      <c r="H60" s="946" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I60" s="920" t="inlineStr">
+      <c r="I60" s="946" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J60" s="920" t="inlineStr">
+      <c r="J60" s="946" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K60" s="921" t="inlineStr">
+      <c r="K60" s="947" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Bootstrap
 エディタ/IDE：VSCode
 その他：Git、Vagrant、Bootstrap</t>
         </is>
       </c>
-      <c r="L60" s="922" t="n"/>
-      <c r="M60" s="922" t="n"/>
-      <c r="N60" s="922" t="n"/>
-      <c r="O60" s="922" t="n"/>
-      <c r="P60" s="922" t="n"/>
-      <c r="Q60" s="922" t="n"/>
-      <c r="R60" s="922" t="n"/>
-      <c r="S60" s="924" t="n"/>
+      <c r="L60" s="965" t="n"/>
+      <c r="M60" s="965" t="n"/>
+      <c r="N60" s="965" t="n"/>
+      <c r="O60" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="P60" s="948" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="Q60" s="965" t="n"/>
+      <c r="R60" s="965" t="n"/>
+      <c r="S60" s="966" t="n"/>
     </row>
-    <row customHeight="1" ht="88" r="61" s="782">
-      <c r="A61" s="889" t="n"/>
-      <c r="B61" s="814" t="n"/>
-      <c r="C61" s="573" t="n"/>
-      <c r="D61" s="574" t="n"/>
-      <c r="E61" s="573" t="n"/>
-      <c r="F61" s="925" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="88" r="61" s="888">
+      <c r="A61" s="891" t="n"/>
+      <c r="B61" s="950" t="n"/>
+      <c r="C61" s="951" t="n"/>
+      <c r="D61" s="952" t="n"/>
+      <c r="E61" s="951" t="n"/>
+      <c r="F61" s="953" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 プログラミングスクール学習サポート(2019年5月〜2019年12月：8ヶ月) ＜副業＞
@@ -7916,50 +8764,50 @@
 受講生サポート、コードレビュー</t>
         </is>
       </c>
-      <c r="G61" s="926" t="inlineStr"/>
-      <c r="H61" s="574" t="n"/>
-      <c r="I61" s="574" t="n"/>
-      <c r="J61" s="574" t="n"/>
-      <c r="K61" s="577" t="n"/>
-      <c r="L61" s="927" t="n"/>
-      <c r="M61" s="927" t="n"/>
-      <c r="N61" s="927" t="n"/>
-      <c r="O61" s="927" t="n"/>
-      <c r="P61" s="927" t="n"/>
-      <c r="Q61" s="927" t="n"/>
-      <c r="R61" s="927" t="n"/>
-      <c r="S61" s="929" t="n"/>
+      <c r="G61" s="954" t="inlineStr"/>
+      <c r="H61" s="952" t="n"/>
+      <c r="I61" s="952" t="n"/>
+      <c r="J61" s="952" t="n"/>
+      <c r="K61" s="955" t="n"/>
+      <c r="L61" s="952" t="n"/>
+      <c r="M61" s="952" t="n"/>
+      <c r="N61" s="952" t="n"/>
+      <c r="O61" s="956" t="n"/>
+      <c r="P61" s="956" t="n"/>
+      <c r="Q61" s="952" t="n"/>
+      <c r="R61" s="952" t="n"/>
+      <c r="S61" s="967" t="n"/>
     </row>
-    <row customHeight="1" ht="24" r="62" s="782">
-      <c r="A62" s="889" t="n"/>
-      <c r="B62" s="579" t="n"/>
-      <c r="C62" s="930" t="inlineStr">
+    <row customFormat="1" customHeight="1" ht="24" r="62" s="888">
+      <c r="A62" s="891" t="n"/>
+      <c r="B62" s="958" t="n"/>
+      <c r="C62" s="954" t="inlineStr">
         <is>
           <t>8ヶ月</t>
         </is>
       </c>
-      <c r="D62" s="581" t="n"/>
-      <c r="E62" s="582" t="n"/>
-      <c r="F62" s="583" t="n"/>
-      <c r="G62" s="583" t="n"/>
-      <c r="H62" s="583" t="n"/>
-      <c r="I62" s="583" t="n"/>
-      <c r="J62" s="583" t="n"/>
-      <c r="K62" s="584" t="n"/>
-      <c r="L62" s="931" t="n"/>
-      <c r="M62" s="931" t="n"/>
-      <c r="N62" s="931" t="n"/>
-      <c r="O62" s="931" t="n"/>
-      <c r="P62" s="931" t="n"/>
-      <c r="Q62" s="931" t="n"/>
-      <c r="R62" s="931" t="n"/>
-      <c r="S62" s="933" t="n"/>
+      <c r="D62" s="959" t="n"/>
+      <c r="E62" s="960" t="n"/>
+      <c r="F62" s="961" t="n"/>
+      <c r="G62" s="961" t="n"/>
+      <c r="H62" s="961" t="n"/>
+      <c r="I62" s="961" t="n"/>
+      <c r="J62" s="961" t="n"/>
+      <c r="K62" s="962" t="n"/>
+      <c r="L62" s="961" t="n"/>
+      <c r="M62" s="961" t="n"/>
+      <c r="N62" s="961" t="n"/>
+      <c r="O62" s="963" t="n"/>
+      <c r="P62" s="963" t="n"/>
+      <c r="Q62" s="961" t="n"/>
+      <c r="R62" s="961" t="n"/>
+      <c r="S62" s="968" t="n"/>
     </row>
-    <row customHeight="1" ht="28" r="63" s="782">
-      <c r="A63" s="889" t="n"/>
-      <c r="B63" s="940" t="inlineStr">
-        <is>
-          <t>●：READMEの工程/作業に明記された担当工程。空欄：未記載（経験なしを意味しません）。案件名のリンクから詳細を確認できます。</t>
+    <row customFormat="1" customHeight="1" ht="28" r="63" s="888">
+      <c r="A63" s="891" t="n"/>
+      <c r="B63" s="972" t="inlineStr">
+        <is>
+          <t>●：担当工程。空欄：未記載（経験なしを意味しません）。案件名のリンクから詳細を確認できます。</t>
         </is>
       </c>
       <c r="C63" s="888" t="n"/>

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -6382,7 +6382,7 @@
       <c r="R8" s="920" t="n"/>
       <c r="S8" s="924" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="169" r="9" s="888">
+    <row customFormat="1" customHeight="1" ht="105" r="9" s="888">
       <c r="A9" s="891" t="n"/>
       <c r="B9" s="921" t="inlineStr">
         <is>
@@ -6397,10 +6397,7 @@
 - AWS/Terraform/Docker/GitHub Actions等を用いた開発・運用基盤整備
 - GraphQL API設計、DB設計・パフォーマンス改善
 - AIエージェント（Cursor、Claude Code）を活用した開発生産性向上
-- リードエンジニアとしての設計、レビュー、見積、チーム支援
-エリア：神奈川
-稼働時期：即日 or 相談
-所属：フリーランス</t>
+- リードエンジニアとしての設計、レビュー、見積、チーム支援</t>
         </is>
       </c>
       <c r="E9" s="920" t="n"/>

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -6201,7 +6201,7 @@
       <c r="H3" s="895" t="n"/>
       <c r="I3" s="900" t="inlineStr">
         <is>
-          <t>14年目</t>
+          <t>14年目（フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09）</t>
         </is>
       </c>
       <c r="J3" s="897" t="n"/>
@@ -6416,7 +6416,7 @@
       <c r="R9" s="920" t="n"/>
       <c r="S9" s="924" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="153" r="10" s="888">
+    <row customFormat="1" customHeight="1" ht="137" r="10" s="888">
       <c r="A10" s="891" t="n"/>
       <c r="B10" s="921" t="inlineStr">
         <is>
@@ -6426,8 +6426,7 @@
       <c r="C10" s="922" t="n"/>
       <c r="D10" s="923" t="inlineStr">
         <is>
-          <t>・キャリア：フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09
-・プログラミング言語：HTML 10年、CSS  10年、Javascript 10年、SQL 10年、Ruby 8年、Java 5年、TypeScript 3年、Python 2年、Kotlin 1年未満
+          <t>・プログラミング言語：HTML 10年、CSS  10年、Javascript 10年、SQL 10年、Ruby 8年、Java 5年、TypeScript 3年、Python 2年、Kotlin 1年未満
 ・FW/ライブラリ：Ruby on Rails 8年、RSpec 8年、JQuery 5年、Bootstrap 3年、React 3年、Next.js 2年、Tailwind CSS 2年、Spring 1年、Vue.js 1年、Nuxt.js 1年、Django 1年未満、Jest 1年未満
 ・DB：MySQL 6年、Oracle 4年、PostgreSQL 4年
 ・クラウド：AWS 6年（EC2、ECS、RDS、S3、Lambda、Elastic Beanstalk、VPC、CloudFront、Route 53、CloudWatch、Clrail、Systems Manager、IAM、Kinesis、Simple Queue Service、Simple Email Service、CodePipeline、ElastiCache、Amazon Connect、Amazon WorkMail、Amazon Bedrock、Amazon Transcribe、など）

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -6201,7 +6201,7 @@
       <c r="H3" s="895" t="n"/>
       <c r="I3" s="900" t="inlineStr">
         <is>
-          <t>14年目（フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09）</t>
+          <t>14年目：フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09</t>
         </is>
       </c>
       <c r="J3" s="897" t="n"/>

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -6182,13 +6182,13 @@
       <c r="A3" s="891" t="n"/>
       <c r="B3" s="894" t="inlineStr">
         <is>
-          <t>フリガナ</t>
+          <t>氏名</t>
         </is>
       </c>
       <c r="C3" s="895" t="n"/>
       <c r="D3" s="896" t="inlineStr">
         <is>
-          <t>ヒラタ トモアキ</t>
+          <t>平田 智昭（ヒラタ トモアキ）</t>
         </is>
       </c>
       <c r="E3" s="897" t="n"/>
@@ -6219,13 +6219,13 @@
       <c r="A4" s="891" t="n"/>
       <c r="B4" s="902" t="inlineStr">
         <is>
-          <t>氏　　名</t>
+          <t>稼働希望</t>
         </is>
       </c>
       <c r="C4" s="903" t="n"/>
       <c r="D4" s="904" t="inlineStr">
         <is>
-          <t>平田 智昭</t>
+          <t>フルリモート(必要時に都度出社)</t>
         </is>
       </c>
       <c r="E4" s="905" t="n"/>
@@ -6262,7 +6262,7 @@
       <c r="C5" s="903" t="n"/>
       <c r="D5" s="910" t="inlineStr">
         <is>
-          <t>東海道線 平塚駅 / 基本リモート(必要に応じて出社)</t>
+          <t>東海道線 平塚駅</t>
         </is>
       </c>
       <c r="E5" s="905" t="n"/>

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -279,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="296">
+  <borders count="315">
     <border/>
     <border>
       <bottom style="medium">
@@ -3237,6 +3237,218 @@
         <color rgb="0017365D"/>
       </top>
       <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E9F1F8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E9F1F8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E9F1F8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E9F1F8"/>
+      </left>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E9F1F8"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0017365D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0017365D"/>
+      </left>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+      <bottom style="medium">
         <color rgb="0017365D"/>
       </bottom>
     </border>
@@ -3247,7 +3459,7 @@
     </xf>
     <xf borderId="84" fillId="0" fontId="1" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="973">
+  <cellXfs count="974">
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5712,10 +5924,11 @@
     <xf applyAlignment="1" borderId="84" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="234" fillId="14" fontId="20" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="234" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="297" fillId="14" fontId="20" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="258" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="262" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf applyAlignment="1" borderId="235" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5787,30 +6000,30 @@
     <xf applyAlignment="1" borderId="84" fillId="13" fontId="27" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="263" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf applyAlignment="1" borderId="308" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="264" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="265" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="266" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="266" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="267" fillId="14" fontId="23" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf borderId="305" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="311" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="311" fillId="14" fontId="32" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="313" fillId="14" fontId="23" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="268" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf borderId="269" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="270" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="271" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="272" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="273" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="274" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf applyAlignment="1" borderId="275" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf borderId="306" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="234" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="307" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="310" fillId="14" fontId="31" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="255" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" borderId="314" fillId="15" fontId="22" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyAlignment="1" borderId="276" fillId="14" fontId="33" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6176,188 +6389,188 @@
       <c r="P2" s="893" t="n"/>
       <c r="Q2" s="893" t="n"/>
       <c r="R2" s="893" t="n"/>
-      <c r="S2" s="893" t="n"/>
+      <c r="S2" s="894" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="3" s="888">
       <c r="A3" s="891" t="n"/>
-      <c r="B3" s="894" t="inlineStr">
+      <c r="B3" s="895" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C3" s="895" t="n"/>
-      <c r="D3" s="896" t="inlineStr">
+      <c r="C3" s="896" t="n"/>
+      <c r="D3" s="897" t="inlineStr">
         <is>
           <t>平田 智昭（ヒラタ トモアキ）</t>
         </is>
       </c>
-      <c r="E3" s="897" t="n"/>
-      <c r="F3" s="898" t="n"/>
-      <c r="G3" s="899" t="inlineStr">
-        <is>
-          <t>業界経験</t>
-        </is>
-      </c>
-      <c r="H3" s="895" t="n"/>
-      <c r="I3" s="900" t="inlineStr">
-        <is>
-          <t>14年目：フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09</t>
-        </is>
-      </c>
-      <c r="J3" s="897" t="n"/>
-      <c r="K3" s="897" t="n"/>
-      <c r="L3" s="897" t="n"/>
-      <c r="M3" s="897" t="n"/>
-      <c r="N3" s="897" t="n"/>
-      <c r="O3" s="897" t="n"/>
-      <c r="P3" s="897" t="n"/>
-      <c r="Q3" s="897" t="n"/>
-      <c r="R3" s="897" t="n"/>
-      <c r="S3" s="901" t="n"/>
+      <c r="E3" s="898" t="n"/>
+      <c r="F3" s="899" t="n"/>
+      <c r="G3" s="900" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="H3" s="896" t="n"/>
+      <c r="I3" s="901" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="J3" s="898" t="n"/>
+      <c r="K3" s="898" t="n"/>
+      <c r="L3" s="898" t="n"/>
+      <c r="M3" s="898" t="n"/>
+      <c r="N3" s="898" t="n"/>
+      <c r="O3" s="898" t="n"/>
+      <c r="P3" s="898" t="n"/>
+      <c r="Q3" s="898" t="n"/>
+      <c r="R3" s="898" t="n"/>
+      <c r="S3" s="902" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="4" s="888">
       <c r="A4" s="891" t="n"/>
-      <c r="B4" s="902" t="inlineStr">
-        <is>
-          <t>稼働希望</t>
-        </is>
-      </c>
-      <c r="C4" s="903" t="n"/>
-      <c r="D4" s="904" t="inlineStr">
-        <is>
-          <t>フルリモート(必要時に都度出社)</t>
-        </is>
-      </c>
-      <c r="E4" s="905" t="n"/>
-      <c r="F4" s="906" t="n"/>
-      <c r="G4" s="907" t="inlineStr">
-        <is>
-          <t>性　　別</t>
-        </is>
-      </c>
-      <c r="H4" s="903" t="n"/>
-      <c r="I4" s="908" t="inlineStr">
-        <is>
-          <t>男性</t>
-        </is>
-      </c>
-      <c r="J4" s="905" t="n"/>
-      <c r="K4" s="905" t="n"/>
-      <c r="L4" s="905" t="n"/>
-      <c r="M4" s="905" t="n"/>
-      <c r="N4" s="905" t="n"/>
-      <c r="O4" s="905" t="n"/>
-      <c r="P4" s="905" t="n"/>
-      <c r="Q4" s="905" t="n"/>
-      <c r="R4" s="905" t="n"/>
-      <c r="S4" s="909" t="n"/>
+      <c r="B4" s="903" t="inlineStr">
+        <is>
+          <t>年齢</t>
+        </is>
+      </c>
+      <c r="C4" s="904" t="n"/>
+      <c r="D4" s="905" t="inlineStr">
+        <is>
+          <t>38歳</t>
+        </is>
+      </c>
+      <c r="E4" s="906" t="n"/>
+      <c r="F4" s="907" t="n"/>
+      <c r="G4" s="908" t="inlineStr">
+        <is>
+          <t>業界経験</t>
+        </is>
+      </c>
+      <c r="H4" s="904" t="n"/>
+      <c r="I4" s="909" t="inlineStr">
+        <is>
+          <t>14年目：フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09</t>
+        </is>
+      </c>
+      <c r="J4" s="906" t="n"/>
+      <c r="K4" s="906" t="n"/>
+      <c r="L4" s="906" t="n"/>
+      <c r="M4" s="906" t="n"/>
+      <c r="N4" s="906" t="n"/>
+      <c r="O4" s="906" t="n"/>
+      <c r="P4" s="906" t="n"/>
+      <c r="Q4" s="906" t="n"/>
+      <c r="R4" s="906" t="n"/>
+      <c r="S4" s="910" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="5" s="888">
       <c r="A5" s="891" t="n"/>
-      <c r="B5" s="902" t="inlineStr">
-        <is>
-          <t>最 寄 駅</t>
-        </is>
-      </c>
-      <c r="C5" s="903" t="n"/>
-      <c r="D5" s="910" t="inlineStr">
+      <c r="B5" s="903" t="inlineStr">
+        <is>
+          <t>最寄駅</t>
+        </is>
+      </c>
+      <c r="C5" s="904" t="n"/>
+      <c r="D5" s="911" t="inlineStr">
         <is>
           <t>東海道線 平塚駅</t>
         </is>
       </c>
-      <c r="E5" s="905" t="n"/>
-      <c r="F5" s="906" t="n"/>
-      <c r="G5" s="907" t="inlineStr">
-        <is>
-          <t>年　　齢</t>
-        </is>
-      </c>
-      <c r="H5" s="903" t="n"/>
-      <c r="I5" s="911" t="inlineStr">
-        <is>
-          <t>38歳</t>
-        </is>
-      </c>
-      <c r="J5" s="905" t="n"/>
-      <c r="K5" s="905" t="n"/>
-      <c r="L5" s="905" t="n"/>
-      <c r="M5" s="905" t="n"/>
-      <c r="N5" s="905" t="n"/>
-      <c r="O5" s="905" t="n"/>
-      <c r="P5" s="905" t="n"/>
-      <c r="Q5" s="905" t="n"/>
-      <c r="R5" s="905" t="n"/>
-      <c r="S5" s="909" t="n"/>
+      <c r="E5" s="906" t="n"/>
+      <c r="F5" s="907" t="n"/>
+      <c r="G5" s="908" t="inlineStr">
+        <is>
+          <t>稼働希望</t>
+        </is>
+      </c>
+      <c r="H5" s="904" t="n"/>
+      <c r="I5" s="912" t="inlineStr">
+        <is>
+          <t>フルリモート(必要時に都度出社)</t>
+        </is>
+      </c>
+      <c r="J5" s="906" t="n"/>
+      <c r="K5" s="906" t="n"/>
+      <c r="L5" s="906" t="n"/>
+      <c r="M5" s="906" t="n"/>
+      <c r="N5" s="906" t="n"/>
+      <c r="O5" s="906" t="n"/>
+      <c r="P5" s="906" t="n"/>
+      <c r="Q5" s="906" t="n"/>
+      <c r="R5" s="906" t="n"/>
+      <c r="S5" s="910" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="57" r="6" s="888">
       <c r="A6" s="891" t="n"/>
-      <c r="B6" s="912" t="inlineStr">
-        <is>
-          <t>資　　格</t>
-        </is>
-      </c>
-      <c r="C6" s="913" t="n"/>
-      <c r="D6" s="914" t="inlineStr">
+      <c r="B6" s="913" t="inlineStr">
+        <is>
+          <t>資格</t>
+        </is>
+      </c>
+      <c r="C6" s="914" t="n"/>
+      <c r="D6" s="915" t="inlineStr">
         <is>
           <t>認定スクラムマスター(LSM) ※2022/12 失効
 基本情報技術者
 Ruby Association Certified Ruby Programmer Gold Version 3</t>
         </is>
       </c>
-      <c r="E6" s="915" t="n"/>
-      <c r="F6" s="915" t="n"/>
-      <c r="G6" s="916" t="inlineStr">
-        <is>
-          <t>学　　歴</t>
-        </is>
-      </c>
-      <c r="H6" s="913" t="n"/>
-      <c r="I6" s="917" t="inlineStr">
+      <c r="E6" s="916" t="n"/>
+      <c r="F6" s="916" t="n"/>
+      <c r="G6" s="917" t="inlineStr">
+        <is>
+          <t>学歴</t>
+        </is>
+      </c>
+      <c r="H6" s="914" t="n"/>
+      <c r="I6" s="918" t="inlineStr">
         <is>
           <t>工学院大学 工学部 機械システム工学科卒</t>
         </is>
       </c>
-      <c r="J6" s="915" t="n"/>
-      <c r="K6" s="915" t="n"/>
-      <c r="L6" s="915" t="n"/>
-      <c r="M6" s="915" t="n"/>
-      <c r="N6" s="915" t="n"/>
-      <c r="O6" s="915" t="n"/>
-      <c r="P6" s="915" t="n"/>
-      <c r="Q6" s="915" t="n"/>
-      <c r="R6" s="915" t="n"/>
-      <c r="S6" s="918" t="n"/>
+      <c r="J6" s="916" t="n"/>
+      <c r="K6" s="916" t="n"/>
+      <c r="L6" s="916" t="n"/>
+      <c r="M6" s="916" t="n"/>
+      <c r="N6" s="916" t="n"/>
+      <c r="O6" s="916" t="n"/>
+      <c r="P6" s="916" t="n"/>
+      <c r="Q6" s="916" t="n"/>
+      <c r="R6" s="916" t="n"/>
+      <c r="S6" s="919" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="10" r="7" s="888">
       <c r="A7" s="891" t="n"/>
-      <c r="B7" s="919" t="n"/>
-      <c r="C7" s="920" t="n"/>
-      <c r="D7" s="920" t="n"/>
-      <c r="E7" s="920" t="n"/>
-      <c r="F7" s="920" t="n"/>
-      <c r="G7" s="920" t="n"/>
-      <c r="H7" s="920" t="n"/>
-      <c r="I7" s="920" t="n"/>
-      <c r="J7" s="920" t="n"/>
-      <c r="K7" s="920" t="n"/>
-      <c r="L7" s="920" t="n"/>
-      <c r="M7" s="920" t="n"/>
-      <c r="N7" s="920" t="n"/>
-      <c r="O7" s="920" t="n"/>
-      <c r="P7" s="920" t="n"/>
-      <c r="Q7" s="920" t="n"/>
-      <c r="R7" s="920" t="n"/>
-      <c r="S7" s="920" t="n"/>
+      <c r="B7" s="920" t="n"/>
+      <c r="C7" s="921" t="n"/>
+      <c r="D7" s="921" t="n"/>
+      <c r="E7" s="921" t="n"/>
+      <c r="F7" s="921" t="n"/>
+      <c r="G7" s="921" t="n"/>
+      <c r="H7" s="921" t="n"/>
+      <c r="I7" s="921" t="n"/>
+      <c r="J7" s="921" t="n"/>
+      <c r="K7" s="921" t="n"/>
+      <c r="L7" s="921" t="n"/>
+      <c r="M7" s="921" t="n"/>
+      <c r="N7" s="921" t="n"/>
+      <c r="O7" s="921" t="n"/>
+      <c r="P7" s="921" t="n"/>
+      <c r="Q7" s="921" t="n"/>
+      <c r="R7" s="921" t="n"/>
+      <c r="S7" s="921" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="201" r="8" s="888">
       <c r="A8" s="891" t="n"/>
-      <c r="B8" s="921" t="inlineStr">
+      <c r="B8" s="922" t="inlineStr">
         <is>
           <t>職務要約</t>
         </is>
       </c>
-      <c r="C8" s="922" t="n"/>
-      <c r="D8" s="923" t="inlineStr">
+      <c r="C8" s="923" t="n"/>
+      <c r="D8" s="924" t="inlineStr">
         <is>
           <t>新卒にて中小ソフトウェア企業に入社後、2013年から正社員として5年間、受託開発や客先開発でJavaやOracleを使ったシステム開発に携わりました。
 2017年にフリーランスに転身してから現在まで8年間、Ruby on Railsを主軸としたバックエンド開発をメインとしながら、React/Next.jsなどのモダンフロントエンド技術、AWSインフラ構築、DBパフォーマンスチューニングまで幅広くフルスタックに対応してきました。
@@ -6366,31 +6579,31 @@
 今後も、AIツールを効果的に活用しながら開発生産性を向上させつつ、チームリードとしての責任を果たし、ビジネス価値の高いプロダクト開発に貢献していきたいと考えております。何卒よろしくお願いいたします。</t>
         </is>
       </c>
-      <c r="E8" s="920" t="n"/>
-      <c r="F8" s="920" t="n"/>
-      <c r="G8" s="920" t="n"/>
-      <c r="H8" s="920" t="n"/>
-      <c r="I8" s="920" t="n"/>
-      <c r="J8" s="920" t="n"/>
-      <c r="K8" s="920" t="n"/>
-      <c r="L8" s="920" t="n"/>
-      <c r="M8" s="920" t="n"/>
-      <c r="N8" s="920" t="n"/>
-      <c r="O8" s="920" t="n"/>
-      <c r="P8" s="920" t="n"/>
-      <c r="Q8" s="920" t="n"/>
-      <c r="R8" s="920" t="n"/>
-      <c r="S8" s="924" t="n"/>
+      <c r="E8" s="921" t="n"/>
+      <c r="F8" s="921" t="n"/>
+      <c r="G8" s="921" t="n"/>
+      <c r="H8" s="921" t="n"/>
+      <c r="I8" s="921" t="n"/>
+      <c r="J8" s="921" t="n"/>
+      <c r="K8" s="921" t="n"/>
+      <c r="L8" s="921" t="n"/>
+      <c r="M8" s="921" t="n"/>
+      <c r="N8" s="921" t="n"/>
+      <c r="O8" s="921" t="n"/>
+      <c r="P8" s="921" t="n"/>
+      <c r="Q8" s="921" t="n"/>
+      <c r="R8" s="921" t="n"/>
+      <c r="S8" s="925" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="105" r="9" s="888">
       <c r="A9" s="891" t="n"/>
-      <c r="B9" s="921" t="inlineStr">
+      <c r="B9" s="922" t="inlineStr">
         <is>
           <t>得意とする分野</t>
         </is>
       </c>
-      <c r="C9" s="922" t="n"/>
-      <c r="D9" s="923" t="inlineStr">
+      <c r="C9" s="923" t="n"/>
+      <c r="D9" s="924" t="inlineStr">
         <is>
           <t>- Ruby on Railsを中心としたWebアプリケーションのバックエンド開発
 - React/Next.js/TypeScriptを用いたフロントエンド開発
@@ -6400,31 +6613,31 @@
 - リードエンジニアとしての設計、レビュー、見積、チーム支援</t>
         </is>
       </c>
-      <c r="E9" s="920" t="n"/>
-      <c r="F9" s="920" t="n"/>
-      <c r="G9" s="920" t="n"/>
-      <c r="H9" s="920" t="n"/>
-      <c r="I9" s="920" t="n"/>
-      <c r="J9" s="920" t="n"/>
-      <c r="K9" s="920" t="n"/>
-      <c r="L9" s="920" t="n"/>
-      <c r="M9" s="920" t="n"/>
-      <c r="N9" s="920" t="n"/>
-      <c r="O9" s="920" t="n"/>
-      <c r="P9" s="920" t="n"/>
-      <c r="Q9" s="920" t="n"/>
-      <c r="R9" s="920" t="n"/>
-      <c r="S9" s="924" t="n"/>
+      <c r="E9" s="921" t="n"/>
+      <c r="F9" s="921" t="n"/>
+      <c r="G9" s="921" t="n"/>
+      <c r="H9" s="921" t="n"/>
+      <c r="I9" s="921" t="n"/>
+      <c r="J9" s="921" t="n"/>
+      <c r="K9" s="921" t="n"/>
+      <c r="L9" s="921" t="n"/>
+      <c r="M9" s="921" t="n"/>
+      <c r="N9" s="921" t="n"/>
+      <c r="O9" s="921" t="n"/>
+      <c r="P9" s="921" t="n"/>
+      <c r="Q9" s="921" t="n"/>
+      <c r="R9" s="921" t="n"/>
+      <c r="S9" s="925" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="137" r="10" s="888">
       <c r="A10" s="891" t="n"/>
-      <c r="B10" s="921" t="inlineStr">
+      <c r="B10" s="922" t="inlineStr">
         <is>
           <t>スキル</t>
         </is>
       </c>
-      <c r="C10" s="922" t="n"/>
-      <c r="D10" s="923" t="inlineStr">
+      <c r="C10" s="923" t="n"/>
+      <c r="D10" s="924" t="inlineStr">
         <is>
           <t>・プログラミング言語：HTML 10年、CSS  10年、Javascript 10年、SQL 10年、Ruby 8年、Java 5年、TypeScript 3年、Python 2年、Kotlin 1年未満
 ・FW/ライブラリ：Ruby on Rails 8年、RSpec 8年、JQuery 5年、Bootstrap 3年、React 3年、Next.js 2年、Tailwind CSS 2年、Spring 1年、Vue.js 1年、Nuxt.js 1年、Django 1年未満、Jest 1年未満
@@ -6434,34 +6647,34 @@
 ・その他ソフトウェアツール、サービス：Slack 8年、Docker 6年、Eclipse 4年、Redmine 3年、CircleCI 3年、Swagger 3年、Google Analytics 2年、Jira 3年、Confluence 2年、Terraform 2年、GitHubActions 2年、Twilio 1年、Vagrant 1年、Zabbix 1年、Jmeter 1年、AndroidStudio 1年</t>
         </is>
       </c>
-      <c r="E10" s="920" t="n"/>
-      <c r="F10" s="920" t="n"/>
-      <c r="G10" s="920" t="n"/>
-      <c r="H10" s="920" t="n"/>
-      <c r="I10" s="920" t="n"/>
-      <c r="J10" s="920" t="n"/>
-      <c r="K10" s="920" t="n"/>
-      <c r="L10" s="920" t="n"/>
-      <c r="M10" s="920" t="n"/>
-      <c r="N10" s="920" t="n"/>
-      <c r="O10" s="920" t="n"/>
-      <c r="P10" s="920" t="n"/>
-      <c r="Q10" s="920" t="n"/>
-      <c r="R10" s="920" t="n"/>
-      <c r="S10" s="924" t="n"/>
+      <c r="E10" s="921" t="n"/>
+      <c r="F10" s="921" t="n"/>
+      <c r="G10" s="921" t="n"/>
+      <c r="H10" s="921" t="n"/>
+      <c r="I10" s="921" t="n"/>
+      <c r="J10" s="921" t="n"/>
+      <c r="K10" s="921" t="n"/>
+      <c r="L10" s="921" t="n"/>
+      <c r="M10" s="921" t="n"/>
+      <c r="N10" s="921" t="n"/>
+      <c r="O10" s="921" t="n"/>
+      <c r="P10" s="921" t="n"/>
+      <c r="Q10" s="921" t="n"/>
+      <c r="R10" s="921" t="n"/>
+      <c r="S10" s="925" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="10" r="11" s="888">
       <c r="A11" s="891" t="n"/>
       <c r="B11" s="891" t="n"/>
       <c r="C11" s="891" t="n"/>
-      <c r="D11" s="925" t="n"/>
+      <c r="D11" s="926" t="n"/>
       <c r="E11" s="891" t="n"/>
-      <c r="F11" s="925" t="n"/>
-      <c r="G11" s="926" t="n"/>
-      <c r="H11" s="925" t="n"/>
-      <c r="I11" s="925" t="n"/>
-      <c r="J11" s="925" t="n"/>
-      <c r="K11" s="925" t="n"/>
+      <c r="F11" s="926" t="n"/>
+      <c r="G11" s="927" t="n"/>
+      <c r="H11" s="926" t="n"/>
+      <c r="I11" s="926" t="n"/>
+      <c r="J11" s="926" t="n"/>
+      <c r="K11" s="926" t="n"/>
       <c r="L11" s="891" t="n"/>
       <c r="M11" s="891" t="n"/>
       <c r="N11" s="891" t="n"/>
@@ -6473,116 +6686,116 @@
     </row>
     <row customFormat="1" customHeight="1" ht="26" r="12" s="888">
       <c r="A12" s="888" t="n"/>
-      <c r="B12" s="927" t="inlineStr">
+      <c r="B12" s="928" t="inlineStr">
         <is>
           <t>期間</t>
         </is>
       </c>
-      <c r="C12" s="928" t="n"/>
-      <c r="D12" s="928" t="n"/>
-      <c r="E12" s="929" t="n"/>
-      <c r="F12" s="930" t="inlineStr">
+      <c r="C12" s="929" t="n"/>
+      <c r="D12" s="929" t="n"/>
+      <c r="E12" s="930" t="n"/>
+      <c r="F12" s="931" t="inlineStr">
         <is>
           <t>業務内容</t>
         </is>
       </c>
-      <c r="G12" s="931" t="inlineStr">
+      <c r="G12" s="932" t="inlineStr">
         <is>
           <t>役割
 規模</t>
         </is>
       </c>
-      <c r="H12" s="930" t="inlineStr">
+      <c r="H12" s="931" t="inlineStr">
         <is>
           <t>言語</t>
         </is>
       </c>
-      <c r="I12" s="930" t="inlineStr">
+      <c r="I12" s="931" t="inlineStr">
         <is>
           <t>DB</t>
         </is>
       </c>
-      <c r="J12" s="930" t="inlineStr">
+      <c r="J12" s="931" t="inlineStr">
         <is>
           <t>機種
 ・
 OS</t>
         </is>
       </c>
-      <c r="K12" s="930" t="inlineStr">
+      <c r="K12" s="931" t="inlineStr">
         <is>
           <t>FW
 ・
 ツール等</t>
         </is>
       </c>
-      <c r="L12" s="932" t="inlineStr">
+      <c r="L12" s="933" t="inlineStr">
         <is>
           <t>担当工程</t>
         </is>
       </c>
-      <c r="M12" s="933" t="n"/>
-      <c r="N12" s="933" t="n"/>
-      <c r="O12" s="933" t="n"/>
-      <c r="P12" s="933" t="n"/>
-      <c r="Q12" s="933" t="n"/>
-      <c r="R12" s="933" t="n"/>
-      <c r="S12" s="934" t="n"/>
+      <c r="M12" s="934" t="n"/>
+      <c r="N12" s="934" t="n"/>
+      <c r="O12" s="934" t="n"/>
+      <c r="P12" s="934" t="n"/>
+      <c r="Q12" s="934" t="n"/>
+      <c r="R12" s="934" t="n"/>
+      <c r="S12" s="935" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="46" r="13" s="888">
       <c r="A13" s="888" t="n"/>
-      <c r="B13" s="935" t="n"/>
-      <c r="C13" s="936" t="n"/>
-      <c r="D13" s="936" t="n"/>
-      <c r="E13" s="937" t="n"/>
-      <c r="F13" s="938" t="n"/>
-      <c r="G13" s="938" t="n"/>
-      <c r="H13" s="938" t="n"/>
-      <c r="I13" s="938" t="n"/>
-      <c r="J13" s="938" t="n"/>
-      <c r="K13" s="938" t="n"/>
-      <c r="L13" s="939" t="inlineStr">
+      <c r="B13" s="936" t="n"/>
+      <c r="C13" s="937" t="n"/>
+      <c r="D13" s="937" t="n"/>
+      <c r="E13" s="938" t="n"/>
+      <c r="F13" s="939" t="n"/>
+      <c r="G13" s="939" t="n"/>
+      <c r="H13" s="939" t="n"/>
+      <c r="I13" s="939" t="n"/>
+      <c r="J13" s="939" t="n"/>
+      <c r="K13" s="939" t="n"/>
+      <c r="L13" s="940" t="inlineStr">
         <is>
           <t>要件
 定義</t>
         </is>
       </c>
-      <c r="M13" s="939" t="inlineStr">
+      <c r="M13" s="940" t="inlineStr">
         <is>
           <t>基本
 設計</t>
         </is>
       </c>
-      <c r="N13" s="939" t="inlineStr">
+      <c r="N13" s="940" t="inlineStr">
         <is>
           <t>詳細
 設計</t>
         </is>
       </c>
-      <c r="O13" s="939" t="inlineStr">
+      <c r="O13" s="940" t="inlineStr">
         <is>
           <t>実装</t>
         </is>
       </c>
-      <c r="P13" s="939" t="inlineStr">
+      <c r="P13" s="940" t="inlineStr">
         <is>
           <t>単体
 テスト</t>
         </is>
       </c>
-      <c r="Q13" s="939" t="inlineStr">
+      <c r="Q13" s="940" t="inlineStr">
         <is>
           <t>結合
 テスト</t>
         </is>
       </c>
-      <c r="R13" s="939" t="inlineStr">
+      <c r="R13" s="940" t="inlineStr">
         <is>
           <t>総合
 テスト</t>
         </is>
       </c>
-      <c r="S13" s="940" t="inlineStr">
+      <c r="S13" s="941" t="inlineStr">
         <is>
           <t>保守
 運用</t>
@@ -6591,50 +6804,50 @@
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="14" s="888">
       <c r="A14" s="891" t="n"/>
-      <c r="B14" s="941" t="n">
+      <c r="B14" s="942" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="942" t="inlineStr">
+      <c r="C14" s="943" t="inlineStr">
         <is>
           <t>2024/10</t>
         </is>
       </c>
-      <c r="D14" s="943" t="inlineStr">
+      <c r="D14" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E14" s="942" t="inlineStr">
+      <c r="E14" s="943" t="inlineStr">
         <is>
           <t>現在</t>
         </is>
       </c>
-      <c r="F14" s="944" t="inlineStr">
+      <c r="F14" s="945" t="inlineStr">
         <is>
           <t>■自治体連携DX推進支援プラットフォームの開発</t>
         </is>
       </c>
-      <c r="G14" s="945" t="inlineStr">
+      <c r="G14" s="946" t="inlineStr">
         <is>
           <t>リードエンジニア</t>
         </is>
       </c>
-      <c r="H14" s="946" t="inlineStr">
+      <c r="H14" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript, Python</t>
         </is>
       </c>
-      <c r="I14" s="946" t="inlineStr">
+      <c r="I14" s="947" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J14" s="946" t="inlineStr">
+      <c r="J14" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K14" s="947" t="inlineStr">
+      <c r="K14" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、React
 エディタ/IDE：Cursor、Orca
@@ -6644,42 +6857,42 @@
 コミュニケーション：Slack、Jira、Notion</t>
         </is>
       </c>
-      <c r="L14" s="948" t="inlineStr">
+      <c r="L14" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M14" s="948" t="inlineStr">
+      <c r="M14" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N14" s="948" t="inlineStr">
+      <c r="N14" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O14" s="948" t="inlineStr">
+      <c r="O14" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P14" s="948" t="inlineStr">
+      <c r="P14" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q14" s="948" t="inlineStr">
+      <c r="Q14" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R14" s="948" t="inlineStr">
+      <c r="R14" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S14" s="949" t="inlineStr">
+      <c r="S14" s="950" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -6687,11 +6900,11 @@
     </row>
     <row customFormat="1" customHeight="1" ht="232" r="15" s="888">
       <c r="A15" s="891" t="n"/>
-      <c r="B15" s="950" t="n"/>
-      <c r="C15" s="951" t="n"/>
-      <c r="D15" s="952" t="n"/>
-      <c r="E15" s="951" t="n"/>
-      <c r="F15" s="953" t="inlineStr">
+      <c r="B15" s="951" t="n"/>
+      <c r="C15" s="952" t="n"/>
+      <c r="D15" s="953" t="n"/>
+      <c r="E15" s="952" t="n"/>
+      <c r="F15" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 自治体連携DX推進支援プラットフォームの開発(2024年10月〜、随時更新）
@@ -6701,96 +6914,96 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G15" s="954" t="inlineStr">
+      <c r="G15" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、PdM、エンジニア、SRE、デザイナー、QA</t>
         </is>
       </c>
-      <c r="H15" s="952" t="n"/>
-      <c r="I15" s="952" t="n"/>
-      <c r="J15" s="952" t="n"/>
-      <c r="K15" s="955" t="n"/>
-      <c r="L15" s="956" t="n"/>
-      <c r="M15" s="956" t="n"/>
-      <c r="N15" s="956" t="n"/>
-      <c r="O15" s="956" t="n"/>
-      <c r="P15" s="956" t="n"/>
-      <c r="Q15" s="956" t="n"/>
-      <c r="R15" s="956" t="n"/>
-      <c r="S15" s="957" t="n"/>
+      <c r="H15" s="953" t="n"/>
+      <c r="I15" s="953" t="n"/>
+      <c r="J15" s="953" t="n"/>
+      <c r="K15" s="956" t="n"/>
+      <c r="L15" s="957" t="n"/>
+      <c r="M15" s="957" t="n"/>
+      <c r="N15" s="957" t="n"/>
+      <c r="O15" s="957" t="n"/>
+      <c r="P15" s="957" t="n"/>
+      <c r="Q15" s="957" t="n"/>
+      <c r="R15" s="957" t="n"/>
+      <c r="S15" s="958" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="16" s="888">
       <c r="A16" s="891" t="n"/>
-      <c r="B16" s="958" t="n"/>
-      <c r="C16" s="954" t="inlineStr">
+      <c r="B16" s="959" t="n"/>
+      <c r="C16" s="955" t="inlineStr">
         <is>
           <t>随時更新</t>
         </is>
       </c>
-      <c r="D16" s="959" t="n"/>
-      <c r="E16" s="960" t="n"/>
-      <c r="F16" s="961" t="n"/>
-      <c r="G16" s="961" t="n"/>
-      <c r="H16" s="961" t="n"/>
-      <c r="I16" s="961" t="n"/>
-      <c r="J16" s="961" t="n"/>
-      <c r="K16" s="962" t="n"/>
-      <c r="L16" s="963" t="n"/>
-      <c r="M16" s="963" t="n"/>
-      <c r="N16" s="963" t="n"/>
-      <c r="O16" s="963" t="n"/>
-      <c r="P16" s="963" t="n"/>
-      <c r="Q16" s="963" t="n"/>
-      <c r="R16" s="963" t="n"/>
-      <c r="S16" s="964" t="n"/>
+      <c r="D16" s="960" t="n"/>
+      <c r="E16" s="961" t="n"/>
+      <c r="F16" s="962" t="n"/>
+      <c r="G16" s="962" t="n"/>
+      <c r="H16" s="962" t="n"/>
+      <c r="I16" s="962" t="n"/>
+      <c r="J16" s="962" t="n"/>
+      <c r="K16" s="963" t="n"/>
+      <c r="L16" s="964" t="n"/>
+      <c r="M16" s="964" t="n"/>
+      <c r="N16" s="964" t="n"/>
+      <c r="O16" s="964" t="n"/>
+      <c r="P16" s="964" t="n"/>
+      <c r="Q16" s="964" t="n"/>
+      <c r="R16" s="964" t="n"/>
+      <c r="S16" s="965" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="17" s="888">
       <c r="A17" s="891" t="n"/>
-      <c r="B17" s="941" t="n">
+      <c r="B17" s="942" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="942" t="inlineStr">
+      <c r="C17" s="943" t="inlineStr">
         <is>
           <t>2024/04</t>
         </is>
       </c>
-      <c r="D17" s="943" t="inlineStr">
+      <c r="D17" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E17" s="942" t="inlineStr">
+      <c r="E17" s="943" t="inlineStr">
         <is>
           <t>2024/08</t>
         </is>
       </c>
-      <c r="F17" s="944" t="inlineStr">
+      <c r="F17" s="945" t="inlineStr">
         <is>
           <t>■電気自動車のEV充電ローミングプロジェクトの新規開発</t>
         </is>
       </c>
-      <c r="G17" s="945" t="inlineStr">
+      <c r="G17" s="946" t="inlineStr">
         <is>
           <t>リードエンジニア</t>
         </is>
       </c>
-      <c r="H17" s="946" t="inlineStr">
+      <c r="H17" s="947" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I17" s="946" t="inlineStr">
+      <c r="I17" s="947" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J17" s="946" t="inlineStr">
+      <c r="J17" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K17" s="947" t="inlineStr">
+      <c r="K17" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec
 エディタ/IDE：VSCode
@@ -6798,42 +7011,42 @@
 コミュニケーション：Slack、Google Meet</t>
         </is>
       </c>
-      <c r="L17" s="948" t="inlineStr">
+      <c r="L17" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M17" s="948" t="inlineStr">
+      <c r="M17" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N17" s="948" t="inlineStr">
+      <c r="N17" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O17" s="948" t="inlineStr">
+      <c r="O17" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P17" s="948" t="inlineStr">
+      <c r="P17" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q17" s="965" t="n"/>
-      <c r="R17" s="965" t="n"/>
-      <c r="S17" s="966" t="n"/>
+      <c r="Q17" s="966" t="n"/>
+      <c r="R17" s="966" t="n"/>
+      <c r="S17" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="161" r="18" s="888">
       <c r="A18" s="891" t="n"/>
-      <c r="B18" s="950" t="n"/>
-      <c r="C18" s="951" t="n"/>
-      <c r="D18" s="952" t="n"/>
-      <c r="E18" s="951" t="n"/>
-      <c r="F18" s="953" t="inlineStr">
+      <c r="B18" s="951" t="n"/>
+      <c r="C18" s="952" t="n"/>
+      <c r="D18" s="953" t="n"/>
+      <c r="E18" s="952" t="n"/>
+      <c r="F18" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 電気自動車のEV充電ローミングプロジェクトの新規開発(2024年4月〜2024年8月：5ヶ月)
@@ -6843,96 +7056,96 @@
 リモート、ウォーターフォール開発</t>
         </is>
       </c>
-      <c r="G18" s="954" t="inlineStr">
+      <c r="G18" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H18" s="952" t="n"/>
-      <c r="I18" s="952" t="n"/>
-      <c r="J18" s="952" t="n"/>
-      <c r="K18" s="955" t="n"/>
-      <c r="L18" s="956" t="n"/>
-      <c r="M18" s="956" t="n"/>
-      <c r="N18" s="956" t="n"/>
-      <c r="O18" s="956" t="n"/>
-      <c r="P18" s="956" t="n"/>
-      <c r="Q18" s="952" t="n"/>
-      <c r="R18" s="952" t="n"/>
-      <c r="S18" s="967" t="n"/>
+      <c r="H18" s="953" t="n"/>
+      <c r="I18" s="953" t="n"/>
+      <c r="J18" s="953" t="n"/>
+      <c r="K18" s="956" t="n"/>
+      <c r="L18" s="957" t="n"/>
+      <c r="M18" s="957" t="n"/>
+      <c r="N18" s="957" t="n"/>
+      <c r="O18" s="957" t="n"/>
+      <c r="P18" s="957" t="n"/>
+      <c r="Q18" s="953" t="n"/>
+      <c r="R18" s="953" t="n"/>
+      <c r="S18" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="19" s="888">
       <c r="A19" s="891" t="n"/>
-      <c r="B19" s="958" t="n"/>
-      <c r="C19" s="954" t="inlineStr">
+      <c r="B19" s="959" t="n"/>
+      <c r="C19" s="955" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D19" s="959" t="n"/>
-      <c r="E19" s="960" t="n"/>
-      <c r="F19" s="961" t="n"/>
-      <c r="G19" s="961" t="n"/>
-      <c r="H19" s="961" t="n"/>
-      <c r="I19" s="961" t="n"/>
-      <c r="J19" s="961" t="n"/>
-      <c r="K19" s="962" t="n"/>
-      <c r="L19" s="963" t="n"/>
-      <c r="M19" s="963" t="n"/>
-      <c r="N19" s="963" t="n"/>
-      <c r="O19" s="963" t="n"/>
-      <c r="P19" s="963" t="n"/>
-      <c r="Q19" s="961" t="n"/>
-      <c r="R19" s="961" t="n"/>
-      <c r="S19" s="968" t="n"/>
+      <c r="D19" s="960" t="n"/>
+      <c r="E19" s="961" t="n"/>
+      <c r="F19" s="962" t="n"/>
+      <c r="G19" s="962" t="n"/>
+      <c r="H19" s="962" t="n"/>
+      <c r="I19" s="962" t="n"/>
+      <c r="J19" s="962" t="n"/>
+      <c r="K19" s="963" t="n"/>
+      <c r="L19" s="964" t="n"/>
+      <c r="M19" s="964" t="n"/>
+      <c r="N19" s="964" t="n"/>
+      <c r="O19" s="964" t="n"/>
+      <c r="P19" s="964" t="n"/>
+      <c r="Q19" s="962" t="n"/>
+      <c r="R19" s="962" t="n"/>
+      <c r="S19" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="20" s="888">
       <c r="A20" s="891" t="n"/>
-      <c r="B20" s="941" t="n">
+      <c r="B20" s="942" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="942" t="inlineStr">
+      <c r="C20" s="943" t="inlineStr">
         <is>
           <t>2023/07</t>
         </is>
       </c>
-      <c r="D20" s="943" t="inlineStr">
+      <c r="D20" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E20" s="942" t="inlineStr">
+      <c r="E20" s="943" t="inlineStr">
         <is>
           <t>2024/03</t>
         </is>
       </c>
-      <c r="F20" s="944" t="inlineStr">
+      <c r="F20" s="945" t="inlineStr">
         <is>
           <t>■不動産テックのバーティカルSaaSプロダクト開発</t>
         </is>
       </c>
-      <c r="G20" s="945" t="inlineStr">
+      <c r="G20" s="946" t="inlineStr">
         <is>
           <t>webエンジニア</t>
         </is>
       </c>
-      <c r="H20" s="946" t="inlineStr">
+      <c r="H20" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、 TypeScript</t>
         </is>
       </c>
-      <c r="I20" s="946" t="inlineStr">
+      <c r="I20" s="947" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J20" s="946" t="inlineStr">
+      <c r="J20" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K20" s="947" t="inlineStr">
+      <c r="K20" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、 React、 Next.js
 エディタ/IDE：VSCode
@@ -6940,34 +7153,34 @@
 コミュニケーション：Slack、Google Meet</t>
         </is>
       </c>
-      <c r="L20" s="965" t="n"/>
-      <c r="M20" s="965" t="n"/>
-      <c r="N20" s="965" t="n"/>
-      <c r="O20" s="948" t="inlineStr">
+      <c r="L20" s="966" t="n"/>
+      <c r="M20" s="966" t="n"/>
+      <c r="N20" s="966" t="n"/>
+      <c r="O20" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P20" s="948" t="inlineStr">
+      <c r="P20" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q20" s="948" t="inlineStr">
+      <c r="Q20" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R20" s="965" t="n"/>
-      <c r="S20" s="966" t="n"/>
+      <c r="R20" s="966" t="n"/>
+      <c r="S20" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="168" r="21" s="888">
       <c r="A21" s="891" t="n"/>
-      <c r="B21" s="950" t="n"/>
-      <c r="C21" s="951" t="n"/>
-      <c r="D21" s="952" t="n"/>
-      <c r="E21" s="951" t="n"/>
-      <c r="F21" s="953" t="inlineStr">
+      <c r="B21" s="951" t="n"/>
+      <c r="C21" s="952" t="n"/>
+      <c r="D21" s="953" t="n"/>
+      <c r="E21" s="952" t="n"/>
+      <c r="F21" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 不動産テックのバーティカルSaaSプロダクト開発(2023年7月〜2024年3月：9ヶ月)
@@ -6977,96 +7190,96 @@
 リモート及び出社、アジャイル開発</t>
         </is>
       </c>
-      <c r="G21" s="954" t="inlineStr">
+      <c r="G21" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H21" s="952" t="n"/>
-      <c r="I21" s="952" t="n"/>
-      <c r="J21" s="952" t="n"/>
-      <c r="K21" s="955" t="n"/>
-      <c r="L21" s="952" t="n"/>
-      <c r="M21" s="952" t="n"/>
-      <c r="N21" s="952" t="n"/>
-      <c r="O21" s="956" t="n"/>
-      <c r="P21" s="956" t="n"/>
-      <c r="Q21" s="956" t="n"/>
-      <c r="R21" s="952" t="n"/>
-      <c r="S21" s="967" t="n"/>
+      <c r="H21" s="953" t="n"/>
+      <c r="I21" s="953" t="n"/>
+      <c r="J21" s="953" t="n"/>
+      <c r="K21" s="956" t="n"/>
+      <c r="L21" s="953" t="n"/>
+      <c r="M21" s="953" t="n"/>
+      <c r="N21" s="953" t="n"/>
+      <c r="O21" s="957" t="n"/>
+      <c r="P21" s="957" t="n"/>
+      <c r="Q21" s="957" t="n"/>
+      <c r="R21" s="953" t="n"/>
+      <c r="S21" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="22" s="888">
       <c r="A22" s="891" t="n"/>
-      <c r="B22" s="958" t="n"/>
-      <c r="C22" s="954" t="inlineStr">
+      <c r="B22" s="959" t="n"/>
+      <c r="C22" s="955" t="inlineStr">
         <is>
           <t>9ヶ月</t>
         </is>
       </c>
-      <c r="D22" s="959" t="n"/>
-      <c r="E22" s="960" t="n"/>
-      <c r="F22" s="961" t="n"/>
-      <c r="G22" s="961" t="n"/>
-      <c r="H22" s="961" t="n"/>
-      <c r="I22" s="961" t="n"/>
-      <c r="J22" s="961" t="n"/>
-      <c r="K22" s="962" t="n"/>
-      <c r="L22" s="961" t="n"/>
-      <c r="M22" s="961" t="n"/>
-      <c r="N22" s="961" t="n"/>
-      <c r="O22" s="963" t="n"/>
-      <c r="P22" s="963" t="n"/>
-      <c r="Q22" s="963" t="n"/>
-      <c r="R22" s="961" t="n"/>
-      <c r="S22" s="968" t="n"/>
+      <c r="D22" s="960" t="n"/>
+      <c r="E22" s="961" t="n"/>
+      <c r="F22" s="962" t="n"/>
+      <c r="G22" s="962" t="n"/>
+      <c r="H22" s="962" t="n"/>
+      <c r="I22" s="962" t="n"/>
+      <c r="J22" s="962" t="n"/>
+      <c r="K22" s="963" t="n"/>
+      <c r="L22" s="962" t="n"/>
+      <c r="M22" s="962" t="n"/>
+      <c r="N22" s="962" t="n"/>
+      <c r="O22" s="964" t="n"/>
+      <c r="P22" s="964" t="n"/>
+      <c r="Q22" s="964" t="n"/>
+      <c r="R22" s="962" t="n"/>
+      <c r="S22" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="23" s="888">
       <c r="A23" s="891" t="n"/>
-      <c r="B23" s="941" t="n">
+      <c r="B23" s="942" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="942" t="inlineStr">
+      <c r="C23" s="943" t="inlineStr">
         <is>
           <t>2022/12</t>
         </is>
       </c>
-      <c r="D23" s="943" t="inlineStr">
+      <c r="D23" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E23" s="942" t="inlineStr">
+      <c r="E23" s="943" t="inlineStr">
         <is>
           <t>2023/06</t>
         </is>
       </c>
-      <c r="F23" s="944" t="inlineStr">
+      <c r="F23" s="945" t="inlineStr">
         <is>
           <t>■ブロックチェーンを活用したクラウドファンディングサービスのサーバーサイド開発</t>
         </is>
       </c>
-      <c r="G23" s="945" t="inlineStr">
+      <c r="G23" s="946" t="inlineStr">
         <is>
           <t>webエンジニア</t>
         </is>
       </c>
-      <c r="H23" s="946" t="inlineStr">
+      <c r="H23" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript、Solidity</t>
         </is>
       </c>
-      <c r="I23" s="946" t="inlineStr">
+      <c r="I23" s="947" t="inlineStr">
         <is>
           <t>MySQL、Firestore</t>
         </is>
       </c>
-      <c r="J23" s="946" t="inlineStr">
+      <c r="J23" s="947" t="inlineStr">
         <is>
           <t>GCP</t>
         </is>
       </c>
-      <c r="K23" s="947" t="inlineStr">
+      <c r="K23" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、React、Next.js、Jest
 エディタ/IDE：VSCode
@@ -7074,34 +7287,34 @@
 コミュニケーション：Slack、Google Meet、Zoom</t>
         </is>
       </c>
-      <c r="L23" s="965" t="n"/>
-      <c r="M23" s="965" t="n"/>
-      <c r="N23" s="965" t="n"/>
-      <c r="O23" s="948" t="inlineStr">
+      <c r="L23" s="966" t="n"/>
+      <c r="M23" s="966" t="n"/>
+      <c r="N23" s="966" t="n"/>
+      <c r="O23" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P23" s="948" t="inlineStr">
+      <c r="P23" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q23" s="948" t="inlineStr">
+      <c r="Q23" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R23" s="965" t="n"/>
-      <c r="S23" s="966" t="n"/>
+      <c r="R23" s="966" t="n"/>
+      <c r="S23" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="184" r="24" s="888">
       <c r="A24" s="891" t="n"/>
-      <c r="B24" s="950" t="n"/>
-      <c r="C24" s="951" t="n"/>
-      <c r="D24" s="952" t="n"/>
-      <c r="E24" s="951" t="n"/>
-      <c r="F24" s="953" t="inlineStr">
+      <c r="B24" s="951" t="n"/>
+      <c r="C24" s="952" t="n"/>
+      <c r="D24" s="953" t="n"/>
+      <c r="E24" s="952" t="n"/>
+      <c r="F24" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 ブロックチェーンを活用したクラウドファンディングサービスのサーバーサイド開発(2022年12月〜2023年6月:7ヶ月)
@@ -7111,96 +7324,96 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G24" s="954" t="inlineStr">
+      <c r="G24" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H24" s="952" t="n"/>
-      <c r="I24" s="952" t="n"/>
-      <c r="J24" s="952" t="n"/>
-      <c r="K24" s="955" t="n"/>
-      <c r="L24" s="952" t="n"/>
-      <c r="M24" s="952" t="n"/>
-      <c r="N24" s="952" t="n"/>
-      <c r="O24" s="956" t="n"/>
-      <c r="P24" s="956" t="n"/>
-      <c r="Q24" s="956" t="n"/>
-      <c r="R24" s="952" t="n"/>
-      <c r="S24" s="967" t="n"/>
+      <c r="H24" s="953" t="n"/>
+      <c r="I24" s="953" t="n"/>
+      <c r="J24" s="953" t="n"/>
+      <c r="K24" s="956" t="n"/>
+      <c r="L24" s="953" t="n"/>
+      <c r="M24" s="953" t="n"/>
+      <c r="N24" s="953" t="n"/>
+      <c r="O24" s="957" t="n"/>
+      <c r="P24" s="957" t="n"/>
+      <c r="Q24" s="957" t="n"/>
+      <c r="R24" s="953" t="n"/>
+      <c r="S24" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="25" s="888">
       <c r="A25" s="891" t="n"/>
-      <c r="B25" s="958" t="n"/>
-      <c r="C25" s="954" t="inlineStr">
+      <c r="B25" s="959" t="n"/>
+      <c r="C25" s="955" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
       </c>
-      <c r="D25" s="959" t="n"/>
-      <c r="E25" s="960" t="n"/>
-      <c r="F25" s="961" t="n"/>
-      <c r="G25" s="961" t="n"/>
-      <c r="H25" s="961" t="n"/>
-      <c r="I25" s="961" t="n"/>
-      <c r="J25" s="961" t="n"/>
-      <c r="K25" s="962" t="n"/>
-      <c r="L25" s="961" t="n"/>
-      <c r="M25" s="961" t="n"/>
-      <c r="N25" s="961" t="n"/>
-      <c r="O25" s="963" t="n"/>
-      <c r="P25" s="963" t="n"/>
-      <c r="Q25" s="963" t="n"/>
-      <c r="R25" s="961" t="n"/>
-      <c r="S25" s="968" t="n"/>
+      <c r="D25" s="960" t="n"/>
+      <c r="E25" s="961" t="n"/>
+      <c r="F25" s="962" t="n"/>
+      <c r="G25" s="962" t="n"/>
+      <c r="H25" s="962" t="n"/>
+      <c r="I25" s="962" t="n"/>
+      <c r="J25" s="962" t="n"/>
+      <c r="K25" s="963" t="n"/>
+      <c r="L25" s="962" t="n"/>
+      <c r="M25" s="962" t="n"/>
+      <c r="N25" s="962" t="n"/>
+      <c r="O25" s="964" t="n"/>
+      <c r="P25" s="964" t="n"/>
+      <c r="Q25" s="964" t="n"/>
+      <c r="R25" s="962" t="n"/>
+      <c r="S25" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="26" s="888">
       <c r="A26" s="891" t="n"/>
-      <c r="B26" s="941" t="n">
+      <c r="B26" s="942" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="942" t="inlineStr">
+      <c r="C26" s="943" t="inlineStr">
         <is>
           <t>2021/04</t>
         </is>
       </c>
-      <c r="D26" s="943" t="inlineStr">
+      <c r="D26" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E26" s="942" t="inlineStr">
+      <c r="E26" s="943" t="inlineStr">
         <is>
           <t>2022/10</t>
         </is>
       </c>
-      <c r="F26" s="944" t="inlineStr">
+      <c r="F26" s="945" t="inlineStr">
         <is>
           <t>■大手携帯ショップの販売端末価格デジタルサイネージアプリケーション開発</t>
         </is>
       </c>
-      <c r="G26" s="945" t="inlineStr">
+      <c r="G26" s="946" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H26" s="946" t="inlineStr">
+      <c r="H26" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css、 kotlin</t>
         </is>
       </c>
-      <c r="I26" s="946" t="inlineStr">
+      <c r="I26" s="947" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J26" s="946" t="inlineStr">
+      <c r="J26" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K26" s="947" t="inlineStr">
+      <c r="K26" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、Bootstrap、Vue.js、Nuxt.js
 アプリ：PWA
@@ -7209,42 +7422,42 @@
 コミュニケーション：Slack、Teams、Zoom、Miro、Jira</t>
         </is>
       </c>
-      <c r="L26" s="948" t="inlineStr">
+      <c r="L26" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M26" s="948" t="inlineStr">
+      <c r="M26" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N26" s="948" t="inlineStr">
+      <c r="N26" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O26" s="948" t="inlineStr">
+      <c r="O26" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P26" s="948" t="inlineStr">
+      <c r="P26" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q26" s="948" t="inlineStr">
+      <c r="Q26" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R26" s="948" t="inlineStr">
+      <c r="R26" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S26" s="949" t="inlineStr">
+      <c r="S26" s="950" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -7252,11 +7465,11 @@
     </row>
     <row customFormat="1" customHeight="1" ht="248" r="27" s="888">
       <c r="A27" s="891" t="n"/>
-      <c r="B27" s="950" t="n"/>
-      <c r="C27" s="951" t="n"/>
-      <c r="D27" s="952" t="n"/>
-      <c r="E27" s="951" t="n"/>
-      <c r="F27" s="953" t="inlineStr">
+      <c r="B27" s="951" t="n"/>
+      <c r="C27" s="952" t="n"/>
+      <c r="D27" s="953" t="n"/>
+      <c r="E27" s="952" t="n"/>
+      <c r="F27" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 大手携帯ショップの販売端末価格デジタルサイネージアプリケーション開発(2021年4月〜2022年10月：19ヶ月)
@@ -7266,96 +7479,96 @@
 フルリモート、スクラム（2週間スプリント）、ペアプロ/モブプロ</t>
         </is>
       </c>
-      <c r="G27" s="954" t="inlineStr">
+      <c r="G27" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PO、SM、デザイナー、エンジニア、QA</t>
         </is>
       </c>
-      <c r="H27" s="952" t="n"/>
-      <c r="I27" s="952" t="n"/>
-      <c r="J27" s="952" t="n"/>
-      <c r="K27" s="955" t="n"/>
-      <c r="L27" s="956" t="n"/>
-      <c r="M27" s="956" t="n"/>
-      <c r="N27" s="956" t="n"/>
-      <c r="O27" s="956" t="n"/>
-      <c r="P27" s="956" t="n"/>
-      <c r="Q27" s="956" t="n"/>
-      <c r="R27" s="956" t="n"/>
-      <c r="S27" s="957" t="n"/>
+      <c r="H27" s="953" t="n"/>
+      <c r="I27" s="953" t="n"/>
+      <c r="J27" s="953" t="n"/>
+      <c r="K27" s="956" t="n"/>
+      <c r="L27" s="957" t="n"/>
+      <c r="M27" s="957" t="n"/>
+      <c r="N27" s="957" t="n"/>
+      <c r="O27" s="957" t="n"/>
+      <c r="P27" s="957" t="n"/>
+      <c r="Q27" s="957" t="n"/>
+      <c r="R27" s="957" t="n"/>
+      <c r="S27" s="958" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="28" s="888">
       <c r="A28" s="891" t="n"/>
-      <c r="B28" s="958" t="n"/>
-      <c r="C28" s="954" t="inlineStr">
+      <c r="B28" s="959" t="n"/>
+      <c r="C28" s="955" t="inlineStr">
         <is>
           <t>19ヶ月</t>
         </is>
       </c>
-      <c r="D28" s="959" t="n"/>
-      <c r="E28" s="960" t="n"/>
-      <c r="F28" s="961" t="n"/>
-      <c r="G28" s="961" t="n"/>
-      <c r="H28" s="961" t="n"/>
-      <c r="I28" s="961" t="n"/>
-      <c r="J28" s="961" t="n"/>
-      <c r="K28" s="962" t="n"/>
-      <c r="L28" s="963" t="n"/>
-      <c r="M28" s="963" t="n"/>
-      <c r="N28" s="963" t="n"/>
-      <c r="O28" s="963" t="n"/>
-      <c r="P28" s="963" t="n"/>
-      <c r="Q28" s="963" t="n"/>
-      <c r="R28" s="963" t="n"/>
-      <c r="S28" s="964" t="n"/>
+      <c r="D28" s="960" t="n"/>
+      <c r="E28" s="961" t="n"/>
+      <c r="F28" s="962" t="n"/>
+      <c r="G28" s="962" t="n"/>
+      <c r="H28" s="962" t="n"/>
+      <c r="I28" s="962" t="n"/>
+      <c r="J28" s="962" t="n"/>
+      <c r="K28" s="963" t="n"/>
+      <c r="L28" s="964" t="n"/>
+      <c r="M28" s="964" t="n"/>
+      <c r="N28" s="964" t="n"/>
+      <c r="O28" s="964" t="n"/>
+      <c r="P28" s="964" t="n"/>
+      <c r="Q28" s="964" t="n"/>
+      <c r="R28" s="964" t="n"/>
+      <c r="S28" s="965" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="29" s="888">
       <c r="A29" s="891" t="n"/>
-      <c r="B29" s="941" t="n">
+      <c r="B29" s="942" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="942" t="inlineStr">
+      <c r="C29" s="943" t="inlineStr">
         <is>
           <t>2020/08</t>
         </is>
       </c>
-      <c r="D29" s="943" t="inlineStr">
+      <c r="D29" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E29" s="942" t="inlineStr">
+      <c r="E29" s="943" t="inlineStr">
         <is>
           <t>2021/01</t>
         </is>
       </c>
-      <c r="F29" s="944" t="inlineStr">
+      <c r="F29" s="945" t="inlineStr">
         <is>
           <t>■医療従事者向けプラットフォーム事業のマイクロサービス開発</t>
         </is>
       </c>
-      <c r="G29" s="945" t="inlineStr">
+      <c r="G29" s="946" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H29" s="946" t="inlineStr">
+      <c r="H29" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、css、TypeScript</t>
         </is>
       </c>
-      <c r="I29" s="946" t="inlineStr">
+      <c r="I29" s="947" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J29" s="946" t="inlineStr">
+      <c r="J29" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K29" s="947" t="inlineStr">
+      <c r="K29" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、React、BULMA
 エディタ/IDE：VSCode
@@ -7363,42 +7576,42 @@
 コミュニケーション：Slack、Zoom</t>
         </is>
       </c>
-      <c r="L29" s="965" t="n"/>
-      <c r="M29" s="948" t="inlineStr">
+      <c r="L29" s="966" t="n"/>
+      <c r="M29" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N29" s="948" t="inlineStr">
+      <c r="N29" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O29" s="948" t="inlineStr">
+      <c r="O29" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P29" s="948" t="inlineStr">
+      <c r="P29" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q29" s="948" t="inlineStr">
+      <c r="Q29" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R29" s="965" t="n"/>
-      <c r="S29" s="966" t="n"/>
+      <c r="R29" s="966" t="n"/>
+      <c r="S29" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="152" r="30" s="888">
       <c r="A30" s="891" t="n"/>
-      <c r="B30" s="950" t="n"/>
-      <c r="C30" s="951" t="n"/>
-      <c r="D30" s="952" t="n"/>
-      <c r="E30" s="951" t="n"/>
-      <c r="F30" s="953" t="inlineStr">
+      <c r="B30" s="951" t="n"/>
+      <c r="C30" s="952" t="n"/>
+      <c r="D30" s="953" t="n"/>
+      <c r="E30" s="952" t="n"/>
+      <c r="F30" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 医療従事者向けプラットフォーム事業のマイクロサービス開発(2020年8月〜2021年1月：６ヶ月)
@@ -7408,96 +7621,96 @@
 フルリモート、issue駆動開発、スクラム（1週間スプリント）</t>
         </is>
       </c>
-      <c r="G30" s="954" t="inlineStr">
+      <c r="G30" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、デザイナー、エンジニア、QA</t>
         </is>
       </c>
-      <c r="H30" s="952" t="n"/>
-      <c r="I30" s="952" t="n"/>
-      <c r="J30" s="952" t="n"/>
-      <c r="K30" s="955" t="n"/>
-      <c r="L30" s="952" t="n"/>
-      <c r="M30" s="956" t="n"/>
-      <c r="N30" s="956" t="n"/>
-      <c r="O30" s="956" t="n"/>
-      <c r="P30" s="956" t="n"/>
-      <c r="Q30" s="956" t="n"/>
-      <c r="R30" s="952" t="n"/>
-      <c r="S30" s="967" t="n"/>
+      <c r="H30" s="953" t="n"/>
+      <c r="I30" s="953" t="n"/>
+      <c r="J30" s="953" t="n"/>
+      <c r="K30" s="956" t="n"/>
+      <c r="L30" s="953" t="n"/>
+      <c r="M30" s="957" t="n"/>
+      <c r="N30" s="957" t="n"/>
+      <c r="O30" s="957" t="n"/>
+      <c r="P30" s="957" t="n"/>
+      <c r="Q30" s="957" t="n"/>
+      <c r="R30" s="953" t="n"/>
+      <c r="S30" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="31" s="888">
       <c r="A31" s="891" t="n"/>
-      <c r="B31" s="958" t="n"/>
-      <c r="C31" s="954" t="inlineStr">
+      <c r="B31" s="959" t="n"/>
+      <c r="C31" s="955" t="inlineStr">
         <is>
           <t>６ヶ月</t>
         </is>
       </c>
-      <c r="D31" s="959" t="n"/>
-      <c r="E31" s="960" t="n"/>
-      <c r="F31" s="961" t="n"/>
-      <c r="G31" s="961" t="n"/>
-      <c r="H31" s="961" t="n"/>
-      <c r="I31" s="961" t="n"/>
-      <c r="J31" s="961" t="n"/>
-      <c r="K31" s="962" t="n"/>
-      <c r="L31" s="961" t="n"/>
-      <c r="M31" s="963" t="n"/>
-      <c r="N31" s="963" t="n"/>
-      <c r="O31" s="963" t="n"/>
-      <c r="P31" s="963" t="n"/>
-      <c r="Q31" s="963" t="n"/>
-      <c r="R31" s="961" t="n"/>
-      <c r="S31" s="968" t="n"/>
+      <c r="D31" s="960" t="n"/>
+      <c r="E31" s="961" t="n"/>
+      <c r="F31" s="962" t="n"/>
+      <c r="G31" s="962" t="n"/>
+      <c r="H31" s="962" t="n"/>
+      <c r="I31" s="962" t="n"/>
+      <c r="J31" s="962" t="n"/>
+      <c r="K31" s="963" t="n"/>
+      <c r="L31" s="962" t="n"/>
+      <c r="M31" s="964" t="n"/>
+      <c r="N31" s="964" t="n"/>
+      <c r="O31" s="964" t="n"/>
+      <c r="P31" s="964" t="n"/>
+      <c r="Q31" s="964" t="n"/>
+      <c r="R31" s="962" t="n"/>
+      <c r="S31" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="32" s="888">
       <c r="A32" s="891" t="n"/>
-      <c r="B32" s="941" t="n">
+      <c r="B32" s="942" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="942" t="inlineStr">
+      <c r="C32" s="943" t="inlineStr">
         <is>
           <t>2018/05</t>
         </is>
       </c>
-      <c r="D32" s="943" t="inlineStr">
+      <c r="D32" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E32" s="942" t="inlineStr">
+      <c r="E32" s="943" t="inlineStr">
         <is>
           <t>2020/06</t>
         </is>
       </c>
-      <c r="F32" s="944" t="inlineStr">
+      <c r="F32" s="945" t="inlineStr">
         <is>
           <t>■自動車会社向けIoTシステムの新規事業開発</t>
         </is>
       </c>
-      <c r="G32" s="945" t="inlineStr">
+      <c r="G32" s="946" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H32" s="946" t="inlineStr">
+      <c r="H32" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css、Python</t>
         </is>
       </c>
-      <c r="I32" s="946" t="inlineStr">
+      <c r="I32" s="947" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J32" s="946" t="inlineStr">
+      <c r="J32" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K32" s="947" t="inlineStr">
+      <c r="K32" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec、Bootstrap
 エディタ/IDE：VSCode
@@ -7505,42 +7718,42 @@
 コミュニケーション：Slack、Zoom、Miro</t>
         </is>
       </c>
-      <c r="L32" s="948" t="inlineStr">
+      <c r="L32" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="M32" s="948" t="inlineStr">
+      <c r="M32" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N32" s="948" t="inlineStr">
+      <c r="N32" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O32" s="948" t="inlineStr">
+      <c r="O32" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P32" s="948" t="inlineStr">
+      <c r="P32" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q32" s="948" t="inlineStr">
+      <c r="Q32" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R32" s="948" t="inlineStr">
+      <c r="R32" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S32" s="949" t="inlineStr">
+      <c r="S32" s="950" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -7548,11 +7761,11 @@
     </row>
     <row customFormat="1" customHeight="1" ht="200" r="33" s="888">
       <c r="A33" s="891" t="n"/>
-      <c r="B33" s="950" t="n"/>
-      <c r="C33" s="951" t="n"/>
-      <c r="D33" s="952" t="n"/>
-      <c r="E33" s="951" t="n"/>
-      <c r="F33" s="953" t="inlineStr">
+      <c r="B33" s="951" t="n"/>
+      <c r="C33" s="952" t="n"/>
+      <c r="D33" s="953" t="n"/>
+      <c r="E33" s="952" t="n"/>
+      <c r="F33" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 自動車会社向けIoTシステムの新規事業開発(2018年5月〜2020年6月：26ヶ月)
@@ -7562,130 +7775,130 @@
 スクラム（1週間スプリント）、ペアプロ/モブプロ</t>
         </is>
       </c>
-      <c r="G33" s="954" t="inlineStr">
+      <c r="G33" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PO、SM、エンジニア</t>
         </is>
       </c>
-      <c r="H33" s="952" t="n"/>
-      <c r="I33" s="952" t="n"/>
-      <c r="J33" s="952" t="n"/>
-      <c r="K33" s="955" t="n"/>
-      <c r="L33" s="956" t="n"/>
-      <c r="M33" s="956" t="n"/>
-      <c r="N33" s="956" t="n"/>
-      <c r="O33" s="956" t="n"/>
-      <c r="P33" s="956" t="n"/>
-      <c r="Q33" s="956" t="n"/>
-      <c r="R33" s="956" t="n"/>
-      <c r="S33" s="957" t="n"/>
+      <c r="H33" s="953" t="n"/>
+      <c r="I33" s="953" t="n"/>
+      <c r="J33" s="953" t="n"/>
+      <c r="K33" s="956" t="n"/>
+      <c r="L33" s="957" t="n"/>
+      <c r="M33" s="957" t="n"/>
+      <c r="N33" s="957" t="n"/>
+      <c r="O33" s="957" t="n"/>
+      <c r="P33" s="957" t="n"/>
+      <c r="Q33" s="957" t="n"/>
+      <c r="R33" s="957" t="n"/>
+      <c r="S33" s="958" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="34" s="888">
       <c r="A34" s="891" t="n"/>
-      <c r="B34" s="958" t="n"/>
-      <c r="C34" s="954" t="inlineStr">
+      <c r="B34" s="959" t="n"/>
+      <c r="C34" s="955" t="inlineStr">
         <is>
           <t>26ヶ月</t>
         </is>
       </c>
-      <c r="D34" s="959" t="n"/>
-      <c r="E34" s="960" t="n"/>
-      <c r="F34" s="961" t="n"/>
-      <c r="G34" s="961" t="n"/>
-      <c r="H34" s="961" t="n"/>
-      <c r="I34" s="961" t="n"/>
-      <c r="J34" s="961" t="n"/>
-      <c r="K34" s="962" t="n"/>
-      <c r="L34" s="963" t="n"/>
-      <c r="M34" s="963" t="n"/>
-      <c r="N34" s="963" t="n"/>
-      <c r="O34" s="963" t="n"/>
-      <c r="P34" s="963" t="n"/>
-      <c r="Q34" s="963" t="n"/>
-      <c r="R34" s="963" t="n"/>
-      <c r="S34" s="964" t="n"/>
+      <c r="D34" s="960" t="n"/>
+      <c r="E34" s="961" t="n"/>
+      <c r="F34" s="962" t="n"/>
+      <c r="G34" s="962" t="n"/>
+      <c r="H34" s="962" t="n"/>
+      <c r="I34" s="962" t="n"/>
+      <c r="J34" s="962" t="n"/>
+      <c r="K34" s="963" t="n"/>
+      <c r="L34" s="964" t="n"/>
+      <c r="M34" s="964" t="n"/>
+      <c r="N34" s="964" t="n"/>
+      <c r="O34" s="964" t="n"/>
+      <c r="P34" s="964" t="n"/>
+      <c r="Q34" s="964" t="n"/>
+      <c r="R34" s="964" t="n"/>
+      <c r="S34" s="965" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="35" s="888">
       <c r="A35" s="891" t="n"/>
-      <c r="B35" s="941" t="n">
+      <c r="B35" s="942" t="n">
         <v>8</v>
       </c>
-      <c r="C35" s="942" t="inlineStr">
+      <c r="C35" s="943" t="inlineStr">
         <is>
           <t>2017/10</t>
         </is>
       </c>
-      <c r="D35" s="943" t="inlineStr">
+      <c r="D35" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E35" s="942" t="inlineStr">
+      <c r="E35" s="943" t="inlineStr">
         <is>
           <t>2018/04</t>
         </is>
       </c>
-      <c r="F35" s="944" t="inlineStr">
+      <c r="F35" s="945" t="inlineStr">
         <is>
           <t>■航空会社向けECサイト開発</t>
         </is>
       </c>
-      <c r="G35" s="945" t="inlineStr">
+      <c r="G35" s="946" t="inlineStr">
         <is>
           <t>システムエンジニア</t>
         </is>
       </c>
-      <c r="H35" s="946" t="inlineStr">
+      <c r="H35" s="947" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I35" s="946" t="inlineStr">
+      <c r="I35" s="947" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J35" s="946" t="inlineStr"/>
-      <c r="K35" s="947" t="inlineStr">
+      <c r="J35" s="947" t="inlineStr"/>
+      <c r="K35" s="948" t="inlineStr">
         <is>
           <t>エディタ/IDE：Eclipse
 その他：Slack、Redmine、svn
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L35" s="965" t="n"/>
-      <c r="M35" s="965" t="n"/>
-      <c r="N35" s="948" t="inlineStr">
+      <c r="L35" s="966" t="n"/>
+      <c r="M35" s="966" t="n"/>
+      <c r="N35" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O35" s="948" t="inlineStr">
+      <c r="O35" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P35" s="948" t="inlineStr">
+      <c r="P35" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q35" s="948" t="inlineStr">
+      <c r="Q35" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R35" s="965" t="n"/>
-      <c r="S35" s="966" t="n"/>
+      <c r="R35" s="966" t="n"/>
+      <c r="S35" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="113" r="36" s="888">
       <c r="A36" s="891" t="n"/>
-      <c r="B36" s="950" t="n"/>
-      <c r="C36" s="951" t="n"/>
-      <c r="D36" s="952" t="n"/>
-      <c r="E36" s="951" t="n"/>
-      <c r="F36" s="953" t="inlineStr">
+      <c r="B36" s="951" t="n"/>
+      <c r="C36" s="952" t="n"/>
+      <c r="D36" s="953" t="n"/>
+      <c r="E36" s="952" t="n"/>
+      <c r="F36" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 航空会社向けECサイト開発(2017年10月〜2018年4月：7ヶ月)
@@ -7695,130 +7908,130 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G36" s="954" t="inlineStr">
+      <c r="G36" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア、テスター</t>
         </is>
       </c>
-      <c r="H36" s="952" t="n"/>
-      <c r="I36" s="952" t="n"/>
-      <c r="J36" s="952" t="n"/>
-      <c r="K36" s="955" t="n"/>
-      <c r="L36" s="952" t="n"/>
-      <c r="M36" s="952" t="n"/>
-      <c r="N36" s="956" t="n"/>
-      <c r="O36" s="956" t="n"/>
-      <c r="P36" s="956" t="n"/>
-      <c r="Q36" s="956" t="n"/>
-      <c r="R36" s="952" t="n"/>
-      <c r="S36" s="967" t="n"/>
+      <c r="H36" s="953" t="n"/>
+      <c r="I36" s="953" t="n"/>
+      <c r="J36" s="953" t="n"/>
+      <c r="K36" s="956" t="n"/>
+      <c r="L36" s="953" t="n"/>
+      <c r="M36" s="953" t="n"/>
+      <c r="N36" s="957" t="n"/>
+      <c r="O36" s="957" t="n"/>
+      <c r="P36" s="957" t="n"/>
+      <c r="Q36" s="957" t="n"/>
+      <c r="R36" s="953" t="n"/>
+      <c r="S36" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="37" s="888">
       <c r="A37" s="891" t="n"/>
-      <c r="B37" s="958" t="n"/>
-      <c r="C37" s="954" t="inlineStr">
+      <c r="B37" s="959" t="n"/>
+      <c r="C37" s="955" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
       </c>
-      <c r="D37" s="959" t="n"/>
-      <c r="E37" s="960" t="n"/>
-      <c r="F37" s="961" t="n"/>
-      <c r="G37" s="961" t="n"/>
-      <c r="H37" s="961" t="n"/>
-      <c r="I37" s="961" t="n"/>
-      <c r="J37" s="961" t="n"/>
-      <c r="K37" s="962" t="n"/>
-      <c r="L37" s="961" t="n"/>
-      <c r="M37" s="961" t="n"/>
-      <c r="N37" s="963" t="n"/>
-      <c r="O37" s="963" t="n"/>
-      <c r="P37" s="963" t="n"/>
-      <c r="Q37" s="963" t="n"/>
-      <c r="R37" s="961" t="n"/>
-      <c r="S37" s="968" t="n"/>
+      <c r="D37" s="960" t="n"/>
+      <c r="E37" s="961" t="n"/>
+      <c r="F37" s="962" t="n"/>
+      <c r="G37" s="962" t="n"/>
+      <c r="H37" s="962" t="n"/>
+      <c r="I37" s="962" t="n"/>
+      <c r="J37" s="962" t="n"/>
+      <c r="K37" s="963" t="n"/>
+      <c r="L37" s="962" t="n"/>
+      <c r="M37" s="962" t="n"/>
+      <c r="N37" s="964" t="n"/>
+      <c r="O37" s="964" t="n"/>
+      <c r="P37" s="964" t="n"/>
+      <c r="Q37" s="964" t="n"/>
+      <c r="R37" s="962" t="n"/>
+      <c r="S37" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="38" s="888">
       <c r="A38" s="891" t="n"/>
-      <c r="B38" s="941" t="n">
+      <c r="B38" s="942" t="n">
         <v>9</v>
       </c>
-      <c r="C38" s="942" t="inlineStr">
+      <c r="C38" s="943" t="inlineStr">
         <is>
           <t>2016/08</t>
         </is>
       </c>
-      <c r="D38" s="943" t="inlineStr">
+      <c r="D38" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E38" s="942" t="inlineStr">
+      <c r="E38" s="943" t="inlineStr">
         <is>
           <t>2017/09</t>
         </is>
       </c>
-      <c r="F38" s="944" t="inlineStr">
+      <c r="F38" s="945" t="inlineStr">
         <is>
           <t>■全自動倉庫管理システム開発</t>
         </is>
       </c>
-      <c r="G38" s="945" t="inlineStr">
+      <c r="G38" s="946" t="inlineStr">
         <is>
           <t>システムエンジニア</t>
         </is>
       </c>
-      <c r="H38" s="946" t="inlineStr">
+      <c r="H38" s="947" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I38" s="946" t="inlineStr">
+      <c r="I38" s="947" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J38" s="946" t="inlineStr"/>
-      <c r="K38" s="947" t="inlineStr">
+      <c r="J38" s="947" t="inlineStr"/>
+      <c r="K38" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Spring
 エディタ/IDE：Eclipse
 その他：Redmine、svn</t>
         </is>
       </c>
-      <c r="L38" s="965" t="n"/>
-      <c r="M38" s="965" t="n"/>
-      <c r="N38" s="948" t="inlineStr">
+      <c r="L38" s="966" t="n"/>
+      <c r="M38" s="966" t="n"/>
+      <c r="N38" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O38" s="948" t="inlineStr">
+      <c r="O38" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P38" s="948" t="inlineStr">
+      <c r="P38" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q38" s="948" t="inlineStr">
+      <c r="Q38" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R38" s="965" t="n"/>
-      <c r="S38" s="966" t="n"/>
+      <c r="R38" s="966" t="n"/>
+      <c r="S38" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="113" r="39" s="888">
       <c r="A39" s="891" t="n"/>
-      <c r="B39" s="950" t="n"/>
-      <c r="C39" s="951" t="n"/>
-      <c r="D39" s="952" t="n"/>
-      <c r="E39" s="951" t="n"/>
-      <c r="F39" s="953" t="inlineStr">
+      <c r="B39" s="951" t="n"/>
+      <c r="C39" s="952" t="n"/>
+      <c r="D39" s="953" t="n"/>
+      <c r="E39" s="952" t="n"/>
+      <c r="F39" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 全自動倉庫管理システム開発(2016年8月〜2017年9月：14ヶ月)
@@ -7828,129 +8041,129 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G39" s="954" t="inlineStr">
+      <c r="G39" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、リーダー、エンジニア</t>
         </is>
       </c>
-      <c r="H39" s="952" t="n"/>
-      <c r="I39" s="952" t="n"/>
-      <c r="J39" s="952" t="n"/>
-      <c r="K39" s="955" t="n"/>
-      <c r="L39" s="952" t="n"/>
-      <c r="M39" s="952" t="n"/>
-      <c r="N39" s="956" t="n"/>
-      <c r="O39" s="956" t="n"/>
-      <c r="P39" s="956" t="n"/>
-      <c r="Q39" s="956" t="n"/>
-      <c r="R39" s="952" t="n"/>
-      <c r="S39" s="967" t="n"/>
+      <c r="H39" s="953" t="n"/>
+      <c r="I39" s="953" t="n"/>
+      <c r="J39" s="953" t="n"/>
+      <c r="K39" s="956" t="n"/>
+      <c r="L39" s="953" t="n"/>
+      <c r="M39" s="953" t="n"/>
+      <c r="N39" s="957" t="n"/>
+      <c r="O39" s="957" t="n"/>
+      <c r="P39" s="957" t="n"/>
+      <c r="Q39" s="957" t="n"/>
+      <c r="R39" s="953" t="n"/>
+      <c r="S39" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="40" s="888">
       <c r="A40" s="891" t="n"/>
-      <c r="B40" s="958" t="n"/>
-      <c r="C40" s="954" t="inlineStr">
+      <c r="B40" s="959" t="n"/>
+      <c r="C40" s="955" t="inlineStr">
         <is>
           <t>14ヶ月</t>
         </is>
       </c>
-      <c r="D40" s="959" t="n"/>
-      <c r="E40" s="960" t="n"/>
-      <c r="F40" s="961" t="n"/>
-      <c r="G40" s="961" t="n"/>
-      <c r="H40" s="961" t="n"/>
-      <c r="I40" s="961" t="n"/>
-      <c r="J40" s="961" t="n"/>
-      <c r="K40" s="962" t="n"/>
-      <c r="L40" s="961" t="n"/>
-      <c r="M40" s="961" t="n"/>
-      <c r="N40" s="963" t="n"/>
-      <c r="O40" s="963" t="n"/>
-      <c r="P40" s="963" t="n"/>
-      <c r="Q40" s="963" t="n"/>
-      <c r="R40" s="961" t="n"/>
-      <c r="S40" s="968" t="n"/>
+      <c r="D40" s="960" t="n"/>
+      <c r="E40" s="961" t="n"/>
+      <c r="F40" s="962" t="n"/>
+      <c r="G40" s="962" t="n"/>
+      <c r="H40" s="962" t="n"/>
+      <c r="I40" s="962" t="n"/>
+      <c r="J40" s="962" t="n"/>
+      <c r="K40" s="963" t="n"/>
+      <c r="L40" s="962" t="n"/>
+      <c r="M40" s="962" t="n"/>
+      <c r="N40" s="964" t="n"/>
+      <c r="O40" s="964" t="n"/>
+      <c r="P40" s="964" t="n"/>
+      <c r="Q40" s="964" t="n"/>
+      <c r="R40" s="962" t="n"/>
+      <c r="S40" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="57" r="41" s="888">
       <c r="A41" s="891" t="n"/>
-      <c r="B41" s="941" t="n">
+      <c r="B41" s="942" t="n">
         <v>10</v>
       </c>
-      <c r="C41" s="942" t="inlineStr">
+      <c r="C41" s="943" t="inlineStr">
         <is>
           <t>2013/09</t>
         </is>
       </c>
-      <c r="D41" s="943" t="inlineStr">
+      <c r="D41" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E41" s="942" t="inlineStr">
+      <c r="E41" s="943" t="inlineStr">
         <is>
           <t>2016/08</t>
         </is>
       </c>
-      <c r="F41" s="944" t="inlineStr">
+      <c r="F41" s="945" t="inlineStr">
         <is>
           <t>■製油所向けオフサイトシステム</t>
         </is>
       </c>
-      <c r="G41" s="945" t="inlineStr">
+      <c r="G41" s="946" t="inlineStr">
         <is>
           <t>プログラマー、システムエンジニア</t>
         </is>
       </c>
-      <c r="H41" s="946" t="inlineStr">
+      <c r="H41" s="947" t="inlineStr">
         <is>
           <t>Java、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I41" s="946" t="inlineStr">
+      <c r="I41" s="947" t="inlineStr">
         <is>
           <t>Oracle</t>
         </is>
       </c>
-      <c r="J41" s="946" t="inlineStr"/>
-      <c r="K41" s="947" t="inlineStr">
+      <c r="J41" s="947" t="inlineStr"/>
+      <c r="K41" s="948" t="inlineStr">
         <is>
           <t>エディタ/IDE：Eclipse
 その他：svn</t>
         </is>
       </c>
-      <c r="L41" s="965" t="n"/>
-      <c r="M41" s="948" t="inlineStr">
+      <c r="L41" s="966" t="n"/>
+      <c r="M41" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="N41" s="948" t="inlineStr">
+      <c r="N41" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="O41" s="948" t="inlineStr">
+      <c r="O41" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P41" s="948" t="inlineStr">
+      <c r="P41" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q41" s="948" t="inlineStr">
+      <c r="Q41" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="R41" s="948" t="inlineStr">
+      <c r="R41" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="S41" s="949" t="inlineStr">
+      <c r="S41" s="950" t="inlineStr">
         <is>
           <t>●</t>
         </is>
@@ -7958,11 +8171,11 @@
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="42" s="888">
       <c r="A42" s="891" t="n"/>
-      <c r="B42" s="950" t="n"/>
-      <c r="C42" s="951" t="n"/>
-      <c r="D42" s="952" t="n"/>
-      <c r="E42" s="951" t="n"/>
-      <c r="F42" s="953" t="inlineStr">
+      <c r="B42" s="951" t="n"/>
+      <c r="C42" s="952" t="n"/>
+      <c r="D42" s="953" t="n"/>
+      <c r="E42" s="952" t="n"/>
+      <c r="F42" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 製油所向けオフサイトシステム(2013年9月〜2016年8月：36ヶ月)
@@ -7972,121 +8185,121 @@
 ウォーターフォール</t>
         </is>
       </c>
-      <c r="G42" s="954" t="inlineStr">
+      <c r="G42" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、リーダー、エンジニア</t>
         </is>
       </c>
-      <c r="H42" s="952" t="n"/>
-      <c r="I42" s="952" t="n"/>
-      <c r="J42" s="952" t="n"/>
-      <c r="K42" s="955" t="n"/>
-      <c r="L42" s="952" t="n"/>
-      <c r="M42" s="956" t="n"/>
-      <c r="N42" s="956" t="n"/>
-      <c r="O42" s="956" t="n"/>
-      <c r="P42" s="956" t="n"/>
-      <c r="Q42" s="956" t="n"/>
-      <c r="R42" s="956" t="n"/>
-      <c r="S42" s="957" t="n"/>
+      <c r="H42" s="953" t="n"/>
+      <c r="I42" s="953" t="n"/>
+      <c r="J42" s="953" t="n"/>
+      <c r="K42" s="956" t="n"/>
+      <c r="L42" s="953" t="n"/>
+      <c r="M42" s="957" t="n"/>
+      <c r="N42" s="957" t="n"/>
+      <c r="O42" s="957" t="n"/>
+      <c r="P42" s="957" t="n"/>
+      <c r="Q42" s="957" t="n"/>
+      <c r="R42" s="957" t="n"/>
+      <c r="S42" s="958" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="43" s="888">
       <c r="A43" s="891" t="n"/>
-      <c r="B43" s="958" t="n"/>
-      <c r="C43" s="954" t="inlineStr">
+      <c r="B43" s="959" t="n"/>
+      <c r="C43" s="955" t="inlineStr">
         <is>
           <t>36ヶ月</t>
         </is>
       </c>
-      <c r="D43" s="959" t="n"/>
-      <c r="E43" s="960" t="n"/>
-      <c r="F43" s="961" t="n"/>
-      <c r="G43" s="961" t="n"/>
-      <c r="H43" s="961" t="n"/>
-      <c r="I43" s="961" t="n"/>
-      <c r="J43" s="961" t="n"/>
-      <c r="K43" s="962" t="n"/>
-      <c r="L43" s="961" t="n"/>
-      <c r="M43" s="963" t="n"/>
-      <c r="N43" s="963" t="n"/>
-      <c r="O43" s="963" t="n"/>
-      <c r="P43" s="963" t="n"/>
-      <c r="Q43" s="963" t="n"/>
-      <c r="R43" s="963" t="n"/>
-      <c r="S43" s="964" t="n"/>
+      <c r="D43" s="960" t="n"/>
+      <c r="E43" s="961" t="n"/>
+      <c r="F43" s="962" t="n"/>
+      <c r="G43" s="962" t="n"/>
+      <c r="H43" s="962" t="n"/>
+      <c r="I43" s="962" t="n"/>
+      <c r="J43" s="962" t="n"/>
+      <c r="K43" s="963" t="n"/>
+      <c r="L43" s="962" t="n"/>
+      <c r="M43" s="964" t="n"/>
+      <c r="N43" s="964" t="n"/>
+      <c r="O43" s="964" t="n"/>
+      <c r="P43" s="964" t="n"/>
+      <c r="Q43" s="964" t="n"/>
+      <c r="R43" s="964" t="n"/>
+      <c r="S43" s="965" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="28" r="44" s="888">
       <c r="A44" s="891" t="n"/>
-      <c r="B44" s="969" t="inlineStr">
+      <c r="B44" s="970" t="inlineStr">
         <is>
           <t>副業案件</t>
         </is>
       </c>
-      <c r="C44" s="970" t="n"/>
-      <c r="D44" s="970" t="n"/>
-      <c r="E44" s="970" t="n"/>
-      <c r="F44" s="970" t="n"/>
-      <c r="G44" s="970" t="n"/>
-      <c r="H44" s="970" t="n"/>
-      <c r="I44" s="970" t="n"/>
-      <c r="J44" s="970" t="n"/>
-      <c r="K44" s="970" t="n"/>
-      <c r="L44" s="970" t="n"/>
-      <c r="M44" s="970" t="n"/>
-      <c r="N44" s="970" t="n"/>
-      <c r="O44" s="970" t="n"/>
-      <c r="P44" s="970" t="n"/>
-      <c r="Q44" s="970" t="n"/>
-      <c r="R44" s="970" t="n"/>
-      <c r="S44" s="971" t="n"/>
+      <c r="C44" s="971" t="n"/>
+      <c r="D44" s="971" t="n"/>
+      <c r="E44" s="971" t="n"/>
+      <c r="F44" s="971" t="n"/>
+      <c r="G44" s="971" t="n"/>
+      <c r="H44" s="971" t="n"/>
+      <c r="I44" s="971" t="n"/>
+      <c r="J44" s="971" t="n"/>
+      <c r="K44" s="971" t="n"/>
+      <c r="L44" s="971" t="n"/>
+      <c r="M44" s="971" t="n"/>
+      <c r="N44" s="971" t="n"/>
+      <c r="O44" s="971" t="n"/>
+      <c r="P44" s="971" t="n"/>
+      <c r="Q44" s="971" t="n"/>
+      <c r="R44" s="971" t="n"/>
+      <c r="S44" s="972" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="45" s="888">
       <c r="A45" s="891" t="n"/>
-      <c r="B45" s="941" t="n">
+      <c r="B45" s="942" t="n">
         <v>11</v>
       </c>
-      <c r="C45" s="942" t="inlineStr">
+      <c r="C45" s="943" t="inlineStr">
         <is>
           <t>2025/08</t>
         </is>
       </c>
-      <c r="D45" s="943" t="inlineStr">
+      <c r="D45" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E45" s="942" t="inlineStr">
+      <c r="E45" s="943" t="inlineStr">
         <is>
           <t>2026/06</t>
         </is>
       </c>
-      <c r="F45" s="944" t="inlineStr">
+      <c r="F45" s="945" t="inlineStr">
         <is>
           <t>■富裕層向けの旅行代事業のCRM新規開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G45" s="945" t="inlineStr">
+      <c r="G45" s="946" t="inlineStr">
         <is>
           <t>フルスタックエンジニア</t>
         </is>
       </c>
-      <c r="H45" s="946" t="inlineStr">
+      <c r="H45" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、TypeScript</t>
         </is>
       </c>
-      <c r="I45" s="946" t="inlineStr">
+      <c r="I45" s="947" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J45" s="946" t="inlineStr">
+      <c r="J45" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K45" s="947" t="inlineStr">
+      <c r="K45" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Next.js
 エディタ/IDE：Cursor
@@ -8095,30 +8308,30 @@
 コミュニケーション：Slack、Notion</t>
         </is>
       </c>
-      <c r="L45" s="965" t="n"/>
-      <c r="M45" s="965" t="n"/>
-      <c r="N45" s="965" t="n"/>
-      <c r="O45" s="948" t="inlineStr">
+      <c r="L45" s="966" t="n"/>
+      <c r="M45" s="966" t="n"/>
+      <c r="N45" s="966" t="n"/>
+      <c r="O45" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P45" s="948" t="inlineStr">
+      <c r="P45" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q45" s="965" t="n"/>
-      <c r="R45" s="965" t="n"/>
-      <c r="S45" s="966" t="n"/>
+      <c r="Q45" s="966" t="n"/>
+      <c r="R45" s="966" t="n"/>
+      <c r="S45" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="152" r="46" s="888">
       <c r="A46" s="891" t="n"/>
-      <c r="B46" s="950" t="n"/>
-      <c r="C46" s="951" t="n"/>
-      <c r="D46" s="952" t="n"/>
-      <c r="E46" s="951" t="n"/>
-      <c r="F46" s="953" t="inlineStr">
+      <c r="B46" s="951" t="n"/>
+      <c r="C46" s="952" t="n"/>
+      <c r="D46" s="953" t="n"/>
+      <c r="E46" s="952" t="n"/>
+      <c r="F46" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 富裕層向けの旅行代事業のCRM新規開発(2025年8月〜2026年6月：11ヶ月） ＜副業＞
@@ -8128,92 +8341,92 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G46" s="954" t="inlineStr">
+      <c r="G46" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア、デザイナー</t>
         </is>
       </c>
-      <c r="H46" s="952" t="n"/>
-      <c r="I46" s="952" t="n"/>
-      <c r="J46" s="952" t="n"/>
-      <c r="K46" s="955" t="n"/>
-      <c r="L46" s="952" t="n"/>
-      <c r="M46" s="952" t="n"/>
-      <c r="N46" s="952" t="n"/>
-      <c r="O46" s="956" t="n"/>
-      <c r="P46" s="956" t="n"/>
-      <c r="Q46" s="952" t="n"/>
-      <c r="R46" s="952" t="n"/>
-      <c r="S46" s="967" t="n"/>
+      <c r="H46" s="953" t="n"/>
+      <c r="I46" s="953" t="n"/>
+      <c r="J46" s="953" t="n"/>
+      <c r="K46" s="956" t="n"/>
+      <c r="L46" s="953" t="n"/>
+      <c r="M46" s="953" t="n"/>
+      <c r="N46" s="953" t="n"/>
+      <c r="O46" s="957" t="n"/>
+      <c r="P46" s="957" t="n"/>
+      <c r="Q46" s="953" t="n"/>
+      <c r="R46" s="953" t="n"/>
+      <c r="S46" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="47" s="888">
       <c r="A47" s="891" t="n"/>
-      <c r="B47" s="958" t="n"/>
-      <c r="C47" s="954" t="inlineStr">
+      <c r="B47" s="959" t="n"/>
+      <c r="C47" s="955" t="inlineStr">
         <is>
           <t>11ヶ月</t>
         </is>
       </c>
-      <c r="D47" s="959" t="n"/>
-      <c r="E47" s="960" t="n"/>
-      <c r="F47" s="961" t="n"/>
-      <c r="G47" s="961" t="n"/>
-      <c r="H47" s="961" t="n"/>
-      <c r="I47" s="961" t="n"/>
-      <c r="J47" s="961" t="n"/>
-      <c r="K47" s="962" t="n"/>
-      <c r="L47" s="961" t="n"/>
-      <c r="M47" s="961" t="n"/>
-      <c r="N47" s="961" t="n"/>
-      <c r="O47" s="963" t="n"/>
-      <c r="P47" s="963" t="n"/>
-      <c r="Q47" s="961" t="n"/>
-      <c r="R47" s="961" t="n"/>
-      <c r="S47" s="968" t="n"/>
+      <c r="D47" s="960" t="n"/>
+      <c r="E47" s="961" t="n"/>
+      <c r="F47" s="962" t="n"/>
+      <c r="G47" s="962" t="n"/>
+      <c r="H47" s="962" t="n"/>
+      <c r="I47" s="962" t="n"/>
+      <c r="J47" s="962" t="n"/>
+      <c r="K47" s="963" t="n"/>
+      <c r="L47" s="962" t="n"/>
+      <c r="M47" s="962" t="n"/>
+      <c r="N47" s="962" t="n"/>
+      <c r="O47" s="964" t="n"/>
+      <c r="P47" s="964" t="n"/>
+      <c r="Q47" s="962" t="n"/>
+      <c r="R47" s="962" t="n"/>
+      <c r="S47" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="48" s="888">
       <c r="A48" s="891" t="n"/>
-      <c r="B48" s="941" t="n">
+      <c r="B48" s="942" t="n">
         <v>12</v>
       </c>
-      <c r="C48" s="942" t="inlineStr">
+      <c r="C48" s="943" t="inlineStr">
         <is>
           <t>2025/03</t>
         </is>
       </c>
-      <c r="D48" s="943" t="inlineStr">
+      <c r="D48" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E48" s="942" t="inlineStr">
+      <c r="E48" s="943" t="inlineStr">
         <is>
           <t>2025/07</t>
         </is>
       </c>
-      <c r="F48" s="944" t="inlineStr">
+      <c r="F48" s="945" t="inlineStr">
         <is>
           <t>■パスキー認証システムの管理サービス開発＜副業＞</t>
         </is>
       </c>
-      <c r="G48" s="945" t="inlineStr">
+      <c r="G48" s="946" t="inlineStr">
         <is>
           <t>エンジニア</t>
         </is>
       </c>
-      <c r="H48" s="946" t="inlineStr">
+      <c r="H48" s="947" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I48" s="946" t="inlineStr">
+      <c r="I48" s="947" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J48" s="946" t="inlineStr"/>
-      <c r="K48" s="947" t="inlineStr">
+      <c r="J48" s="947" t="inlineStr"/>
+      <c r="K48" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails
 エディタ/IDE：Cursor
@@ -8222,30 +8435,30 @@
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L48" s="965" t="n"/>
-      <c r="M48" s="965" t="n"/>
-      <c r="N48" s="965" t="n"/>
-      <c r="O48" s="948" t="inlineStr">
+      <c r="L48" s="966" t="n"/>
+      <c r="M48" s="966" t="n"/>
+      <c r="N48" s="966" t="n"/>
+      <c r="O48" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P48" s="948" t="inlineStr">
+      <c r="P48" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q48" s="965" t="n"/>
-      <c r="R48" s="965" t="n"/>
-      <c r="S48" s="966" t="n"/>
+      <c r="Q48" s="966" t="n"/>
+      <c r="R48" s="966" t="n"/>
+      <c r="S48" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="136" r="49" s="888">
       <c r="A49" s="891" t="n"/>
-      <c r="B49" s="950" t="n"/>
-      <c r="C49" s="951" t="n"/>
-      <c r="D49" s="952" t="n"/>
-      <c r="E49" s="951" t="n"/>
-      <c r="F49" s="953" t="inlineStr">
+      <c r="B49" s="951" t="n"/>
+      <c r="C49" s="952" t="n"/>
+      <c r="D49" s="953" t="n"/>
+      <c r="E49" s="952" t="n"/>
+      <c r="F49" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 パスキー認証システムの管理サービス開発(2025年3月〜2025年7月：5ヶ月）＜副業＞
@@ -8255,92 +8468,92 @@
 フルリモート</t>
         </is>
       </c>
-      <c r="G49" s="954" t="inlineStr">
+      <c r="G49" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H49" s="952" t="n"/>
-      <c r="I49" s="952" t="n"/>
-      <c r="J49" s="952" t="n"/>
-      <c r="K49" s="955" t="n"/>
-      <c r="L49" s="952" t="n"/>
-      <c r="M49" s="952" t="n"/>
-      <c r="N49" s="952" t="n"/>
-      <c r="O49" s="956" t="n"/>
-      <c r="P49" s="956" t="n"/>
-      <c r="Q49" s="952" t="n"/>
-      <c r="R49" s="952" t="n"/>
-      <c r="S49" s="967" t="n"/>
+      <c r="H49" s="953" t="n"/>
+      <c r="I49" s="953" t="n"/>
+      <c r="J49" s="953" t="n"/>
+      <c r="K49" s="956" t="n"/>
+      <c r="L49" s="953" t="n"/>
+      <c r="M49" s="953" t="n"/>
+      <c r="N49" s="953" t="n"/>
+      <c r="O49" s="957" t="n"/>
+      <c r="P49" s="957" t="n"/>
+      <c r="Q49" s="953" t="n"/>
+      <c r="R49" s="953" t="n"/>
+      <c r="S49" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="50" s="888">
       <c r="A50" s="891" t="n"/>
-      <c r="B50" s="958" t="n"/>
-      <c r="C50" s="954" t="inlineStr">
+      <c r="B50" s="959" t="n"/>
+      <c r="C50" s="955" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D50" s="959" t="n"/>
-      <c r="E50" s="960" t="n"/>
-      <c r="F50" s="961" t="n"/>
-      <c r="G50" s="961" t="n"/>
-      <c r="H50" s="961" t="n"/>
-      <c r="I50" s="961" t="n"/>
-      <c r="J50" s="961" t="n"/>
-      <c r="K50" s="962" t="n"/>
-      <c r="L50" s="961" t="n"/>
-      <c r="M50" s="961" t="n"/>
-      <c r="N50" s="961" t="n"/>
-      <c r="O50" s="963" t="n"/>
-      <c r="P50" s="963" t="n"/>
-      <c r="Q50" s="961" t="n"/>
-      <c r="R50" s="961" t="n"/>
-      <c r="S50" s="968" t="n"/>
+      <c r="D50" s="960" t="n"/>
+      <c r="E50" s="961" t="n"/>
+      <c r="F50" s="962" t="n"/>
+      <c r="G50" s="962" t="n"/>
+      <c r="H50" s="962" t="n"/>
+      <c r="I50" s="962" t="n"/>
+      <c r="J50" s="962" t="n"/>
+      <c r="K50" s="963" t="n"/>
+      <c r="L50" s="962" t="n"/>
+      <c r="M50" s="962" t="n"/>
+      <c r="N50" s="962" t="n"/>
+      <c r="O50" s="964" t="n"/>
+      <c r="P50" s="964" t="n"/>
+      <c r="Q50" s="962" t="n"/>
+      <c r="R50" s="962" t="n"/>
+      <c r="S50" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="51" s="888">
       <c r="A51" s="891" t="n"/>
-      <c r="B51" s="941" t="n">
+      <c r="B51" s="942" t="n">
         <v>13</v>
       </c>
-      <c r="C51" s="942" t="inlineStr">
+      <c r="C51" s="943" t="inlineStr">
         <is>
           <t>2022/04</t>
         </is>
       </c>
-      <c r="D51" s="943" t="inlineStr">
+      <c r="D51" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E51" s="942" t="inlineStr">
+      <c r="E51" s="943" t="inlineStr">
         <is>
           <t>2022/08</t>
         </is>
       </c>
-      <c r="F51" s="944" t="inlineStr">
+      <c r="F51" s="945" t="inlineStr">
         <is>
           <t>■セールステック領域SaaSのプロダクト開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G51" s="945" t="inlineStr">
+      <c r="G51" s="946" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H51" s="946" t="inlineStr">
+      <c r="H51" s="947" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I51" s="946" t="inlineStr">
+      <c r="I51" s="947" t="inlineStr">
         <is>
           <t>MySQL</t>
         </is>
       </c>
-      <c r="J51" s="946" t="inlineStr"/>
-      <c r="K51" s="947" t="inlineStr">
+      <c r="J51" s="947" t="inlineStr"/>
+      <c r="K51" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Rspec
 エディタ/IDE：VSCode
@@ -8348,30 +8561,30 @@
 コミュニケーション：Slack、Zoom</t>
         </is>
       </c>
-      <c r="L51" s="965" t="n"/>
-      <c r="M51" s="965" t="n"/>
-      <c r="N51" s="965" t="n"/>
-      <c r="O51" s="948" t="inlineStr">
+      <c r="L51" s="966" t="n"/>
+      <c r="M51" s="966" t="n"/>
+      <c r="N51" s="966" t="n"/>
+      <c r="O51" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P51" s="948" t="inlineStr">
+      <c r="P51" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q51" s="965" t="n"/>
-      <c r="R51" s="965" t="n"/>
-      <c r="S51" s="966" t="n"/>
+      <c r="Q51" s="966" t="n"/>
+      <c r="R51" s="966" t="n"/>
+      <c r="S51" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="52" s="888">
       <c r="A52" s="891" t="n"/>
-      <c r="B52" s="950" t="n"/>
-      <c r="C52" s="951" t="n"/>
-      <c r="D52" s="952" t="n"/>
-      <c r="E52" s="951" t="n"/>
-      <c r="F52" s="953" t="inlineStr">
+      <c r="B52" s="951" t="n"/>
+      <c r="C52" s="952" t="n"/>
+      <c r="D52" s="953" t="n"/>
+      <c r="E52" s="952" t="n"/>
+      <c r="F52" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 セールステック領域SaaSのプロダクト開発(2022年4月〜2022年8月：5ヶ月) ＜副業＞
@@ -8381,92 +8594,92 @@
 フルリモート、チケット駆動開発</t>
         </is>
       </c>
-      <c r="G52" s="954" t="inlineStr">
+      <c r="G52" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H52" s="952" t="n"/>
-      <c r="I52" s="952" t="n"/>
-      <c r="J52" s="952" t="n"/>
-      <c r="K52" s="955" t="n"/>
-      <c r="L52" s="952" t="n"/>
-      <c r="M52" s="952" t="n"/>
-      <c r="N52" s="952" t="n"/>
-      <c r="O52" s="956" t="n"/>
-      <c r="P52" s="956" t="n"/>
-      <c r="Q52" s="952" t="n"/>
-      <c r="R52" s="952" t="n"/>
-      <c r="S52" s="967" t="n"/>
+      <c r="H52" s="953" t="n"/>
+      <c r="I52" s="953" t="n"/>
+      <c r="J52" s="953" t="n"/>
+      <c r="K52" s="956" t="n"/>
+      <c r="L52" s="953" t="n"/>
+      <c r="M52" s="953" t="n"/>
+      <c r="N52" s="953" t="n"/>
+      <c r="O52" s="957" t="n"/>
+      <c r="P52" s="957" t="n"/>
+      <c r="Q52" s="953" t="n"/>
+      <c r="R52" s="953" t="n"/>
+      <c r="S52" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="53" s="888">
       <c r="A53" s="891" t="n"/>
-      <c r="B53" s="958" t="n"/>
-      <c r="C53" s="954" t="inlineStr">
+      <c r="B53" s="959" t="n"/>
+      <c r="C53" s="955" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D53" s="959" t="n"/>
-      <c r="E53" s="960" t="n"/>
-      <c r="F53" s="961" t="n"/>
-      <c r="G53" s="961" t="n"/>
-      <c r="H53" s="961" t="n"/>
-      <c r="I53" s="961" t="n"/>
-      <c r="J53" s="961" t="n"/>
-      <c r="K53" s="962" t="n"/>
-      <c r="L53" s="961" t="n"/>
-      <c r="M53" s="961" t="n"/>
-      <c r="N53" s="961" t="n"/>
-      <c r="O53" s="963" t="n"/>
-      <c r="P53" s="963" t="n"/>
-      <c r="Q53" s="961" t="n"/>
-      <c r="R53" s="961" t="n"/>
-      <c r="S53" s="968" t="n"/>
+      <c r="D53" s="960" t="n"/>
+      <c r="E53" s="961" t="n"/>
+      <c r="F53" s="962" t="n"/>
+      <c r="G53" s="962" t="n"/>
+      <c r="H53" s="962" t="n"/>
+      <c r="I53" s="962" t="n"/>
+      <c r="J53" s="962" t="n"/>
+      <c r="K53" s="963" t="n"/>
+      <c r="L53" s="962" t="n"/>
+      <c r="M53" s="962" t="n"/>
+      <c r="N53" s="962" t="n"/>
+      <c r="O53" s="964" t="n"/>
+      <c r="P53" s="964" t="n"/>
+      <c r="Q53" s="962" t="n"/>
+      <c r="R53" s="962" t="n"/>
+      <c r="S53" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="54" s="888">
       <c r="A54" s="891" t="n"/>
-      <c r="B54" s="941" t="n">
+      <c r="B54" s="942" t="n">
         <v>14</v>
       </c>
-      <c r="C54" s="942" t="inlineStr">
+      <c r="C54" s="943" t="inlineStr">
         <is>
           <t>2020/10</t>
         </is>
       </c>
-      <c r="D54" s="943" t="inlineStr">
+      <c r="D54" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E54" s="942" t="inlineStr">
+      <c r="E54" s="943" t="inlineStr">
         <is>
           <t>2021/01</t>
         </is>
       </c>
-      <c r="F54" s="944" t="inlineStr">
+      <c r="F54" s="945" t="inlineStr">
         <is>
           <t>■営業支援SaaSのプロダクト開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G54" s="945" t="inlineStr">
+      <c r="G54" s="946" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H54" s="946" t="inlineStr">
+      <c r="H54" s="947" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="I54" s="946" t="inlineStr">
+      <c r="I54" s="947" t="inlineStr">
         <is>
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="J54" s="946" t="inlineStr"/>
-      <c r="K54" s="947" t="inlineStr">
+      <c r="J54" s="947" t="inlineStr"/>
+      <c r="K54" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Django、Tailwind CSS
 エディタ/IDE：VSCode
@@ -8474,30 +8687,30 @@
 コミュニケーション：Slack、trello</t>
         </is>
       </c>
-      <c r="L54" s="965" t="n"/>
-      <c r="M54" s="965" t="n"/>
-      <c r="N54" s="965" t="n"/>
-      <c r="O54" s="948" t="inlineStr">
+      <c r="L54" s="966" t="n"/>
+      <c r="M54" s="966" t="n"/>
+      <c r="N54" s="966" t="n"/>
+      <c r="O54" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P54" s="948" t="inlineStr">
+      <c r="P54" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q54" s="965" t="n"/>
-      <c r="R54" s="965" t="n"/>
-      <c r="S54" s="966" t="n"/>
+      <c r="Q54" s="966" t="n"/>
+      <c r="R54" s="966" t="n"/>
+      <c r="S54" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="55" s="888">
       <c r="A55" s="891" t="n"/>
-      <c r="B55" s="950" t="n"/>
-      <c r="C55" s="951" t="n"/>
-      <c r="D55" s="952" t="n"/>
-      <c r="E55" s="951" t="n"/>
-      <c r="F55" s="953" t="inlineStr">
+      <c r="B55" s="951" t="n"/>
+      <c r="C55" s="952" t="n"/>
+      <c r="D55" s="953" t="n"/>
+      <c r="E55" s="952" t="n"/>
+      <c r="F55" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 営業支援SaaSのプロダクト開発(2020年10月〜2021年1月：４ヶ月) ＜副業＞
@@ -8507,92 +8720,92 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G55" s="954" t="inlineStr">
+      <c r="G55" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H55" s="952" t="n"/>
-      <c r="I55" s="952" t="n"/>
-      <c r="J55" s="952" t="n"/>
-      <c r="K55" s="955" t="n"/>
-      <c r="L55" s="952" t="n"/>
-      <c r="M55" s="952" t="n"/>
-      <c r="N55" s="952" t="n"/>
-      <c r="O55" s="956" t="n"/>
-      <c r="P55" s="956" t="n"/>
-      <c r="Q55" s="952" t="n"/>
-      <c r="R55" s="952" t="n"/>
-      <c r="S55" s="967" t="n"/>
+      <c r="H55" s="953" t="n"/>
+      <c r="I55" s="953" t="n"/>
+      <c r="J55" s="953" t="n"/>
+      <c r="K55" s="956" t="n"/>
+      <c r="L55" s="953" t="n"/>
+      <c r="M55" s="953" t="n"/>
+      <c r="N55" s="953" t="n"/>
+      <c r="O55" s="957" t="n"/>
+      <c r="P55" s="957" t="n"/>
+      <c r="Q55" s="953" t="n"/>
+      <c r="R55" s="953" t="n"/>
+      <c r="S55" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="56" s="888">
       <c r="A56" s="891" t="n"/>
-      <c r="B56" s="958" t="n"/>
-      <c r="C56" s="954" t="inlineStr">
+      <c r="B56" s="959" t="n"/>
+      <c r="C56" s="955" t="inlineStr">
         <is>
           <t>４ヶ月</t>
         </is>
       </c>
-      <c r="D56" s="959" t="n"/>
-      <c r="E56" s="960" t="n"/>
-      <c r="F56" s="961" t="n"/>
-      <c r="G56" s="961" t="n"/>
-      <c r="H56" s="961" t="n"/>
-      <c r="I56" s="961" t="n"/>
-      <c r="J56" s="961" t="n"/>
-      <c r="K56" s="962" t="n"/>
-      <c r="L56" s="961" t="n"/>
-      <c r="M56" s="961" t="n"/>
-      <c r="N56" s="961" t="n"/>
-      <c r="O56" s="963" t="n"/>
-      <c r="P56" s="963" t="n"/>
-      <c r="Q56" s="961" t="n"/>
-      <c r="R56" s="961" t="n"/>
-      <c r="S56" s="968" t="n"/>
+      <c r="D56" s="960" t="n"/>
+      <c r="E56" s="961" t="n"/>
+      <c r="F56" s="962" t="n"/>
+      <c r="G56" s="962" t="n"/>
+      <c r="H56" s="962" t="n"/>
+      <c r="I56" s="962" t="n"/>
+      <c r="J56" s="962" t="n"/>
+      <c r="K56" s="963" t="n"/>
+      <c r="L56" s="962" t="n"/>
+      <c r="M56" s="962" t="n"/>
+      <c r="N56" s="962" t="n"/>
+      <c r="O56" s="964" t="n"/>
+      <c r="P56" s="964" t="n"/>
+      <c r="Q56" s="962" t="n"/>
+      <c r="R56" s="962" t="n"/>
+      <c r="S56" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="57" s="888">
       <c r="A57" s="891" t="n"/>
-      <c r="B57" s="941" t="n">
+      <c r="B57" s="942" t="n">
         <v>15</v>
       </c>
-      <c r="C57" s="942" t="inlineStr">
+      <c r="C57" s="943" t="inlineStr">
         <is>
           <t>2020/02</t>
         </is>
       </c>
-      <c r="D57" s="943" t="inlineStr">
+      <c r="D57" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E57" s="942" t="inlineStr">
+      <c r="E57" s="943" t="inlineStr">
         <is>
           <t>2020/07</t>
         </is>
       </c>
-      <c r="F57" s="944" t="inlineStr">
+      <c r="F57" s="945" t="inlineStr">
         <is>
           <t>■エンジニア組織のパフォーマンス最大化サービス開発 ＜副業＞</t>
         </is>
       </c>
-      <c r="G57" s="945" t="inlineStr">
+      <c r="G57" s="946" t="inlineStr">
         <is>
           <t>バックエンドエンジニア</t>
         </is>
       </c>
-      <c r="H57" s="946" t="inlineStr">
+      <c r="H57" s="947" t="inlineStr">
         <is>
           <t>Ruby</t>
         </is>
       </c>
-      <c r="I57" s="946" t="inlineStr">
+      <c r="I57" s="947" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J57" s="946" t="inlineStr"/>
-      <c r="K57" s="947" t="inlineStr">
+      <c r="J57" s="947" t="inlineStr"/>
+      <c r="K57" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails
 エディタ/IDE：VSCode
@@ -8600,30 +8813,30 @@
 コミュニケーション：Slack</t>
         </is>
       </c>
-      <c r="L57" s="965" t="n"/>
-      <c r="M57" s="965" t="n"/>
-      <c r="N57" s="965" t="n"/>
-      <c r="O57" s="948" t="inlineStr">
+      <c r="L57" s="966" t="n"/>
+      <c r="M57" s="966" t="n"/>
+      <c r="N57" s="966" t="n"/>
+      <c r="O57" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P57" s="948" t="inlineStr">
+      <c r="P57" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q57" s="965" t="n"/>
-      <c r="R57" s="965" t="n"/>
-      <c r="S57" s="966" t="n"/>
+      <c r="Q57" s="966" t="n"/>
+      <c r="R57" s="966" t="n"/>
+      <c r="S57" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="58" s="888">
       <c r="A58" s="891" t="n"/>
-      <c r="B58" s="950" t="n"/>
-      <c r="C58" s="951" t="n"/>
-      <c r="D58" s="952" t="n"/>
-      <c r="E58" s="951" t="n"/>
-      <c r="F58" s="953" t="inlineStr">
+      <c r="B58" s="951" t="n"/>
+      <c r="C58" s="952" t="n"/>
+      <c r="D58" s="953" t="n"/>
+      <c r="E58" s="952" t="n"/>
+      <c r="F58" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 エンジニア組織のパフォーマンス最大化サービス開発(2020年2月〜2020年7月:6ヶ月) ＜副業＞
@@ -8633,126 +8846,126 @@
 フルリモート、issue駆動開発</t>
         </is>
       </c>
-      <c r="G58" s="954" t="inlineStr">
+      <c r="G58" s="955" t="inlineStr">
         <is>
           <t>チーム体制
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H58" s="952" t="n"/>
-      <c r="I58" s="952" t="n"/>
-      <c r="J58" s="952" t="n"/>
-      <c r="K58" s="955" t="n"/>
-      <c r="L58" s="952" t="n"/>
-      <c r="M58" s="952" t="n"/>
-      <c r="N58" s="952" t="n"/>
-      <c r="O58" s="956" t="n"/>
-      <c r="P58" s="956" t="n"/>
-      <c r="Q58" s="952" t="n"/>
-      <c r="R58" s="952" t="n"/>
-      <c r="S58" s="967" t="n"/>
+      <c r="H58" s="953" t="n"/>
+      <c r="I58" s="953" t="n"/>
+      <c r="J58" s="953" t="n"/>
+      <c r="K58" s="956" t="n"/>
+      <c r="L58" s="953" t="n"/>
+      <c r="M58" s="953" t="n"/>
+      <c r="N58" s="953" t="n"/>
+      <c r="O58" s="957" t="n"/>
+      <c r="P58" s="957" t="n"/>
+      <c r="Q58" s="953" t="n"/>
+      <c r="R58" s="953" t="n"/>
+      <c r="S58" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="59" s="888">
       <c r="A59" s="891" t="n"/>
-      <c r="B59" s="958" t="n"/>
-      <c r="C59" s="954" t="inlineStr">
+      <c r="B59" s="959" t="n"/>
+      <c r="C59" s="955" t="inlineStr">
         <is>
           <t>6ヶ月</t>
         </is>
       </c>
-      <c r="D59" s="959" t="n"/>
-      <c r="E59" s="960" t="n"/>
-      <c r="F59" s="961" t="n"/>
-      <c r="G59" s="961" t="n"/>
-      <c r="H59" s="961" t="n"/>
-      <c r="I59" s="961" t="n"/>
-      <c r="J59" s="961" t="n"/>
-      <c r="K59" s="962" t="n"/>
-      <c r="L59" s="961" t="n"/>
-      <c r="M59" s="961" t="n"/>
-      <c r="N59" s="961" t="n"/>
-      <c r="O59" s="963" t="n"/>
-      <c r="P59" s="963" t="n"/>
-      <c r="Q59" s="961" t="n"/>
-      <c r="R59" s="961" t="n"/>
-      <c r="S59" s="968" t="n"/>
+      <c r="D59" s="960" t="n"/>
+      <c r="E59" s="961" t="n"/>
+      <c r="F59" s="962" t="n"/>
+      <c r="G59" s="962" t="n"/>
+      <c r="H59" s="962" t="n"/>
+      <c r="I59" s="962" t="n"/>
+      <c r="J59" s="962" t="n"/>
+      <c r="K59" s="963" t="n"/>
+      <c r="L59" s="962" t="n"/>
+      <c r="M59" s="962" t="n"/>
+      <c r="N59" s="962" t="n"/>
+      <c r="O59" s="964" t="n"/>
+      <c r="P59" s="964" t="n"/>
+      <c r="Q59" s="962" t="n"/>
+      <c r="R59" s="962" t="n"/>
+      <c r="S59" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="60" s="888">
       <c r="A60" s="891" t="n"/>
-      <c r="B60" s="941" t="n">
+      <c r="B60" s="942" t="n">
         <v>16</v>
       </c>
-      <c r="C60" s="942" t="inlineStr">
+      <c r="C60" s="943" t="inlineStr">
         <is>
           <t>2019/05</t>
         </is>
       </c>
-      <c r="D60" s="943" t="inlineStr">
+      <c r="D60" s="944" t="inlineStr">
         <is>
           <t>−</t>
         </is>
       </c>
-      <c r="E60" s="942" t="inlineStr">
+      <c r="E60" s="943" t="inlineStr">
         <is>
           <t>2019/12</t>
         </is>
       </c>
-      <c r="F60" s="944" t="inlineStr">
+      <c r="F60" s="945" t="inlineStr">
         <is>
           <t>■プログラミングスクール学習サポート ＜副業＞</t>
         </is>
       </c>
-      <c r="G60" s="945" t="inlineStr">
+      <c r="G60" s="946" t="inlineStr">
         <is>
           <t>メンター</t>
         </is>
       </c>
-      <c r="H60" s="946" t="inlineStr">
+      <c r="H60" s="947" t="inlineStr">
         <is>
           <t>Ruby、Javascript、html、css</t>
         </is>
       </c>
-      <c r="I60" s="946" t="inlineStr">
+      <c r="I60" s="947" t="inlineStr">
         <is>
           <t>Mysql</t>
         </is>
       </c>
-      <c r="J60" s="946" t="inlineStr">
+      <c r="J60" s="947" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="K60" s="947" t="inlineStr">
+      <c r="K60" s="948" t="inlineStr">
         <is>
           <t>FW/ライブラリ：Ruby on Rails、Bootstrap
 エディタ/IDE：VSCode
 その他：Git、Vagrant、Bootstrap</t>
         </is>
       </c>
-      <c r="L60" s="965" t="n"/>
-      <c r="M60" s="965" t="n"/>
-      <c r="N60" s="965" t="n"/>
-      <c r="O60" s="948" t="inlineStr">
+      <c r="L60" s="966" t="n"/>
+      <c r="M60" s="966" t="n"/>
+      <c r="N60" s="966" t="n"/>
+      <c r="O60" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="P60" s="948" t="inlineStr">
+      <c r="P60" s="949" t="inlineStr">
         <is>
           <t>●</t>
         </is>
       </c>
-      <c r="Q60" s="965" t="n"/>
-      <c r="R60" s="965" t="n"/>
-      <c r="S60" s="966" t="n"/>
+      <c r="Q60" s="966" t="n"/>
+      <c r="R60" s="966" t="n"/>
+      <c r="S60" s="967" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="88" r="61" s="888">
       <c r="A61" s="891" t="n"/>
-      <c r="B61" s="950" t="n"/>
-      <c r="C61" s="951" t="n"/>
-      <c r="D61" s="952" t="n"/>
-      <c r="E61" s="951" t="n"/>
-      <c r="F61" s="953" t="inlineStr">
+      <c r="B61" s="951" t="n"/>
+      <c r="C61" s="952" t="n"/>
+      <c r="D61" s="953" t="n"/>
+      <c r="E61" s="952" t="n"/>
+      <c r="F61" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
 プログラミングスクール学習サポート(2019年5月〜2019年12月：8ヶ月) ＜副業＞
@@ -8760,48 +8973,48 @@
 受講生サポート、コードレビュー</t>
         </is>
       </c>
-      <c r="G61" s="954" t="inlineStr"/>
-      <c r="H61" s="952" t="n"/>
-      <c r="I61" s="952" t="n"/>
-      <c r="J61" s="952" t="n"/>
-      <c r="K61" s="955" t="n"/>
-      <c r="L61" s="952" t="n"/>
-      <c r="M61" s="952" t="n"/>
-      <c r="N61" s="952" t="n"/>
-      <c r="O61" s="956" t="n"/>
-      <c r="P61" s="956" t="n"/>
-      <c r="Q61" s="952" t="n"/>
-      <c r="R61" s="952" t="n"/>
-      <c r="S61" s="967" t="n"/>
+      <c r="G61" s="955" t="inlineStr"/>
+      <c r="H61" s="953" t="n"/>
+      <c r="I61" s="953" t="n"/>
+      <c r="J61" s="953" t="n"/>
+      <c r="K61" s="956" t="n"/>
+      <c r="L61" s="953" t="n"/>
+      <c r="M61" s="953" t="n"/>
+      <c r="N61" s="953" t="n"/>
+      <c r="O61" s="957" t="n"/>
+      <c r="P61" s="957" t="n"/>
+      <c r="Q61" s="953" t="n"/>
+      <c r="R61" s="953" t="n"/>
+      <c r="S61" s="968" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="62" s="888">
       <c r="A62" s="891" t="n"/>
-      <c r="B62" s="958" t="n"/>
-      <c r="C62" s="954" t="inlineStr">
+      <c r="B62" s="959" t="n"/>
+      <c r="C62" s="955" t="inlineStr">
         <is>
           <t>8ヶ月</t>
         </is>
       </c>
-      <c r="D62" s="959" t="n"/>
-      <c r="E62" s="960" t="n"/>
-      <c r="F62" s="961" t="n"/>
-      <c r="G62" s="961" t="n"/>
-      <c r="H62" s="961" t="n"/>
-      <c r="I62" s="961" t="n"/>
-      <c r="J62" s="961" t="n"/>
-      <c r="K62" s="962" t="n"/>
-      <c r="L62" s="961" t="n"/>
-      <c r="M62" s="961" t="n"/>
-      <c r="N62" s="961" t="n"/>
-      <c r="O62" s="963" t="n"/>
-      <c r="P62" s="963" t="n"/>
-      <c r="Q62" s="961" t="n"/>
-      <c r="R62" s="961" t="n"/>
-      <c r="S62" s="968" t="n"/>
+      <c r="D62" s="960" t="n"/>
+      <c r="E62" s="961" t="n"/>
+      <c r="F62" s="962" t="n"/>
+      <c r="G62" s="962" t="n"/>
+      <c r="H62" s="962" t="n"/>
+      <c r="I62" s="962" t="n"/>
+      <c r="J62" s="962" t="n"/>
+      <c r="K62" s="963" t="n"/>
+      <c r="L62" s="962" t="n"/>
+      <c r="M62" s="962" t="n"/>
+      <c r="N62" s="962" t="n"/>
+      <c r="O62" s="964" t="n"/>
+      <c r="P62" s="964" t="n"/>
+      <c r="Q62" s="962" t="n"/>
+      <c r="R62" s="962" t="n"/>
+      <c r="S62" s="969" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="28" r="63" s="888">
       <c r="A63" s="891" t="n"/>
-      <c r="B63" s="972" t="inlineStr">
+      <c r="B63" s="973" t="inlineStr">
         <is>
           <t>●：担当工程。空欄：未記載（経験なしを意味しません）。案件名のリンクから詳細を確認できます。</t>
         </is>

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -279,7 +279,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="315">
+  <borders count="328">
     <border/>
     <border>
       <bottom style="medium">
@@ -3451,6 +3451,92 @@
       <bottom style="medium">
         <color rgb="0017365D"/>
       </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="medium">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="0017365D"/>
+      </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+    </border>
+    <border>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="thin">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="hair">
+        <color rgb="0017365D"/>
+      </left>
+    </border>
+    <border>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <right style="hair">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E9F1F8"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E9F1F8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E9F1F8"/>
+      </right>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="0017365D"/>
+      </right>
+      <top style="hair">
+        <color rgb="0017365D"/>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="2">
@@ -3459,7 +3545,7 @@
     </xf>
     <xf borderId="84" fillId="0" fontId="1" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="974">
+  <cellXfs count="1010">
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6088,6 +6174,42 @@
     <xf applyAlignment="1" borderId="84" fillId="13" fontId="25" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf borderId="84" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="258" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="262" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="236" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="238" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="239" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="242" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="244" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="246" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="247" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="250" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="252" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="254" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="257" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="260" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="264" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="305" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="268" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="269" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="306" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="234" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="307" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="310" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="283" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="284" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="285" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="287" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="288" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="289" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="290" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="291" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="292" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="293" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="294" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="295" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="281" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0"/>
@@ -6348,7 +6470,7 @@
       <c r="D1" s="888" t="n"/>
       <c r="E1" s="888" t="n"/>
       <c r="F1" s="888" t="n"/>
-      <c r="G1" s="889" t="n"/>
+      <c r="G1" s="927" t="n"/>
       <c r="H1" s="888" t="n"/>
       <c r="I1" s="888" t="n"/>
       <c r="J1" s="888" t="n"/>
@@ -6359,12 +6481,12 @@
           <t>2026/10 更新</t>
         </is>
       </c>
-      <c r="N1" s="888" t="n"/>
-      <c r="O1" s="888" t="n"/>
-      <c r="P1" s="888" t="n"/>
-      <c r="Q1" s="888" t="n"/>
-      <c r="R1" s="888" t="n"/>
-      <c r="S1" s="888" t="n"/>
+      <c r="N1" s="974" t="n"/>
+      <c r="O1" s="974" t="n"/>
+      <c r="P1" s="974" t="n"/>
+      <c r="Q1" s="974" t="n"/>
+      <c r="R1" s="974" t="n"/>
+      <c r="S1" s="974" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="30" r="2" s="888">
       <c r="A2" s="891" t="n"/>
@@ -6373,23 +6495,23 @@
           <t>スキルシート</t>
         </is>
       </c>
-      <c r="C2" s="893" t="n"/>
-      <c r="D2" s="893" t="n"/>
-      <c r="E2" s="893" t="n"/>
-      <c r="F2" s="893" t="n"/>
-      <c r="G2" s="893" t="n"/>
-      <c r="H2" s="893" t="n"/>
-      <c r="I2" s="893" t="n"/>
-      <c r="J2" s="893" t="n"/>
-      <c r="K2" s="893" t="n"/>
-      <c r="L2" s="893" t="n"/>
-      <c r="M2" s="893" t="n"/>
-      <c r="N2" s="893" t="n"/>
-      <c r="O2" s="893" t="n"/>
-      <c r="P2" s="893" t="n"/>
-      <c r="Q2" s="893" t="n"/>
-      <c r="R2" s="893" t="n"/>
-      <c r="S2" s="894" t="n"/>
+      <c r="C2" s="975" t="n"/>
+      <c r="D2" s="975" t="n"/>
+      <c r="E2" s="975" t="n"/>
+      <c r="F2" s="975" t="n"/>
+      <c r="G2" s="975" t="n"/>
+      <c r="H2" s="975" t="n"/>
+      <c r="I2" s="975" t="n"/>
+      <c r="J2" s="975" t="n"/>
+      <c r="K2" s="975" t="n"/>
+      <c r="L2" s="975" t="n"/>
+      <c r="M2" s="975" t="n"/>
+      <c r="N2" s="975" t="n"/>
+      <c r="O2" s="975" t="n"/>
+      <c r="P2" s="975" t="n"/>
+      <c r="Q2" s="975" t="n"/>
+      <c r="R2" s="975" t="n"/>
+      <c r="S2" s="976" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="3" s="888">
       <c r="A3" s="891" t="n"/>
@@ -6398,35 +6520,35 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="C3" s="896" t="n"/>
+      <c r="C3" s="977" t="n"/>
       <c r="D3" s="897" t="inlineStr">
         <is>
           <t>平田 智昭（ヒラタ トモアキ）</t>
         </is>
       </c>
-      <c r="E3" s="898" t="n"/>
-      <c r="F3" s="899" t="n"/>
+      <c r="E3" s="978" t="n"/>
+      <c r="F3" s="979" t="n"/>
       <c r="G3" s="900" t="inlineStr">
         <is>
           <t>性別</t>
         </is>
       </c>
-      <c r="H3" s="896" t="n"/>
+      <c r="H3" s="977" t="n"/>
       <c r="I3" s="901" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="J3" s="898" t="n"/>
-      <c r="K3" s="898" t="n"/>
-      <c r="L3" s="898" t="n"/>
-      <c r="M3" s="898" t="n"/>
-      <c r="N3" s="898" t="n"/>
-      <c r="O3" s="898" t="n"/>
-      <c r="P3" s="898" t="n"/>
-      <c r="Q3" s="898" t="n"/>
-      <c r="R3" s="898" t="n"/>
-      <c r="S3" s="902" t="n"/>
+      <c r="J3" s="978" t="n"/>
+      <c r="K3" s="978" t="n"/>
+      <c r="L3" s="978" t="n"/>
+      <c r="M3" s="978" t="n"/>
+      <c r="N3" s="978" t="n"/>
+      <c r="O3" s="978" t="n"/>
+      <c r="P3" s="978" t="n"/>
+      <c r="Q3" s="978" t="n"/>
+      <c r="R3" s="978" t="n"/>
+      <c r="S3" s="980" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="4" s="888">
       <c r="A4" s="891" t="n"/>
@@ -6435,35 +6557,35 @@
           <t>年齢</t>
         </is>
       </c>
-      <c r="C4" s="904" t="n"/>
+      <c r="C4" s="981" t="n"/>
       <c r="D4" s="905" t="inlineStr">
         <is>
           <t>38歳</t>
         </is>
       </c>
-      <c r="E4" s="906" t="n"/>
-      <c r="F4" s="907" t="n"/>
+      <c r="E4" s="982" t="n"/>
+      <c r="F4" s="983" t="n"/>
       <c r="G4" s="908" t="inlineStr">
         <is>
           <t>業界経験</t>
         </is>
       </c>
-      <c r="H4" s="904" t="n"/>
+      <c r="H4" s="981" t="n"/>
       <c r="I4" s="909" t="inlineStr">
         <is>
           <t>14年目：フリーランス 2017/10 ~ 現在、ソフトウェア会社(正社員) 2013/04 ~ 2017/09</t>
         </is>
       </c>
-      <c r="J4" s="906" t="n"/>
-      <c r="K4" s="906" t="n"/>
-      <c r="L4" s="906" t="n"/>
-      <c r="M4" s="906" t="n"/>
-      <c r="N4" s="906" t="n"/>
-      <c r="O4" s="906" t="n"/>
-      <c r="P4" s="906" t="n"/>
-      <c r="Q4" s="906" t="n"/>
-      <c r="R4" s="906" t="n"/>
-      <c r="S4" s="910" t="n"/>
+      <c r="J4" s="982" t="n"/>
+      <c r="K4" s="982" t="n"/>
+      <c r="L4" s="982" t="n"/>
+      <c r="M4" s="982" t="n"/>
+      <c r="N4" s="982" t="n"/>
+      <c r="O4" s="982" t="n"/>
+      <c r="P4" s="982" t="n"/>
+      <c r="Q4" s="982" t="n"/>
+      <c r="R4" s="982" t="n"/>
+      <c r="S4" s="984" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="5" s="888">
       <c r="A5" s="891" t="n"/>
@@ -6472,35 +6594,35 @@
           <t>最寄駅</t>
         </is>
       </c>
-      <c r="C5" s="904" t="n"/>
+      <c r="C5" s="981" t="n"/>
       <c r="D5" s="911" t="inlineStr">
         <is>
           <t>東海道線 平塚駅</t>
         </is>
       </c>
-      <c r="E5" s="906" t="n"/>
-      <c r="F5" s="907" t="n"/>
+      <c r="E5" s="982" t="n"/>
+      <c r="F5" s="983" t="n"/>
       <c r="G5" s="908" t="inlineStr">
         <is>
           <t>稼働希望</t>
         </is>
       </c>
-      <c r="H5" s="904" t="n"/>
+      <c r="H5" s="981" t="n"/>
       <c r="I5" s="912" t="inlineStr">
         <is>
           <t>フルリモート(必要時に都度出社)</t>
         </is>
       </c>
-      <c r="J5" s="906" t="n"/>
-      <c r="K5" s="906" t="n"/>
-      <c r="L5" s="906" t="n"/>
-      <c r="M5" s="906" t="n"/>
-      <c r="N5" s="906" t="n"/>
-      <c r="O5" s="906" t="n"/>
-      <c r="P5" s="906" t="n"/>
-      <c r="Q5" s="906" t="n"/>
-      <c r="R5" s="906" t="n"/>
-      <c r="S5" s="910" t="n"/>
+      <c r="J5" s="982" t="n"/>
+      <c r="K5" s="982" t="n"/>
+      <c r="L5" s="982" t="n"/>
+      <c r="M5" s="982" t="n"/>
+      <c r="N5" s="982" t="n"/>
+      <c r="O5" s="982" t="n"/>
+      <c r="P5" s="982" t="n"/>
+      <c r="Q5" s="982" t="n"/>
+      <c r="R5" s="982" t="n"/>
+      <c r="S5" s="984" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="57" r="6" s="888">
       <c r="A6" s="891" t="n"/>
@@ -6509,7 +6631,7 @@
           <t>資格</t>
         </is>
       </c>
-      <c r="C6" s="914" t="n"/>
+      <c r="C6" s="985" t="n"/>
       <c r="D6" s="915" t="inlineStr">
         <is>
           <t>認定スクラムマスター(LSM) ※2022/12 失効
@@ -6517,83 +6639,84 @@
 Ruby Association Certified Ruby Programmer Gold Version 3</t>
         </is>
       </c>
-      <c r="E6" s="916" t="n"/>
-      <c r="F6" s="916" t="n"/>
+      <c r="E6" s="986" t="n"/>
+      <c r="F6" s="986" t="n"/>
       <c r="G6" s="917" t="inlineStr">
         <is>
           <t>学歴</t>
         </is>
       </c>
-      <c r="H6" s="914" t="n"/>
+      <c r="H6" s="985" t="n"/>
       <c r="I6" s="918" t="inlineStr">
         <is>
           <t>工学院大学 工学部 機械システム工学科卒</t>
         </is>
       </c>
-      <c r="J6" s="916" t="n"/>
-      <c r="K6" s="916" t="n"/>
-      <c r="L6" s="916" t="n"/>
-      <c r="M6" s="916" t="n"/>
-      <c r="N6" s="916" t="n"/>
-      <c r="O6" s="916" t="n"/>
-      <c r="P6" s="916" t="n"/>
-      <c r="Q6" s="916" t="n"/>
-      <c r="R6" s="916" t="n"/>
-      <c r="S6" s="919" t="n"/>
+      <c r="J6" s="986" t="n"/>
+      <c r="K6" s="986" t="n"/>
+      <c r="L6" s="986" t="n"/>
+      <c r="M6" s="986" t="n"/>
+      <c r="N6" s="986" t="n"/>
+      <c r="O6" s="986" t="n"/>
+      <c r="P6" s="986" t="n"/>
+      <c r="Q6" s="986" t="n"/>
+      <c r="R6" s="986" t="n"/>
+      <c r="S6" s="987" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="10" r="7" s="888">
       <c r="A7" s="891" t="n"/>
       <c r="B7" s="920" t="n"/>
-      <c r="C7" s="921" t="n"/>
-      <c r="D7" s="921" t="n"/>
-      <c r="E7" s="921" t="n"/>
-      <c r="F7" s="921" t="n"/>
-      <c r="G7" s="921" t="n"/>
-      <c r="H7" s="921" t="n"/>
-      <c r="I7" s="921" t="n"/>
-      <c r="J7" s="921" t="n"/>
-      <c r="K7" s="921" t="n"/>
-      <c r="L7" s="921" t="n"/>
-      <c r="M7" s="921" t="n"/>
-      <c r="N7" s="921" t="n"/>
-      <c r="O7" s="921" t="n"/>
-      <c r="P7" s="921" t="n"/>
-      <c r="Q7" s="921" t="n"/>
-      <c r="R7" s="921" t="n"/>
-      <c r="S7" s="921" t="n"/>
+      <c r="C7" s="975" t="n"/>
+      <c r="D7" s="975" t="n"/>
+      <c r="E7" s="975" t="n"/>
+      <c r="F7" s="975" t="n"/>
+      <c r="G7" s="975" t="n"/>
+      <c r="H7" s="975" t="n"/>
+      <c r="I7" s="975" t="n"/>
+      <c r="J7" s="975" t="n"/>
+      <c r="K7" s="975" t="n"/>
+      <c r="L7" s="975" t="n"/>
+      <c r="M7" s="975" t="n"/>
+      <c r="N7" s="975" t="n"/>
+      <c r="O7" s="975" t="n"/>
+      <c r="P7" s="975" t="n"/>
+      <c r="Q7" s="975" t="n"/>
+      <c r="R7" s="975" t="n"/>
+      <c r="S7" s="975" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="201" r="8" s="888">
+    <row customFormat="1" customHeight="1" ht="249" r="8" s="888">
       <c r="A8" s="891" t="n"/>
       <c r="B8" s="922" t="inlineStr">
         <is>
           <t>職務要約</t>
         </is>
       </c>
-      <c r="C8" s="923" t="n"/>
+      <c r="C8" s="988" t="n"/>
       <c r="D8" s="924" t="inlineStr">
         <is>
           <t>新卒にて中小ソフトウェア企業に入社後、2013年から正社員として5年間、受託開発や客先開発でJavaやOracleを使ったシステム開発に携わりました。
 2017年にフリーランスに転身してから現在まで8年間、Ruby on Railsを主軸としたバックエンド開発をメインとしながら、React/Next.jsなどのモダンフロントエンド技術、AWSインフラ構築、DBパフォーマンスチューニングまで幅広くフルスタックに対応してきました。
 近年の技術的な強みとして、GraphQLを活用したAPI設計、Terraformによるインフラコード化、CursorやClaude CodeなどのAIエージェントを活用した効率的な開発プロセスの確立があげられます。現在はリードエンジニアとして、アーキテクチャ設計から実装、チームマネジメントまで包括的に担当しております。
+個人開発のPBSでは、Claude Codeによる実装・PR作成とCodexによるレビューを連携させ、Issue駆動で実装からレビューまでを完全自動化する運用を試行しました。開発速度の低下や実装意図とのずれを受け、実装・レビューの各段階で人がAIへ依頼し、内容を確認・判断する半自動の運用へ変更しました。
 プロジェクトや開発組織に対しては、エンジニアとして開発に従事しながら、認定スクラムマスターの資格の知見を活かし、アジャイル開発におけるチームファシリテーション、エンジニア採用面談、新規メンバーのオンボーディング、チームビルディングなど、開発面以外での組織貢献も積極的に行っています。
 今後も、AIツールを効果的に活用しながら開発生産性を向上させつつ、チームリードとしての責任を果たし、ビジネス価値の高いプロダクト開発に貢献していきたいと考えております。何卒よろしくお願いいたします。</t>
         </is>
       </c>
-      <c r="E8" s="921" t="n"/>
-      <c r="F8" s="921" t="n"/>
-      <c r="G8" s="921" t="n"/>
-      <c r="H8" s="921" t="n"/>
-      <c r="I8" s="921" t="n"/>
-      <c r="J8" s="921" t="n"/>
-      <c r="K8" s="921" t="n"/>
-      <c r="L8" s="921" t="n"/>
-      <c r="M8" s="921" t="n"/>
-      <c r="N8" s="921" t="n"/>
-      <c r="O8" s="921" t="n"/>
-      <c r="P8" s="921" t="n"/>
-      <c r="Q8" s="921" t="n"/>
-      <c r="R8" s="921" t="n"/>
-      <c r="S8" s="925" t="n"/>
+      <c r="E8" s="975" t="n"/>
+      <c r="F8" s="975" t="n"/>
+      <c r="G8" s="975" t="n"/>
+      <c r="H8" s="975" t="n"/>
+      <c r="I8" s="975" t="n"/>
+      <c r="J8" s="975" t="n"/>
+      <c r="K8" s="975" t="n"/>
+      <c r="L8" s="975" t="n"/>
+      <c r="M8" s="975" t="n"/>
+      <c r="N8" s="975" t="n"/>
+      <c r="O8" s="975" t="n"/>
+      <c r="P8" s="975" t="n"/>
+      <c r="Q8" s="975" t="n"/>
+      <c r="R8" s="975" t="n"/>
+      <c r="S8" s="976" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="105" r="9" s="888">
       <c r="A9" s="891" t="n"/>
@@ -6602,32 +6725,32 @@
           <t>得意とする分野</t>
         </is>
       </c>
-      <c r="C9" s="923" t="n"/>
+      <c r="C9" s="988" t="n"/>
       <c r="D9" s="924" t="inlineStr">
         <is>
           <t>- Ruby on Railsを中心としたWebアプリケーションのバックエンド開発
 - React/Next.js/TypeScriptを用いたフロントエンド開発
 - AWS/Terraform/Docker/GitHub Actions等を用いた開発・運用基盤整備
 - GraphQL API設計、DB設計・パフォーマンス改善
-- AIエージェント（Cursor、Claude Code）を活用した開発生産性向上
+- AIエージェント（Cursor、Claude Code、Codex）を活用した開発と、自動化範囲の検証・見直し
 - リードエンジニアとしての設計、レビュー、見積、チーム支援</t>
         </is>
       </c>
-      <c r="E9" s="921" t="n"/>
-      <c r="F9" s="921" t="n"/>
-      <c r="G9" s="921" t="n"/>
-      <c r="H9" s="921" t="n"/>
-      <c r="I9" s="921" t="n"/>
-      <c r="J9" s="921" t="n"/>
-      <c r="K9" s="921" t="n"/>
-      <c r="L9" s="921" t="n"/>
-      <c r="M9" s="921" t="n"/>
-      <c r="N9" s="921" t="n"/>
-      <c r="O9" s="921" t="n"/>
-      <c r="P9" s="921" t="n"/>
-      <c r="Q9" s="921" t="n"/>
-      <c r="R9" s="921" t="n"/>
-      <c r="S9" s="925" t="n"/>
+      <c r="E9" s="975" t="n"/>
+      <c r="F9" s="975" t="n"/>
+      <c r="G9" s="975" t="n"/>
+      <c r="H9" s="975" t="n"/>
+      <c r="I9" s="975" t="n"/>
+      <c r="J9" s="975" t="n"/>
+      <c r="K9" s="975" t="n"/>
+      <c r="L9" s="975" t="n"/>
+      <c r="M9" s="975" t="n"/>
+      <c r="N9" s="975" t="n"/>
+      <c r="O9" s="975" t="n"/>
+      <c r="P9" s="975" t="n"/>
+      <c r="Q9" s="975" t="n"/>
+      <c r="R9" s="975" t="n"/>
+      <c r="S9" s="976" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="137" r="10" s="888">
       <c r="A10" s="891" t="n"/>
@@ -6636,7 +6759,7 @@
           <t>スキル</t>
         </is>
       </c>
-      <c r="C10" s="923" t="n"/>
+      <c r="C10" s="988" t="n"/>
       <c r="D10" s="924" t="inlineStr">
         <is>
           <t>・プログラミング言語：HTML 10年、CSS  10年、Javascript 10年、SQL 10年、Ruby 8年、Java 5年、TypeScript 3年、Python 2年、Kotlin 1年未満
@@ -6647,21 +6770,21 @@
 ・その他ソフトウェアツール、サービス：Slack 8年、Docker 6年、Eclipse 4年、Redmine 3年、CircleCI 3年、Swagger 3年、Google Analytics 2年、Jira 3年、Confluence 2年、Terraform 2年、GitHubActions 2年、Twilio 1年、Vagrant 1年、Zabbix 1年、Jmeter 1年、AndroidStudio 1年</t>
         </is>
       </c>
-      <c r="E10" s="921" t="n"/>
-      <c r="F10" s="921" t="n"/>
-      <c r="G10" s="921" t="n"/>
-      <c r="H10" s="921" t="n"/>
-      <c r="I10" s="921" t="n"/>
-      <c r="J10" s="921" t="n"/>
-      <c r="K10" s="921" t="n"/>
-      <c r="L10" s="921" t="n"/>
-      <c r="M10" s="921" t="n"/>
-      <c r="N10" s="921" t="n"/>
-      <c r="O10" s="921" t="n"/>
-      <c r="P10" s="921" t="n"/>
-      <c r="Q10" s="921" t="n"/>
-      <c r="R10" s="921" t="n"/>
-      <c r="S10" s="925" t="n"/>
+      <c r="E10" s="975" t="n"/>
+      <c r="F10" s="975" t="n"/>
+      <c r="G10" s="975" t="n"/>
+      <c r="H10" s="975" t="n"/>
+      <c r="I10" s="975" t="n"/>
+      <c r="J10" s="975" t="n"/>
+      <c r="K10" s="975" t="n"/>
+      <c r="L10" s="975" t="n"/>
+      <c r="M10" s="975" t="n"/>
+      <c r="N10" s="975" t="n"/>
+      <c r="O10" s="975" t="n"/>
+      <c r="P10" s="975" t="n"/>
+      <c r="Q10" s="975" t="n"/>
+      <c r="R10" s="975" t="n"/>
+      <c r="S10" s="976" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="10" r="11" s="888">
       <c r="A11" s="891" t="n"/>
@@ -6691,9 +6814,9 @@
           <t>期間</t>
         </is>
       </c>
-      <c r="C12" s="929" t="n"/>
-      <c r="D12" s="929" t="n"/>
-      <c r="E12" s="930" t="n"/>
+      <c r="C12" s="989" t="n"/>
+      <c r="D12" s="989" t="n"/>
+      <c r="E12" s="990" t="n"/>
       <c r="F12" s="931" t="inlineStr">
         <is>
           <t>業務内容</t>
@@ -6734,26 +6857,26 @@
           <t>担当工程</t>
         </is>
       </c>
-      <c r="M12" s="934" t="n"/>
-      <c r="N12" s="934" t="n"/>
-      <c r="O12" s="934" t="n"/>
-      <c r="P12" s="934" t="n"/>
-      <c r="Q12" s="934" t="n"/>
-      <c r="R12" s="934" t="n"/>
-      <c r="S12" s="935" t="n"/>
+      <c r="M12" s="991" t="n"/>
+      <c r="N12" s="991" t="n"/>
+      <c r="O12" s="991" t="n"/>
+      <c r="P12" s="991" t="n"/>
+      <c r="Q12" s="991" t="n"/>
+      <c r="R12" s="991" t="n"/>
+      <c r="S12" s="992" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="46" r="13" s="888">
       <c r="A13" s="888" t="n"/>
-      <c r="B13" s="936" t="n"/>
-      <c r="C13" s="937" t="n"/>
-      <c r="D13" s="937" t="n"/>
-      <c r="E13" s="938" t="n"/>
-      <c r="F13" s="939" t="n"/>
-      <c r="G13" s="939" t="n"/>
-      <c r="H13" s="939" t="n"/>
-      <c r="I13" s="939" t="n"/>
-      <c r="J13" s="939" t="n"/>
-      <c r="K13" s="939" t="n"/>
+      <c r="B13" s="993" t="n"/>
+      <c r="C13" s="994" t="n"/>
+      <c r="D13" s="994" t="n"/>
+      <c r="E13" s="995" t="n"/>
+      <c r="F13" s="996" t="n"/>
+      <c r="G13" s="996" t="n"/>
+      <c r="H13" s="996" t="n"/>
+      <c r="I13" s="996" t="n"/>
+      <c r="J13" s="996" t="n"/>
+      <c r="K13" s="996" t="n"/>
       <c r="L13" s="940" t="inlineStr">
         <is>
           <t>要件
@@ -6900,10 +7023,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="232" r="15" s="888">
       <c r="A15" s="891" t="n"/>
-      <c r="B15" s="951" t="n"/>
-      <c r="C15" s="952" t="n"/>
-      <c r="D15" s="953" t="n"/>
-      <c r="E15" s="952" t="n"/>
+      <c r="B15" s="997" t="n"/>
+      <c r="C15" s="998" t="n"/>
+      <c r="D15" s="999" t="n"/>
+      <c r="E15" s="998" t="n"/>
       <c r="F15" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -6920,43 +7043,43 @@
 PM、PdM、エンジニア、SRE、デザイナー、QA</t>
         </is>
       </c>
-      <c r="H15" s="953" t="n"/>
-      <c r="I15" s="953" t="n"/>
-      <c r="J15" s="953" t="n"/>
-      <c r="K15" s="956" t="n"/>
-      <c r="L15" s="957" t="n"/>
-      <c r="M15" s="957" t="n"/>
-      <c r="N15" s="957" t="n"/>
-      <c r="O15" s="957" t="n"/>
-      <c r="P15" s="957" t="n"/>
-      <c r="Q15" s="957" t="n"/>
-      <c r="R15" s="957" t="n"/>
-      <c r="S15" s="958" t="n"/>
+      <c r="H15" s="999" t="n"/>
+      <c r="I15" s="999" t="n"/>
+      <c r="J15" s="999" t="n"/>
+      <c r="K15" s="1000" t="n"/>
+      <c r="L15" s="999" t="n"/>
+      <c r="M15" s="999" t="n"/>
+      <c r="N15" s="999" t="n"/>
+      <c r="O15" s="999" t="n"/>
+      <c r="P15" s="999" t="n"/>
+      <c r="Q15" s="999" t="n"/>
+      <c r="R15" s="999" t="n"/>
+      <c r="S15" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="16" s="888">
       <c r="A16" s="891" t="n"/>
-      <c r="B16" s="959" t="n"/>
+      <c r="B16" s="1002" t="n"/>
       <c r="C16" s="955" t="inlineStr">
         <is>
           <t>随時更新</t>
         </is>
       </c>
-      <c r="D16" s="960" t="n"/>
-      <c r="E16" s="961" t="n"/>
-      <c r="F16" s="962" t="n"/>
-      <c r="G16" s="962" t="n"/>
-      <c r="H16" s="962" t="n"/>
-      <c r="I16" s="962" t="n"/>
-      <c r="J16" s="962" t="n"/>
-      <c r="K16" s="963" t="n"/>
-      <c r="L16" s="964" t="n"/>
-      <c r="M16" s="964" t="n"/>
-      <c r="N16" s="964" t="n"/>
-      <c r="O16" s="964" t="n"/>
-      <c r="P16" s="964" t="n"/>
-      <c r="Q16" s="964" t="n"/>
-      <c r="R16" s="964" t="n"/>
-      <c r="S16" s="965" t="n"/>
+      <c r="D16" s="1003" t="n"/>
+      <c r="E16" s="1004" t="n"/>
+      <c r="F16" s="1005" t="n"/>
+      <c r="G16" s="1005" t="n"/>
+      <c r="H16" s="1005" t="n"/>
+      <c r="I16" s="1005" t="n"/>
+      <c r="J16" s="1005" t="n"/>
+      <c r="K16" s="1006" t="n"/>
+      <c r="L16" s="1005" t="n"/>
+      <c r="M16" s="1005" t="n"/>
+      <c r="N16" s="1005" t="n"/>
+      <c r="O16" s="1005" t="n"/>
+      <c r="P16" s="1005" t="n"/>
+      <c r="Q16" s="1005" t="n"/>
+      <c r="R16" s="1005" t="n"/>
+      <c r="S16" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="17" s="888">
       <c r="A17" s="891" t="n"/>
@@ -7042,10 +7165,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="161" r="18" s="888">
       <c r="A18" s="891" t="n"/>
-      <c r="B18" s="951" t="n"/>
-      <c r="C18" s="952" t="n"/>
-      <c r="D18" s="953" t="n"/>
-      <c r="E18" s="952" t="n"/>
+      <c r="B18" s="997" t="n"/>
+      <c r="C18" s="998" t="n"/>
+      <c r="D18" s="999" t="n"/>
+      <c r="E18" s="998" t="n"/>
       <c r="F18" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -7062,43 +7185,43 @@
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H18" s="953" t="n"/>
-      <c r="I18" s="953" t="n"/>
-      <c r="J18" s="953" t="n"/>
-      <c r="K18" s="956" t="n"/>
-      <c r="L18" s="957" t="n"/>
-      <c r="M18" s="957" t="n"/>
-      <c r="N18" s="957" t="n"/>
-      <c r="O18" s="957" t="n"/>
-      <c r="P18" s="957" t="n"/>
-      <c r="Q18" s="953" t="n"/>
-      <c r="R18" s="953" t="n"/>
-      <c r="S18" s="968" t="n"/>
+      <c r="H18" s="999" t="n"/>
+      <c r="I18" s="999" t="n"/>
+      <c r="J18" s="999" t="n"/>
+      <c r="K18" s="1000" t="n"/>
+      <c r="L18" s="999" t="n"/>
+      <c r="M18" s="999" t="n"/>
+      <c r="N18" s="999" t="n"/>
+      <c r="O18" s="999" t="n"/>
+      <c r="P18" s="999" t="n"/>
+      <c r="Q18" s="999" t="n"/>
+      <c r="R18" s="999" t="n"/>
+      <c r="S18" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="19" s="888">
       <c r="A19" s="891" t="n"/>
-      <c r="B19" s="959" t="n"/>
+      <c r="B19" s="1002" t="n"/>
       <c r="C19" s="955" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D19" s="960" t="n"/>
-      <c r="E19" s="961" t="n"/>
-      <c r="F19" s="962" t="n"/>
-      <c r="G19" s="962" t="n"/>
-      <c r="H19" s="962" t="n"/>
-      <c r="I19" s="962" t="n"/>
-      <c r="J19" s="962" t="n"/>
-      <c r="K19" s="963" t="n"/>
-      <c r="L19" s="964" t="n"/>
-      <c r="M19" s="964" t="n"/>
-      <c r="N19" s="964" t="n"/>
-      <c r="O19" s="964" t="n"/>
-      <c r="P19" s="964" t="n"/>
-      <c r="Q19" s="962" t="n"/>
-      <c r="R19" s="962" t="n"/>
-      <c r="S19" s="969" t="n"/>
+      <c r="D19" s="1003" t="n"/>
+      <c r="E19" s="1004" t="n"/>
+      <c r="F19" s="1005" t="n"/>
+      <c r="G19" s="1005" t="n"/>
+      <c r="H19" s="1005" t="n"/>
+      <c r="I19" s="1005" t="n"/>
+      <c r="J19" s="1005" t="n"/>
+      <c r="K19" s="1006" t="n"/>
+      <c r="L19" s="1005" t="n"/>
+      <c r="M19" s="1005" t="n"/>
+      <c r="N19" s="1005" t="n"/>
+      <c r="O19" s="1005" t="n"/>
+      <c r="P19" s="1005" t="n"/>
+      <c r="Q19" s="1005" t="n"/>
+      <c r="R19" s="1005" t="n"/>
+      <c r="S19" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="20" s="888">
       <c r="A20" s="891" t="n"/>
@@ -7176,10 +7299,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="168" r="21" s="888">
       <c r="A21" s="891" t="n"/>
-      <c r="B21" s="951" t="n"/>
-      <c r="C21" s="952" t="n"/>
-      <c r="D21" s="953" t="n"/>
-      <c r="E21" s="952" t="n"/>
+      <c r="B21" s="997" t="n"/>
+      <c r="C21" s="998" t="n"/>
+      <c r="D21" s="999" t="n"/>
+      <c r="E21" s="998" t="n"/>
       <c r="F21" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -7196,43 +7319,43 @@
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H21" s="953" t="n"/>
-      <c r="I21" s="953" t="n"/>
-      <c r="J21" s="953" t="n"/>
-      <c r="K21" s="956" t="n"/>
-      <c r="L21" s="953" t="n"/>
-      <c r="M21" s="953" t="n"/>
-      <c r="N21" s="953" t="n"/>
-      <c r="O21" s="957" t="n"/>
-      <c r="P21" s="957" t="n"/>
-      <c r="Q21" s="957" t="n"/>
-      <c r="R21" s="953" t="n"/>
-      <c r="S21" s="968" t="n"/>
+      <c r="H21" s="999" t="n"/>
+      <c r="I21" s="999" t="n"/>
+      <c r="J21" s="999" t="n"/>
+      <c r="K21" s="1000" t="n"/>
+      <c r="L21" s="999" t="n"/>
+      <c r="M21" s="999" t="n"/>
+      <c r="N21" s="999" t="n"/>
+      <c r="O21" s="999" t="n"/>
+      <c r="P21" s="999" t="n"/>
+      <c r="Q21" s="999" t="n"/>
+      <c r="R21" s="999" t="n"/>
+      <c r="S21" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="22" s="888">
       <c r="A22" s="891" t="n"/>
-      <c r="B22" s="959" t="n"/>
+      <c r="B22" s="1002" t="n"/>
       <c r="C22" s="955" t="inlineStr">
         <is>
           <t>9ヶ月</t>
         </is>
       </c>
-      <c r="D22" s="960" t="n"/>
-      <c r="E22" s="961" t="n"/>
-      <c r="F22" s="962" t="n"/>
-      <c r="G22" s="962" t="n"/>
-      <c r="H22" s="962" t="n"/>
-      <c r="I22" s="962" t="n"/>
-      <c r="J22" s="962" t="n"/>
-      <c r="K22" s="963" t="n"/>
-      <c r="L22" s="962" t="n"/>
-      <c r="M22" s="962" t="n"/>
-      <c r="N22" s="962" t="n"/>
-      <c r="O22" s="964" t="n"/>
-      <c r="P22" s="964" t="n"/>
-      <c r="Q22" s="964" t="n"/>
-      <c r="R22" s="962" t="n"/>
-      <c r="S22" s="969" t="n"/>
+      <c r="D22" s="1003" t="n"/>
+      <c r="E22" s="1004" t="n"/>
+      <c r="F22" s="1005" t="n"/>
+      <c r="G22" s="1005" t="n"/>
+      <c r="H22" s="1005" t="n"/>
+      <c r="I22" s="1005" t="n"/>
+      <c r="J22" s="1005" t="n"/>
+      <c r="K22" s="1006" t="n"/>
+      <c r="L22" s="1005" t="n"/>
+      <c r="M22" s="1005" t="n"/>
+      <c r="N22" s="1005" t="n"/>
+      <c r="O22" s="1005" t="n"/>
+      <c r="P22" s="1005" t="n"/>
+      <c r="Q22" s="1005" t="n"/>
+      <c r="R22" s="1005" t="n"/>
+      <c r="S22" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="23" s="888">
       <c r="A23" s="891" t="n"/>
@@ -7310,10 +7433,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="184" r="24" s="888">
       <c r="A24" s="891" t="n"/>
-      <c r="B24" s="951" t="n"/>
-      <c r="C24" s="952" t="n"/>
-      <c r="D24" s="953" t="n"/>
-      <c r="E24" s="952" t="n"/>
+      <c r="B24" s="997" t="n"/>
+      <c r="C24" s="998" t="n"/>
+      <c r="D24" s="999" t="n"/>
+      <c r="E24" s="998" t="n"/>
       <c r="F24" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -7330,43 +7453,43 @@
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H24" s="953" t="n"/>
-      <c r="I24" s="953" t="n"/>
-      <c r="J24" s="953" t="n"/>
-      <c r="K24" s="956" t="n"/>
-      <c r="L24" s="953" t="n"/>
-      <c r="M24" s="953" t="n"/>
-      <c r="N24" s="953" t="n"/>
-      <c r="O24" s="957" t="n"/>
-      <c r="P24" s="957" t="n"/>
-      <c r="Q24" s="957" t="n"/>
-      <c r="R24" s="953" t="n"/>
-      <c r="S24" s="968" t="n"/>
+      <c r="H24" s="999" t="n"/>
+      <c r="I24" s="999" t="n"/>
+      <c r="J24" s="999" t="n"/>
+      <c r="K24" s="1000" t="n"/>
+      <c r="L24" s="999" t="n"/>
+      <c r="M24" s="999" t="n"/>
+      <c r="N24" s="999" t="n"/>
+      <c r="O24" s="999" t="n"/>
+      <c r="P24" s="999" t="n"/>
+      <c r="Q24" s="999" t="n"/>
+      <c r="R24" s="999" t="n"/>
+      <c r="S24" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="25" s="888">
       <c r="A25" s="891" t="n"/>
-      <c r="B25" s="959" t="n"/>
+      <c r="B25" s="1002" t="n"/>
       <c r="C25" s="955" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
       </c>
-      <c r="D25" s="960" t="n"/>
-      <c r="E25" s="961" t="n"/>
-      <c r="F25" s="962" t="n"/>
-      <c r="G25" s="962" t="n"/>
-      <c r="H25" s="962" t="n"/>
-      <c r="I25" s="962" t="n"/>
-      <c r="J25" s="962" t="n"/>
-      <c r="K25" s="963" t="n"/>
-      <c r="L25" s="962" t="n"/>
-      <c r="M25" s="962" t="n"/>
-      <c r="N25" s="962" t="n"/>
-      <c r="O25" s="964" t="n"/>
-      <c r="P25" s="964" t="n"/>
-      <c r="Q25" s="964" t="n"/>
-      <c r="R25" s="962" t="n"/>
-      <c r="S25" s="969" t="n"/>
+      <c r="D25" s="1003" t="n"/>
+      <c r="E25" s="1004" t="n"/>
+      <c r="F25" s="1005" t="n"/>
+      <c r="G25" s="1005" t="n"/>
+      <c r="H25" s="1005" t="n"/>
+      <c r="I25" s="1005" t="n"/>
+      <c r="J25" s="1005" t="n"/>
+      <c r="K25" s="1006" t="n"/>
+      <c r="L25" s="1005" t="n"/>
+      <c r="M25" s="1005" t="n"/>
+      <c r="N25" s="1005" t="n"/>
+      <c r="O25" s="1005" t="n"/>
+      <c r="P25" s="1005" t="n"/>
+      <c r="Q25" s="1005" t="n"/>
+      <c r="R25" s="1005" t="n"/>
+      <c r="S25" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="26" s="888">
       <c r="A26" s="891" t="n"/>
@@ -7465,10 +7588,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="248" r="27" s="888">
       <c r="A27" s="891" t="n"/>
-      <c r="B27" s="951" t="n"/>
-      <c r="C27" s="952" t="n"/>
-      <c r="D27" s="953" t="n"/>
-      <c r="E27" s="952" t="n"/>
+      <c r="B27" s="997" t="n"/>
+      <c r="C27" s="998" t="n"/>
+      <c r="D27" s="999" t="n"/>
+      <c r="E27" s="998" t="n"/>
       <c r="F27" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -7485,43 +7608,43 @@
 PO、SM、デザイナー、エンジニア、QA</t>
         </is>
       </c>
-      <c r="H27" s="953" t="n"/>
-      <c r="I27" s="953" t="n"/>
-      <c r="J27" s="953" t="n"/>
-      <c r="K27" s="956" t="n"/>
-      <c r="L27" s="957" t="n"/>
-      <c r="M27" s="957" t="n"/>
-      <c r="N27" s="957" t="n"/>
-      <c r="O27" s="957" t="n"/>
-      <c r="P27" s="957" t="n"/>
-      <c r="Q27" s="957" t="n"/>
-      <c r="R27" s="957" t="n"/>
-      <c r="S27" s="958" t="n"/>
+      <c r="H27" s="999" t="n"/>
+      <c r="I27" s="999" t="n"/>
+      <c r="J27" s="999" t="n"/>
+      <c r="K27" s="1000" t="n"/>
+      <c r="L27" s="999" t="n"/>
+      <c r="M27" s="999" t="n"/>
+      <c r="N27" s="999" t="n"/>
+      <c r="O27" s="999" t="n"/>
+      <c r="P27" s="999" t="n"/>
+      <c r="Q27" s="999" t="n"/>
+      <c r="R27" s="999" t="n"/>
+      <c r="S27" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="28" s="888">
       <c r="A28" s="891" t="n"/>
-      <c r="B28" s="959" t="n"/>
+      <c r="B28" s="1002" t="n"/>
       <c r="C28" s="955" t="inlineStr">
         <is>
           <t>19ヶ月</t>
         </is>
       </c>
-      <c r="D28" s="960" t="n"/>
-      <c r="E28" s="961" t="n"/>
-      <c r="F28" s="962" t="n"/>
-      <c r="G28" s="962" t="n"/>
-      <c r="H28" s="962" t="n"/>
-      <c r="I28" s="962" t="n"/>
-      <c r="J28" s="962" t="n"/>
-      <c r="K28" s="963" t="n"/>
-      <c r="L28" s="964" t="n"/>
-      <c r="M28" s="964" t="n"/>
-      <c r="N28" s="964" t="n"/>
-      <c r="O28" s="964" t="n"/>
-      <c r="P28" s="964" t="n"/>
-      <c r="Q28" s="964" t="n"/>
-      <c r="R28" s="964" t="n"/>
-      <c r="S28" s="965" t="n"/>
+      <c r="D28" s="1003" t="n"/>
+      <c r="E28" s="1004" t="n"/>
+      <c r="F28" s="1005" t="n"/>
+      <c r="G28" s="1005" t="n"/>
+      <c r="H28" s="1005" t="n"/>
+      <c r="I28" s="1005" t="n"/>
+      <c r="J28" s="1005" t="n"/>
+      <c r="K28" s="1006" t="n"/>
+      <c r="L28" s="1005" t="n"/>
+      <c r="M28" s="1005" t="n"/>
+      <c r="N28" s="1005" t="n"/>
+      <c r="O28" s="1005" t="n"/>
+      <c r="P28" s="1005" t="n"/>
+      <c r="Q28" s="1005" t="n"/>
+      <c r="R28" s="1005" t="n"/>
+      <c r="S28" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="29" s="888">
       <c r="A29" s="891" t="n"/>
@@ -7607,10 +7730,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="152" r="30" s="888">
       <c r="A30" s="891" t="n"/>
-      <c r="B30" s="951" t="n"/>
-      <c r="C30" s="952" t="n"/>
-      <c r="D30" s="953" t="n"/>
-      <c r="E30" s="952" t="n"/>
+      <c r="B30" s="997" t="n"/>
+      <c r="C30" s="998" t="n"/>
+      <c r="D30" s="999" t="n"/>
+      <c r="E30" s="998" t="n"/>
       <c r="F30" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -7627,43 +7750,43 @@
 PM、デザイナー、エンジニア、QA</t>
         </is>
       </c>
-      <c r="H30" s="953" t="n"/>
-      <c r="I30" s="953" t="n"/>
-      <c r="J30" s="953" t="n"/>
-      <c r="K30" s="956" t="n"/>
-      <c r="L30" s="953" t="n"/>
-      <c r="M30" s="957" t="n"/>
-      <c r="N30" s="957" t="n"/>
-      <c r="O30" s="957" t="n"/>
-      <c r="P30" s="957" t="n"/>
-      <c r="Q30" s="957" t="n"/>
-      <c r="R30" s="953" t="n"/>
-      <c r="S30" s="968" t="n"/>
+      <c r="H30" s="999" t="n"/>
+      <c r="I30" s="999" t="n"/>
+      <c r="J30" s="999" t="n"/>
+      <c r="K30" s="1000" t="n"/>
+      <c r="L30" s="999" t="n"/>
+      <c r="M30" s="999" t="n"/>
+      <c r="N30" s="999" t="n"/>
+      <c r="O30" s="999" t="n"/>
+      <c r="P30" s="999" t="n"/>
+      <c r="Q30" s="999" t="n"/>
+      <c r="R30" s="999" t="n"/>
+      <c r="S30" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="31" s="888">
       <c r="A31" s="891" t="n"/>
-      <c r="B31" s="959" t="n"/>
+      <c r="B31" s="1002" t="n"/>
       <c r="C31" s="955" t="inlineStr">
         <is>
           <t>６ヶ月</t>
         </is>
       </c>
-      <c r="D31" s="960" t="n"/>
-      <c r="E31" s="961" t="n"/>
-      <c r="F31" s="962" t="n"/>
-      <c r="G31" s="962" t="n"/>
-      <c r="H31" s="962" t="n"/>
-      <c r="I31" s="962" t="n"/>
-      <c r="J31" s="962" t="n"/>
-      <c r="K31" s="963" t="n"/>
-      <c r="L31" s="962" t="n"/>
-      <c r="M31" s="964" t="n"/>
-      <c r="N31" s="964" t="n"/>
-      <c r="O31" s="964" t="n"/>
-      <c r="P31" s="964" t="n"/>
-      <c r="Q31" s="964" t="n"/>
-      <c r="R31" s="962" t="n"/>
-      <c r="S31" s="969" t="n"/>
+      <c r="D31" s="1003" t="n"/>
+      <c r="E31" s="1004" t="n"/>
+      <c r="F31" s="1005" t="n"/>
+      <c r="G31" s="1005" t="n"/>
+      <c r="H31" s="1005" t="n"/>
+      <c r="I31" s="1005" t="n"/>
+      <c r="J31" s="1005" t="n"/>
+      <c r="K31" s="1006" t="n"/>
+      <c r="L31" s="1005" t="n"/>
+      <c r="M31" s="1005" t="n"/>
+      <c r="N31" s="1005" t="n"/>
+      <c r="O31" s="1005" t="n"/>
+      <c r="P31" s="1005" t="n"/>
+      <c r="Q31" s="1005" t="n"/>
+      <c r="R31" s="1005" t="n"/>
+      <c r="S31" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="32" s="888">
       <c r="A32" s="891" t="n"/>
@@ -7761,10 +7884,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="200" r="33" s="888">
       <c r="A33" s="891" t="n"/>
-      <c r="B33" s="951" t="n"/>
-      <c r="C33" s="952" t="n"/>
-      <c r="D33" s="953" t="n"/>
-      <c r="E33" s="952" t="n"/>
+      <c r="B33" s="997" t="n"/>
+      <c r="C33" s="998" t="n"/>
+      <c r="D33" s="999" t="n"/>
+      <c r="E33" s="998" t="n"/>
       <c r="F33" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -7781,43 +7904,43 @@
 PO、SM、エンジニア</t>
         </is>
       </c>
-      <c r="H33" s="953" t="n"/>
-      <c r="I33" s="953" t="n"/>
-      <c r="J33" s="953" t="n"/>
-      <c r="K33" s="956" t="n"/>
-      <c r="L33" s="957" t="n"/>
-      <c r="M33" s="957" t="n"/>
-      <c r="N33" s="957" t="n"/>
-      <c r="O33" s="957" t="n"/>
-      <c r="P33" s="957" t="n"/>
-      <c r="Q33" s="957" t="n"/>
-      <c r="R33" s="957" t="n"/>
-      <c r="S33" s="958" t="n"/>
+      <c r="H33" s="999" t="n"/>
+      <c r="I33" s="999" t="n"/>
+      <c r="J33" s="999" t="n"/>
+      <c r="K33" s="1000" t="n"/>
+      <c r="L33" s="999" t="n"/>
+      <c r="M33" s="999" t="n"/>
+      <c r="N33" s="999" t="n"/>
+      <c r="O33" s="999" t="n"/>
+      <c r="P33" s="999" t="n"/>
+      <c r="Q33" s="999" t="n"/>
+      <c r="R33" s="999" t="n"/>
+      <c r="S33" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="34" s="888">
       <c r="A34" s="891" t="n"/>
-      <c r="B34" s="959" t="n"/>
+      <c r="B34" s="1002" t="n"/>
       <c r="C34" s="955" t="inlineStr">
         <is>
           <t>26ヶ月</t>
         </is>
       </c>
-      <c r="D34" s="960" t="n"/>
-      <c r="E34" s="961" t="n"/>
-      <c r="F34" s="962" t="n"/>
-      <c r="G34" s="962" t="n"/>
-      <c r="H34" s="962" t="n"/>
-      <c r="I34" s="962" t="n"/>
-      <c r="J34" s="962" t="n"/>
-      <c r="K34" s="963" t="n"/>
-      <c r="L34" s="964" t="n"/>
-      <c r="M34" s="964" t="n"/>
-      <c r="N34" s="964" t="n"/>
-      <c r="O34" s="964" t="n"/>
-      <c r="P34" s="964" t="n"/>
-      <c r="Q34" s="964" t="n"/>
-      <c r="R34" s="964" t="n"/>
-      <c r="S34" s="965" t="n"/>
+      <c r="D34" s="1003" t="n"/>
+      <c r="E34" s="1004" t="n"/>
+      <c r="F34" s="1005" t="n"/>
+      <c r="G34" s="1005" t="n"/>
+      <c r="H34" s="1005" t="n"/>
+      <c r="I34" s="1005" t="n"/>
+      <c r="J34" s="1005" t="n"/>
+      <c r="K34" s="1006" t="n"/>
+      <c r="L34" s="1005" t="n"/>
+      <c r="M34" s="1005" t="n"/>
+      <c r="N34" s="1005" t="n"/>
+      <c r="O34" s="1005" t="n"/>
+      <c r="P34" s="1005" t="n"/>
+      <c r="Q34" s="1005" t="n"/>
+      <c r="R34" s="1005" t="n"/>
+      <c r="S34" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="35" s="888">
       <c r="A35" s="891" t="n"/>
@@ -7894,10 +8017,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="113" r="36" s="888">
       <c r="A36" s="891" t="n"/>
-      <c r="B36" s="951" t="n"/>
-      <c r="C36" s="952" t="n"/>
-      <c r="D36" s="953" t="n"/>
-      <c r="E36" s="952" t="n"/>
+      <c r="B36" s="997" t="n"/>
+      <c r="C36" s="998" t="n"/>
+      <c r="D36" s="999" t="n"/>
+      <c r="E36" s="998" t="n"/>
       <c r="F36" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -7914,43 +8037,43 @@
 PM、エンジニア、テスター</t>
         </is>
       </c>
-      <c r="H36" s="953" t="n"/>
-      <c r="I36" s="953" t="n"/>
-      <c r="J36" s="953" t="n"/>
-      <c r="K36" s="956" t="n"/>
-      <c r="L36" s="953" t="n"/>
-      <c r="M36" s="953" t="n"/>
-      <c r="N36" s="957" t="n"/>
-      <c r="O36" s="957" t="n"/>
-      <c r="P36" s="957" t="n"/>
-      <c r="Q36" s="957" t="n"/>
-      <c r="R36" s="953" t="n"/>
-      <c r="S36" s="968" t="n"/>
+      <c r="H36" s="999" t="n"/>
+      <c r="I36" s="999" t="n"/>
+      <c r="J36" s="999" t="n"/>
+      <c r="K36" s="1000" t="n"/>
+      <c r="L36" s="999" t="n"/>
+      <c r="M36" s="999" t="n"/>
+      <c r="N36" s="999" t="n"/>
+      <c r="O36" s="999" t="n"/>
+      <c r="P36" s="999" t="n"/>
+      <c r="Q36" s="999" t="n"/>
+      <c r="R36" s="999" t="n"/>
+      <c r="S36" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="37" s="888">
       <c r="A37" s="891" t="n"/>
-      <c r="B37" s="959" t="n"/>
+      <c r="B37" s="1002" t="n"/>
       <c r="C37" s="955" t="inlineStr">
         <is>
           <t>7ヶ月</t>
         </is>
       </c>
-      <c r="D37" s="960" t="n"/>
-      <c r="E37" s="961" t="n"/>
-      <c r="F37" s="962" t="n"/>
-      <c r="G37" s="962" t="n"/>
-      <c r="H37" s="962" t="n"/>
-      <c r="I37" s="962" t="n"/>
-      <c r="J37" s="962" t="n"/>
-      <c r="K37" s="963" t="n"/>
-      <c r="L37" s="962" t="n"/>
-      <c r="M37" s="962" t="n"/>
-      <c r="N37" s="964" t="n"/>
-      <c r="O37" s="964" t="n"/>
-      <c r="P37" s="964" t="n"/>
-      <c r="Q37" s="964" t="n"/>
-      <c r="R37" s="962" t="n"/>
-      <c r="S37" s="969" t="n"/>
+      <c r="D37" s="1003" t="n"/>
+      <c r="E37" s="1004" t="n"/>
+      <c r="F37" s="1005" t="n"/>
+      <c r="G37" s="1005" t="n"/>
+      <c r="H37" s="1005" t="n"/>
+      <c r="I37" s="1005" t="n"/>
+      <c r="J37" s="1005" t="n"/>
+      <c r="K37" s="1006" t="n"/>
+      <c r="L37" s="1005" t="n"/>
+      <c r="M37" s="1005" t="n"/>
+      <c r="N37" s="1005" t="n"/>
+      <c r="O37" s="1005" t="n"/>
+      <c r="P37" s="1005" t="n"/>
+      <c r="Q37" s="1005" t="n"/>
+      <c r="R37" s="1005" t="n"/>
+      <c r="S37" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="38" s="888">
       <c r="A38" s="891" t="n"/>
@@ -8027,10 +8150,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="113" r="39" s="888">
       <c r="A39" s="891" t="n"/>
-      <c r="B39" s="951" t="n"/>
-      <c r="C39" s="952" t="n"/>
-      <c r="D39" s="953" t="n"/>
-      <c r="E39" s="952" t="n"/>
+      <c r="B39" s="997" t="n"/>
+      <c r="C39" s="998" t="n"/>
+      <c r="D39" s="999" t="n"/>
+      <c r="E39" s="998" t="n"/>
       <c r="F39" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8047,43 +8170,43 @@
 PM、リーダー、エンジニア</t>
         </is>
       </c>
-      <c r="H39" s="953" t="n"/>
-      <c r="I39" s="953" t="n"/>
-      <c r="J39" s="953" t="n"/>
-      <c r="K39" s="956" t="n"/>
-      <c r="L39" s="953" t="n"/>
-      <c r="M39" s="953" t="n"/>
-      <c r="N39" s="957" t="n"/>
-      <c r="O39" s="957" t="n"/>
-      <c r="P39" s="957" t="n"/>
-      <c r="Q39" s="957" t="n"/>
-      <c r="R39" s="953" t="n"/>
-      <c r="S39" s="968" t="n"/>
+      <c r="H39" s="999" t="n"/>
+      <c r="I39" s="999" t="n"/>
+      <c r="J39" s="999" t="n"/>
+      <c r="K39" s="1000" t="n"/>
+      <c r="L39" s="999" t="n"/>
+      <c r="M39" s="999" t="n"/>
+      <c r="N39" s="999" t="n"/>
+      <c r="O39" s="999" t="n"/>
+      <c r="P39" s="999" t="n"/>
+      <c r="Q39" s="999" t="n"/>
+      <c r="R39" s="999" t="n"/>
+      <c r="S39" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="40" s="888">
       <c r="A40" s="891" t="n"/>
-      <c r="B40" s="959" t="n"/>
+      <c r="B40" s="1002" t="n"/>
       <c r="C40" s="955" t="inlineStr">
         <is>
           <t>14ヶ月</t>
         </is>
       </c>
-      <c r="D40" s="960" t="n"/>
-      <c r="E40" s="961" t="n"/>
-      <c r="F40" s="962" t="n"/>
-      <c r="G40" s="962" t="n"/>
-      <c r="H40" s="962" t="n"/>
-      <c r="I40" s="962" t="n"/>
-      <c r="J40" s="962" t="n"/>
-      <c r="K40" s="963" t="n"/>
-      <c r="L40" s="962" t="n"/>
-      <c r="M40" s="962" t="n"/>
-      <c r="N40" s="964" t="n"/>
-      <c r="O40" s="964" t="n"/>
-      <c r="P40" s="964" t="n"/>
-      <c r="Q40" s="964" t="n"/>
-      <c r="R40" s="962" t="n"/>
-      <c r="S40" s="969" t="n"/>
+      <c r="D40" s="1003" t="n"/>
+      <c r="E40" s="1004" t="n"/>
+      <c r="F40" s="1005" t="n"/>
+      <c r="G40" s="1005" t="n"/>
+      <c r="H40" s="1005" t="n"/>
+      <c r="I40" s="1005" t="n"/>
+      <c r="J40" s="1005" t="n"/>
+      <c r="K40" s="1006" t="n"/>
+      <c r="L40" s="1005" t="n"/>
+      <c r="M40" s="1005" t="n"/>
+      <c r="N40" s="1005" t="n"/>
+      <c r="O40" s="1005" t="n"/>
+      <c r="P40" s="1005" t="n"/>
+      <c r="Q40" s="1005" t="n"/>
+      <c r="R40" s="1005" t="n"/>
+      <c r="S40" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="57" r="41" s="888">
       <c r="A41" s="891" t="n"/>
@@ -8171,10 +8294,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="42" s="888">
       <c r="A42" s="891" t="n"/>
-      <c r="B42" s="951" t="n"/>
-      <c r="C42" s="952" t="n"/>
-      <c r="D42" s="953" t="n"/>
-      <c r="E42" s="952" t="n"/>
+      <c r="B42" s="997" t="n"/>
+      <c r="C42" s="998" t="n"/>
+      <c r="D42" s="999" t="n"/>
+      <c r="E42" s="998" t="n"/>
       <c r="F42" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8191,43 +8314,43 @@
 PM、リーダー、エンジニア</t>
         </is>
       </c>
-      <c r="H42" s="953" t="n"/>
-      <c r="I42" s="953" t="n"/>
-      <c r="J42" s="953" t="n"/>
-      <c r="K42" s="956" t="n"/>
-      <c r="L42" s="953" t="n"/>
-      <c r="M42" s="957" t="n"/>
-      <c r="N42" s="957" t="n"/>
-      <c r="O42" s="957" t="n"/>
-      <c r="P42" s="957" t="n"/>
-      <c r="Q42" s="957" t="n"/>
-      <c r="R42" s="957" t="n"/>
-      <c r="S42" s="958" t="n"/>
+      <c r="H42" s="999" t="n"/>
+      <c r="I42" s="999" t="n"/>
+      <c r="J42" s="999" t="n"/>
+      <c r="K42" s="1000" t="n"/>
+      <c r="L42" s="999" t="n"/>
+      <c r="M42" s="999" t="n"/>
+      <c r="N42" s="999" t="n"/>
+      <c r="O42" s="999" t="n"/>
+      <c r="P42" s="999" t="n"/>
+      <c r="Q42" s="999" t="n"/>
+      <c r="R42" s="999" t="n"/>
+      <c r="S42" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="43" s="888">
       <c r="A43" s="891" t="n"/>
-      <c r="B43" s="959" t="n"/>
+      <c r="B43" s="1002" t="n"/>
       <c r="C43" s="955" t="inlineStr">
         <is>
           <t>36ヶ月</t>
         </is>
       </c>
-      <c r="D43" s="960" t="n"/>
-      <c r="E43" s="961" t="n"/>
-      <c r="F43" s="962" t="n"/>
-      <c r="G43" s="962" t="n"/>
-      <c r="H43" s="962" t="n"/>
-      <c r="I43" s="962" t="n"/>
-      <c r="J43" s="962" t="n"/>
-      <c r="K43" s="963" t="n"/>
-      <c r="L43" s="962" t="n"/>
-      <c r="M43" s="964" t="n"/>
-      <c r="N43" s="964" t="n"/>
-      <c r="O43" s="964" t="n"/>
-      <c r="P43" s="964" t="n"/>
-      <c r="Q43" s="964" t="n"/>
-      <c r="R43" s="964" t="n"/>
-      <c r="S43" s="965" t="n"/>
+      <c r="D43" s="1003" t="n"/>
+      <c r="E43" s="1004" t="n"/>
+      <c r="F43" s="1005" t="n"/>
+      <c r="G43" s="1005" t="n"/>
+      <c r="H43" s="1005" t="n"/>
+      <c r="I43" s="1005" t="n"/>
+      <c r="J43" s="1005" t="n"/>
+      <c r="K43" s="1006" t="n"/>
+      <c r="L43" s="1005" t="n"/>
+      <c r="M43" s="1005" t="n"/>
+      <c r="N43" s="1005" t="n"/>
+      <c r="O43" s="1005" t="n"/>
+      <c r="P43" s="1005" t="n"/>
+      <c r="Q43" s="1005" t="n"/>
+      <c r="R43" s="1005" t="n"/>
+      <c r="S43" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="28" r="44" s="888">
       <c r="A44" s="891" t="n"/>
@@ -8236,23 +8359,23 @@
           <t>副業案件</t>
         </is>
       </c>
-      <c r="C44" s="971" t="n"/>
-      <c r="D44" s="971" t="n"/>
-      <c r="E44" s="971" t="n"/>
-      <c r="F44" s="971" t="n"/>
-      <c r="G44" s="971" t="n"/>
-      <c r="H44" s="971" t="n"/>
-      <c r="I44" s="971" t="n"/>
-      <c r="J44" s="971" t="n"/>
-      <c r="K44" s="971" t="n"/>
-      <c r="L44" s="971" t="n"/>
-      <c r="M44" s="971" t="n"/>
-      <c r="N44" s="971" t="n"/>
-      <c r="O44" s="971" t="n"/>
-      <c r="P44" s="971" t="n"/>
-      <c r="Q44" s="971" t="n"/>
-      <c r="R44" s="971" t="n"/>
-      <c r="S44" s="972" t="n"/>
+      <c r="C44" s="1008" t="n"/>
+      <c r="D44" s="1008" t="n"/>
+      <c r="E44" s="1008" t="n"/>
+      <c r="F44" s="1008" t="n"/>
+      <c r="G44" s="1008" t="n"/>
+      <c r="H44" s="1008" t="n"/>
+      <c r="I44" s="1008" t="n"/>
+      <c r="J44" s="1008" t="n"/>
+      <c r="K44" s="1008" t="n"/>
+      <c r="L44" s="1008" t="n"/>
+      <c r="M44" s="1008" t="n"/>
+      <c r="N44" s="1008" t="n"/>
+      <c r="O44" s="1008" t="n"/>
+      <c r="P44" s="1008" t="n"/>
+      <c r="Q44" s="1008" t="n"/>
+      <c r="R44" s="1008" t="n"/>
+      <c r="S44" s="1009" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="45" s="888">
       <c r="A45" s="891" t="n"/>
@@ -8327,10 +8450,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="152" r="46" s="888">
       <c r="A46" s="891" t="n"/>
-      <c r="B46" s="951" t="n"/>
-      <c r="C46" s="952" t="n"/>
-      <c r="D46" s="953" t="n"/>
-      <c r="E46" s="952" t="n"/>
+      <c r="B46" s="997" t="n"/>
+      <c r="C46" s="998" t="n"/>
+      <c r="D46" s="999" t="n"/>
+      <c r="E46" s="998" t="n"/>
       <c r="F46" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8347,43 +8470,43 @@
 PM、エンジニア、デザイナー</t>
         </is>
       </c>
-      <c r="H46" s="953" t="n"/>
-      <c r="I46" s="953" t="n"/>
-      <c r="J46" s="953" t="n"/>
-      <c r="K46" s="956" t="n"/>
-      <c r="L46" s="953" t="n"/>
-      <c r="M46" s="953" t="n"/>
-      <c r="N46" s="953" t="n"/>
-      <c r="O46" s="957" t="n"/>
-      <c r="P46" s="957" t="n"/>
-      <c r="Q46" s="953" t="n"/>
-      <c r="R46" s="953" t="n"/>
-      <c r="S46" s="968" t="n"/>
+      <c r="H46" s="999" t="n"/>
+      <c r="I46" s="999" t="n"/>
+      <c r="J46" s="999" t="n"/>
+      <c r="K46" s="1000" t="n"/>
+      <c r="L46" s="999" t="n"/>
+      <c r="M46" s="999" t="n"/>
+      <c r="N46" s="999" t="n"/>
+      <c r="O46" s="999" t="n"/>
+      <c r="P46" s="999" t="n"/>
+      <c r="Q46" s="999" t="n"/>
+      <c r="R46" s="999" t="n"/>
+      <c r="S46" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="47" s="888">
       <c r="A47" s="891" t="n"/>
-      <c r="B47" s="959" t="n"/>
+      <c r="B47" s="1002" t="n"/>
       <c r="C47" s="955" t="inlineStr">
         <is>
           <t>11ヶ月</t>
         </is>
       </c>
-      <c r="D47" s="960" t="n"/>
-      <c r="E47" s="961" t="n"/>
-      <c r="F47" s="962" t="n"/>
-      <c r="G47" s="962" t="n"/>
-      <c r="H47" s="962" t="n"/>
-      <c r="I47" s="962" t="n"/>
-      <c r="J47" s="962" t="n"/>
-      <c r="K47" s="963" t="n"/>
-      <c r="L47" s="962" t="n"/>
-      <c r="M47" s="962" t="n"/>
-      <c r="N47" s="962" t="n"/>
-      <c r="O47" s="964" t="n"/>
-      <c r="P47" s="964" t="n"/>
-      <c r="Q47" s="962" t="n"/>
-      <c r="R47" s="962" t="n"/>
-      <c r="S47" s="969" t="n"/>
+      <c r="D47" s="1003" t="n"/>
+      <c r="E47" s="1004" t="n"/>
+      <c r="F47" s="1005" t="n"/>
+      <c r="G47" s="1005" t="n"/>
+      <c r="H47" s="1005" t="n"/>
+      <c r="I47" s="1005" t="n"/>
+      <c r="J47" s="1005" t="n"/>
+      <c r="K47" s="1006" t="n"/>
+      <c r="L47" s="1005" t="n"/>
+      <c r="M47" s="1005" t="n"/>
+      <c r="N47" s="1005" t="n"/>
+      <c r="O47" s="1005" t="n"/>
+      <c r="P47" s="1005" t="n"/>
+      <c r="Q47" s="1005" t="n"/>
+      <c r="R47" s="1005" t="n"/>
+      <c r="S47" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="48" s="888">
       <c r="A48" s="891" t="n"/>
@@ -8454,10 +8577,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="136" r="49" s="888">
       <c r="A49" s="891" t="n"/>
-      <c r="B49" s="951" t="n"/>
-      <c r="C49" s="952" t="n"/>
-      <c r="D49" s="953" t="n"/>
-      <c r="E49" s="952" t="n"/>
+      <c r="B49" s="997" t="n"/>
+      <c r="C49" s="998" t="n"/>
+      <c r="D49" s="999" t="n"/>
+      <c r="E49" s="998" t="n"/>
       <c r="F49" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8474,43 +8597,43 @@
 PM、エンジニア</t>
         </is>
       </c>
-      <c r="H49" s="953" t="n"/>
-      <c r="I49" s="953" t="n"/>
-      <c r="J49" s="953" t="n"/>
-      <c r="K49" s="956" t="n"/>
-      <c r="L49" s="953" t="n"/>
-      <c r="M49" s="953" t="n"/>
-      <c r="N49" s="953" t="n"/>
-      <c r="O49" s="957" t="n"/>
-      <c r="P49" s="957" t="n"/>
-      <c r="Q49" s="953" t="n"/>
-      <c r="R49" s="953" t="n"/>
-      <c r="S49" s="968" t="n"/>
+      <c r="H49" s="999" t="n"/>
+      <c r="I49" s="999" t="n"/>
+      <c r="J49" s="999" t="n"/>
+      <c r="K49" s="1000" t="n"/>
+      <c r="L49" s="999" t="n"/>
+      <c r="M49" s="999" t="n"/>
+      <c r="N49" s="999" t="n"/>
+      <c r="O49" s="999" t="n"/>
+      <c r="P49" s="999" t="n"/>
+      <c r="Q49" s="999" t="n"/>
+      <c r="R49" s="999" t="n"/>
+      <c r="S49" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="50" s="888">
       <c r="A50" s="891" t="n"/>
-      <c r="B50" s="959" t="n"/>
+      <c r="B50" s="1002" t="n"/>
       <c r="C50" s="955" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D50" s="960" t="n"/>
-      <c r="E50" s="961" t="n"/>
-      <c r="F50" s="962" t="n"/>
-      <c r="G50" s="962" t="n"/>
-      <c r="H50" s="962" t="n"/>
-      <c r="I50" s="962" t="n"/>
-      <c r="J50" s="962" t="n"/>
-      <c r="K50" s="963" t="n"/>
-      <c r="L50" s="962" t="n"/>
-      <c r="M50" s="962" t="n"/>
-      <c r="N50" s="962" t="n"/>
-      <c r="O50" s="964" t="n"/>
-      <c r="P50" s="964" t="n"/>
-      <c r="Q50" s="962" t="n"/>
-      <c r="R50" s="962" t="n"/>
-      <c r="S50" s="969" t="n"/>
+      <c r="D50" s="1003" t="n"/>
+      <c r="E50" s="1004" t="n"/>
+      <c r="F50" s="1005" t="n"/>
+      <c r="G50" s="1005" t="n"/>
+      <c r="H50" s="1005" t="n"/>
+      <c r="I50" s="1005" t="n"/>
+      <c r="J50" s="1005" t="n"/>
+      <c r="K50" s="1006" t="n"/>
+      <c r="L50" s="1005" t="n"/>
+      <c r="M50" s="1005" t="n"/>
+      <c r="N50" s="1005" t="n"/>
+      <c r="O50" s="1005" t="n"/>
+      <c r="P50" s="1005" t="n"/>
+      <c r="Q50" s="1005" t="n"/>
+      <c r="R50" s="1005" t="n"/>
+      <c r="S50" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="51" s="888">
       <c r="A51" s="891" t="n"/>
@@ -8580,10 +8703,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="52" s="888">
       <c r="A52" s="891" t="n"/>
-      <c r="B52" s="951" t="n"/>
-      <c r="C52" s="952" t="n"/>
-      <c r="D52" s="953" t="n"/>
-      <c r="E52" s="952" t="n"/>
+      <c r="B52" s="997" t="n"/>
+      <c r="C52" s="998" t="n"/>
+      <c r="D52" s="999" t="n"/>
+      <c r="E52" s="998" t="n"/>
       <c r="F52" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8600,43 +8723,43 @@
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H52" s="953" t="n"/>
-      <c r="I52" s="953" t="n"/>
-      <c r="J52" s="953" t="n"/>
-      <c r="K52" s="956" t="n"/>
-      <c r="L52" s="953" t="n"/>
-      <c r="M52" s="953" t="n"/>
-      <c r="N52" s="953" t="n"/>
-      <c r="O52" s="957" t="n"/>
-      <c r="P52" s="957" t="n"/>
-      <c r="Q52" s="953" t="n"/>
-      <c r="R52" s="953" t="n"/>
-      <c r="S52" s="968" t="n"/>
+      <c r="H52" s="999" t="n"/>
+      <c r="I52" s="999" t="n"/>
+      <c r="J52" s="999" t="n"/>
+      <c r="K52" s="1000" t="n"/>
+      <c r="L52" s="999" t="n"/>
+      <c r="M52" s="999" t="n"/>
+      <c r="N52" s="999" t="n"/>
+      <c r="O52" s="999" t="n"/>
+      <c r="P52" s="999" t="n"/>
+      <c r="Q52" s="999" t="n"/>
+      <c r="R52" s="999" t="n"/>
+      <c r="S52" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="53" s="888">
       <c r="A53" s="891" t="n"/>
-      <c r="B53" s="959" t="n"/>
+      <c r="B53" s="1002" t="n"/>
       <c r="C53" s="955" t="inlineStr">
         <is>
           <t>5ヶ月</t>
         </is>
       </c>
-      <c r="D53" s="960" t="n"/>
-      <c r="E53" s="961" t="n"/>
-      <c r="F53" s="962" t="n"/>
-      <c r="G53" s="962" t="n"/>
-      <c r="H53" s="962" t="n"/>
-      <c r="I53" s="962" t="n"/>
-      <c r="J53" s="962" t="n"/>
-      <c r="K53" s="963" t="n"/>
-      <c r="L53" s="962" t="n"/>
-      <c r="M53" s="962" t="n"/>
-      <c r="N53" s="962" t="n"/>
-      <c r="O53" s="964" t="n"/>
-      <c r="P53" s="964" t="n"/>
-      <c r="Q53" s="962" t="n"/>
-      <c r="R53" s="962" t="n"/>
-      <c r="S53" s="969" t="n"/>
+      <c r="D53" s="1003" t="n"/>
+      <c r="E53" s="1004" t="n"/>
+      <c r="F53" s="1005" t="n"/>
+      <c r="G53" s="1005" t="n"/>
+      <c r="H53" s="1005" t="n"/>
+      <c r="I53" s="1005" t="n"/>
+      <c r="J53" s="1005" t="n"/>
+      <c r="K53" s="1006" t="n"/>
+      <c r="L53" s="1005" t="n"/>
+      <c r="M53" s="1005" t="n"/>
+      <c r="N53" s="1005" t="n"/>
+      <c r="O53" s="1005" t="n"/>
+      <c r="P53" s="1005" t="n"/>
+      <c r="Q53" s="1005" t="n"/>
+      <c r="R53" s="1005" t="n"/>
+      <c r="S53" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="54" s="888">
       <c r="A54" s="891" t="n"/>
@@ -8706,10 +8829,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="55" s="888">
       <c r="A55" s="891" t="n"/>
-      <c r="B55" s="951" t="n"/>
-      <c r="C55" s="952" t="n"/>
-      <c r="D55" s="953" t="n"/>
-      <c r="E55" s="952" t="n"/>
+      <c r="B55" s="997" t="n"/>
+      <c r="C55" s="998" t="n"/>
+      <c r="D55" s="999" t="n"/>
+      <c r="E55" s="998" t="n"/>
       <c r="F55" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8726,43 +8849,43 @@
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H55" s="953" t="n"/>
-      <c r="I55" s="953" t="n"/>
-      <c r="J55" s="953" t="n"/>
-      <c r="K55" s="956" t="n"/>
-      <c r="L55" s="953" t="n"/>
-      <c r="M55" s="953" t="n"/>
-      <c r="N55" s="953" t="n"/>
-      <c r="O55" s="957" t="n"/>
-      <c r="P55" s="957" t="n"/>
-      <c r="Q55" s="953" t="n"/>
-      <c r="R55" s="953" t="n"/>
-      <c r="S55" s="968" t="n"/>
+      <c r="H55" s="999" t="n"/>
+      <c r="I55" s="999" t="n"/>
+      <c r="J55" s="999" t="n"/>
+      <c r="K55" s="1000" t="n"/>
+      <c r="L55" s="999" t="n"/>
+      <c r="M55" s="999" t="n"/>
+      <c r="N55" s="999" t="n"/>
+      <c r="O55" s="999" t="n"/>
+      <c r="P55" s="999" t="n"/>
+      <c r="Q55" s="999" t="n"/>
+      <c r="R55" s="999" t="n"/>
+      <c r="S55" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="56" s="888">
       <c r="A56" s="891" t="n"/>
-      <c r="B56" s="959" t="n"/>
+      <c r="B56" s="1002" t="n"/>
       <c r="C56" s="955" t="inlineStr">
         <is>
           <t>４ヶ月</t>
         </is>
       </c>
-      <c r="D56" s="960" t="n"/>
-      <c r="E56" s="961" t="n"/>
-      <c r="F56" s="962" t="n"/>
-      <c r="G56" s="962" t="n"/>
-      <c r="H56" s="962" t="n"/>
-      <c r="I56" s="962" t="n"/>
-      <c r="J56" s="962" t="n"/>
-      <c r="K56" s="963" t="n"/>
-      <c r="L56" s="962" t="n"/>
-      <c r="M56" s="962" t="n"/>
-      <c r="N56" s="962" t="n"/>
-      <c r="O56" s="964" t="n"/>
-      <c r="P56" s="964" t="n"/>
-      <c r="Q56" s="962" t="n"/>
-      <c r="R56" s="962" t="n"/>
-      <c r="S56" s="969" t="n"/>
+      <c r="D56" s="1003" t="n"/>
+      <c r="E56" s="1004" t="n"/>
+      <c r="F56" s="1005" t="n"/>
+      <c r="G56" s="1005" t="n"/>
+      <c r="H56" s="1005" t="n"/>
+      <c r="I56" s="1005" t="n"/>
+      <c r="J56" s="1005" t="n"/>
+      <c r="K56" s="1006" t="n"/>
+      <c r="L56" s="1005" t="n"/>
+      <c r="M56" s="1005" t="n"/>
+      <c r="N56" s="1005" t="n"/>
+      <c r="O56" s="1005" t="n"/>
+      <c r="P56" s="1005" t="n"/>
+      <c r="Q56" s="1005" t="n"/>
+      <c r="R56" s="1005" t="n"/>
+      <c r="S56" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="41" r="57" s="888">
       <c r="A57" s="891" t="n"/>
@@ -8832,10 +8955,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="129" r="58" s="888">
       <c r="A58" s="891" t="n"/>
-      <c r="B58" s="951" t="n"/>
-      <c r="C58" s="952" t="n"/>
-      <c r="D58" s="953" t="n"/>
-      <c r="E58" s="952" t="n"/>
+      <c r="B58" s="997" t="n"/>
+      <c r="C58" s="998" t="n"/>
+      <c r="D58" s="999" t="n"/>
+      <c r="E58" s="998" t="n"/>
       <c r="F58" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8852,43 +8975,43 @@
 リードエンジニア、エンジニア</t>
         </is>
       </c>
-      <c r="H58" s="953" t="n"/>
-      <c r="I58" s="953" t="n"/>
-      <c r="J58" s="953" t="n"/>
-      <c r="K58" s="956" t="n"/>
-      <c r="L58" s="953" t="n"/>
-      <c r="M58" s="953" t="n"/>
-      <c r="N58" s="953" t="n"/>
-      <c r="O58" s="957" t="n"/>
-      <c r="P58" s="957" t="n"/>
-      <c r="Q58" s="953" t="n"/>
-      <c r="R58" s="953" t="n"/>
-      <c r="S58" s="968" t="n"/>
+      <c r="H58" s="999" t="n"/>
+      <c r="I58" s="999" t="n"/>
+      <c r="J58" s="999" t="n"/>
+      <c r="K58" s="1000" t="n"/>
+      <c r="L58" s="999" t="n"/>
+      <c r="M58" s="999" t="n"/>
+      <c r="N58" s="999" t="n"/>
+      <c r="O58" s="999" t="n"/>
+      <c r="P58" s="999" t="n"/>
+      <c r="Q58" s="999" t="n"/>
+      <c r="R58" s="999" t="n"/>
+      <c r="S58" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="59" s="888">
       <c r="A59" s="891" t="n"/>
-      <c r="B59" s="959" t="n"/>
+      <c r="B59" s="1002" t="n"/>
       <c r="C59" s="955" t="inlineStr">
         <is>
           <t>6ヶ月</t>
         </is>
       </c>
-      <c r="D59" s="960" t="n"/>
-      <c r="E59" s="961" t="n"/>
-      <c r="F59" s="962" t="n"/>
-      <c r="G59" s="962" t="n"/>
-      <c r="H59" s="962" t="n"/>
-      <c r="I59" s="962" t="n"/>
-      <c r="J59" s="962" t="n"/>
-      <c r="K59" s="963" t="n"/>
-      <c r="L59" s="962" t="n"/>
-      <c r="M59" s="962" t="n"/>
-      <c r="N59" s="962" t="n"/>
-      <c r="O59" s="964" t="n"/>
-      <c r="P59" s="964" t="n"/>
-      <c r="Q59" s="962" t="n"/>
-      <c r="R59" s="962" t="n"/>
-      <c r="S59" s="969" t="n"/>
+      <c r="D59" s="1003" t="n"/>
+      <c r="E59" s="1004" t="n"/>
+      <c r="F59" s="1005" t="n"/>
+      <c r="G59" s="1005" t="n"/>
+      <c r="H59" s="1005" t="n"/>
+      <c r="I59" s="1005" t="n"/>
+      <c r="J59" s="1005" t="n"/>
+      <c r="K59" s="1006" t="n"/>
+      <c r="L59" s="1005" t="n"/>
+      <c r="M59" s="1005" t="n"/>
+      <c r="N59" s="1005" t="n"/>
+      <c r="O59" s="1005" t="n"/>
+      <c r="P59" s="1005" t="n"/>
+      <c r="Q59" s="1005" t="n"/>
+      <c r="R59" s="1005" t="n"/>
+      <c r="S59" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="25" r="60" s="888">
       <c r="A60" s="891" t="n"/>
@@ -8961,10 +9084,10 @@
     </row>
     <row customFormat="1" customHeight="1" ht="88" r="61" s="888">
       <c r="A61" s="891" t="n"/>
-      <c r="B61" s="951" t="n"/>
-      <c r="C61" s="952" t="n"/>
-      <c r="D61" s="953" t="n"/>
-      <c r="E61" s="952" t="n"/>
+      <c r="B61" s="997" t="n"/>
+      <c r="C61" s="998" t="n"/>
+      <c r="D61" s="999" t="n"/>
+      <c r="E61" s="998" t="n"/>
       <c r="F61" s="954" t="inlineStr">
         <is>
           <t>≪プロジェクト内容≫
@@ -8974,43 +9097,43 @@
         </is>
       </c>
       <c r="G61" s="955" t="inlineStr"/>
-      <c r="H61" s="953" t="n"/>
-      <c r="I61" s="953" t="n"/>
-      <c r="J61" s="953" t="n"/>
-      <c r="K61" s="956" t="n"/>
-      <c r="L61" s="953" t="n"/>
-      <c r="M61" s="953" t="n"/>
-      <c r="N61" s="953" t="n"/>
-      <c r="O61" s="957" t="n"/>
-      <c r="P61" s="957" t="n"/>
-      <c r="Q61" s="953" t="n"/>
-      <c r="R61" s="953" t="n"/>
-      <c r="S61" s="968" t="n"/>
+      <c r="H61" s="999" t="n"/>
+      <c r="I61" s="999" t="n"/>
+      <c r="J61" s="999" t="n"/>
+      <c r="K61" s="1000" t="n"/>
+      <c r="L61" s="999" t="n"/>
+      <c r="M61" s="999" t="n"/>
+      <c r="N61" s="999" t="n"/>
+      <c r="O61" s="999" t="n"/>
+      <c r="P61" s="999" t="n"/>
+      <c r="Q61" s="999" t="n"/>
+      <c r="R61" s="999" t="n"/>
+      <c r="S61" s="1001" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="24" r="62" s="888">
       <c r="A62" s="891" t="n"/>
-      <c r="B62" s="959" t="n"/>
+      <c r="B62" s="1002" t="n"/>
       <c r="C62" s="955" t="inlineStr">
         <is>
           <t>8ヶ月</t>
         </is>
       </c>
-      <c r="D62" s="960" t="n"/>
-      <c r="E62" s="961" t="n"/>
-      <c r="F62" s="962" t="n"/>
-      <c r="G62" s="962" t="n"/>
-      <c r="H62" s="962" t="n"/>
-      <c r="I62" s="962" t="n"/>
-      <c r="J62" s="962" t="n"/>
-      <c r="K62" s="963" t="n"/>
-      <c r="L62" s="962" t="n"/>
-      <c r="M62" s="962" t="n"/>
-      <c r="N62" s="962" t="n"/>
-      <c r="O62" s="964" t="n"/>
-      <c r="P62" s="964" t="n"/>
-      <c r="Q62" s="962" t="n"/>
-      <c r="R62" s="962" t="n"/>
-      <c r="S62" s="969" t="n"/>
+      <c r="D62" s="1003" t="n"/>
+      <c r="E62" s="1004" t="n"/>
+      <c r="F62" s="1005" t="n"/>
+      <c r="G62" s="1005" t="n"/>
+      <c r="H62" s="1005" t="n"/>
+      <c r="I62" s="1005" t="n"/>
+      <c r="J62" s="1005" t="n"/>
+      <c r="K62" s="1006" t="n"/>
+      <c r="L62" s="1005" t="n"/>
+      <c r="M62" s="1005" t="n"/>
+      <c r="N62" s="1005" t="n"/>
+      <c r="O62" s="1005" t="n"/>
+      <c r="P62" s="1005" t="n"/>
+      <c r="Q62" s="1005" t="n"/>
+      <c r="R62" s="1005" t="n"/>
+      <c r="S62" s="1007" t="n"/>
     </row>
     <row customFormat="1" customHeight="1" ht="28" r="63" s="888">
       <c r="A63" s="891" t="n"/>
@@ -9019,23 +9142,23 @@
           <t>●：担当工程。空欄：未記載（経験なしを意味しません）。案件名のリンクから詳細を確認できます。</t>
         </is>
       </c>
-      <c r="C63" s="888" t="n"/>
-      <c r="D63" s="888" t="n"/>
-      <c r="E63" s="888" t="n"/>
-      <c r="F63" s="888" t="n"/>
-      <c r="G63" s="888" t="n"/>
-      <c r="H63" s="888" t="n"/>
-      <c r="I63" s="888" t="n"/>
-      <c r="J63" s="888" t="n"/>
-      <c r="K63" s="888" t="n"/>
-      <c r="L63" s="888" t="n"/>
-      <c r="M63" s="888" t="n"/>
-      <c r="N63" s="888" t="n"/>
-      <c r="O63" s="888" t="n"/>
-      <c r="P63" s="888" t="n"/>
-      <c r="Q63" s="888" t="n"/>
-      <c r="R63" s="888" t="n"/>
-      <c r="S63" s="888" t="n"/>
+      <c r="C63" s="974" t="n"/>
+      <c r="D63" s="974" t="n"/>
+      <c r="E63" s="974" t="n"/>
+      <c r="F63" s="974" t="n"/>
+      <c r="G63" s="974" t="n"/>
+      <c r="H63" s="974" t="n"/>
+      <c r="I63" s="974" t="n"/>
+      <c r="J63" s="974" t="n"/>
+      <c r="K63" s="974" t="n"/>
+      <c r="L63" s="974" t="n"/>
+      <c r="M63" s="974" t="n"/>
+      <c r="N63" s="974" t="n"/>
+      <c r="O63" s="974" t="n"/>
+      <c r="P63" s="974" t="n"/>
+      <c r="Q63" s="974" t="n"/>
+      <c r="R63" s="974" t="n"/>
+      <c r="S63" s="974" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="339">

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -6697,7 +6697,7 @@
           <t>新卒にて中小ソフトウェア企業に入社後、2013年から正社員として5年間、受託開発や客先開発でJavaやOracleを使ったシステム開発に携わりました。
 2017年にフリーランスに転身してから現在まで8年間、Ruby on Railsを主軸としたバックエンド開発をメインとしながら、React/Next.jsなどのモダンフロントエンド技術、AWSインフラ構築、DBパフォーマンスチューニングまで幅広くフルスタックに対応してきました。
 近年の技術的な強みとして、GraphQLを活用したAPI設計、Terraformによるインフラコード化、CursorやClaude CodeなどのAIエージェントを活用した効率的な開発プロセスの確立があげられます。現在はリードエンジニアとして、アーキテクチャ設計から実装、チームマネジメントまで包括的に担当しております。
-個人開発のPBSでは、Claude Codeによる実装・PR作成とCodexによるレビューを連携させ、Issue駆動で実装からレビューまでを完全自動化する運用を試行しました。開発速度の低下や実装意図とのずれを受け、実装・レビューの各段階で人がAIへ依頼し、内容を確認・判断する半自動の運用へ変更しました。
+個人開発では、Claude Codeによる実装・PR作成とCodexによるレビューを連携させ、Issue駆動で実装からレビューまでを完全自動化する運用を試行しました。開発速度の低下や実装意図とのずれを受け、実装・レビューの各段階で人がAIへ依頼し、内容を確認・判断する半自動の運用へ変更しました。
 プロジェクトや開発組織に対しては、エンジニアとして開発に従事しながら、認定スクラムマスターの資格の知見を活かし、アジャイル開発におけるチームファシリテーション、エンジニア採用面談、新規メンバーのオンボーディング、チームビルディングなど、開発面以外での組織貢献も積極的に行っています。
 今後も、AIツールを効果的に活用しながら開発生産性を向上させつつ、チームリードとしての責任を果たし、ビジネス価値の高いプロダクト開発に貢献していきたいと考えております。何卒よろしくお願いいたします。</t>
         </is>

--- a/excel/skill-sheet.xlsx
+++ b/excel/skill-sheet.xlsx
@@ -6684,7 +6684,7 @@
       <c r="R7" s="975" t="n"/>
       <c r="S7" s="975" t="n"/>
     </row>
-    <row customFormat="1" customHeight="1" ht="249" r="8" s="888">
+    <row customFormat="1" customHeight="1" ht="233" r="8" s="888">
       <c r="A8" s="891" t="n"/>
       <c r="B8" s="922" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
           <t>新卒にて中小ソフトウェア企業に入社後、2013年から正社員として5年間、受託開発や客先開発でJavaやOracleを使ったシステム開発に携わりました。
 2017年にフリーランスに転身してから現在まで8年間、Ruby on Railsを主軸としたバックエンド開発をメインとしながら、React/Next.jsなどのモダンフロントエンド技術、AWSインフラ構築、DBパフォーマンスチューニングまで幅広くフルスタックに対応してきました。
 近年の技術的な強みとして、GraphQLを活用したAPI設計、Terraformによるインフラコード化、CursorやClaude CodeなどのAIエージェントを活用した効率的な開発プロセスの確立があげられます。現在はリードエンジニアとして、アーキテクチャ設計から実装、チームマネジメントまで包括的に担当しております。
-個人開発では、Claude Codeによる実装・PR作成とCodexによるレビューを連携させ、Issue駆動で実装からレビューまでを完全自動化する運用を試行しました。開発速度の低下や実装意図とのずれを受け、実装・レビューの各段階で人がAIへ依頼し、内容を確認・判断する半自動の運用へ変更しました。
+個人開発では、Claude Codeによる実装・PR作成とCodexによるレビューを連携させ、Issue駆動で実装からレビューまでを完全自動化する運用の試行や、有名サービスを模倣したアプリ開発などを通じて、技術選定の経験を積んでいます。
 プロジェクトや開発組織に対しては、エンジニアとして開発に従事しながら、認定スクラムマスターの資格の知見を活かし、アジャイル開発におけるチームファシリテーション、エンジニア採用面談、新規メンバーのオンボーディング、チームビルディングなど、開発面以外での組織貢献も積極的に行っています。
 今後も、AIツールを効果的に活用しながら開発生産性を向上させつつ、チームリードとしての責任を果たし、ビジネス価値の高いプロダクト開発に貢献していきたいと考えております。何卒よろしくお願いいたします。</t>
         </is>
